--- a/hall/resources/sample/condition.xlsx
+++ b/hall/resources/sample/condition.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="condition" sheetId="1" r:id="rId1"/>
@@ -360,6 +360,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
       <t>11003_当日累计充值大于等于金额_</t>
     </r>
     <r>
@@ -386,6 +391,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
       <t>11004 账号个人累计充值</t>
     </r>
     <r>
@@ -735,12 +745,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1746,7 +1756,7 @@
         <v>29</v>
       </c>
       <c r="F7" s="6">
-        <v>48001</v>
+        <v>49161</v>
       </c>
       <c r="G7" s="8" t="s">
         <v>30</v>

--- a/hall/resources/sample/condition.xlsx
+++ b/hall/resources/sample/condition.xlsx
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="114">
   <si>
     <t>id</t>
   </si>
@@ -546,6 +546,33 @@
   <si>
     <t>12102_道具ID_等于大于目标数量(游戏下注产生的消耗不计算，其它地方都计算 例 系统升级、兑换 )</t>
   </si>
+  <si>
+    <t>经营建筑升N次</t>
+  </si>
+  <si>
+    <t>观看广告N次</t>
+  </si>
+  <si>
+    <t>雇员招募N个</t>
+  </si>
+  <si>
+    <t>雇员星级达到N星</t>
+  </si>
+  <si>
+    <t>经营收益累积达到N金币</t>
+  </si>
+  <si>
+    <t>能量收闪达到N</t>
+  </si>
+  <si>
+    <t>招商N个游客</t>
+  </si>
+  <si>
+    <t>接待游客N人次</t>
+  </si>
+  <si>
+    <t>研发N个游戏</t>
+  </si>
 </sst>
 </file>
 
@@ -756,7 +783,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -772,6 +799,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1088,7 +1121,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1112,16 +1145,16 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1130,89 +1163,89 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="25" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1280,6 +1313,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1602,7 +1638,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O25"/>
+  <dimension ref="A1:O34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="5"/>
@@ -2257,6 +2293,150 @@
       <c r="E25" s="5" t="s">
         <v>104</v>
       </c>
+    </row>
+    <row r="26" spans="1:15">
+      <c r="A26" s="23">
+        <v>12201</v>
+      </c>
+      <c r="B26" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="C26" s="23"/>
+      <c r="D26" s="23">
+        <v>1</v>
+      </c>
+      <c r="E26" s="23"/>
+      <c r="F26" s="23"/>
+      <c r="G26" s="23"/>
+      <c r="H26" s="23"/>
+    </row>
+    <row r="27" spans="1:15">
+      <c r="A27" s="23">
+        <v>12202</v>
+      </c>
+      <c r="B27" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="C27" s="23"/>
+      <c r="D27" s="23">
+        <v>1</v>
+      </c>
+      <c r="E27" s="23"/>
+      <c r="F27" s="23"/>
+      <c r="G27" s="23"/>
+      <c r="H27" s="23"/>
+    </row>
+    <row r="28" spans="1:15">
+      <c r="A28" s="23">
+        <v>12203</v>
+      </c>
+      <c r="B28" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="C28" s="23"/>
+      <c r="D28" s="23">
+        <v>1</v>
+      </c>
+      <c r="E28" s="23"/>
+      <c r="F28" s="23"/>
+      <c r="G28" s="23"/>
+      <c r="H28" s="23"/>
+    </row>
+    <row r="29" spans="1:15">
+      <c r="A29" s="23">
+        <v>12204</v>
+      </c>
+      <c r="B29" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="C29" s="23"/>
+      <c r="D29" s="23">
+        <v>1</v>
+      </c>
+      <c r="E29" s="23"/>
+      <c r="F29" s="23"/>
+      <c r="G29" s="23"/>
+      <c r="H29" s="23"/>
+    </row>
+    <row r="30" spans="1:15">
+      <c r="A30" s="23">
+        <v>12205</v>
+      </c>
+      <c r="B30" s="23" t="s">
+        <v>109</v>
+      </c>
+      <c r="C30" s="23"/>
+      <c r="D30" s="23">
+        <v>1</v>
+      </c>
+      <c r="E30" s="23"/>
+      <c r="F30" s="23"/>
+      <c r="G30" s="23"/>
+      <c r="H30" s="23"/>
+    </row>
+    <row r="31" spans="1:15">
+      <c r="A31" s="23">
+        <v>12206</v>
+      </c>
+      <c r="B31" s="23" t="s">
+        <v>110</v>
+      </c>
+      <c r="C31" s="23"/>
+      <c r="D31" s="23">
+        <v>1</v>
+      </c>
+      <c r="E31" s="23"/>
+      <c r="F31" s="23"/>
+      <c r="G31" s="23"/>
+      <c r="H31" s="23"/>
+    </row>
+    <row r="32" spans="1:15">
+      <c r="A32" s="23">
+        <v>12207</v>
+      </c>
+      <c r="B32" s="23" t="s">
+        <v>111</v>
+      </c>
+      <c r="C32" s="23"/>
+      <c r="D32" s="23">
+        <v>1</v>
+      </c>
+      <c r="E32" s="23"/>
+      <c r="F32" s="23"/>
+      <c r="G32" s="23"/>
+      <c r="H32" s="23"/>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" s="23">
+        <v>12208</v>
+      </c>
+      <c r="B33" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="C33" s="23"/>
+      <c r="D33" s="23">
+        <v>1</v>
+      </c>
+      <c r="E33" s="23"/>
+      <c r="F33" s="23"/>
+      <c r="G33" s="23"/>
+      <c r="H33" s="23"/>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" s="23">
+        <v>12209</v>
+      </c>
+      <c r="B34" s="23" t="s">
+        <v>113</v>
+      </c>
+      <c r="C34" s="23"/>
+      <c r="D34" s="23">
+        <v>1</v>
+      </c>
+      <c r="E34" s="23"/>
+      <c r="F34" s="23"/>
+      <c r="G34" s="23"/>
+      <c r="H34" s="23"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="D5">

--- a/hall/resources/sample/condition.xlsx
+++ b/hall/resources/sample/condition.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="condition" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="130">
   <si>
     <t>id</t>
   </si>
@@ -572,6 +572,54 @@
   </si>
   <si>
     <t>研发N个游戏</t>
+  </si>
+  <si>
+    <t>游戏中奖倍数</t>
+  </si>
+  <si>
+    <t>12301_游戏ID（0=任意游戏）_大于等于总押注条件_游戏中奖具体倍数_大于等于中奖倍数的次数（接取任务后，截止到任务时间结束期间）</t>
+  </si>
+  <si>
+    <t>卡池抽奖次数</t>
+  </si>
+  <si>
+    <t>12302_卡池ID（0=任意卡池）_卡池中抽奖的次数（接取任务后，截止到任务时间结束期间）</t>
+  </si>
+  <si>
+    <t>技能研究次数</t>
+  </si>
+  <si>
+    <t>12303_游戏ID（0=任意游戏）_研究院游戏属性研究次数（接取任务后，截止到任务时间结束期间）</t>
+  </si>
+  <si>
+    <t>建筑升级次数</t>
+  </si>
+  <si>
+    <t>12304_建筑ID（0=任意建筑）_升级的次数（接取任务后，截止到任务时间结束期间）</t>
+  </si>
+  <si>
+    <t>游戏下注次数</t>
+  </si>
+  <si>
+    <t>12305_游戏ID（0=任意游戏）_大于等于总押注条件_等于目标投注次数（接取任务后，截止到任务时间结束期间，消耗能量的下注）</t>
+  </si>
+  <si>
+    <t>游戏赢奖金额</t>
+  </si>
+  <si>
+    <t>12306_游戏ID（0=任意游戏）_大于等于总押注条件_大于等于目标获胜金额_货币ID（接取任务后，截止到任务时间结束期间，消耗能量的下注条件作为前提）</t>
+  </si>
+  <si>
+    <t>接取联盟任务后的个人累计充值</t>
+  </si>
+  <si>
+    <t>12307_接取任务后，截止到任务时间结束期间，个人累计充值大于等于金额_渠道ID</t>
+  </si>
+  <si>
+    <t>联盟捐献次数</t>
+  </si>
+  <si>
+    <t>12308_大于等于捐献条件_大于等于目标的捐献次数（接取任务后，截止到任务时间结束期间）</t>
   </si>
 </sst>
 </file>
@@ -1638,7 +1686,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O34"/>
+  <dimension ref="A1:O42"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="5"/>
@@ -2437,6 +2485,118 @@
       <c r="F34" s="23"/>
       <c r="G34" s="23"/>
       <c r="H34" s="23"/>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" s="5">
+        <v>12301</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D35" s="5">
+        <v>4</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" s="5">
+        <v>12302</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="D36" s="5">
+        <v>2</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37" s="5">
+        <v>12303</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="D37" s="5">
+        <v>2</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="38" ht="17" customHeight="1" spans="1:8">
+      <c r="A38" s="5">
+        <v>12304</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="D38" s="5">
+        <v>2</v>
+      </c>
+      <c r="E38" s="5" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39" s="5">
+        <v>12305</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="D39" s="5">
+        <v>3</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" s="5">
+        <v>12306</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="D40" s="5">
+        <v>4</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" s="5">
+        <v>12307</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="D41" s="5">
+        <v>2</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42" s="5">
+        <v>12308</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="D42" s="5">
+        <v>2</v>
+      </c>
+      <c r="E42" s="5" t="s">
+        <v>129</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="D5">

--- a/hall/resources/sample/condition.xlsx
+++ b/hall/resources/sample/condition.xlsx
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="146">
   <si>
     <t>id</t>
   </si>
@@ -620,6 +620,54 @@
   </si>
   <si>
     <t>12308_大于等于捐献条件_大于等于目标的捐献次数（接取任务后，截止到任务时间结束期间）</t>
+  </si>
+  <si>
+    <t>模拟经营-SLOT建筑-金币增加收益(‰)/min</t>
+  </si>
+  <si>
+    <t>12401_具体‰数值</t>
+  </si>
+  <si>
+    <t>模拟经营-扑克建筑-金币增加收益(‰)/min</t>
+  </si>
+  <si>
+    <t>12402_具体‰数值</t>
+  </si>
+  <si>
+    <t>模拟经营-捕鱼建筑-金币增加收益(‰)/min</t>
+  </si>
+  <si>
+    <t>12403_具体‰数值</t>
+  </si>
+  <si>
+    <t>模拟经营-休息建筑-能量增加收益(‰)/min</t>
+  </si>
+  <si>
+    <t>12404_具‰体数值</t>
+  </si>
+  <si>
+    <t>模拟经营-所有产金币的建筑增加收益(‰)/min</t>
+  </si>
+  <si>
+    <t>12405_具体‰数值</t>
+  </si>
+  <si>
+    <t>模拟经营-知名度增加(‰)</t>
+  </si>
+  <si>
+    <t>12406_具体‰数值</t>
+  </si>
+  <si>
+    <t>模拟经营-曝光度上限增加(值)</t>
+  </si>
+  <si>
+    <t>12407_具体数值</t>
+  </si>
+  <si>
+    <t>模拟经营-广告金币收益增加(‰)</t>
+  </si>
+  <si>
+    <t>12408_具体‰数值</t>
   </si>
 </sst>
 </file>
@@ -831,7 +879,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -853,6 +901,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1169,7 +1223,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1193,16 +1247,16 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1211,89 +1265,89 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="25" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1365,6 +1419,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1686,11 +1746,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O42"/>
+  <dimension ref="A1:O50"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="5"/>
-    <col min="2" max="2" width="31.625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="38.525" style="5" customWidth="1"/>
     <col min="3" max="3" width="19.625" style="5" customWidth="1"/>
     <col min="4" max="4" width="17.625" style="5" customWidth="1"/>
     <col min="5" max="5" width="102.375" style="5" customWidth="1"/>
@@ -2596,6 +2656,118 @@
       </c>
       <c r="E42" s="5" t="s">
         <v>129</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="A43" s="24">
+        <v>12401</v>
+      </c>
+      <c r="B43" s="24" t="s">
+        <v>130</v>
+      </c>
+      <c r="D43" s="5">
+        <v>1</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44" s="24">
+        <v>12402</v>
+      </c>
+      <c r="B44" s="24" t="s">
+        <v>132</v>
+      </c>
+      <c r="D44" s="5">
+        <v>1</v>
+      </c>
+      <c r="E44" s="25" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45" s="24">
+        <v>12403</v>
+      </c>
+      <c r="B45" s="24" t="s">
+        <v>134</v>
+      </c>
+      <c r="D45" s="5">
+        <v>1</v>
+      </c>
+      <c r="E45" s="25" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46" s="24">
+        <v>12404</v>
+      </c>
+      <c r="B46" s="24" t="s">
+        <v>136</v>
+      </c>
+      <c r="D46" s="5">
+        <v>1</v>
+      </c>
+      <c r="E46" s="25" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="A47" s="24">
+        <v>12405</v>
+      </c>
+      <c r="B47" s="24" t="s">
+        <v>138</v>
+      </c>
+      <c r="D47" s="5">
+        <v>1</v>
+      </c>
+      <c r="E47" s="25" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="A48" s="24">
+        <v>12406</v>
+      </c>
+      <c r="B48" s="24" t="s">
+        <v>140</v>
+      </c>
+      <c r="D48" s="5">
+        <v>1</v>
+      </c>
+      <c r="E48" s="25" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="24">
+        <v>12407</v>
+      </c>
+      <c r="B49" s="24" t="s">
+        <v>142</v>
+      </c>
+      <c r="D49" s="5">
+        <v>1</v>
+      </c>
+      <c r="E49" s="25" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="24">
+        <v>12408</v>
+      </c>
+      <c r="B50" s="24" t="s">
+        <v>144</v>
+      </c>
+      <c r="D50" s="5">
+        <v>1</v>
+      </c>
+      <c r="E50" s="25" t="s">
+        <v>145</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/condition.xlsx
+++ b/hall/resources/sample/condition.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="condition" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="183">
   <si>
     <t>id</t>
   </si>
@@ -189,31 +189,7 @@
     <t>betFrequency</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t>10001_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t>游戏ID(0 = 任意游戏)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（不区分倍场)_大于等于总押注条件_等于目标投注次数</t>
-    </r>
+    <t>10001_游戏ID(0 = 任意游戏)（不区分倍场)_大于等于总押注条件_等于目标投注次数</t>
   </si>
   <si>
     <t>您还未完成任务，请继续游戏</t>
@@ -228,31 +204,7 @@
     <t>playGameCount</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t>10002_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t>游戏ID(0 = 任意游戏)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（不区分倍场）_大于等于总押注条件_等于目标局数次数</t>
-    </r>
+    <t>10002_游戏ID(0 = 任意游戏)（不区分倍场）_大于等于总押注条件_等于目标局数次数</t>
   </si>
   <si>
     <t>个人游戏实际赢钱</t>
@@ -261,40 +213,7 @@
     <t>playGameWinMoney</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t>10003_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t>游戏ID(0 = 任意游戏)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（不区分倍场）_大于等于总押注条件_大于等于目标获胜金额</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t>_货币ID(金币或钻石)</t>
-    </r>
+    <t>10003_游戏ID(0 = 任意游戏)（不区分倍场）_大于等于总押注条件_大于等于目标获胜金额_货币ID(金币或钻石)</t>
   </si>
   <si>
     <t>个人单次充值</t>
@@ -303,23 +222,7 @@
     <t>singleRecharge</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t>11001_单次充值大于等于金额</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t>_次数_渠道ID(0=默认所有)</t>
-    </r>
+    <t>11001_单次充值大于等于金额_次数_渠道ID(0=默认所有)</t>
   </si>
   <si>
     <t>您的充值金额不足%s，请稍后再试</t>
@@ -334,23 +237,7 @@
     <t>activityTotalRecharge</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t>11002 活动开始后，总累计充值大于等于金额_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t>渠道ID</t>
-    </r>
+    <t>11002 活动开始后，总累计充值大于等于金额_渠道ID</t>
   </si>
   <si>
     <t>个人今日累计充值</t>
@@ -359,23 +246,7 @@
     <t>todayDeposit</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t>11003_当日累计充值大于等于金额_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t>渠道ID(0=默认所有)</t>
-    </r>
+    <t>11003_当日累计充值大于等于金额_渠道ID(0=默认所有)</t>
   </si>
   <si>
     <t>您今日的充值金额不足%s，请稍后再试</t>
@@ -390,23 +261,7 @@
     <t>totalRecharge</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t>11004 账号个人累计充值</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t>_渠道ID(0=默认所有)</t>
-    </r>
+    <t>11004 账号个人累计充值_渠道ID(0=默认所有)</t>
   </si>
   <si>
     <t>账号个人累计充值</t>
@@ -424,31 +279,7 @@
     <t>effectiveBetAll</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t>12001_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t>游戏ID(0 = 任意游戏)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t>_每累积达到设定有效下注数量（计算所有游戏）</t>
-    </r>
+    <t>12001_游戏ID(0 = 任意游戏)_每累积达到设定有效下注数量（计算所有游戏）</t>
   </si>
   <si>
     <t>bet</t>
@@ -547,31 +378,124 @@
     <t>12102_道具ID_等于大于目标数量(游戏下注产生的消耗不计算，其它地方都计算 例 系统升级、兑换 )</t>
   </si>
   <si>
-    <t>经营建筑升N次</t>
-  </si>
-  <si>
-    <t>观看广告N次</t>
-  </si>
-  <si>
-    <t>雇员招募N个</t>
-  </si>
-  <si>
-    <t>雇员星级达到N星</t>
-  </si>
-  <si>
-    <t>经营收益累积达到N金币</t>
-  </si>
-  <si>
-    <t>能量收闪达到N</t>
-  </si>
-  <si>
-    <t>招商N个游客</t>
-  </si>
-  <si>
-    <t>接待游客N人次</t>
-  </si>
-  <si>
-    <t>研发N个游戏</t>
+    <t>在SLOT游戏中单次赢奖N金币</t>
+  </si>
+  <si>
+    <t>12201_游戏ID(0)_金币数量</t>
+  </si>
+  <si>
+    <t>在SLOT游戏中获得N个X道具</t>
+  </si>
+  <si>
+    <t>12202_游戏ID(0)_道具ID_道具数量</t>
+  </si>
+  <si>
+    <t>累计触发SWEET WIN N次</t>
+  </si>
+  <si>
+    <t>12203_大奖类型_次数</t>
+  </si>
+  <si>
+    <t>累计触发MINI奖池N次</t>
+  </si>
+  <si>
+    <t>12204_奖池类型_次数</t>
+  </si>
+  <si>
+    <t>累计触发免费游戏模式N次</t>
+  </si>
+  <si>
+    <t>12205_次数</t>
+  </si>
+  <si>
+    <t>建筑升级N次</t>
+  </si>
+  <si>
+    <t>12206_建筑ID(0)_次数</t>
+  </si>
+  <si>
+    <t>建筑升到N级</t>
+  </si>
+  <si>
+    <t>12207_建筑ID(0)_等级</t>
+  </si>
+  <si>
+    <t>拥有N个X级以上建筑</t>
+  </si>
+  <si>
+    <t>12208_数量_等级</t>
+  </si>
+  <si>
+    <t>观看N次广告</t>
+  </si>
+  <si>
+    <t>12209_次数</t>
+  </si>
+  <si>
+    <t>观看广告金币\钻石收益达到N</t>
+  </si>
+  <si>
+    <t>12210_道具ID_数量</t>
+  </si>
+  <si>
+    <t>招募N个X类型的雇员</t>
+  </si>
+  <si>
+    <t>12211_雇员类型_数量</t>
+  </si>
+  <si>
+    <t>拥有N个X星雇员</t>
+  </si>
+  <si>
+    <t>12212_雇员类型_数量_星级</t>
+  </si>
+  <si>
+    <t>招商游客N次</t>
+  </si>
+  <si>
+    <t>12213_免费0(付费1)_次数</t>
+  </si>
+  <si>
+    <t>拥有N个X星游客</t>
+  </si>
+  <si>
+    <t>12214_数量_星级</t>
+  </si>
+  <si>
+    <t>经营收益 金币\能量\道具 累积达到N</t>
+  </si>
+  <si>
+    <t>12215_道具ID_数量</t>
+  </si>
+  <si>
+    <t>累积研发N个游戏</t>
+  </si>
+  <si>
+    <t>12216_数量</t>
+  </si>
+  <si>
+    <t>累积拜访N次</t>
+  </si>
+  <si>
+    <t>12217_数量</t>
+  </si>
+  <si>
+    <t>累积登陆N天</t>
+  </si>
+  <si>
+    <t>12218_数量</t>
+  </si>
+  <si>
+    <t>累积解锁N个娱乐城</t>
+  </si>
+  <si>
+    <t>12219_数量</t>
+  </si>
+  <si>
+    <t>累积消费N金币\钻石</t>
+  </si>
+  <si>
+    <t>12220_道具ID_数量</t>
   </si>
   <si>
     <t>游戏中奖倍数</t>
@@ -580,46 +504,40 @@
     <t>12301_游戏ID（0=任意游戏）_大于等于总押注条件_游戏中奖具体倍数_大于等于中奖倍数的次数（接取任务后，截止到任务时间结束期间）</t>
   </si>
   <si>
+    <t>游戏下注次数(消耗能量)</t>
+  </si>
+  <si>
+    <t>12302_游戏ID（0=任意游戏）_大于等于总押注条件_等于目标投注次数（接取任务后，截止到任务时间结束期间，消耗能量的下注）</t>
+  </si>
+  <si>
     <t>卡池抽奖次数</t>
   </si>
   <si>
-    <t>12302_卡池ID（0=任意卡池）_卡池中抽奖的次数（接取任务后，截止到任务时间结束期间）</t>
+    <t>12303_卡池ID（0=任意卡池）_卡池中抽奖的次数（接取任务后，截止到任务时间结束期间）</t>
   </si>
   <si>
     <t>技能研究次数</t>
   </si>
   <si>
-    <t>12303_游戏ID（0=任意游戏）_研究院游戏属性研究次数（接取任务后，截止到任务时间结束期间）</t>
-  </si>
-  <si>
-    <t>建筑升级次数</t>
-  </si>
-  <si>
-    <t>12304_建筑ID（0=任意建筑）_升级的次数（接取任务后，截止到任务时间结束期间）</t>
-  </si>
-  <si>
-    <t>游戏下注次数</t>
-  </si>
-  <si>
-    <t>12305_游戏ID（0=任意游戏）_大于等于总押注条件_等于目标投注次数（接取任务后，截止到任务时间结束期间，消耗能量的下注）</t>
-  </si>
-  <si>
-    <t>游戏赢奖金额</t>
-  </si>
-  <si>
-    <t>12306_游戏ID（0=任意游戏）_大于等于总押注条件_大于等于目标获胜金额_货币ID（接取任务后，截止到任务时间结束期间，消耗能量的下注条件作为前提）</t>
-  </si>
-  <si>
-    <t>接取联盟任务后的个人累计充值</t>
-  </si>
-  <si>
-    <t>12307_接取任务后，截止到任务时间结束期间，个人累计充值大于等于金额_渠道ID</t>
+    <t>12304_游戏ID（0=任意游戏）_研究院游戏属性研究次数（接取任务后，截止到任务时间结束期间）</t>
   </si>
   <si>
     <t>联盟捐献次数</t>
   </si>
   <si>
-    <t>12308_大于等于捐献条件_大于等于目标的捐献次数（接取任务后，截止到任务时间结束期间）</t>
+    <t>12305_大于等于捐献条件_大于等于目标的捐献次数（接取任务后，截止到任务时间结束期间）</t>
+  </si>
+  <si>
+    <t>游戏赢奖金额(时间限制)</t>
+  </si>
+  <si>
+    <t>12306_游戏ID（0=任意游戏）_大于等于总押注条件_货币ID_大于等于目标获胜金额（接取任务后，截止到任务时间结束期间，消耗能量的下注条件作为前提）</t>
+  </si>
+  <si>
+    <t>接取联盟任务后的个人累计充值(时间限制)</t>
+  </si>
+  <si>
+    <t>12307_接取任务后，截止到任务时间结束期间，渠道ID_个人累计充值大于等于金额</t>
   </si>
   <si>
     <t>模拟经营-SLOT建筑-金币增加收益(‰)/min</t>
@@ -668,6 +586,30 @@
   </si>
   <si>
     <t>12408_具体‰数值</t>
+  </si>
+  <si>
+    <t>游戏下注次数(消耗能量,触发特殊模式)</t>
+  </si>
+  <si>
+    <t>12501_游戏id（0=任意游戏）_下注具体次数_游戏模式id_触发模式次数</t>
+  </si>
+  <si>
+    <t>游戏下注次数（消耗能量，累计赢奖）</t>
+  </si>
+  <si>
+    <t>12502_游戏id（0=任意游戏）_下注具体次数_累计赢奖</t>
+  </si>
+  <si>
+    <t>游戏下注次数（消耗能量，触发大奖次数）</t>
+  </si>
+  <si>
+    <t>12503_游戏id（0=任意游戏）_下注具体次数_中奖倍数（大于或等于此倍数）_大奖次数</t>
+  </si>
+  <si>
+    <t>游戏下注次数（消耗能量，累计下注金额）</t>
+  </si>
+  <si>
+    <t>12502_游戏id（0=任意游戏）_下注具体次数_累计下注金额</t>
   </si>
 </sst>
 </file>
@@ -680,13 +622,24 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -697,29 +650,11 @@
     <font>
       <i/>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF7030A0"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -879,7 +814,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -888,145 +823,157 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="6" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4F8B9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1217,106 +1164,100 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1325,10 +1266,10 @@
     <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1337,94 +1278,79 @@
     <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1488,6 +1414,11 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="00F4F8B9"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1746,336 +1677,349 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O50"/>
+  <dimension ref="A1:O64"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="9" style="5"/>
-    <col min="2" max="2" width="38.525" style="5" customWidth="1"/>
-    <col min="3" max="3" width="19.625" style="5" customWidth="1"/>
-    <col min="4" max="4" width="17.625" style="5" customWidth="1"/>
-    <col min="5" max="5" width="102.375" style="5" customWidth="1"/>
-    <col min="6" max="6" width="21.375" style="5" customWidth="1"/>
-    <col min="7" max="7" width="38.625" style="5" customWidth="1"/>
-    <col min="8" max="8" width="17.125" style="5" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="5"/>
+    <col min="1" max="1" width="9" style="4"/>
+    <col min="2" max="2" width="38.525" style="4" customWidth="1"/>
+    <col min="3" max="3" width="19.625" style="4" customWidth="1"/>
+    <col min="4" max="4" width="17.625" style="4" customWidth="1"/>
+    <col min="5" max="5" width="102.375" style="4" customWidth="1"/>
+    <col min="6" max="6" width="21.375" style="4" customWidth="1"/>
+    <col min="7" max="7" width="38.625" style="4" customWidth="1"/>
+    <col min="8" max="8" width="17.125" style="4" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="6" t="s">
+    <row r="1" s="1" customFormat="1" ht="15" spans="1:10">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6"/>
-      <c r="F1" s="5" t="s">
+      <c r="E1" s="5"/>
+      <c r="F1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="6" t="s">
+    <row r="2" s="1" customFormat="1" ht="15" spans="1:10">
+      <c r="A2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="B2" s="6"/>
+      <c r="C2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6" t="s">
+      <c r="E2" s="5"/>
+      <c r="F2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="6" t="s">
+    <row r="3" s="1" customFormat="1" ht="15" spans="1:10">
+      <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="B3" s="6"/>
+      <c r="C3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="E3" s="6"/>
+      <c r="F3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="6" t="s">
         <v>14</v>
       </c>
     </row>
+    <row r="4" s="1" customFormat="1" ht="15" spans="1:10">
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+    </row>
     <row r="5" ht="17.25" spans="1:10">
-      <c r="A5" s="5">
+      <c r="A5" s="4">
         <v>1</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="4">
         <v>1</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="8">
         <v>48001</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="G5" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="H5" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="I5" s="4" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="6" ht="17.25" spans="1:10">
-      <c r="A6" s="5">
+      <c r="A6" s="4">
         <v>2</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="4" t="s">
         <v>21</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="4">
         <v>1</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="8">
         <v>48002</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="G6" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="H6" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="I6" s="5" t="s">
+      <c r="I6" s="4" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="7" ht="17.25" spans="1:10">
-      <c r="A7" s="5">
+      <c r="A7" s="4">
         <v>3</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="4" t="s">
         <v>27</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="4">
         <v>1</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="8">
         <v>49161</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="G7" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H7" s="5" t="s">
+      <c r="H7" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="I7" s="5" t="s">
+      <c r="I7" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" ht="17.25" spans="1:10">
-      <c r="A8" s="1">
+    <row r="8" s="2" customFormat="1" ht="17.25" spans="1:10">
+      <c r="A8" s="2">
         <v>4</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D8" s="2">
         <v>1</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="F8" s="10">
+      <c r="F8" s="11">
         <v>48005</v>
       </c>
-      <c r="G8" s="8" t="s">
+      <c r="G8" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="H8" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="I8" s="1" t="s">
+      <c r="I8" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" ht="17.25" spans="1:10">
-      <c r="A9" s="1">
+    <row r="9" s="2" customFormat="1" ht="17.25" spans="1:10">
+      <c r="A9" s="2">
         <v>5</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D9" s="2">
         <v>3</v>
       </c>
       <c r="E9" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="F9" s="10"/>
-      <c r="G9" s="8"/>
-      <c r="I9" s="1" t="s">
+      <c r="F9" s="11"/>
+      <c r="G9" s="9"/>
+      <c r="I9" s="2" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="10" ht="17.25" spans="1:10">
-      <c r="A10" s="5">
+      <c r="A10" s="4">
         <v>10001</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="4" t="s">
         <v>40</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D10" s="5">
+      <c r="D10" s="4">
         <v>3</v>
       </c>
-      <c r="E10" s="12" t="s">
+      <c r="E10" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="8">
         <v>48003</v>
       </c>
-      <c r="G10" s="8" t="s">
+      <c r="G10" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="H10" s="5" t="s">
+      <c r="H10" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="I10" s="5" t="s">
+      <c r="I10" s="4" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="11" ht="17.25" spans="1:10">
-      <c r="A11" s="5">
+      <c r="A11" s="4">
         <v>10002</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="4" t="s">
         <v>45</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="D11" s="5">
+      <c r="D11" s="4">
         <v>3</v>
       </c>
-      <c r="E11" s="12" t="s">
+      <c r="E11" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="F11" s="6">
+      <c r="F11" s="8">
         <v>48003</v>
       </c>
-      <c r="G11" s="8" t="s">
+      <c r="G11" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="H11" s="5" t="s">
+      <c r="H11" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="I11" s="5" t="s">
+      <c r="I11" s="4" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="12" ht="17.25" spans="1:10">
-      <c r="A12" s="5">
+      <c r="A12" s="4">
         <v>10003</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="4" t="s">
         <v>48</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="D12" s="13">
+      <c r="D12" s="4">
         <v>4</v>
       </c>
-      <c r="E12" s="12" t="s">
+      <c r="E12" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="F12" s="6">
+      <c r="F12" s="8">
         <v>48003</v>
       </c>
-      <c r="G12" s="8" t="s">
+      <c r="G12" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="H12" s="5" t="s">
+      <c r="H12" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="I12" s="5" t="s">
+      <c r="I12" s="4" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="13" ht="17.25" spans="1:10">
-      <c r="A13" s="5">
+      <c r="A13" s="4">
         <v>11001</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="4" t="s">
         <v>51</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="D13" s="13">
+      <c r="D13" s="4">
         <v>3</v>
       </c>
-      <c r="E13" s="12" t="s">
+      <c r="E13" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="F13" s="6">
+      <c r="F13" s="8">
         <v>48004</v>
       </c>
-      <c r="G13" s="8" t="s">
+      <c r="G13" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="H13" s="5" t="s">
+      <c r="H13" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="I13" s="5" t="s">
+      <c r="I13" s="4" t="s">
         <v>26</v>
       </c>
     </row>
@@ -2086,110 +2030,110 @@
       <c r="B14" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C14" s="14" t="s">
+      <c r="C14" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="D14" s="15">
+      <c r="D14" s="2">
         <v>2</v>
       </c>
-      <c r="E14" s="16" t="s">
+      <c r="E14" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="F14" s="17">
+      <c r="F14" s="11">
         <v>48004</v>
       </c>
-      <c r="G14" s="18" t="s">
+      <c r="G14" s="9" t="s">
         <v>54</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="I14" s="5" t="s">
+      <c r="I14" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="15" ht="17.25" spans="1:10">
-      <c r="A15" s="5">
+    <row r="15" s="2" customFormat="1" ht="17.25" spans="1:10">
+      <c r="A15" s="2">
         <v>11003</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="D15" s="13">
+      <c r="D15" s="2">
         <v>2</v>
       </c>
-      <c r="E15" s="12" t="s">
+      <c r="E15" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="F15" s="17">
+      <c r="F15" s="11">
         <v>48006</v>
       </c>
-      <c r="G15" s="8" t="s">
+      <c r="G15" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="H15" s="5" t="s">
+      <c r="H15" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="I15" s="5" t="s">
+      <c r="I15" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="J15" s="19" t="s">
+      <c r="J15" s="11" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="16" customFormat="1" ht="17.25" spans="1:10">
-      <c r="A16" s="5">
+    <row r="16" s="2" customFormat="1" ht="17.25" spans="1:10">
+      <c r="A16" s="2">
         <v>11004</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="D16" s="13">
+      <c r="D16" s="2">
         <v>2</v>
       </c>
-      <c r="E16" s="12" t="s">
+      <c r="E16" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="F16" s="6">
+      <c r="F16" s="11">
         <v>48004</v>
       </c>
-      <c r="G16" s="8" t="s">
+      <c r="G16" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="H16" s="5" t="s">
+      <c r="H16" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="I16" s="5" t="s">
+      <c r="I16" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="J16" s="19"/>
-    </row>
-    <row r="17" s="3" customFormat="1" ht="17.25" spans="1:15">
+      <c r="J16" s="11"/>
+    </row>
+    <row r="17" s="2" customFormat="1" ht="17.25" spans="1:15">
       <c r="A17" s="2">
         <v>11005</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C17" s="14" t="s">
+      <c r="C17" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="D17" s="15">
+      <c r="D17" s="2">
         <v>1</v>
       </c>
-      <c r="E17" s="16" t="s">
+      <c r="E17" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="F17" s="17">
+      <c r="F17" s="11">
         <v>48004</v>
       </c>
-      <c r="G17" s="18" t="s">
+      <c r="G17" s="9" t="s">
         <v>54</v>
       </c>
       <c r="H17" s="2" t="s">
@@ -2198,576 +2142,834 @@
       <c r="I17" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="J17" s="20"/>
-    </row>
-    <row r="18" s="4" customFormat="1" spans="1:15">
-      <c r="A18" s="4">
+      <c r="J17" s="11"/>
+    </row>
+    <row r="18" s="2" customFormat="1" spans="1:15">
+      <c r="A18" s="2">
         <v>12001</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="D18" s="21">
+      <c r="D18" s="2">
         <v>2</v>
       </c>
-      <c r="E18" s="22" t="s">
+      <c r="E18" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="H18" s="4" t="s">
+      <c r="H18" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="I18" s="5" t="s">
+      <c r="I18" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="19" s="4" customFormat="1" spans="1:15">
-      <c r="A19" s="4">
+    <row r="19" s="2" customFormat="1" spans="1:15">
+      <c r="A19" s="2">
         <v>12002</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C19" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="D19" s="4">
+      <c r="D19" s="2">
         <v>1</v>
       </c>
-      <c r="E19" s="22" t="s">
+      <c r="E19" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="H19" s="4" t="s">
+      <c r="H19" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="I19" s="5" t="s">
+      <c r="I19" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="20" s="4" customFormat="1" spans="1:15">
-      <c r="A20" s="4">
+    <row r="20" s="2" customFormat="1" spans="1:15">
+      <c r="A20" s="2">
         <v>12003</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="C20" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="D20" s="4">
+      <c r="D20" s="2">
         <v>2</v>
       </c>
-      <c r="E20" s="22" t="s">
+      <c r="E20" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="H20" s="4" t="s">
+      <c r="H20" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="I20" s="5" t="s">
+      <c r="I20" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="J20" s="4" t="s">
+      <c r="J20" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="M20" s="4" t="s">
+      <c r="M20" s="2" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="21" s="4" customFormat="1" spans="1:15">
-      <c r="A21" s="4">
+    <row r="21" s="2" customFormat="1" spans="1:15">
+      <c r="A21" s="2">
         <v>12004</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="C21" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="D21" s="4">
+      <c r="D21" s="2">
         <v>2</v>
       </c>
-      <c r="E21" s="22" t="s">
+      <c r="E21" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="H21" s="4" t="s">
+      <c r="H21" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="I21" s="5" t="s">
+      <c r="I21" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="22" s="4" customFormat="1" spans="1:15">
-      <c r="A22" s="4">
+    <row r="22" s="2" customFormat="1" spans="1:15">
+      <c r="A22" s="2">
         <v>12005</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="C22" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="D22" s="4">
+      <c r="D22" s="2">
         <v>2</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="E22" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="H22" s="4" t="s">
+      <c r="H22" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="I22" s="5" t="s">
+      <c r="I22" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="J22" s="4" t="s">
+      <c r="J22" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="M22" s="4" t="s">
+      <c r="M22" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="O22" s="4" t="s">
+      <c r="O22" s="2" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="23" s="4" customFormat="1" spans="1:15">
-      <c r="A23" s="4">
+    <row r="23" s="2" customFormat="1" spans="1:15">
+      <c r="A23" s="2">
         <v>12006</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="C23" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="D23" s="4">
+      <c r="D23" s="2">
         <v>2</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="E23" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="H23" s="4" t="s">
+      <c r="H23" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="I23" s="5" t="s">
+      <c r="I23" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="J23" s="4" t="s">
+      <c r="J23" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="M23" s="4" t="s">
+      <c r="M23" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="O23" s="4" t="s">
+      <c r="O23" s="2" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="24" s="4" customFormat="1" spans="1:15">
-      <c r="A24" s="4">
+    <row r="24" s="2" customFormat="1" spans="1:15">
+      <c r="A24" s="2">
         <v>12007</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="C24" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="D24" s="4">
+      <c r="D24" s="2">
         <v>1</v>
       </c>
-      <c r="E24" s="22" t="s">
+      <c r="E24" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="H24" s="4" t="s">
+      <c r="H24" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="I24" s="5" t="s">
+      <c r="I24" s="2" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:15">
-      <c r="A25" s="5">
+      <c r="A25" s="4">
         <v>12101</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="4" t="s">
         <v>102</v>
       </c>
       <c r="C25" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="D25" s="5">
+      <c r="D25" s="4">
         <v>2</v>
       </c>
-      <c r="E25" s="5" t="s">
+      <c r="E25" s="4" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="26" spans="1:15">
-      <c r="A26" s="23">
+      <c r="A26" s="12">
         <v>12201</v>
       </c>
-      <c r="B26" s="23" t="s">
+      <c r="B26" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="C26" s="23"/>
-      <c r="D26" s="23">
+      <c r="C26" s="2"/>
+      <c r="D26" s="2">
+        <v>2</v>
+      </c>
+      <c r="E26" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+    </row>
+    <row r="27" spans="1:15">
+      <c r="A27" s="12">
+        <v>12202</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2">
+        <v>3</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+    </row>
+    <row r="28" spans="1:15">
+      <c r="A28" s="12">
+        <v>12203</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2">
+        <v>2</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+    </row>
+    <row r="29" spans="1:15">
+      <c r="A29" s="12">
+        <v>12204</v>
+      </c>
+      <c r="B29" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2">
+        <v>2</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+    </row>
+    <row r="30" spans="1:15">
+      <c r="A30" s="12">
+        <v>12205</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2">
         <v>1</v>
       </c>
-      <c r="E26" s="23"/>
-      <c r="F26" s="23"/>
-      <c r="G26" s="23"/>
-      <c r="H26" s="23"/>
-    </row>
-    <row r="27" spans="1:15">
-      <c r="A27" s="23">
-        <v>12202</v>
-      </c>
-      <c r="B27" s="23" t="s">
-        <v>106</v>
-      </c>
-      <c r="C27" s="23"/>
-      <c r="D27" s="23">
+      <c r="E30" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+    </row>
+    <row r="31" spans="1:15">
+      <c r="A31" s="12">
+        <v>12206</v>
+      </c>
+      <c r="B31" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2">
+        <v>2</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+    </row>
+    <row r="32" spans="1:15">
+      <c r="A32" s="12">
+        <v>12207</v>
+      </c>
+      <c r="B32" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2">
+        <v>2</v>
+      </c>
+      <c r="E32" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" s="12">
+        <v>12208</v>
+      </c>
+      <c r="B33" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2">
+        <v>2</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" s="12">
+        <v>12209</v>
+      </c>
+      <c r="B34" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2">
         <v>1</v>
       </c>
-      <c r="E27" s="23"/>
-      <c r="F27" s="23"/>
-      <c r="G27" s="23"/>
-      <c r="H27" s="23"/>
-    </row>
-    <row r="28" spans="1:15">
-      <c r="A28" s="23">
-        <v>12203</v>
-      </c>
-      <c r="B28" s="23" t="s">
-        <v>107</v>
-      </c>
-      <c r="C28" s="23"/>
-      <c r="D28" s="23">
+      <c r="E34" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" s="12">
+        <v>12210</v>
+      </c>
+      <c r="B35" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2">
+        <v>2</v>
+      </c>
+      <c r="E35" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" s="12">
+        <v>12211</v>
+      </c>
+      <c r="B36" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2">
+        <v>2</v>
+      </c>
+      <c r="E36" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37" s="12">
+        <v>12212</v>
+      </c>
+      <c r="B37" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2">
+        <v>3</v>
+      </c>
+      <c r="E37" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" s="12">
+        <v>12213</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2">
+        <v>2</v>
+      </c>
+      <c r="E38" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39" s="12">
+        <v>12214</v>
+      </c>
+      <c r="B39" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2">
+        <v>2</v>
+      </c>
+      <c r="E39" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" s="12">
+        <v>12215</v>
+      </c>
+      <c r="B40" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2">
+        <v>2</v>
+      </c>
+      <c r="E40" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" s="12">
+        <v>12216</v>
+      </c>
+      <c r="B41" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2">
         <v>1</v>
       </c>
-      <c r="E28" s="23"/>
-      <c r="F28" s="23"/>
-      <c r="G28" s="23"/>
-      <c r="H28" s="23"/>
-    </row>
-    <row r="29" spans="1:15">
-      <c r="A29" s="23">
-        <v>12204</v>
-      </c>
-      <c r="B29" s="23" t="s">
-        <v>108</v>
-      </c>
-      <c r="C29" s="23"/>
-      <c r="D29" s="23">
+      <c r="E41" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="F41" s="2"/>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42" s="12">
+        <v>12217</v>
+      </c>
+      <c r="B42" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2">
         <v>1</v>
       </c>
-      <c r="E29" s="23"/>
-      <c r="F29" s="23"/>
-      <c r="G29" s="23"/>
-      <c r="H29" s="23"/>
-    </row>
-    <row r="30" spans="1:15">
-      <c r="A30" s="23">
-        <v>12205</v>
-      </c>
-      <c r="B30" s="23" t="s">
-        <v>109</v>
-      </c>
-      <c r="C30" s="23"/>
-      <c r="D30" s="23">
+      <c r="E42" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="F42" s="2"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="A43" s="12">
+        <v>12218</v>
+      </c>
+      <c r="B43" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2">
         <v>1</v>
       </c>
-      <c r="E30" s="23"/>
-      <c r="F30" s="23"/>
-      <c r="G30" s="23"/>
-      <c r="H30" s="23"/>
-    </row>
-    <row r="31" spans="1:15">
-      <c r="A31" s="23">
-        <v>12206</v>
-      </c>
-      <c r="B31" s="23" t="s">
-        <v>110</v>
-      </c>
-      <c r="C31" s="23"/>
-      <c r="D31" s="23">
+      <c r="E43" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="F43" s="2"/>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44" s="12">
+        <v>12219</v>
+      </c>
+      <c r="B44" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2">
         <v>1</v>
       </c>
-      <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
-      <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
-    </row>
-    <row r="32" spans="1:15">
-      <c r="A32" s="23">
-        <v>12207</v>
-      </c>
-      <c r="B32" s="23" t="s">
-        <v>111</v>
-      </c>
-      <c r="C32" s="23"/>
-      <c r="D32" s="23">
+      <c r="E44" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="F44" s="2"/>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45" s="12">
+        <v>12220</v>
+      </c>
+      <c r="B45" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="C45" s="2"/>
+      <c r="D45" s="2">
+        <v>2</v>
+      </c>
+      <c r="E45" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="F45" s="2"/>
+      <c r="G45" s="2"/>
+      <c r="H45" s="2"/>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46" s="14">
+        <v>12301</v>
+      </c>
+      <c r="B46" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="D46" s="4">
+        <v>4</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="47" s="3" customFormat="1" spans="1:8">
+      <c r="A47" s="15">
+        <v>12302</v>
+      </c>
+      <c r="B47" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="D47" s="3">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="A48" s="14">
+        <v>12303</v>
+      </c>
+      <c r="B48" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="D48" s="4">
+        <v>2</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="15">
+        <v>12304</v>
+      </c>
+      <c r="B49" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="D49" s="4">
+        <v>2</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="14">
+        <v>12305</v>
+      </c>
+      <c r="B50" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="D50" s="4">
+        <v>2</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="51" s="3" customFormat="1" spans="1:5">
+      <c r="A51" s="15">
+        <v>12306</v>
+      </c>
+      <c r="B51" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="D51" s="3">
+        <v>4</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="52" s="3" customFormat="1" spans="1:5">
+      <c r="A52" s="14">
+        <v>12307</v>
+      </c>
+      <c r="B52" s="15" t="s">
+        <v>157</v>
+      </c>
+      <c r="D52" s="3">
+        <v>2</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="16">
+        <v>12401</v>
+      </c>
+      <c r="B53" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="D53" s="4">
         <v>1</v>
       </c>
-      <c r="E32" s="23"/>
-      <c r="F32" s="23"/>
-      <c r="G32" s="23"/>
-      <c r="H32" s="23"/>
-    </row>
-    <row r="33" spans="1:8">
-      <c r="A33" s="23">
-        <v>12208</v>
-      </c>
-      <c r="B33" s="23" t="s">
-        <v>112</v>
-      </c>
-      <c r="C33" s="23"/>
-      <c r="D33" s="23">
+      <c r="E53" s="4" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="16">
+        <v>12402</v>
+      </c>
+      <c r="B54" s="16" t="s">
+        <v>161</v>
+      </c>
+      <c r="D54" s="4">
         <v>1</v>
       </c>
-      <c r="E33" s="23"/>
-      <c r="F33" s="23"/>
-      <c r="G33" s="23"/>
-      <c r="H33" s="23"/>
-    </row>
-    <row r="34" spans="1:8">
-      <c r="A34" s="23">
-        <v>12209</v>
-      </c>
-      <c r="B34" s="23" t="s">
-        <v>113</v>
-      </c>
-      <c r="C34" s="23"/>
-      <c r="D34" s="23">
+      <c r="E54" s="17" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="16">
+        <v>12403</v>
+      </c>
+      <c r="B55" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="D55" s="4">
         <v>1</v>
       </c>
-      <c r="E34" s="23"/>
-      <c r="F34" s="23"/>
-      <c r="G34" s="23"/>
-      <c r="H34" s="23"/>
-    </row>
-    <row r="35" spans="1:8">
-      <c r="A35" s="5">
-        <v>12301</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="D35" s="5">
+      <c r="E55" s="17" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="16">
+        <v>12404</v>
+      </c>
+      <c r="B56" s="16" t="s">
+        <v>165</v>
+      </c>
+      <c r="D56" s="4">
+        <v>1</v>
+      </c>
+      <c r="E56" s="17" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="16">
+        <v>12405</v>
+      </c>
+      <c r="B57" s="16" t="s">
+        <v>167</v>
+      </c>
+      <c r="D57" s="4">
+        <v>1</v>
+      </c>
+      <c r="E57" s="17" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="16">
+        <v>12406</v>
+      </c>
+      <c r="B58" s="16" t="s">
+        <v>169</v>
+      </c>
+      <c r="D58" s="4">
+        <v>1</v>
+      </c>
+      <c r="E58" s="17" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="16">
+        <v>12407</v>
+      </c>
+      <c r="B59" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="D59" s="4">
+        <v>1</v>
+      </c>
+      <c r="E59" s="17" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="16">
+        <v>12408</v>
+      </c>
+      <c r="B60" s="16" t="s">
+        <v>173</v>
+      </c>
+      <c r="D60" s="4">
+        <v>1</v>
+      </c>
+      <c r="E60" s="17" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="18">
+        <v>12501</v>
+      </c>
+      <c r="B61" s="18" t="s">
+        <v>175</v>
+      </c>
+      <c r="D61" s="4">
         <v>4</v>
       </c>
-      <c r="E35" s="5" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8">
-      <c r="A36" s="5">
-        <v>12302</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="D36" s="5">
-        <v>2</v>
-      </c>
-      <c r="E36" s="5" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8">
-      <c r="A37" s="5">
-        <v>12303</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="D37" s="5">
-        <v>2</v>
-      </c>
-      <c r="E37" s="5" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="38" ht="17" customHeight="1" spans="1:8">
-      <c r="A38" s="5">
-        <v>12304</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="D38" s="5">
-        <v>2</v>
-      </c>
-      <c r="E38" s="5" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8">
-      <c r="A39" s="5">
-        <v>12305</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="D39" s="5">
+      <c r="E61" s="4" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="18">
+        <v>12502</v>
+      </c>
+      <c r="B62" s="18" t="s">
+        <v>177</v>
+      </c>
+      <c r="D62" s="4">
         <v>3</v>
       </c>
-      <c r="E39" s="5" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8">
-      <c r="A40" s="5">
-        <v>12306</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="D40" s="5">
+      <c r="E62" s="4" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="18">
+        <v>12503</v>
+      </c>
+      <c r="B63" s="18" t="s">
+        <v>179</v>
+      </c>
+      <c r="D63" s="4">
         <v>4</v>
       </c>
-      <c r="E40" s="5" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8">
-      <c r="A41" s="5">
-        <v>12307</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="D41" s="5">
-        <v>2</v>
-      </c>
-      <c r="E41" s="5" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8">
-      <c r="A42" s="5">
-        <v>12308</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="D42" s="5">
-        <v>2</v>
-      </c>
-      <c r="E42" s="5" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8">
-      <c r="A43" s="24">
-        <v>12401</v>
-      </c>
-      <c r="B43" s="24" t="s">
-        <v>130</v>
-      </c>
-      <c r="D43" s="5">
-        <v>1</v>
-      </c>
-      <c r="E43" s="5" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8">
-      <c r="A44" s="24">
-        <v>12402</v>
-      </c>
-      <c r="B44" s="24" t="s">
-        <v>132</v>
-      </c>
-      <c r="D44" s="5">
-        <v>1</v>
-      </c>
-      <c r="E44" s="25" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8">
-      <c r="A45" s="24">
-        <v>12403</v>
-      </c>
-      <c r="B45" s="24" t="s">
-        <v>134</v>
-      </c>
-      <c r="D45" s="5">
-        <v>1</v>
-      </c>
-      <c r="E45" s="25" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8">
-      <c r="A46" s="24">
-        <v>12404</v>
-      </c>
-      <c r="B46" s="24" t="s">
-        <v>136</v>
-      </c>
-      <c r="D46" s="5">
-        <v>1</v>
-      </c>
-      <c r="E46" s="25" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8">
-      <c r="A47" s="24">
-        <v>12405</v>
-      </c>
-      <c r="B47" s="24" t="s">
-        <v>138</v>
-      </c>
-      <c r="D47" s="5">
-        <v>1</v>
-      </c>
-      <c r="E47" s="25" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8">
-      <c r="A48" s="24">
-        <v>12406</v>
-      </c>
-      <c r="B48" s="24" t="s">
-        <v>140</v>
-      </c>
-      <c r="D48" s="5">
-        <v>1</v>
-      </c>
-      <c r="E48" s="25" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="24">
-        <v>12407</v>
-      </c>
-      <c r="B49" s="24" t="s">
-        <v>142</v>
-      </c>
-      <c r="D49" s="5">
-        <v>1</v>
-      </c>
-      <c r="E49" s="25" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="24">
-        <v>12408</v>
-      </c>
-      <c r="B50" s="24" t="s">
-        <v>144</v>
-      </c>
-      <c r="D50" s="5">
-        <v>1</v>
-      </c>
-      <c r="E50" s="25" t="s">
-        <v>145</v>
+      <c r="E63" s="4" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="18">
+        <v>12504</v>
+      </c>
+      <c r="B64" s="18" t="s">
+        <v>181</v>
+      </c>
+      <c r="D64" s="4">
+        <v>3</v>
+      </c>
+      <c r="E64" s="4" t="s">
+        <v>182</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/condition.xlsx
+++ b/hall/resources/sample/condition.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="condition" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="195">
   <si>
     <t>id</t>
   </si>
@@ -610,6 +610,42 @@
   </si>
   <si>
     <t>12502_游戏id（0=任意游戏）_下注具体次数_累计下注金额</t>
+  </si>
+  <si>
+    <t>游戏下注次数（赛季玩法，累计赢奖）</t>
+  </si>
+  <si>
+    <t>12601_游戏id（0=任意游戏）_下注具体次数_累计赢奖</t>
+  </si>
+  <si>
+    <t>游戏下注次数(赛季玩法,触发特殊模式)</t>
+  </si>
+  <si>
+    <t>12602_游戏id（0=任意游戏）_下注具体次数_游戏模式id_触发模式次数</t>
+  </si>
+  <si>
+    <t>游戏中奖倍数（赛季玩法）</t>
+  </si>
+  <si>
+    <t>12603_游戏ID（0=任意游戏）_下注具体次数_游戏中奖具体倍数_大于等于中奖倍数的次数</t>
+  </si>
+  <si>
+    <t>游戏中奖次数（赛季玩法）</t>
+  </si>
+  <si>
+    <t>12604_游戏ID（0=任意游戏）_下注具体次数_中奖次数</t>
+  </si>
+  <si>
+    <t>游戏图标出现次数（赛季玩法）</t>
+  </si>
+  <si>
+    <t>12605_游戏ID（0=任意游戏）_下注具体次数_游戏元素ID_出现的次数</t>
+  </si>
+  <si>
+    <t>游戏某局的中奖金额（赛季玩法）</t>
+  </si>
+  <si>
+    <t>12606_游戏ID（0=任意游戏）_下注具体次数_任意局数大于等于目标获胜金额</t>
   </si>
 </sst>
 </file>
@@ -1677,7 +1713,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O64"/>
+  <dimension ref="A1:O70"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="4"/>
@@ -2970,6 +3006,90 @@
       </c>
       <c r="E64" s="4" t="s">
         <v>182</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="4">
+        <v>12601</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="D65" s="4">
+        <v>3</v>
+      </c>
+      <c r="E65" s="4" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="4">
+        <v>12602</v>
+      </c>
+      <c r="B66" s="18" t="s">
+        <v>185</v>
+      </c>
+      <c r="D66" s="4">
+        <v>4</v>
+      </c>
+      <c r="E66" s="4" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="4">
+        <v>12603</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="D67" s="4">
+        <v>4</v>
+      </c>
+      <c r="E67" s="4" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="4">
+        <v>12604</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="D68" s="4">
+        <v>3</v>
+      </c>
+      <c r="E68" s="4" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="4">
+        <v>12605</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="D69" s="4">
+        <v>4</v>
+      </c>
+      <c r="E69" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="4">
+        <v>12606</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="D70" s="4">
+        <v>3</v>
+      </c>
+      <c r="E70" s="4" t="s">
+        <v>194</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/condition.xlsx
+++ b/hall/resources/sample/condition.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="condition" sheetId="1" r:id="rId1"/>
@@ -540,40 +540,40 @@
     <t>12307_接取任务后，截止到任务时间结束期间，渠道ID_个人累计充值大于等于金额</t>
   </si>
   <si>
-    <t>模拟经营-SLOT建筑-金币增加收益(‰)/min</t>
-  </si>
-  <si>
-    <t>12401_具体‰数值</t>
-  </si>
-  <si>
-    <t>模拟经营-扑克建筑-金币增加收益(‰)/min</t>
-  </si>
-  <si>
-    <t>12402_具体‰数值</t>
-  </si>
-  <si>
-    <t>模拟经营-捕鱼建筑-金币增加收益(‰)/min</t>
-  </si>
-  <si>
-    <t>12403_具体‰数值</t>
-  </si>
-  <si>
-    <t>模拟经营-休息建筑-能量增加收益(‰)/min</t>
-  </si>
-  <si>
-    <t>12404_具‰体数值</t>
-  </si>
-  <si>
-    <t>模拟经营-所有产金币的建筑增加收益(‰)/min</t>
-  </si>
-  <si>
-    <t>12405_具体‰数值</t>
-  </si>
-  <si>
-    <t>模拟经营-知名度增加(‰)</t>
-  </si>
-  <si>
-    <t>12406_具体‰数值</t>
+    <t>模拟经营-SLOT建筑-金币增加收益(%s)/min</t>
+  </si>
+  <si>
+    <t>12401_具体%s数值</t>
+  </si>
+  <si>
+    <t>模拟经营-扑克建筑-金币增加收益(%s)/min</t>
+  </si>
+  <si>
+    <t>12402_具体%s数值</t>
+  </si>
+  <si>
+    <t>模拟经营-捕鱼建筑-金币增加收益(%s)/min</t>
+  </si>
+  <si>
+    <t>12403_具体%s数值</t>
+  </si>
+  <si>
+    <t>模拟经营-休息建筑-能量增加收益(%s)/min</t>
+  </si>
+  <si>
+    <t>12404_具%s体数值</t>
+  </si>
+  <si>
+    <t>模拟经营-所有产金币的建筑增加收益(%s)/min</t>
+  </si>
+  <si>
+    <t>12405_具体%s数值</t>
+  </si>
+  <si>
+    <t>模拟经营-知名度增加(%s)</t>
+  </si>
+  <si>
+    <t>12406_具体%s数值</t>
   </si>
   <si>
     <t>模拟经营-曝光度上限增加(值)</t>
@@ -582,10 +582,10 @@
     <t>12407_具体数值</t>
   </si>
   <si>
-    <t>模拟经营-广告金币收益增加(‰)</t>
-  </si>
-  <si>
-    <t>12408_具体‰数值</t>
+    <t>模拟经营-广告金币收益增加(%s)</t>
+  </si>
+  <si>
+    <t>12408_具体%s数值</t>
   </si>
   <si>
     <t>游戏下注次数(消耗能量,触发特殊模式)</t>

--- a/hall/resources/sample/condition.xlsx
+++ b/hall/resources/sample/condition.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="condition" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="203">
   <si>
     <t>id</t>
   </si>
@@ -646,6 +646,30 @@
   </si>
   <si>
     <t>12606_游戏ID（0=任意游戏）_下注具体次数_任意局数大于等于目标获胜金额</t>
+  </si>
+  <si>
+    <t>挖掘格子数量</t>
+  </si>
+  <si>
+    <t>12701_游戏ID（0=任意游戏）_挖掘格子的数量</t>
+  </si>
+  <si>
+    <t>挖掘深度</t>
+  </si>
+  <si>
+    <t>12702_游戏ID（0=任意游戏）_挖掘的深度</t>
+  </si>
+  <si>
+    <t>挖掘过程使用的道具</t>
+  </si>
+  <si>
+    <t>12702_游戏ID（0=任意游戏）_挖掘使用的道具ID_挖掘使用该道具的数量</t>
+  </si>
+  <si>
+    <t>在挖矿小游戏中兑换的次数</t>
+  </si>
+  <si>
+    <t>12702_游戏ID（0=任意游戏）_在兑换商店使用兑换物的ID（0=所有兑换物）_兑换的次数</t>
   </si>
 </sst>
 </file>
@@ -1713,7 +1737,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O70"/>
+  <dimension ref="A1:O74"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="4"/>
@@ -3090,6 +3114,62 @@
       </c>
       <c r="E70" s="4" t="s">
         <v>194</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="4">
+        <v>12701</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="D71" s="4">
+        <v>2</v>
+      </c>
+      <c r="E71" s="4" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="4">
+        <v>12702</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="D72" s="4">
+        <v>2</v>
+      </c>
+      <c r="E72" s="4" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="4">
+        <v>12703</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="D73" s="4">
+        <v>3</v>
+      </c>
+      <c r="E73" s="4" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="4">
+        <v>12704</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="D74" s="4">
+        <v>3</v>
+      </c>
+      <c r="E74" s="4" t="s">
+        <v>202</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/condition.xlsx
+++ b/hall/resources/sample/condition.xlsx
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="211">
   <si>
     <t>id</t>
   </si>
@@ -612,7 +612,7 @@
     <t>12502_游戏id（0=任意游戏）_下注具体次数_累计下注金额</t>
   </si>
   <si>
-    <t>游戏下注次数（赛季玩法，累计赢奖）</t>
+    <t>游戏赢奖金额（赛季玩法，累计赢奖）</t>
   </si>
   <si>
     <t>12601_游戏id（0=任意游戏）_下注具体次数_累计赢奖</t>
@@ -646,6 +646,30 @@
   </si>
   <si>
     <t>12606_游戏ID（0=任意游戏）_下注具体次数_任意局数大于等于目标获胜金额</t>
+  </si>
+  <si>
+    <t>游戏竞技匹配次数（赛季玩法）</t>
+  </si>
+  <si>
+    <t>12607_游戏ID（0=任意游戏）_竞技匹配成功的次数</t>
+  </si>
+  <si>
+    <t>宝石掉落次数（赛季玩法）</t>
+  </si>
+  <si>
+    <t>12608_游戏ID（0=任意游戏）_宝石掉落的次数</t>
+  </si>
+  <si>
+    <t>赛季币累计赢取金额（赛季玩法）</t>
+  </si>
+  <si>
+    <t>12609_游戏ID(0 = 任意游戏)（不区分倍场）_大于等于总押注条件_货币ID(赛季币)_大于等于目标获胜金额</t>
+  </si>
+  <si>
+    <t>游戏投注次数（赛季玩法）</t>
+  </si>
+  <si>
+    <t>12610_游戏ID(0 = 任意游戏)（不区分倍场)_大于等于总押注条件_货币ID(赛季币)_等于目标投注次数</t>
   </si>
   <si>
     <t>挖掘格子数量</t>
@@ -1737,7 +1761,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O74"/>
+  <dimension ref="A1:O78"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="4"/>
@@ -3118,7 +3142,7 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="4">
-        <v>12701</v>
+        <v>12607</v>
       </c>
       <c r="B71" s="4" t="s">
         <v>195</v>
@@ -3132,7 +3156,7 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="4">
-        <v>12702</v>
+        <v>12608</v>
       </c>
       <c r="B72" s="4" t="s">
         <v>197</v>
@@ -3146,13 +3170,13 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="4">
-        <v>12703</v>
+        <v>12609</v>
       </c>
       <c r="B73" s="4" t="s">
         <v>199</v>
       </c>
       <c r="D73" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E73" s="4" t="s">
         <v>200</v>
@@ -3160,16 +3184,72 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="4">
-        <v>12704</v>
+        <v>12610</v>
       </c>
       <c r="B74" s="4" t="s">
         <v>201</v>
       </c>
       <c r="D74" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E74" s="4" t="s">
         <v>202</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="4">
+        <v>12701</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="D75" s="4">
+        <v>2</v>
+      </c>
+      <c r="E75" s="4" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="4">
+        <v>12702</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="D76" s="4">
+        <v>2</v>
+      </c>
+      <c r="E76" s="4" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="4">
+        <v>12703</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="D77" s="4">
+        <v>3</v>
+      </c>
+      <c r="E77" s="4" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="4">
+        <v>12704</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="D78" s="4">
+        <v>3</v>
+      </c>
+      <c r="E78" s="4" t="s">
+        <v>210</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/condition.xlsx
+++ b/hall/resources/sample/condition.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="condition" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="195">
   <si>
     <t>id</t>
   </si>
@@ -538,54 +538,6 @@
   </si>
   <si>
     <t>12307_接取任务后，截止到任务时间结束期间，渠道ID_个人累计充值大于等于金额</t>
-  </si>
-  <si>
-    <t>模拟经营-SLOT建筑-金币增加收益(%s)/min</t>
-  </si>
-  <si>
-    <t>12401_具体%s数值</t>
-  </si>
-  <si>
-    <t>模拟经营-扑克建筑-金币增加收益(%s)/min</t>
-  </si>
-  <si>
-    <t>12402_具体%s数值</t>
-  </si>
-  <si>
-    <t>模拟经营-捕鱼建筑-金币增加收益(%s)/min</t>
-  </si>
-  <si>
-    <t>12403_具体%s数值</t>
-  </si>
-  <si>
-    <t>模拟经营-休息建筑-能量增加收益(%s)/min</t>
-  </si>
-  <si>
-    <t>12404_具%s体数值</t>
-  </si>
-  <si>
-    <t>模拟经营-所有产金币的建筑增加收益(%s)/min</t>
-  </si>
-  <si>
-    <t>12405_具体%s数值</t>
-  </si>
-  <si>
-    <t>模拟经营-知名度增加(%s)</t>
-  </si>
-  <si>
-    <t>12406_具体%s数值</t>
-  </si>
-  <si>
-    <t>模拟经营-曝光度上限增加(值)</t>
-  </si>
-  <si>
-    <t>12407_具体数值</t>
-  </si>
-  <si>
-    <t>模拟经营-广告金币收益增加(%s)</t>
-  </si>
-  <si>
-    <t>12408_具体%s数值</t>
   </si>
   <si>
     <t>游戏下注次数(消耗能量,触发特殊模式)</t>
@@ -898,7 +850,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="38">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -920,12 +872,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1254,7 +1200,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1278,16 +1224,16 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1296,89 +1242,89 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1428,12 +1374,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1761,7 +1701,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O78"/>
+  <dimension ref="A1:O70"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="4"/>
@@ -2890,13 +2830,13 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="16">
-        <v>12401</v>
+        <v>12501</v>
       </c>
       <c r="B53" s="16" t="s">
         <v>159</v>
       </c>
       <c r="D53" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E53" s="4" t="s">
         <v>160</v>
@@ -2904,107 +2844,107 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="16">
-        <v>12402</v>
+        <v>12502</v>
       </c>
       <c r="B54" s="16" t="s">
         <v>161</v>
       </c>
       <c r="D54" s="4">
-        <v>1</v>
-      </c>
-      <c r="E54" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="E54" s="4" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="16">
-        <v>12403</v>
+        <v>12503</v>
       </c>
       <c r="B55" s="16" t="s">
         <v>163</v>
       </c>
       <c r="D55" s="4">
-        <v>1</v>
-      </c>
-      <c r="E55" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="E55" s="4" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="16">
-        <v>12404</v>
+        <v>12504</v>
       </c>
       <c r="B56" s="16" t="s">
         <v>165</v>
       </c>
       <c r="D56" s="4">
-        <v>1</v>
-      </c>
-      <c r="E56" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="E56" s="4" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="57" spans="1:5">
-      <c r="A57" s="16">
-        <v>12405</v>
-      </c>
-      <c r="B57" s="16" t="s">
+      <c r="A57" s="4">
+        <v>12601</v>
+      </c>
+      <c r="B57" s="4" t="s">
         <v>167</v>
       </c>
       <c r="D57" s="4">
-        <v>1</v>
-      </c>
-      <c r="E57" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="E57" s="4" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="58" spans="1:5">
-      <c r="A58" s="16">
-        <v>12406</v>
+      <c r="A58" s="4">
+        <v>12602</v>
       </c>
       <c r="B58" s="16" t="s">
         <v>169</v>
       </c>
       <c r="D58" s="4">
-        <v>1</v>
-      </c>
-      <c r="E58" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="E58" s="4" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="59" spans="1:5">
-      <c r="A59" s="16">
-        <v>12407</v>
-      </c>
-      <c r="B59" s="16" t="s">
+      <c r="A59" s="4">
+        <v>12603</v>
+      </c>
+      <c r="B59" s="4" t="s">
         <v>171</v>
       </c>
       <c r="D59" s="4">
-        <v>1</v>
-      </c>
-      <c r="E59" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="E59" s="4" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="60" spans="1:5">
-      <c r="A60" s="16">
-        <v>12408</v>
-      </c>
-      <c r="B60" s="16" t="s">
+      <c r="A60" s="4">
+        <v>12604</v>
+      </c>
+      <c r="B60" s="4" t="s">
         <v>173</v>
       </c>
       <c r="D60" s="4">
-        <v>1</v>
-      </c>
-      <c r="E60" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="E60" s="4" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="61" spans="1:5">
-      <c r="A61" s="18">
-        <v>12501</v>
-      </c>
-      <c r="B61" s="18" t="s">
+      <c r="A61" s="4">
+        <v>12605</v>
+      </c>
+      <c r="B61" s="4" t="s">
         <v>175</v>
       </c>
       <c r="D61" s="4">
@@ -3015,10 +2955,10 @@
       </c>
     </row>
     <row r="62" spans="1:5">
-      <c r="A62" s="18">
-        <v>12502</v>
-      </c>
-      <c r="B62" s="18" t="s">
+      <c r="A62" s="4">
+        <v>12606</v>
+      </c>
+      <c r="B62" s="4" t="s">
         <v>177</v>
       </c>
       <c r="D62" s="4">
@@ -3029,28 +2969,28 @@
       </c>
     </row>
     <row r="63" spans="1:5">
-      <c r="A63" s="18">
-        <v>12503</v>
-      </c>
-      <c r="B63" s="18" t="s">
+      <c r="A63" s="4">
+        <v>12607</v>
+      </c>
+      <c r="B63" s="4" t="s">
         <v>179</v>
       </c>
       <c r="D63" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E63" s="4" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="64" spans="1:5">
-      <c r="A64" s="18">
-        <v>12504</v>
-      </c>
-      <c r="B64" s="18" t="s">
+      <c r="A64" s="4">
+        <v>12608</v>
+      </c>
+      <c r="B64" s="4" t="s">
         <v>181</v>
       </c>
       <c r="D64" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E64" s="4" t="s">
         <v>182</v>
@@ -3058,13 +2998,13 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="4">
-        <v>12601</v>
+        <v>12609</v>
       </c>
       <c r="B65" s="4" t="s">
         <v>183</v>
       </c>
       <c r="D65" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E65" s="4" t="s">
         <v>184</v>
@@ -3072,9 +3012,9 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="4">
-        <v>12602</v>
-      </c>
-      <c r="B66" s="18" t="s">
+        <v>12610</v>
+      </c>
+      <c r="B66" s="4" t="s">
         <v>185</v>
       </c>
       <c r="D66" s="4">
@@ -3086,13 +3026,13 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="4">
-        <v>12603</v>
+        <v>12701</v>
       </c>
       <c r="B67" s="4" t="s">
         <v>187</v>
       </c>
       <c r="D67" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E67" s="4" t="s">
         <v>188</v>
@@ -3100,13 +3040,13 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="4">
-        <v>12604</v>
+        <v>12702</v>
       </c>
       <c r="B68" s="4" t="s">
         <v>189</v>
       </c>
       <c r="D68" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E68" s="4" t="s">
         <v>190</v>
@@ -3114,13 +3054,13 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="4">
-        <v>12605</v>
+        <v>12703</v>
       </c>
       <c r="B69" s="4" t="s">
         <v>191</v>
       </c>
       <c r="D69" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E69" s="4" t="s">
         <v>192</v>
@@ -3128,7 +3068,7 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="4">
-        <v>12606</v>
+        <v>12704</v>
       </c>
       <c r="B70" s="4" t="s">
         <v>193</v>
@@ -3138,118 +3078,6 @@
       </c>
       <c r="E70" s="4" t="s">
         <v>194</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="4">
-        <v>12607</v>
-      </c>
-      <c r="B71" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="D71" s="4">
-        <v>2</v>
-      </c>
-      <c r="E71" s="4" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="4">
-        <v>12608</v>
-      </c>
-      <c r="B72" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="D72" s="4">
-        <v>2</v>
-      </c>
-      <c r="E72" s="4" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="4">
-        <v>12609</v>
-      </c>
-      <c r="B73" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="D73" s="4">
-        <v>4</v>
-      </c>
-      <c r="E73" s="4" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="4">
-        <v>12610</v>
-      </c>
-      <c r="B74" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="D74" s="4">
-        <v>4</v>
-      </c>
-      <c r="E74" s="4" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="4">
-        <v>12701</v>
-      </c>
-      <c r="B75" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="D75" s="4">
-        <v>2</v>
-      </c>
-      <c r="E75" s="4" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="4">
-        <v>12702</v>
-      </c>
-      <c r="B76" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="D76" s="4">
-        <v>2</v>
-      </c>
-      <c r="E76" s="4" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="4">
-        <v>12703</v>
-      </c>
-      <c r="B77" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="D77" s="4">
-        <v>3</v>
-      </c>
-      <c r="E77" s="4" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="4">
-        <v>12704</v>
-      </c>
-      <c r="B78" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="D78" s="4">
-        <v>3</v>
-      </c>
-      <c r="E78" s="4" t="s">
-        <v>210</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/condition.xlsx
+++ b/hall/resources/sample/condition.xlsx
@@ -56,6 +56,60 @@
         </r>
       </text>
     </comment>
+    <comment ref="E28" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+大奖名称	大奖类型
+sweet win	1
+big win	2
+mega win	3
+epic win	4
+legendary win	5
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E29" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+奖池名称	奖池类型
+mini	1
+minor	2
+major	3
+grand	4</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -237,7 +291,7 @@
     <t>activityTotalRecharge</t>
   </si>
   <si>
-    <t>11002 活动开始后，总累计充值大于等于金额_渠道ID</t>
+    <t>11002 活动开始后，渠道ID_总累计充值大于等于金额</t>
   </si>
   <si>
     <t>个人今日累计充值</t>

--- a/hall/resources/sample/condition.xlsx
+++ b/hall/resources/sample/condition.xlsx
@@ -444,19 +444,19 @@
     <t>12202_游戏ID(0)_道具ID_道具数量</t>
   </si>
   <si>
-    <t>累计触发SWEET WIN N次</t>
+    <t>累积：触发SWEET WIN N次</t>
   </si>
   <si>
     <t>12203_大奖类型_次数</t>
   </si>
   <si>
-    <t>累计触发MINI奖池N次</t>
+    <t>累积：触发MINI奖池N次</t>
   </si>
   <si>
     <t>12204_奖池类型_次数</t>
   </si>
   <si>
-    <t>累计触发免费游戏模式N次</t>
+    <t>累积：触发免费游戏模式N次</t>
   </si>
   <si>
     <t>12205_次数</t>
@@ -468,13 +468,13 @@
     <t>12206_建筑ID(0)_次数</t>
   </si>
   <si>
-    <t>建筑升到N级</t>
+    <t>累积：X建筑升到N级</t>
   </si>
   <si>
     <t>12207_建筑ID(0)_等级</t>
   </si>
   <si>
-    <t>拥有N个X级以上建筑</t>
+    <t>累积：拥有N个X级以上建筑</t>
   </si>
   <si>
     <t>12208_数量_等级</t>
@@ -486,19 +486,19 @@
     <t>12209_次数</t>
   </si>
   <si>
-    <t>观看广告金币\钻石收益达到N</t>
+    <t>累积：观看广告金币\钻石收益达到N</t>
   </si>
   <si>
     <t>12210_道具ID_数量</t>
   </si>
   <si>
-    <t>招募N个X类型的雇员</t>
+    <t>累积：招募N个X类型的雇员</t>
   </si>
   <si>
     <t>12211_雇员类型_数量</t>
   </si>
   <si>
-    <t>拥有N个X星雇员</t>
+    <t>累积：拥有N个X星雇员</t>
   </si>
   <si>
     <t>12212_雇员类型_数量_星级</t>
@@ -510,43 +510,43 @@
     <t>12213_免费0(付费1)_次数</t>
   </si>
   <si>
-    <t>拥有N个X星游客</t>
+    <t>累积：拥有N个X星游客</t>
   </si>
   <si>
     <t>12214_数量_星级</t>
   </si>
   <si>
-    <t>经营收益 金币\能量\道具 累积达到N</t>
+    <t>累积：经营收益 金币\能量\道具 累积达到N</t>
   </si>
   <si>
     <t>12215_道具ID_数量</t>
   </si>
   <si>
-    <t>累积研发N个游戏</t>
+    <t>累积：研发N个游戏</t>
   </si>
   <si>
     <t>12216_数量</t>
   </si>
   <si>
-    <t>累积拜访N次</t>
+    <t>累积：拜访N次</t>
   </si>
   <si>
     <t>12217_数量</t>
   </si>
   <si>
-    <t>累积登陆N天</t>
+    <t>累积：登陆N天</t>
   </si>
   <si>
     <t>12218_数量</t>
   </si>
   <si>
-    <t>累积解锁N个娱乐城</t>
+    <t>累积：解锁N个娱乐城</t>
   </si>
   <si>
     <t>12219_数量</t>
   </si>
   <si>
-    <t>累积消费N金币\钻石</t>
+    <t>累积：消费N金币\钻石</t>
   </si>
   <si>
     <t>12220_道具ID_数量</t>

--- a/hall/resources/sample/condition.xlsx
+++ b/hall/resources/sample/condition.xlsx
@@ -110,12 +110,66 @@
         </r>
       </text>
     </comment>
+    <comment ref="E47" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+大奖名称	大奖类型
+sweet win	1
+big win	2
+mega win	3
+epic win	4
+legendary win	5
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E48" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+奖池名称	奖池类型
+mini	1
+minor	2
+major	3
+grand	4</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="212">
   <si>
     <t>id</t>
   </si>
@@ -432,124 +486,175 @@
     <t>12102_道具ID_等于大于目标数量(游戏下注产生的消耗不计算，其它地方都计算 例 系统升级、兑换 )</t>
   </si>
   <si>
-    <t>在SLOT游戏中单次赢奖N金币</t>
+    <t>接取：在SLOT游戏中单次赢奖N金币</t>
   </si>
   <si>
     <t>12201_游戏ID(0)_金币数量</t>
   </si>
   <si>
-    <t>在SLOT游戏中获得N个X道具</t>
+    <t>接取：在SLOT游戏中获得N个X道具</t>
   </si>
   <si>
     <t>12202_游戏ID(0)_道具ID_道具数量</t>
   </si>
   <si>
+    <t>接取：触发SWEET WIN N次</t>
+  </si>
+  <si>
+    <t>12203_大奖类型_次数</t>
+  </si>
+  <si>
+    <t>接取：触发MINI奖池N次</t>
+  </si>
+  <si>
+    <t>12204_奖池类型_次数</t>
+  </si>
+  <si>
+    <t>接取：触发免费游戏模式N次</t>
+  </si>
+  <si>
+    <t>12205_次数</t>
+  </si>
+  <si>
+    <t>接取：建筑升级N次</t>
+  </si>
+  <si>
+    <t>12206_建筑ID(0)_次数</t>
+  </si>
+  <si>
+    <t>接取：X建筑升到N级</t>
+  </si>
+  <si>
+    <t>12207_建筑ID(0)_等级</t>
+  </si>
+  <si>
+    <t>接取：拥有N个X级以上建筑</t>
+  </si>
+  <si>
+    <t>12208_数量_等级</t>
+  </si>
+  <si>
+    <t>接取：观看N次广告</t>
+  </si>
+  <si>
+    <t>12209_次数</t>
+  </si>
+  <si>
+    <t>接取：观看广告金币\钻石收益达到N</t>
+  </si>
+  <si>
+    <t>12210_道具ID_数量</t>
+  </si>
+  <si>
+    <t>接取：招募N个X类型的雇员</t>
+  </si>
+  <si>
+    <t>12211_雇员类型_数量</t>
+  </si>
+  <si>
+    <t>接取：拥有N个X星雇员</t>
+  </si>
+  <si>
+    <t>12212_雇员类型_数量_星级</t>
+  </si>
+  <si>
+    <t>接取：招商游客N次</t>
+  </si>
+  <si>
+    <t>12213_免费0(付费1)_次数</t>
+  </si>
+  <si>
+    <t>接取：拥有N个X星游客</t>
+  </si>
+  <si>
+    <t>12214_数量_星级</t>
+  </si>
+  <si>
+    <t>接取：经营收益 金币\能量\道具 累积达到N</t>
+  </si>
+  <si>
+    <t>12215_道具ID_数量</t>
+  </si>
+  <si>
+    <t>接取：研发N个游戏</t>
+  </si>
+  <si>
+    <t>12216_数量</t>
+  </si>
+  <si>
+    <t>接取：拜访N次</t>
+  </si>
+  <si>
+    <t>12217_数量</t>
+  </si>
+  <si>
+    <t>接取：登陆N天</t>
+  </si>
+  <si>
+    <t>12218_数量</t>
+  </si>
+  <si>
+    <t>接取：解锁N个娱乐城</t>
+  </si>
+  <si>
+    <t>12219_数量</t>
+  </si>
+  <si>
+    <t>接取：消费N金币\钻石</t>
+  </si>
+  <si>
+    <t>12220_道具ID_数量</t>
+  </si>
+  <si>
+    <t>累积：在SLOT游戏中获得N个X道具</t>
+  </si>
+  <si>
     <t>累积：触发SWEET WIN N次</t>
   </si>
   <si>
-    <t>12203_大奖类型_次数</t>
-  </si>
-  <si>
     <t>累积：触发MINI奖池N次</t>
   </si>
   <si>
-    <t>12204_奖池类型_次数</t>
-  </si>
-  <si>
     <t>累积：触发免费游戏模式N次</t>
   </si>
   <si>
-    <t>12205_次数</t>
-  </si>
-  <si>
-    <t>建筑升级N次</t>
-  </si>
-  <si>
-    <t>12206_建筑ID(0)_次数</t>
-  </si>
-  <si>
-    <t>累积：X建筑升到N级</t>
-  </si>
-  <si>
-    <t>12207_建筑ID(0)_等级</t>
+    <t>累积：建筑升级N次</t>
   </si>
   <si>
     <t>累积：拥有N个X级以上建筑</t>
   </si>
   <si>
-    <t>12208_数量_等级</t>
-  </si>
-  <si>
-    <t>观看N次广告</t>
-  </si>
-  <si>
-    <t>12209_次数</t>
+    <t>累积：观看N次广告</t>
   </si>
   <si>
     <t>累积：观看广告金币\钻石收益达到N</t>
   </si>
   <si>
-    <t>12210_道具ID_数量</t>
-  </si>
-  <si>
-    <t>累积：招募N个X类型的雇员</t>
-  </si>
-  <si>
-    <t>12211_雇员类型_数量</t>
-  </si>
-  <si>
     <t>累积：拥有N个X星雇员</t>
   </si>
   <si>
-    <t>12212_雇员类型_数量_星级</t>
-  </si>
-  <si>
-    <t>招商游客N次</t>
-  </si>
-  <si>
-    <t>12213_免费0(付费1)_次数</t>
+    <t>累积：招商游客N次</t>
   </si>
   <si>
     <t>累积：拥有N个X星游客</t>
   </si>
   <si>
-    <t>12214_数量_星级</t>
-  </si>
-  <si>
     <t>累积：经营收益 金币\能量\道具 累积达到N</t>
   </si>
   <si>
-    <t>12215_道具ID_数量</t>
-  </si>
-  <si>
     <t>累积：研发N个游戏</t>
   </si>
   <si>
-    <t>12216_数量</t>
-  </si>
-  <si>
     <t>累积：拜访N次</t>
   </si>
   <si>
-    <t>12217_数量</t>
-  </si>
-  <si>
     <t>累积：登陆N天</t>
   </si>
   <si>
-    <t>12218_数量</t>
-  </si>
-  <si>
     <t>累积：解锁N个娱乐城</t>
   </si>
   <si>
-    <t>12219_数量</t>
-  </si>
-  <si>
     <t>累积：消费N金币\钻石</t>
-  </si>
-  <si>
-    <t>12220_道具ID_数量</t>
   </si>
   <si>
     <t>游戏中奖倍数</t>
@@ -712,7 +817,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -745,6 +850,12 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF7030A0"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -1248,137 +1359,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1420,6 +1531,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1755,7 +1869,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O70"/>
+  <dimension ref="A1:O87"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="4"/>
@@ -2786,352 +2900,658 @@
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="14">
-        <v>12301</v>
+        <v>12251</v>
       </c>
       <c r="B46" s="14" t="s">
         <v>145</v>
       </c>
-      <c r="D46" s="4">
-        <v>4</v>
-      </c>
-      <c r="E46" s="4" t="s">
+      <c r="C46" s="2"/>
+      <c r="D46" s="2">
+        <v>3</v>
+      </c>
+      <c r="E46" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="F46" s="2"/>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="A47" s="14">
+        <v>12252</v>
+      </c>
+      <c r="B47" s="14" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="47" s="3" customFormat="1" spans="1:8">
-      <c r="A47" s="15">
-        <v>12302</v>
-      </c>
-      <c r="B47" s="15" t="s">
-        <v>147</v>
-      </c>
-      <c r="D47" s="3">
-        <v>3</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>148</v>
-      </c>
+      <c r="C47" s="2"/>
+      <c r="D47" s="2">
+        <v>2</v>
+      </c>
+      <c r="E47" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="F47" s="2"/>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2"/>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="14">
+        <v>12253</v>
+      </c>
+      <c r="B48" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="C48" s="2"/>
+      <c r="D48" s="2">
+        <v>2</v>
+      </c>
+      <c r="E48" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="F48" s="2"/>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2"/>
+    </row>
+    <row r="49" spans="1:8">
+      <c r="A49" s="14">
+        <v>12254</v>
+      </c>
+      <c r="B49" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2">
+        <v>1</v>
+      </c>
+      <c r="E49" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="F49" s="2"/>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2"/>
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50" s="14">
+        <v>12255</v>
+      </c>
+      <c r="B50" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" s="2">
+        <v>2</v>
+      </c>
+      <c r="E50" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="F50" s="2"/>
+      <c r="G50" s="2"/>
+      <c r="H50" s="2"/>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51" s="14">
+        <v>12256</v>
+      </c>
+      <c r="B51" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="C51" s="2"/>
+      <c r="D51" s="2">
+        <v>2</v>
+      </c>
+      <c r="E51" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="F51" s="2"/>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2"/>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52" s="14">
+        <v>12257</v>
+      </c>
+      <c r="B52" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="C52" s="2"/>
+      <c r="D52" s="2">
+        <v>1</v>
+      </c>
+      <c r="E52" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="F52" s="2"/>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2"/>
+    </row>
+    <row r="53" spans="1:8">
+      <c r="A53" s="14">
+        <v>12258</v>
+      </c>
+      <c r="B53" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" s="2">
+        <v>2</v>
+      </c>
+      <c r="E53" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="F53" s="2"/>
+      <c r="G53" s="2"/>
+      <c r="H53" s="2"/>
+    </row>
+    <row r="54" spans="1:8">
+      <c r="A54" s="14">
+        <v>12259</v>
+      </c>
+      <c r="B54" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" s="2">
+        <v>3</v>
+      </c>
+      <c r="E54" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="F54" s="2"/>
+      <c r="G54" s="2"/>
+      <c r="H54" s="2"/>
+    </row>
+    <row r="55" spans="1:8">
+      <c r="A55" s="14">
+        <v>12260</v>
+      </c>
+      <c r="B55" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" s="2">
+        <v>2</v>
+      </c>
+      <c r="E55" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="F55" s="2"/>
+      <c r="G55" s="2"/>
+      <c r="H55" s="2"/>
+    </row>
+    <row r="56" spans="1:8">
+      <c r="A56" s="14">
+        <v>12261</v>
+      </c>
+      <c r="B56" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" s="2">
+        <v>2</v>
+      </c>
+      <c r="E56" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="F56" s="2"/>
+      <c r="G56" s="2"/>
+      <c r="H56" s="2"/>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="A57" s="14">
+        <v>12262</v>
+      </c>
+      <c r="B57" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" s="2">
+        <v>2</v>
+      </c>
+      <c r="E57" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="F57" s="2"/>
+      <c r="G57" s="2"/>
+      <c r="H57" s="2"/>
+    </row>
+    <row r="58" spans="1:8">
+      <c r="A58" s="14">
+        <v>12263</v>
+      </c>
+      <c r="B58" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" s="2">
+        <v>1</v>
+      </c>
+      <c r="E58" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="F58" s="2"/>
+      <c r="G58" s="2"/>
+      <c r="H58" s="2"/>
+    </row>
+    <row r="59" spans="1:8">
+      <c r="A59" s="14">
+        <v>12264</v>
+      </c>
+      <c r="B59" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" s="2">
+        <v>1</v>
+      </c>
+      <c r="E59" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="F59" s="2"/>
+      <c r="G59" s="2"/>
+      <c r="H59" s="2"/>
+    </row>
+    <row r="60" spans="1:8">
+      <c r="A60" s="14">
+        <v>12265</v>
+      </c>
+      <c r="B60" s="14" t="s">
+        <v>159</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" s="2">
+        <v>1</v>
+      </c>
+      <c r="E60" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="F60" s="2"/>
+      <c r="G60" s="2"/>
+      <c r="H60" s="2"/>
+    </row>
+    <row r="61" spans="1:8">
+      <c r="A61" s="14">
+        <v>12266</v>
+      </c>
+      <c r="B61" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" s="2">
+        <v>1</v>
+      </c>
+      <c r="E61" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="F61" s="2"/>
+      <c r="G61" s="2"/>
+      <c r="H61" s="2"/>
+    </row>
+    <row r="62" spans="1:8">
+      <c r="A62" s="14">
+        <v>12267</v>
+      </c>
+      <c r="B62" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" s="2">
+        <v>2</v>
+      </c>
+      <c r="E62" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="F62" s="2"/>
+      <c r="G62" s="2"/>
+      <c r="H62" s="2"/>
+    </row>
+    <row r="63" spans="1:8">
+      <c r="A63" s="15">
+        <v>12301</v>
+      </c>
+      <c r="B63" s="15" t="s">
+        <v>162</v>
+      </c>
+      <c r="D63" s="4">
+        <v>4</v>
+      </c>
+      <c r="E63" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="64" s="3" customFormat="1" spans="1:8">
+      <c r="A64" s="16">
+        <v>12302</v>
+      </c>
+      <c r="B64" s="16" t="s">
+        <v>164</v>
+      </c>
+      <c r="D64" s="3">
+        <v>3</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="15">
         <v>12303</v>
       </c>
-      <c r="B48" s="14" t="s">
-        <v>149</v>
-      </c>
-      <c r="D48" s="4">
-        <v>2</v>
-      </c>
-      <c r="E48" s="4" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="15">
+      <c r="B65" s="15" t="s">
+        <v>166</v>
+      </c>
+      <c r="D65" s="4">
+        <v>2</v>
+      </c>
+      <c r="E65" s="4" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="16">
         <v>12304</v>
       </c>
-      <c r="B49" s="14" t="s">
-        <v>151</v>
-      </c>
-      <c r="D49" s="4">
-        <v>2</v>
-      </c>
-      <c r="E49" s="4" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="14">
+      <c r="B66" s="15" t="s">
+        <v>168</v>
+      </c>
+      <c r="D66" s="4">
+        <v>2</v>
+      </c>
+      <c r="E66" s="4" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="15">
         <v>12305</v>
       </c>
-      <c r="B50" s="14" t="s">
-        <v>153</v>
-      </c>
-      <c r="D50" s="4">
-        <v>2</v>
-      </c>
-      <c r="E50" s="4" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="51" s="3" customFormat="1" spans="1:5">
-      <c r="A51" s="15">
+      <c r="B67" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="D67" s="4">
+        <v>2</v>
+      </c>
+      <c r="E67" s="4" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="68" s="3" customFormat="1" spans="1:5">
+      <c r="A68" s="16">
         <v>12306</v>
       </c>
-      <c r="B51" s="15" t="s">
-        <v>155</v>
-      </c>
-      <c r="D51" s="3">
+      <c r="B68" s="16" t="s">
+        <v>172</v>
+      </c>
+      <c r="D68" s="3">
         <v>4</v>
       </c>
-      <c r="E51" s="3" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="52" s="3" customFormat="1" spans="1:5">
-      <c r="A52" s="14">
+      <c r="E68" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="69" s="3" customFormat="1" spans="1:5">
+      <c r="A69" s="15">
         <v>12307</v>
       </c>
-      <c r="B52" s="15" t="s">
-        <v>157</v>
-      </c>
-      <c r="D52" s="3">
-        <v>2</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="16">
+      <c r="B69" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="D69" s="3">
+        <v>2</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="17">
         <v>12501</v>
       </c>
-      <c r="B53" s="16" t="s">
-        <v>159</v>
-      </c>
-      <c r="D53" s="4">
+      <c r="B70" s="17" t="s">
+        <v>176</v>
+      </c>
+      <c r="D70" s="4">
         <v>4</v>
       </c>
-      <c r="E53" s="4" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="16">
+      <c r="E70" s="4" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="17">
         <v>12502</v>
       </c>
-      <c r="B54" s="16" t="s">
-        <v>161</v>
-      </c>
-      <c r="D54" s="4">
+      <c r="B71" s="17" t="s">
+        <v>178</v>
+      </c>
+      <c r="D71" s="4">
         <v>3</v>
       </c>
-      <c r="E54" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="16">
+      <c r="E71" s="4" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="17">
         <v>12503</v>
       </c>
-      <c r="B55" s="16" t="s">
-        <v>163</v>
-      </c>
-      <c r="D55" s="4">
+      <c r="B72" s="17" t="s">
+        <v>180</v>
+      </c>
+      <c r="D72" s="4">
         <v>4</v>
       </c>
-      <c r="E55" s="4" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="16">
+      <c r="E72" s="4" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="17">
         <v>12504</v>
       </c>
-      <c r="B56" s="16" t="s">
-        <v>165</v>
-      </c>
-      <c r="D56" s="4">
+      <c r="B73" s="17" t="s">
+        <v>182</v>
+      </c>
+      <c r="D73" s="4">
         <v>3</v>
       </c>
-      <c r="E56" s="4" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="4">
+      <c r="E73" s="4" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="4">
         <v>12601</v>
       </c>
-      <c r="B57" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="D57" s="4">
+      <c r="B74" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="D74" s="4">
         <v>3</v>
       </c>
-      <c r="E57" s="4" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="4">
+      <c r="E74" s="4" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="4">
         <v>12602</v>
       </c>
-      <c r="B58" s="16" t="s">
-        <v>169</v>
-      </c>
-      <c r="D58" s="4">
+      <c r="B75" s="17" t="s">
+        <v>186</v>
+      </c>
+      <c r="D75" s="4">
         <v>4</v>
       </c>
-      <c r="E58" s="4" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="4">
+      <c r="E75" s="4" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="4">
         <v>12603</v>
       </c>
-      <c r="B59" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="D59" s="4">
+      <c r="B76" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="D76" s="4">
         <v>4</v>
       </c>
-      <c r="E59" s="4" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="4">
+      <c r="E76" s="4" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="4">
         <v>12604</v>
       </c>
-      <c r="B60" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="D60" s="4">
+      <c r="B77" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="D77" s="4">
         <v>3</v>
       </c>
-      <c r="E60" s="4" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="4">
+      <c r="E77" s="4" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="4">
         <v>12605</v>
       </c>
-      <c r="B61" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="D61" s="4">
+      <c r="B78" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="D78" s="4">
         <v>4</v>
       </c>
-      <c r="E61" s="4" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="4">
+      <c r="E78" s="4" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="4">
         <v>12606</v>
       </c>
-      <c r="B62" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="D62" s="4">
+      <c r="B79" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="D79" s="4">
         <v>3</v>
       </c>
-      <c r="E62" s="4" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="4">
+      <c r="E79" s="4" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="4">
         <v>12607</v>
       </c>
-      <c r="B63" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="D63" s="4">
-        <v>2</v>
-      </c>
-      <c r="E63" s="4" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="4">
+      <c r="B80" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="D80" s="4">
+        <v>2</v>
+      </c>
+      <c r="E80" s="4" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="4">
         <v>12608</v>
       </c>
-      <c r="B64" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="D64" s="4">
-        <v>2</v>
-      </c>
-      <c r="E64" s="4" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="4">
+      <c r="B81" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="D81" s="4">
+        <v>2</v>
+      </c>
+      <c r="E81" s="4" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="4">
         <v>12609</v>
       </c>
-      <c r="B65" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="D65" s="4">
+      <c r="B82" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="D82" s="4">
         <v>4</v>
       </c>
-      <c r="E65" s="4" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="4">
+      <c r="E82" s="4" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" s="4">
         <v>12610</v>
       </c>
-      <c r="B66" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="D66" s="4">
+      <c r="B83" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="D83" s="4">
         <v>4</v>
       </c>
-      <c r="E66" s="4" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="4">
+      <c r="E83" s="4" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84" s="4">
         <v>12701</v>
       </c>
-      <c r="B67" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="D67" s="4">
-        <v>2</v>
-      </c>
-      <c r="E67" s="4" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="4">
+      <c r="B84" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="D84" s="4">
+        <v>2</v>
+      </c>
+      <c r="E84" s="4" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85" s="4">
         <v>12702</v>
       </c>
-      <c r="B68" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="D68" s="4">
-        <v>2</v>
-      </c>
-      <c r="E68" s="4" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="4">
+      <c r="B85" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="D85" s="4">
+        <v>2</v>
+      </c>
+      <c r="E85" s="4" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="A86" s="4">
         <v>12703</v>
       </c>
-      <c r="B69" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="D69" s="4">
+      <c r="B86" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="D86" s="4">
         <v>3</v>
       </c>
-      <c r="E69" s="4" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="4">
+      <c r="E86" s="4" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5">
+      <c r="A87" s="4">
         <v>12704</v>
       </c>
-      <c r="B70" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="D70" s="4">
+      <c r="B87" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="D87" s="4">
         <v>3</v>
       </c>
-      <c r="E70" s="4" t="s">
-        <v>194</v>
+      <c r="E87" s="4" t="s">
+        <v>211</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/condition.xlsx
+++ b/hall/resources/sample/condition.xlsx
@@ -110,12 +110,66 @@
         </r>
       </text>
     </comment>
+    <comment ref="E47" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+大奖名称	大奖类型
+sweet win	1
+big win	2
+mega win	3
+epic win	4
+legendary win	5
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E48" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+奖池名称	奖池类型
+mini	1
+minor	2
+major	3
+grand	4</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="227">
   <si>
     <t>id</t>
   </si>
@@ -432,124 +486,220 @@
     <t>12102_道具ID_等于大于目标数量(游戏下注产生的消耗不计算，其它地方都计算 例 系统升级、兑换 )</t>
   </si>
   <si>
-    <t>在SLOT游戏中单次赢奖N金币</t>
+    <t>接取：在SLOT游戏中单次赢奖N金币</t>
   </si>
   <si>
     <t>12201_游戏ID(0)_金币数量</t>
   </si>
   <si>
-    <t>在SLOT游戏中获得N个X道具</t>
+    <t>接取：在SLOT游戏中获得N个X道具</t>
   </si>
   <si>
     <t>12202_游戏ID(0)_道具ID_道具数量</t>
   </si>
   <si>
+    <t>接取：触发SWEET WIN N次</t>
+  </si>
+  <si>
+    <t>12203_大奖类型_次数</t>
+  </si>
+  <si>
+    <t>接取：触发MINI奖池N次</t>
+  </si>
+  <si>
+    <t>12204_奖池类型_次数</t>
+  </si>
+  <si>
+    <t>接取：触发免费游戏模式N次</t>
+  </si>
+  <si>
+    <t>12205_次数</t>
+  </si>
+  <si>
+    <t>接取：建筑升级N次</t>
+  </si>
+  <si>
+    <t>12206_建筑ID(0)_次数</t>
+  </si>
+  <si>
+    <t>接取：X建筑升到N级</t>
+  </si>
+  <si>
+    <t>12207_建筑ID(0)_等级</t>
+  </si>
+  <si>
+    <t>接取：拥有N个X级以上建筑</t>
+  </si>
+  <si>
+    <t>12208_数量_等级</t>
+  </si>
+  <si>
+    <t>接取：观看N次广告</t>
+  </si>
+  <si>
+    <t>12209_次数</t>
+  </si>
+  <si>
+    <t>接取：观看广告金币\钻石收益达到N</t>
+  </si>
+  <si>
+    <t>12210_道具ID_数量</t>
+  </si>
+  <si>
+    <t>接取：招募N个X类型的雇员</t>
+  </si>
+  <si>
+    <t>12211_雇员类型_数量</t>
+  </si>
+  <si>
+    <t>接取：拥有N个X星雇员</t>
+  </si>
+  <si>
+    <t>12212_雇员类型_数量_星级</t>
+  </si>
+  <si>
+    <t>接取：招商游客N次</t>
+  </si>
+  <si>
+    <t>12213_免费0(付费1)_次数</t>
+  </si>
+  <si>
+    <t>接取：拥有N个X星游客</t>
+  </si>
+  <si>
+    <t>12214_数量_星级</t>
+  </si>
+  <si>
+    <t>接取：经营收益 金币\能量\道具 累积达到N</t>
+  </si>
+  <si>
+    <t>12215_道具ID_数量</t>
+  </si>
+  <si>
+    <t>接取：研发N个游戏</t>
+  </si>
+  <si>
+    <t>12216_数量</t>
+  </si>
+  <si>
+    <t>接取：拜访N次</t>
+  </si>
+  <si>
+    <t>12217_数量</t>
+  </si>
+  <si>
+    <t>接取：登陆N天</t>
+  </si>
+  <si>
+    <t>12218_数量</t>
+  </si>
+  <si>
+    <t>接取：解锁N个娱乐城</t>
+  </si>
+  <si>
+    <t>12219_数量</t>
+  </si>
+  <si>
+    <t>接取：消费N金币\钻石</t>
+  </si>
+  <si>
+    <t>12220_道具ID(仅钻石或金币)_数量</t>
+  </si>
+  <si>
+    <t>累积：在SLOT游戏中获得N个X道具</t>
+  </si>
+  <si>
+    <t>12251_游戏ID(0)_道具ID_道具数量</t>
+  </si>
+  <si>
     <t>累积：触发SWEET WIN N次</t>
   </si>
   <si>
-    <t>12203_大奖类型_次数</t>
+    <t>12252_大奖类型_次数</t>
   </si>
   <si>
     <t>累积：触发MINI奖池N次</t>
   </si>
   <si>
-    <t>12204_奖池类型_次数</t>
+    <t>12253_奖池类型_次数</t>
   </si>
   <si>
     <t>累积：触发免费游戏模式N次</t>
   </si>
   <si>
-    <t>12205_次数</t>
-  </si>
-  <si>
-    <t>建筑升级N次</t>
-  </si>
-  <si>
-    <t>12206_建筑ID(0)_次数</t>
-  </si>
-  <si>
-    <t>累积：X建筑升到N级</t>
-  </si>
-  <si>
-    <t>12207_建筑ID(0)_等级</t>
+    <t>12254_次数</t>
+  </si>
+  <si>
+    <t>累积：建筑升级N次</t>
+  </si>
+  <si>
+    <t>12255_建筑ID(0)_次数</t>
   </si>
   <si>
     <t>累积：拥有N个X级以上建筑</t>
   </si>
   <si>
-    <t>12208_数量_等级</t>
-  </si>
-  <si>
-    <t>观看N次广告</t>
-  </si>
-  <si>
-    <t>12209_次数</t>
-  </si>
-  <si>
-    <t>累积：观看广告金币\钻石收益达到N</t>
-  </si>
-  <si>
-    <t>12210_道具ID_数量</t>
-  </si>
-  <si>
-    <t>累积：招募N个X类型的雇员</t>
-  </si>
-  <si>
-    <t>12211_雇员类型_数量</t>
+    <t>12256_数量_等级</t>
+  </si>
+  <si>
+    <t>累积：观看N次广告</t>
+  </si>
+  <si>
+    <t>12257_次数</t>
   </si>
   <si>
     <t>累积：拥有N个X星雇员</t>
   </si>
   <si>
-    <t>12212_雇员类型_数量_星级</t>
-  </si>
-  <si>
-    <t>招商游客N次</t>
-  </si>
-  <si>
-    <t>12213_免费0(付费1)_次数</t>
+    <t>12259_雇员类型_数量_星级</t>
+  </si>
+  <si>
+    <t>累积：招商游客N次</t>
+  </si>
+  <si>
+    <t>12260_免费0(付费1)_次数</t>
   </si>
   <si>
     <t>累积：拥有N个X星游客</t>
   </si>
   <si>
-    <t>12214_数量_星级</t>
+    <t>12261_数量_星级</t>
   </si>
   <si>
     <t>累积：经营收益 金币\能量\道具 累积达到N</t>
   </si>
   <si>
-    <t>12215_道具ID_数量</t>
+    <t>12262_道具ID_数量</t>
   </si>
   <si>
     <t>累积：研发N个游戏</t>
   </si>
   <si>
-    <t>12216_数量</t>
+    <t>12263_数量</t>
   </si>
   <si>
     <t>累积：拜访N次</t>
   </si>
   <si>
-    <t>12217_数量</t>
+    <t>12264_数量</t>
   </si>
   <si>
     <t>累积：登陆N天</t>
   </si>
   <si>
-    <t>12218_数量</t>
+    <t>12265_数量</t>
   </si>
   <si>
     <t>累积：解锁N个娱乐城</t>
   </si>
   <si>
-    <t>12219_数量</t>
+    <t>12266_数量</t>
   </si>
   <si>
     <t>累积：消费N金币\钻石</t>
   </si>
   <si>
-    <t>12220_道具ID_数量</t>
+    <t>12267_道具ID(仅钻石或金币)_数量</t>
   </si>
   <si>
     <t>游戏中奖倍数</t>
@@ -712,7 +862,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -745,6 +895,12 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF7030A0"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -1248,137 +1404,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1420,6 +1576,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1755,7 +1914,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O70"/>
+  <dimension ref="A1:O86"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="4"/>
@@ -2786,261 +2945,325 @@
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="14">
-        <v>12301</v>
+        <v>12251</v>
       </c>
       <c r="B46" s="14" t="s">
         <v>145</v>
       </c>
-      <c r="D46" s="4">
-        <v>4</v>
-      </c>
-      <c r="E46" s="4" t="s">
+      <c r="C46" s="2"/>
+      <c r="D46" s="2">
+        <v>3</v>
+      </c>
+      <c r="E46" s="13" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="47" s="3" customFormat="1" spans="1:8">
-      <c r="A47" s="15">
-        <v>12302</v>
-      </c>
-      <c r="B47" s="15" t="s">
+      <c r="F46" s="2"/>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="A47" s="14">
+        <v>12252</v>
+      </c>
+      <c r="B47" s="14" t="s">
         <v>147</v>
       </c>
-      <c r="D47" s="3">
-        <v>3</v>
-      </c>
-      <c r="E47" s="3" t="s">
+      <c r="C47" s="2"/>
+      <c r="D47" s="2">
+        <v>2</v>
+      </c>
+      <c r="E47" s="13" t="s">
         <v>148</v>
       </c>
+      <c r="F47" s="2"/>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2"/>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="14">
-        <v>12303</v>
+        <v>12253</v>
       </c>
       <c r="B48" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="D48" s="4">
-        <v>2</v>
-      </c>
-      <c r="E48" s="4" t="s">
+      <c r="C48" s="2"/>
+      <c r="D48" s="2">
+        <v>2</v>
+      </c>
+      <c r="E48" s="13" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="15">
-        <v>12304</v>
+      <c r="F48" s="2"/>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2"/>
+    </row>
+    <row r="49" spans="1:8">
+      <c r="A49" s="14">
+        <v>12254</v>
       </c>
       <c r="B49" s="14" t="s">
         <v>151</v>
       </c>
-      <c r="D49" s="4">
-        <v>2</v>
-      </c>
-      <c r="E49" s="4" t="s">
+      <c r="C49" s="2"/>
+      <c r="D49" s="2">
+        <v>1</v>
+      </c>
+      <c r="E49" s="13" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="50" spans="1:5">
+      <c r="F49" s="2"/>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2"/>
+    </row>
+    <row r="50" spans="1:8">
       <c r="A50" s="14">
-        <v>12305</v>
+        <v>12255</v>
       </c>
       <c r="B50" s="14" t="s">
         <v>153</v>
       </c>
-      <c r="D50" s="4">
-        <v>2</v>
-      </c>
-      <c r="E50" s="4" t="s">
+      <c r="C50" s="2"/>
+      <c r="D50" s="2">
+        <v>2</v>
+      </c>
+      <c r="E50" s="13" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="51" s="3" customFormat="1" spans="1:5">
-      <c r="A51" s="15">
-        <v>12306</v>
-      </c>
-      <c r="B51" s="15" t="s">
+      <c r="F50" s="2"/>
+      <c r="G50" s="2"/>
+      <c r="H50" s="2"/>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51" s="14">
+        <v>12256</v>
+      </c>
+      <c r="B51" s="14" t="s">
         <v>155</v>
       </c>
-      <c r="D51" s="3">
+      <c r="C51" s="2"/>
+      <c r="D51" s="2">
+        <v>2</v>
+      </c>
+      <c r="E51" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="F51" s="2"/>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2"/>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52" s="14">
+        <v>12257</v>
+      </c>
+      <c r="B52" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="C52" s="2"/>
+      <c r="D52" s="2">
+        <v>1</v>
+      </c>
+      <c r="E52" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="F52" s="2"/>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2"/>
+    </row>
+    <row r="53" spans="1:8">
+      <c r="A53" s="14">
+        <v>12259</v>
+      </c>
+      <c r="B53" s="14" t="s">
+        <v>159</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" s="2">
+        <v>3</v>
+      </c>
+      <c r="E53" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="F53" s="2"/>
+      <c r="G53" s="2"/>
+      <c r="H53" s="2"/>
+    </row>
+    <row r="54" spans="1:8">
+      <c r="A54" s="14">
+        <v>12260</v>
+      </c>
+      <c r="B54" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" s="2">
+        <v>2</v>
+      </c>
+      <c r="E54" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="F54" s="2"/>
+      <c r="G54" s="2"/>
+      <c r="H54" s="2"/>
+    </row>
+    <row r="55" spans="1:8">
+      <c r="A55" s="14">
+        <v>12261</v>
+      </c>
+      <c r="B55" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" s="2">
+        <v>2</v>
+      </c>
+      <c r="E55" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="F55" s="2"/>
+      <c r="G55" s="2"/>
+      <c r="H55" s="2"/>
+    </row>
+    <row r="56" spans="1:8">
+      <c r="A56" s="14">
+        <v>12262</v>
+      </c>
+      <c r="B56" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" s="2">
+        <v>2</v>
+      </c>
+      <c r="E56" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="F56" s="2"/>
+      <c r="G56" s="2"/>
+      <c r="H56" s="2"/>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="A57" s="14">
+        <v>12263</v>
+      </c>
+      <c r="B57" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" s="2">
+        <v>1</v>
+      </c>
+      <c r="E57" s="13" t="s">
+        <v>168</v>
+      </c>
+      <c r="F57" s="2"/>
+      <c r="G57" s="2"/>
+      <c r="H57" s="2"/>
+    </row>
+    <row r="58" spans="1:8">
+      <c r="A58" s="14">
+        <v>12264</v>
+      </c>
+      <c r="B58" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" s="2">
+        <v>1</v>
+      </c>
+      <c r="E58" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="F58" s="2"/>
+      <c r="G58" s="2"/>
+      <c r="H58" s="2"/>
+    </row>
+    <row r="59" spans="1:8">
+      <c r="A59" s="14">
+        <v>12265</v>
+      </c>
+      <c r="B59" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" s="2">
+        <v>1</v>
+      </c>
+      <c r="E59" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="F59" s="2"/>
+      <c r="G59" s="2"/>
+      <c r="H59" s="2"/>
+    </row>
+    <row r="60" spans="1:8">
+      <c r="A60" s="14">
+        <v>12266</v>
+      </c>
+      <c r="B60" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" s="2">
+        <v>1</v>
+      </c>
+      <c r="E60" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="F60" s="2"/>
+      <c r="G60" s="2"/>
+      <c r="H60" s="2"/>
+    </row>
+    <row r="61" spans="1:8">
+      <c r="A61" s="14">
+        <v>12267</v>
+      </c>
+      <c r="B61" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" s="2">
+        <v>2</v>
+      </c>
+      <c r="E61" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="F61" s="2"/>
+      <c r="G61" s="2"/>
+      <c r="H61" s="2"/>
+    </row>
+    <row r="62" spans="1:8">
+      <c r="A62" s="15">
+        <v>12301</v>
+      </c>
+      <c r="B62" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="D62" s="4">
         <v>4</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="52" s="3" customFormat="1" spans="1:5">
-      <c r="A52" s="14">
-        <v>12307</v>
-      </c>
-      <c r="B52" s="15" t="s">
-        <v>157</v>
-      </c>
-      <c r="D52" s="3">
-        <v>2</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="16">
-        <v>12501</v>
-      </c>
-      <c r="B53" s="16" t="s">
-        <v>159</v>
-      </c>
-      <c r="D53" s="4">
-        <v>4</v>
-      </c>
-      <c r="E53" s="4" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="16">
-        <v>12502</v>
-      </c>
-      <c r="B54" s="16" t="s">
-        <v>161</v>
-      </c>
-      <c r="D54" s="4">
-        <v>3</v>
-      </c>
-      <c r="E54" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="16">
-        <v>12503</v>
-      </c>
-      <c r="B55" s="16" t="s">
-        <v>163</v>
-      </c>
-      <c r="D55" s="4">
-        <v>4</v>
-      </c>
-      <c r="E55" s="4" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="16">
-        <v>12504</v>
-      </c>
-      <c r="B56" s="16" t="s">
-        <v>165</v>
-      </c>
-      <c r="D56" s="4">
-        <v>3</v>
-      </c>
-      <c r="E56" s="4" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="4">
-        <v>12601</v>
-      </c>
-      <c r="B57" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="D57" s="4">
-        <v>3</v>
-      </c>
-      <c r="E57" s="4" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="4">
-        <v>12602</v>
-      </c>
-      <c r="B58" s="16" t="s">
-        <v>169</v>
-      </c>
-      <c r="D58" s="4">
-        <v>4</v>
-      </c>
-      <c r="E58" s="4" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="4">
-        <v>12603</v>
-      </c>
-      <c r="B59" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="D59" s="4">
-        <v>4</v>
-      </c>
-      <c r="E59" s="4" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="4">
-        <v>12604</v>
-      </c>
-      <c r="B60" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="D60" s="4">
-        <v>3</v>
-      </c>
-      <c r="E60" s="4" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="4">
-        <v>12605</v>
-      </c>
-      <c r="B61" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="D61" s="4">
-        <v>4</v>
-      </c>
-      <c r="E61" s="4" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="4">
-        <v>12606</v>
-      </c>
-      <c r="B62" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="D62" s="4">
-        <v>3</v>
       </c>
       <c r="E62" s="4" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="4">
-        <v>12607</v>
-      </c>
-      <c r="B63" s="4" t="s">
+    <row r="63" s="3" customFormat="1" spans="1:8">
+      <c r="A63" s="16">
+        <v>12302</v>
+      </c>
+      <c r="B63" s="16" t="s">
         <v>179</v>
       </c>
-      <c r="D63" s="4">
-        <v>2</v>
-      </c>
-      <c r="E63" s="4" t="s">
+      <c r="D63" s="3">
+        <v>3</v>
+      </c>
+      <c r="E63" s="3" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="4">
-        <v>12608</v>
-      </c>
-      <c r="B64" s="4" t="s">
+    <row r="64" spans="1:8">
+      <c r="A64" s="15">
+        <v>12303</v>
+      </c>
+      <c r="B64" s="15" t="s">
         <v>181</v>
       </c>
       <c r="D64" s="4">
@@ -3051,80 +3274,80 @@
       </c>
     </row>
     <row r="65" spans="1:5">
-      <c r="A65" s="4">
-        <v>12609</v>
-      </c>
-      <c r="B65" s="4" t="s">
+      <c r="A65" s="16">
+        <v>12304</v>
+      </c>
+      <c r="B65" s="15" t="s">
         <v>183</v>
       </c>
       <c r="D65" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E65" s="4" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="66" spans="1:5">
-      <c r="A66" s="4">
-        <v>12610</v>
-      </c>
-      <c r="B66" s="4" t="s">
+      <c r="A66" s="15">
+        <v>12305</v>
+      </c>
+      <c r="B66" s="15" t="s">
         <v>185</v>
       </c>
       <c r="D66" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E66" s="4" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="4">
-        <v>12701</v>
-      </c>
-      <c r="B67" s="4" t="s">
+    <row r="67" s="3" customFormat="1" spans="1:5">
+      <c r="A67" s="16">
+        <v>12306</v>
+      </c>
+      <c r="B67" s="16" t="s">
         <v>187</v>
       </c>
-      <c r="D67" s="4">
-        <v>2</v>
-      </c>
-      <c r="E67" s="4" t="s">
+      <c r="D67" s="3">
+        <v>4</v>
+      </c>
+      <c r="E67" s="3" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="4">
-        <v>12702</v>
-      </c>
-      <c r="B68" s="4" t="s">
+    <row r="68" s="3" customFormat="1" spans="1:5">
+      <c r="A68" s="15">
+        <v>12307</v>
+      </c>
+      <c r="B68" s="16" t="s">
         <v>189</v>
       </c>
-      <c r="D68" s="4">
-        <v>2</v>
-      </c>
-      <c r="E68" s="4" t="s">
+      <c r="D68" s="3">
+        <v>2</v>
+      </c>
+      <c r="E68" s="3" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="69" spans="1:5">
-      <c r="A69" s="4">
-        <v>12703</v>
-      </c>
-      <c r="B69" s="4" t="s">
+      <c r="A69" s="17">
+        <v>12501</v>
+      </c>
+      <c r="B69" s="17" t="s">
         <v>191</v>
       </c>
       <c r="D69" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E69" s="4" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="70" spans="1:5">
-      <c r="A70" s="4">
-        <v>12704</v>
-      </c>
-      <c r="B70" s="4" t="s">
+      <c r="A70" s="17">
+        <v>12502</v>
+      </c>
+      <c r="B70" s="17" t="s">
         <v>193</v>
       </c>
       <c r="D70" s="4">
@@ -3132,6 +3355,230 @@
       </c>
       <c r="E70" s="4" t="s">
         <v>194</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="17">
+        <v>12503</v>
+      </c>
+      <c r="B71" s="17" t="s">
+        <v>195</v>
+      </c>
+      <c r="D71" s="4">
+        <v>4</v>
+      </c>
+      <c r="E71" s="4" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="17">
+        <v>12504</v>
+      </c>
+      <c r="B72" s="17" t="s">
+        <v>197</v>
+      </c>
+      <c r="D72" s="4">
+        <v>3</v>
+      </c>
+      <c r="E72" s="4" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="4">
+        <v>12601</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="D73" s="4">
+        <v>3</v>
+      </c>
+      <c r="E73" s="4" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="4">
+        <v>12602</v>
+      </c>
+      <c r="B74" s="17" t="s">
+        <v>201</v>
+      </c>
+      <c r="D74" s="4">
+        <v>4</v>
+      </c>
+      <c r="E74" s="4" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="4">
+        <v>12603</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="D75" s="4">
+        <v>4</v>
+      </c>
+      <c r="E75" s="4" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="4">
+        <v>12604</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="D76" s="4">
+        <v>3</v>
+      </c>
+      <c r="E76" s="4" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="4">
+        <v>12605</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="D77" s="4">
+        <v>4</v>
+      </c>
+      <c r="E77" s="4" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="4">
+        <v>12606</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="D78" s="4">
+        <v>3</v>
+      </c>
+      <c r="E78" s="4" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="4">
+        <v>12607</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="D79" s="4">
+        <v>2</v>
+      </c>
+      <c r="E79" s="4" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="4">
+        <v>12608</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="D80" s="4">
+        <v>2</v>
+      </c>
+      <c r="E80" s="4" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="4">
+        <v>12609</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="D81" s="4">
+        <v>4</v>
+      </c>
+      <c r="E81" s="4" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="4">
+        <v>12610</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="D82" s="4">
+        <v>4</v>
+      </c>
+      <c r="E82" s="4" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" s="4">
+        <v>12701</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="D83" s="4">
+        <v>2</v>
+      </c>
+      <c r="E83" s="4" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84" s="4">
+        <v>12702</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="D84" s="4">
+        <v>2</v>
+      </c>
+      <c r="E84" s="4" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85" s="4">
+        <v>12703</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="D85" s="4">
+        <v>3</v>
+      </c>
+      <c r="E85" s="4" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="A86" s="4">
+        <v>12704</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="D86" s="4">
+        <v>3</v>
+      </c>
+      <c r="E86" s="4" t="s">
+        <v>226</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/condition.xlsx
+++ b/hall/resources/sample/condition.xlsx
@@ -169,7 +169,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="227">
   <si>
     <t>id</t>
   </si>
@@ -603,58 +603,103 @@
     <t>接取：消费N金币\钻石</t>
   </si>
   <si>
-    <t>12220_道具ID_数量</t>
+    <t>12220_道具ID(仅钻石或金币)_数量</t>
   </si>
   <si>
     <t>累积：在SLOT游戏中获得N个X道具</t>
   </si>
   <si>
+    <t>12251_游戏ID(0)_道具ID_道具数量</t>
+  </si>
+  <si>
     <t>累积：触发SWEET WIN N次</t>
   </si>
   <si>
+    <t>12252_大奖类型_次数</t>
+  </si>
+  <si>
     <t>累积：触发MINI奖池N次</t>
   </si>
   <si>
+    <t>12253_奖池类型_次数</t>
+  </si>
+  <si>
     <t>累积：触发免费游戏模式N次</t>
   </si>
   <si>
+    <t>12254_次数</t>
+  </si>
+  <si>
     <t>累积：建筑升级N次</t>
   </si>
   <si>
+    <t>12255_建筑ID(0)_次数</t>
+  </si>
+  <si>
     <t>累积：拥有N个X级以上建筑</t>
   </si>
   <si>
+    <t>12256_数量_等级</t>
+  </si>
+  <si>
     <t>累积：观看N次广告</t>
   </si>
   <si>
-    <t>累积：观看广告金币\钻石收益达到N</t>
+    <t>12257_次数</t>
   </si>
   <si>
     <t>累积：拥有N个X星雇员</t>
   </si>
   <si>
+    <t>12259_雇员类型_数量_星级</t>
+  </si>
+  <si>
     <t>累积：招商游客N次</t>
   </si>
   <si>
+    <t>12260_免费0(付费1)_次数</t>
+  </si>
+  <si>
     <t>累积：拥有N个X星游客</t>
   </si>
   <si>
+    <t>12261_数量_星级</t>
+  </si>
+  <si>
     <t>累积：经营收益 金币\能量\道具 累积达到N</t>
   </si>
   <si>
+    <t>12262_道具ID_数量</t>
+  </si>
+  <si>
     <t>累积：研发N个游戏</t>
   </si>
   <si>
+    <t>12263_数量</t>
+  </si>
+  <si>
     <t>累积：拜访N次</t>
   </si>
   <si>
+    <t>12264_数量</t>
+  </si>
+  <si>
     <t>累积：登陆N天</t>
   </si>
   <si>
+    <t>12265_数量</t>
+  </si>
+  <si>
     <t>累积：解锁N个娱乐城</t>
   </si>
   <si>
+    <t>12266_数量</t>
+  </si>
+  <si>
     <t>累积：消费N金币\钻石</t>
+  </si>
+  <si>
+    <t>12267_道具ID(仅钻石或金币)_数量</t>
   </si>
   <si>
     <t>游戏中奖倍数</t>
@@ -1869,7 +1914,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O87"/>
+  <dimension ref="A1:O86"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="4"/>
@@ -2910,7 +2955,7 @@
         <v>3</v>
       </c>
       <c r="E46" s="13" t="s">
-        <v>108</v>
+        <v>146</v>
       </c>
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
@@ -2921,14 +2966,14 @@
         <v>12252</v>
       </c>
       <c r="B47" s="14" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" s="2">
         <v>2</v>
       </c>
       <c r="E47" s="13" t="s">
-        <v>110</v>
+        <v>148</v>
       </c>
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
@@ -2939,14 +2984,14 @@
         <v>12253</v>
       </c>
       <c r="B48" s="14" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" s="2">
         <v>2</v>
       </c>
       <c r="E48" s="13" t="s">
-        <v>112</v>
+        <v>150</v>
       </c>
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
@@ -2957,14 +3002,14 @@
         <v>12254</v>
       </c>
       <c r="B49" s="14" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" s="2">
         <v>1</v>
       </c>
       <c r="E49" s="13" t="s">
-        <v>114</v>
+        <v>152</v>
       </c>
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
@@ -2975,14 +3020,14 @@
         <v>12255</v>
       </c>
       <c r="B50" s="14" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" s="2">
         <v>2</v>
       </c>
       <c r="E50" s="13" t="s">
-        <v>116</v>
+        <v>154</v>
       </c>
       <c r="F50" s="2"/>
       <c r="G50" s="2"/>
@@ -2993,14 +3038,14 @@
         <v>12256</v>
       </c>
       <c r="B51" s="14" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" s="2">
         <v>2</v>
       </c>
       <c r="E51" s="13" t="s">
-        <v>120</v>
+        <v>156</v>
       </c>
       <c r="F51" s="2"/>
       <c r="G51" s="2"/>
@@ -3011,14 +3056,14 @@
         <v>12257</v>
       </c>
       <c r="B52" s="14" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" s="2">
         <v>1</v>
       </c>
       <c r="E52" s="13" t="s">
-        <v>122</v>
+        <v>158</v>
       </c>
       <c r="F52" s="2"/>
       <c r="G52" s="2"/>
@@ -3026,17 +3071,17 @@
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="14">
-        <v>12258</v>
+        <v>12259</v>
       </c>
       <c r="B53" s="14" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E53" s="13" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="F53" s="2"/>
       <c r="G53" s="2"/>
@@ -3044,17 +3089,17 @@
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="14">
-        <v>12259</v>
+        <v>12260</v>
       </c>
       <c r="B54" s="14" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E54" s="13" t="s">
-        <v>128</v>
+        <v>162</v>
       </c>
       <c r="F54" s="2"/>
       <c r="G54" s="2"/>
@@ -3062,17 +3107,17 @@
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="14">
-        <v>12260</v>
+        <v>12261</v>
       </c>
       <c r="B55" s="14" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" s="2">
         <v>2</v>
       </c>
       <c r="E55" s="13" t="s">
-        <v>130</v>
+        <v>164</v>
       </c>
       <c r="F55" s="2"/>
       <c r="G55" s="2"/>
@@ -3080,17 +3125,17 @@
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="14">
-        <v>12261</v>
+        <v>12262</v>
       </c>
       <c r="B56" s="14" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" s="2">
         <v>2</v>
       </c>
       <c r="E56" s="13" t="s">
-        <v>132</v>
+        <v>166</v>
       </c>
       <c r="F56" s="2"/>
       <c r="G56" s="2"/>
@@ -3098,17 +3143,17 @@
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="14">
-        <v>12262</v>
+        <v>12263</v>
       </c>
       <c r="B57" s="14" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E57" s="13" t="s">
-        <v>134</v>
+        <v>168</v>
       </c>
       <c r="F57" s="2"/>
       <c r="G57" s="2"/>
@@ -3116,17 +3161,17 @@
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="14">
-        <v>12263</v>
+        <v>12264</v>
       </c>
       <c r="B58" s="14" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" s="2">
         <v>1</v>
       </c>
       <c r="E58" s="13" t="s">
-        <v>136</v>
+        <v>170</v>
       </c>
       <c r="F58" s="2"/>
       <c r="G58" s="2"/>
@@ -3134,17 +3179,17 @@
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="14">
-        <v>12264</v>
+        <v>12265</v>
       </c>
       <c r="B59" s="14" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" s="2">
         <v>1</v>
       </c>
       <c r="E59" s="13" t="s">
-        <v>138</v>
+        <v>172</v>
       </c>
       <c r="F59" s="2"/>
       <c r="G59" s="2"/>
@@ -3152,17 +3197,17 @@
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="14">
-        <v>12265</v>
+        <v>12266</v>
       </c>
       <c r="B60" s="14" t="s">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" s="2">
         <v>1</v>
       </c>
       <c r="E60" s="13" t="s">
-        <v>140</v>
+        <v>174</v>
       </c>
       <c r="F60" s="2"/>
       <c r="G60" s="2"/>
@@ -3170,388 +3215,370 @@
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="14">
-        <v>12266</v>
+        <v>12267</v>
       </c>
       <c r="B61" s="14" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E61" s="13" t="s">
-        <v>142</v>
+        <v>176</v>
       </c>
       <c r="F61" s="2"/>
       <c r="G61" s="2"/>
       <c r="H61" s="2"/>
     </row>
     <row r="62" spans="1:8">
-      <c r="A62" s="14">
-        <v>12267</v>
-      </c>
-      <c r="B62" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="C62" s="2"/>
-      <c r="D62" s="2">
-        <v>2</v>
-      </c>
-      <c r="E62" s="13" t="s">
-        <v>144</v>
-      </c>
-      <c r="F62" s="2"/>
-      <c r="G62" s="2"/>
-      <c r="H62" s="2"/>
-    </row>
-    <row r="63" spans="1:8">
-      <c r="A63" s="15">
+      <c r="A62" s="15">
         <v>12301</v>
       </c>
-      <c r="B63" s="15" t="s">
-        <v>162</v>
-      </c>
-      <c r="D63" s="4">
+      <c r="B62" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="D62" s="4">
         <v>4</v>
       </c>
-      <c r="E63" s="4" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="64" s="3" customFormat="1" spans="1:8">
-      <c r="A64" s="16">
+      <c r="E62" s="4" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="63" s="3" customFormat="1" spans="1:8">
+      <c r="A63" s="16">
         <v>12302</v>
       </c>
-      <c r="B64" s="16" t="s">
-        <v>164</v>
-      </c>
-      <c r="D64" s="3">
+      <c r="B63" s="16" t="s">
+        <v>179</v>
+      </c>
+      <c r="D63" s="3">
         <v>3</v>
       </c>
-      <c r="E64" s="3" t="s">
-        <v>165</v>
+      <c r="E63" s="3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8">
+      <c r="A64" s="15">
+        <v>12303</v>
+      </c>
+      <c r="B64" s="15" t="s">
+        <v>181</v>
+      </c>
+      <c r="D64" s="4">
+        <v>2</v>
+      </c>
+      <c r="E64" s="4" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="65" spans="1:5">
-      <c r="A65" s="15">
-        <v>12303</v>
+      <c r="A65" s="16">
+        <v>12304</v>
       </c>
       <c r="B65" s="15" t="s">
-        <v>166</v>
+        <v>183</v>
       </c>
       <c r="D65" s="4">
         <v>2</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="66" spans="1:5">
-      <c r="A66" s="16">
-        <v>12304</v>
+      <c r="A66" s="15">
+        <v>12305</v>
       </c>
       <c r="B66" s="15" t="s">
-        <v>168</v>
+        <v>185</v>
       </c>
       <c r="D66" s="4">
         <v>2</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="15">
-        <v>12305</v>
-      </c>
-      <c r="B67" s="15" t="s">
-        <v>170</v>
-      </c>
-      <c r="D67" s="4">
-        <v>2</v>
-      </c>
-      <c r="E67" s="4" t="s">
-        <v>171</v>
+        <v>186</v>
+      </c>
+    </row>
+    <row r="67" s="3" customFormat="1" spans="1:5">
+      <c r="A67" s="16">
+        <v>12306</v>
+      </c>
+      <c r="B67" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="D67" s="3">
+        <v>4</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="68" s="3" customFormat="1" spans="1:5">
-      <c r="A68" s="16">
-        <v>12306</v>
+      <c r="A68" s="15">
+        <v>12307</v>
       </c>
       <c r="B68" s="16" t="s">
-        <v>172</v>
+        <v>189</v>
       </c>
       <c r="D68" s="3">
+        <v>2</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="17">
+        <v>12501</v>
+      </c>
+      <c r="B69" s="17" t="s">
+        <v>191</v>
+      </c>
+      <c r="D69" s="4">
         <v>4</v>
       </c>
-      <c r="E68" s="3" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="69" s="3" customFormat="1" spans="1:5">
-      <c r="A69" s="15">
-        <v>12307</v>
-      </c>
-      <c r="B69" s="16" t="s">
-        <v>174</v>
-      </c>
-      <c r="D69" s="3">
-        <v>2</v>
-      </c>
-      <c r="E69" s="3" t="s">
-        <v>175</v>
+      <c r="E69" s="4" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="17">
-        <v>12501</v>
+        <v>12502</v>
       </c>
       <c r="B70" s="17" t="s">
-        <v>176</v>
+        <v>193</v>
       </c>
       <c r="D70" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>177</v>
+        <v>194</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="17">
-        <v>12502</v>
+        <v>12503</v>
       </c>
       <c r="B71" s="17" t="s">
-        <v>178</v>
+        <v>195</v>
       </c>
       <c r="D71" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>179</v>
+        <v>196</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="17">
-        <v>12503</v>
+        <v>12504</v>
       </c>
       <c r="B72" s="17" t="s">
-        <v>180</v>
+        <v>197</v>
       </c>
       <c r="D72" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>181</v>
+        <v>198</v>
       </c>
     </row>
     <row r="73" spans="1:5">
-      <c r="A73" s="17">
-        <v>12504</v>
-      </c>
-      <c r="B73" s="17" t="s">
-        <v>182</v>
+      <c r="A73" s="4">
+        <v>12601</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>199</v>
       </c>
       <c r="D73" s="4">
         <v>3</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>183</v>
+        <v>200</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="4">
-        <v>12601</v>
-      </c>
-      <c r="B74" s="4" t="s">
-        <v>184</v>
+        <v>12602</v>
+      </c>
+      <c r="B74" s="17" t="s">
+        <v>201</v>
       </c>
       <c r="D74" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>185</v>
+        <v>202</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="4">
-        <v>12602</v>
-      </c>
-      <c r="B75" s="17" t="s">
-        <v>186</v>
+        <v>12603</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>203</v>
       </c>
       <c r="D75" s="4">
         <v>4</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>187</v>
+        <v>204</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="4">
-        <v>12603</v>
+        <v>12604</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>188</v>
+        <v>205</v>
       </c>
       <c r="D76" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>189</v>
+        <v>206</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="4">
-        <v>12604</v>
+        <v>12605</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>190</v>
+        <v>207</v>
       </c>
       <c r="D77" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>191</v>
+        <v>208</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="4">
-        <v>12605</v>
+        <v>12606</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>192</v>
+        <v>209</v>
       </c>
       <c r="D78" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>193</v>
+        <v>210</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="4">
-        <v>12606</v>
+        <v>12607</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="D79" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>195</v>
+        <v>212</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="4">
-        <v>12607</v>
+        <v>12608</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="D80" s="4">
         <v>2</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>197</v>
+        <v>214</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="4">
-        <v>12608</v>
+        <v>12609</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="D81" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="4">
-        <v>12609</v>
+        <v>12610</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="D82" s="4">
         <v>4</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>201</v>
+        <v>218</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="4">
-        <v>12610</v>
+        <v>12701</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>202</v>
+        <v>219</v>
       </c>
       <c r="D83" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="4">
-        <v>12701</v>
+        <v>12702</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>204</v>
+        <v>221</v>
       </c>
       <c r="D84" s="4">
         <v>2</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>205</v>
+        <v>222</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="4">
-        <v>12702</v>
+        <v>12703</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="D85" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>207</v>
+        <v>224</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="4">
-        <v>12703</v>
+        <v>12704</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>208</v>
+        <v>225</v>
       </c>
       <c r="D86" s="4">
         <v>3</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5">
-      <c r="A87" s="4">
-        <v>12704</v>
-      </c>
-      <c r="B87" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="D87" s="4">
-        <v>3</v>
-      </c>
-      <c r="E87" s="4" t="s">
-        <v>211</v>
+        <v>226</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/condition.xlsx
+++ b/hall/resources/sample/condition.xlsx
@@ -169,7 +169,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="231">
   <si>
     <t>id</t>
   </si>
@@ -700,6 +700,18 @@
   </si>
   <si>
     <t>12267_道具ID(仅钻石或金币)_数量</t>
+  </si>
+  <si>
+    <t>累积：场景等级达到N级</t>
+  </si>
+  <si>
+    <t>12268_场景ID_数量</t>
+  </si>
+  <si>
+    <t>累积：指定SLOT游戏技能战力达到N</t>
+  </si>
+  <si>
+    <t>12269_游戏ID_数量</t>
   </si>
   <si>
     <t>游戏中奖倍数</t>
@@ -1914,7 +1926,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O86"/>
+  <dimension ref="A1:O88"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="4"/>
@@ -3232,64 +3244,72 @@
       <c r="H61" s="2"/>
     </row>
     <row r="62" spans="1:8">
-      <c r="A62" s="15">
-        <v>12301</v>
-      </c>
-      <c r="B62" s="15" t="s">
+      <c r="A62" s="14">
+        <v>12268</v>
+      </c>
+      <c r="B62" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="D62" s="4">
-        <v>4</v>
-      </c>
-      <c r="E62" s="4" t="s">
+      <c r="C62" s="2"/>
+      <c r="D62" s="2">
+        <v>2</v>
+      </c>
+      <c r="E62" s="13" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="63" s="3" customFormat="1" spans="1:8">
-      <c r="A63" s="16">
-        <v>12302</v>
-      </c>
-      <c r="B63" s="16" t="s">
+      <c r="F62" s="2"/>
+      <c r="G62" s="2"/>
+      <c r="H62" s="2"/>
+    </row>
+    <row r="63" spans="1:8">
+      <c r="A63" s="14">
+        <v>12269</v>
+      </c>
+      <c r="B63" s="14" t="s">
         <v>179</v>
       </c>
-      <c r="D63" s="3">
-        <v>3</v>
-      </c>
-      <c r="E63" s="3" t="s">
+      <c r="C63" s="2"/>
+      <c r="D63" s="2">
+        <v>2</v>
+      </c>
+      <c r="E63" s="13" t="s">
         <v>180</v>
       </c>
+      <c r="F63" s="2"/>
+      <c r="G63" s="2"/>
+      <c r="H63" s="2"/>
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="15">
-        <v>12303</v>
+        <v>12301</v>
       </c>
       <c r="B64" s="15" t="s">
         <v>181</v>
       </c>
       <c r="D64" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E64" s="4" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="65" spans="1:5">
+    <row r="65" s="3" customFormat="1" spans="1:5">
       <c r="A65" s="16">
-        <v>12304</v>
-      </c>
-      <c r="B65" s="15" t="s">
+        <v>12302</v>
+      </c>
+      <c r="B65" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="D65" s="4">
-        <v>2</v>
-      </c>
-      <c r="E65" s="4" t="s">
+      <c r="D65" s="3">
+        <v>3</v>
+      </c>
+      <c r="E65" s="3" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="15">
-        <v>12305</v>
+        <v>12303</v>
       </c>
       <c r="B66" s="15" t="s">
         <v>185</v>
@@ -3301,65 +3321,65 @@
         <v>186</v>
       </c>
     </row>
-    <row r="67" s="3" customFormat="1" spans="1:5">
+    <row r="67" spans="1:5">
       <c r="A67" s="16">
+        <v>12304</v>
+      </c>
+      <c r="B67" s="15" t="s">
+        <v>187</v>
+      </c>
+      <c r="D67" s="4">
+        <v>2</v>
+      </c>
+      <c r="E67" s="4" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="15">
+        <v>12305</v>
+      </c>
+      <c r="B68" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="D68" s="4">
+        <v>2</v>
+      </c>
+      <c r="E68" s="4" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="69" s="3" customFormat="1" spans="1:5">
+      <c r="A69" s="16">
         <v>12306</v>
       </c>
-      <c r="B67" s="16" t="s">
-        <v>187</v>
-      </c>
-      <c r="D67" s="3">
+      <c r="B69" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="D69" s="3">
         <v>4</v>
       </c>
-      <c r="E67" s="3" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="68" s="3" customFormat="1" spans="1:5">
-      <c r="A68" s="15">
+      <c r="E69" s="3" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="70" s="3" customFormat="1" spans="1:5">
+      <c r="A70" s="15">
         <v>12307</v>
       </c>
-      <c r="B68" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="D68" s="3">
-        <v>2</v>
-      </c>
-      <c r="E68" s="3" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="17">
-        <v>12501</v>
-      </c>
-      <c r="B69" s="17" t="s">
-        <v>191</v>
-      </c>
-      <c r="D69" s="4">
-        <v>4</v>
-      </c>
-      <c r="E69" s="4" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="17">
-        <v>12502</v>
-      </c>
-      <c r="B70" s="17" t="s">
+      <c r="B70" s="16" t="s">
         <v>193</v>
       </c>
-      <c r="D70" s="4">
-        <v>3</v>
-      </c>
-      <c r="E70" s="4" t="s">
+      <c r="D70" s="3">
+        <v>2</v>
+      </c>
+      <c r="E70" s="3" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="17">
-        <v>12503</v>
+        <v>12501</v>
       </c>
       <c r="B71" s="17" t="s">
         <v>195</v>
@@ -3373,7 +3393,7 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="17">
-        <v>12504</v>
+        <v>12502</v>
       </c>
       <c r="B72" s="17" t="s">
         <v>197</v>
@@ -3386,28 +3406,28 @@
       </c>
     </row>
     <row r="73" spans="1:5">
-      <c r="A73" s="4">
-        <v>12601</v>
-      </c>
-      <c r="B73" s="4" t="s">
+      <c r="A73" s="17">
+        <v>12503</v>
+      </c>
+      <c r="B73" s="17" t="s">
         <v>199</v>
       </c>
       <c r="D73" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E73" s="4" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="74" spans="1:5">
-      <c r="A74" s="4">
-        <v>12602</v>
+      <c r="A74" s="17">
+        <v>12504</v>
       </c>
       <c r="B74" s="17" t="s">
         <v>201</v>
       </c>
       <c r="D74" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E74" s="4" t="s">
         <v>202</v>
@@ -3415,13 +3435,13 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="4">
-        <v>12603</v>
+        <v>12601</v>
       </c>
       <c r="B75" s="4" t="s">
         <v>203</v>
       </c>
       <c r="D75" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E75" s="4" t="s">
         <v>204</v>
@@ -3429,13 +3449,13 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="4">
-        <v>12604</v>
-      </c>
-      <c r="B76" s="4" t="s">
+        <v>12602</v>
+      </c>
+      <c r="B76" s="17" t="s">
         <v>205</v>
       </c>
       <c r="D76" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E76" s="4" t="s">
         <v>206</v>
@@ -3443,7 +3463,7 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="4">
-        <v>12605</v>
+        <v>12603</v>
       </c>
       <c r="B77" s="4" t="s">
         <v>207</v>
@@ -3457,7 +3477,7 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="4">
-        <v>12606</v>
+        <v>12604</v>
       </c>
       <c r="B78" s="4" t="s">
         <v>209</v>
@@ -3471,13 +3491,13 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="4">
-        <v>12607</v>
+        <v>12605</v>
       </c>
       <c r="B79" s="4" t="s">
         <v>211</v>
       </c>
       <c r="D79" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E79" s="4" t="s">
         <v>212</v>
@@ -3485,13 +3505,13 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="4">
-        <v>12608</v>
+        <v>12606</v>
       </c>
       <c r="B80" s="4" t="s">
         <v>213</v>
       </c>
       <c r="D80" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E80" s="4" t="s">
         <v>214</v>
@@ -3499,13 +3519,13 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="4">
-        <v>12609</v>
+        <v>12607</v>
       </c>
       <c r="B81" s="4" t="s">
         <v>215</v>
       </c>
       <c r="D81" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E81" s="4" t="s">
         <v>216</v>
@@ -3513,13 +3533,13 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="4">
-        <v>12610</v>
+        <v>12608</v>
       </c>
       <c r="B82" s="4" t="s">
         <v>217</v>
       </c>
       <c r="D82" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E82" s="4" t="s">
         <v>218</v>
@@ -3527,13 +3547,13 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="4">
-        <v>12701</v>
+        <v>12609</v>
       </c>
       <c r="B83" s="4" t="s">
         <v>219</v>
       </c>
       <c r="D83" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E83" s="4" t="s">
         <v>220</v>
@@ -3541,13 +3561,13 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="4">
-        <v>12702</v>
+        <v>12610</v>
       </c>
       <c r="B84" s="4" t="s">
         <v>221</v>
       </c>
       <c r="D84" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E84" s="4" t="s">
         <v>222</v>
@@ -3555,13 +3575,13 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="4">
-        <v>12703</v>
+        <v>12701</v>
       </c>
       <c r="B85" s="4" t="s">
         <v>223</v>
       </c>
       <c r="D85" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E85" s="4" t="s">
         <v>224</v>
@@ -3569,16 +3589,44 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="4">
-        <v>12704</v>
+        <v>12702</v>
       </c>
       <c r="B86" s="4" t="s">
         <v>225</v>
       </c>
       <c r="D86" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E86" s="4" t="s">
         <v>226</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5">
+      <c r="A87" s="4">
+        <v>12703</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="D87" s="4">
+        <v>3</v>
+      </c>
+      <c r="E87" s="4" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5">
+      <c r="A88" s="4">
+        <v>12704</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="D88" s="4">
+        <v>3</v>
+      </c>
+      <c r="E88" s="4" t="s">
+        <v>230</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/condition.xlsx
+++ b/hall/resources/sample/condition.xlsx
@@ -110,7 +110,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E47" authorId="0">
+    <comment ref="E48" authorId="0">
       <text>
         <r>
           <rPr>
@@ -138,7 +138,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E48" authorId="0">
+    <comment ref="E49" authorId="0">
       <text>
         <r>
           <rPr>
@@ -169,7 +169,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="237">
   <si>
     <t>id</t>
   </si>
@@ -516,19 +516,19 @@
     <t>12205_次数</t>
   </si>
   <si>
-    <t>接取：建筑升级N次</t>
+    <t>接取：建筑升级N次大等级</t>
   </si>
   <si>
     <t>12206_建筑ID(0)_次数</t>
   </si>
   <si>
-    <t>接取：X建筑升到N级</t>
+    <t>累积：X建筑升到N级</t>
   </si>
   <si>
     <t>12207_建筑ID(0)_等级</t>
   </si>
   <si>
-    <t>接取：拥有N个X级以上建筑</t>
+    <t>累积：拥有N个X级以上建筑&lt;重复,可删除&gt;</t>
   </si>
   <si>
     <t>12208_数量_等级</t>
@@ -549,10 +549,10 @@
     <t>接取：招募N个X类型的雇员</t>
   </si>
   <si>
-    <t>12211_雇员类型_数量</t>
-  </si>
-  <si>
-    <t>接取：拥有N个X星雇员</t>
+    <t>12211_雇员类型(游戏经理\服务经理\公关经理)_数量</t>
+  </si>
+  <si>
+    <t>累积：拥有N个X星雇员&lt;重复,可删除&gt;</t>
   </si>
   <si>
     <t>12212_雇员类型_数量_星级</t>
@@ -564,7 +564,7 @@
     <t>12213_免费0(付费1)_次数</t>
   </si>
   <si>
-    <t>接取：拥有N个X星游客</t>
+    <t>累积：拥有N个X星游客</t>
   </si>
   <si>
     <t>12214_数量_星级</t>
@@ -576,7 +576,7 @@
     <t>12215_道具ID_数量</t>
   </si>
   <si>
-    <t>接取：研发N个游戏</t>
+    <t>累积：研发N个游戏</t>
   </si>
   <si>
     <t>12216_数量</t>
@@ -594,7 +594,7 @@
     <t>12218_数量</t>
   </si>
   <si>
-    <t>接取：解锁N个娱乐城</t>
+    <t>累积：解锁N个娱乐城&lt;重复,可删除&gt;</t>
   </si>
   <si>
     <t>12219_数量</t>
@@ -606,6 +606,12 @@
     <t>12220_道具ID(仅钻石或金币)_数量</t>
   </si>
   <si>
+    <t>接取：指定\任意SLOT游戏投注N次</t>
+  </si>
+  <si>
+    <t>12221_游戏ID(0)_数量(默认金币)</t>
+  </si>
+  <si>
     <t>累积：在SLOT游戏中获得N个X道具</t>
   </si>
   <si>
@@ -660,9 +666,6 @@
     <t>12260_免费0(付费1)_次数</t>
   </si>
   <si>
-    <t>累积：拥有N个X星游客</t>
-  </si>
-  <si>
     <t>12261_数量_星级</t>
   </si>
   <si>
@@ -672,9 +675,6 @@
     <t>12262_道具ID_数量</t>
   </si>
   <si>
-    <t>累积：研发N个游戏</t>
-  </si>
-  <si>
     <t>12263_数量</t>
   </si>
   <si>
@@ -708,10 +708,28 @@
     <t>12268_场景ID_数量</t>
   </si>
   <si>
-    <t>累积：指定SLOT游戏技能战力达到N</t>
-  </si>
-  <si>
-    <t>12269_游戏ID_数量</t>
+    <t>累积：指定\任意SLOT游戏技能战力达到N</t>
+  </si>
+  <si>
+    <t>12269_游戏ID(0)_数量</t>
+  </si>
+  <si>
+    <t>累积：游客卡池抽卡N次</t>
+  </si>
+  <si>
+    <t>12270_数量</t>
+  </si>
+  <si>
+    <t>累积：雇员卡池抽卡N次</t>
+  </si>
+  <si>
+    <t>12271_数量</t>
+  </si>
+  <si>
+    <t>累积：指定\任意SLOT游戏投注N次</t>
+  </si>
+  <si>
+    <t>12272_游戏ID(0)_数量(默认金币)</t>
   </si>
   <si>
     <t>游戏中奖倍数</t>
@@ -874,7 +892,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -890,6 +908,18 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF7030A0"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -912,7 +942,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF7030A0"/>
+      <color theme="9" tint="-0.25"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -1061,18 +1091,18 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="37">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1082,6 +1112,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1416,137 +1452,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1562,22 +1598,28 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
@@ -1589,16 +1631,37 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1926,7 +1989,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O88"/>
+  <dimension ref="A1:O92"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="4"/>
@@ -1941,82 +2004,82 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="15" spans="1:10">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="5" t="s">
+      <c r="C1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5"/>
-      <c r="F1" s="6" t="s">
+      <c r="E1" s="7"/>
+      <c r="F1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="8" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="15" spans="1:10">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6" t="s">
+      <c r="B2" s="8"/>
+      <c r="C2" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5" t="s">
+      <c r="E2" s="7"/>
+      <c r="F2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="8" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="15" spans="1:10">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="5" t="s">
+      <c r="B3" s="8"/>
+      <c r="C3" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6" t="s">
+      <c r="E3" s="8"/>
+      <c r="F3" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="8" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" ht="15" spans="1:10">
-      <c r="A4" s="6"/>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
     </row>
     <row r="5" ht="17.25" spans="1:10">
       <c r="A5" s="4">
@@ -2025,7 +2088,7 @@
       <c r="B5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="9" t="s">
         <v>16</v>
       </c>
       <c r="D5" s="4">
@@ -2034,10 +2097,10 @@
       <c r="E5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="F5" s="8">
+      <c r="F5" s="10">
         <v>48001</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="G5" s="11" t="s">
         <v>18</v>
       </c>
       <c r="H5" s="4" t="s">
@@ -2054,7 +2117,7 @@
       <c r="B6" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="9" t="s">
         <v>22</v>
       </c>
       <c r="D6" s="4">
@@ -2063,10 +2126,10 @@
       <c r="E6" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="8">
+      <c r="F6" s="10">
         <v>48002</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="G6" s="11" t="s">
         <v>24</v>
       </c>
       <c r="H6" s="4" t="s">
@@ -2083,7 +2146,7 @@
       <c r="B7" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="9" t="s">
         <v>28</v>
       </c>
       <c r="D7" s="4">
@@ -2092,10 +2155,10 @@
       <c r="E7" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="F7" s="8">
+      <c r="F7" s="10">
         <v>49161</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="G7" s="11" t="s">
         <v>30</v>
       </c>
       <c r="H7" s="4" t="s">
@@ -2112,7 +2175,7 @@
       <c r="B8" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="12" t="s">
         <v>33</v>
       </c>
       <c r="D8" s="2">
@@ -2121,10 +2184,10 @@
       <c r="E8" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="F8" s="11">
+      <c r="F8" s="13">
         <v>48005</v>
       </c>
-      <c r="G8" s="9" t="s">
+      <c r="G8" s="11" t="s">
         <v>35</v>
       </c>
       <c r="H8" s="2" t="s">
@@ -2141,17 +2204,17 @@
       <c r="B9" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="12" t="s">
         <v>38</v>
       </c>
       <c r="D9" s="2">
         <v>3</v>
       </c>
-      <c r="E9" s="11" t="s">
+      <c r="E9" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="F9" s="11"/>
-      <c r="G9" s="9"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="11"/>
       <c r="I9" s="2" t="s">
         <v>20</v>
       </c>
@@ -2163,7 +2226,7 @@
       <c r="B10" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D10" s="4">
@@ -2172,10 +2235,10 @@
       <c r="E10" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F10" s="8">
+      <c r="F10" s="10">
         <v>48003</v>
       </c>
-      <c r="G10" s="9" t="s">
+      <c r="G10" s="11" t="s">
         <v>43</v>
       </c>
       <c r="H10" s="4" t="s">
@@ -2192,7 +2255,7 @@
       <c r="B11" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="9" t="s">
         <v>46</v>
       </c>
       <c r="D11" s="4">
@@ -2201,10 +2264,10 @@
       <c r="E11" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="F11" s="8">
+      <c r="F11" s="10">
         <v>48003</v>
       </c>
-      <c r="G11" s="9" t="s">
+      <c r="G11" s="11" t="s">
         <v>43</v>
       </c>
       <c r="H11" s="4" t="s">
@@ -2221,7 +2284,7 @@
       <c r="B12" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="9" t="s">
         <v>49</v>
       </c>
       <c r="D12" s="4">
@@ -2230,10 +2293,10 @@
       <c r="E12" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="F12" s="8">
+      <c r="F12" s="10">
         <v>48003</v>
       </c>
-      <c r="G12" s="9" t="s">
+      <c r="G12" s="11" t="s">
         <v>43</v>
       </c>
       <c r="H12" s="4" t="s">
@@ -2250,7 +2313,7 @@
       <c r="B13" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="9" t="s">
         <v>52</v>
       </c>
       <c r="D13" s="4">
@@ -2259,10 +2322,10 @@
       <c r="E13" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="F13" s="8">
+      <c r="F13" s="10">
         <v>48004</v>
       </c>
-      <c r="G13" s="9" t="s">
+      <c r="G13" s="11" t="s">
         <v>54</v>
       </c>
       <c r="H13" s="4" t="s">
@@ -2279,7 +2342,7 @@
       <c r="B14" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C14" s="12" t="s">
         <v>57</v>
       </c>
       <c r="D14" s="2">
@@ -2288,10 +2351,10 @@
       <c r="E14" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="F14" s="11">
+      <c r="F14" s="13">
         <v>48004</v>
       </c>
-      <c r="G14" s="9" t="s">
+      <c r="G14" s="11" t="s">
         <v>54</v>
       </c>
       <c r="H14" s="2" t="s">
@@ -2308,7 +2371,7 @@
       <c r="B15" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C15" s="10" t="s">
+      <c r="C15" s="12" t="s">
         <v>60</v>
       </c>
       <c r="D15" s="2">
@@ -2317,10 +2380,10 @@
       <c r="E15" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="F15" s="11">
+      <c r="F15" s="13">
         <v>48006</v>
       </c>
-      <c r="G15" s="9" t="s">
+      <c r="G15" s="11" t="s">
         <v>62</v>
       </c>
       <c r="H15" s="2" t="s">
@@ -2329,7 +2392,7 @@
       <c r="I15" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="J15" s="11" t="s">
+      <c r="J15" s="13" t="s">
         <v>63</v>
       </c>
     </row>
@@ -2340,7 +2403,7 @@
       <c r="B16" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="C16" s="12" t="s">
         <v>65</v>
       </c>
       <c r="D16" s="2">
@@ -2349,10 +2412,10 @@
       <c r="E16" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="F16" s="11">
+      <c r="F16" s="13">
         <v>48004</v>
       </c>
-      <c r="G16" s="9" t="s">
+      <c r="G16" s="11" t="s">
         <v>54</v>
       </c>
       <c r="H16" s="2" t="s">
@@ -2361,7 +2424,7 @@
       <c r="I16" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="J16" s="11"/>
+      <c r="J16" s="13"/>
     </row>
     <row r="17" s="2" customFormat="1" ht="17.25" spans="1:15">
       <c r="A17" s="2">
@@ -2370,7 +2433,7 @@
       <c r="B17" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="C17" s="12" t="s">
         <v>68</v>
       </c>
       <c r="D17" s="2">
@@ -2379,10 +2442,10 @@
       <c r="E17" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="F17" s="11">
+      <c r="F17" s="13">
         <v>48004</v>
       </c>
-      <c r="G17" s="9" t="s">
+      <c r="G17" s="11" t="s">
         <v>54</v>
       </c>
       <c r="H17" s="2" t="s">
@@ -2391,7 +2454,7 @@
       <c r="I17" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="J17" s="11"/>
+      <c r="J17" s="13"/>
     </row>
     <row r="18" s="2" customFormat="1" spans="1:15">
       <c r="A18" s="2">
@@ -2400,7 +2463,7 @@
       <c r="B18" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C18" s="10" t="s">
+      <c r="C18" s="12" t="s">
         <v>71</v>
       </c>
       <c r="D18" s="2">
@@ -2423,7 +2486,7 @@
       <c r="B19" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C19" s="10" t="s">
+      <c r="C19" s="12" t="s">
         <v>74</v>
       </c>
       <c r="D19" s="2">
@@ -2446,7 +2509,7 @@
       <c r="B20" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C20" s="10" t="s">
+      <c r="C20" s="12" t="s">
         <v>77</v>
       </c>
       <c r="D20" s="2">
@@ -2475,7 +2538,7 @@
       <c r="B21" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C21" s="10" t="s">
+      <c r="C21" s="12" t="s">
         <v>83</v>
       </c>
       <c r="D21" s="2">
@@ -2498,7 +2561,7 @@
       <c r="B22" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="C22" s="10" t="s">
+      <c r="C22" s="12" t="s">
         <v>86</v>
       </c>
       <c r="D22" s="2">
@@ -2530,7 +2593,7 @@
       <c r="B23" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C23" s="10" t="s">
+      <c r="C23" s="12" t="s">
         <v>93</v>
       </c>
       <c r="D23" s="2">
@@ -2562,7 +2625,7 @@
       <c r="B24" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C24" s="10" t="s">
+      <c r="C24" s="12" t="s">
         <v>100</v>
       </c>
       <c r="D24" s="2">
@@ -2585,7 +2648,7 @@
       <c r="B25" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="C25" s="7" t="s">
+      <c r="C25" s="9" t="s">
         <v>103</v>
       </c>
       <c r="D25" s="4">
@@ -2596,17 +2659,17 @@
       </c>
     </row>
     <row r="26" spans="1:15">
-      <c r="A26" s="12">
+      <c r="A26" s="14">
         <v>12201</v>
       </c>
-      <c r="B26" s="12" t="s">
+      <c r="B26" s="14" t="s">
         <v>105</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" s="2">
         <v>2</v>
       </c>
-      <c r="E26" s="13" t="s">
+      <c r="E26" s="15" t="s">
         <v>106</v>
       </c>
       <c r="F26" s="2"/>
@@ -2614,17 +2677,17 @@
       <c r="H26" s="2"/>
     </row>
     <row r="27" spans="1:15">
-      <c r="A27" s="12">
+      <c r="A27" s="14">
         <v>12202</v>
       </c>
-      <c r="B27" s="12" t="s">
+      <c r="B27" s="14" t="s">
         <v>107</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" s="2">
         <v>3</v>
       </c>
-      <c r="E27" s="13" t="s">
+      <c r="E27" s="15" t="s">
         <v>108</v>
       </c>
       <c r="F27" s="2"/>
@@ -2632,17 +2695,17 @@
       <c r="H27" s="2"/>
     </row>
     <row r="28" spans="1:15">
-      <c r="A28" s="12">
+      <c r="A28" s="14">
         <v>12203</v>
       </c>
-      <c r="B28" s="12" t="s">
+      <c r="B28" s="14" t="s">
         <v>109</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" s="2">
         <v>2</v>
       </c>
-      <c r="E28" s="13" t="s">
+      <c r="E28" s="15" t="s">
         <v>110</v>
       </c>
       <c r="F28" s="2"/>
@@ -2650,17 +2713,17 @@
       <c r="H28" s="2"/>
     </row>
     <row r="29" spans="1:15">
-      <c r="A29" s="12">
+      <c r="A29" s="14">
         <v>12204</v>
       </c>
-      <c r="B29" s="12" t="s">
+      <c r="B29" s="14" t="s">
         <v>111</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" s="2">
         <v>2</v>
       </c>
-      <c r="E29" s="13" t="s">
+      <c r="E29" s="15" t="s">
         <v>112</v>
       </c>
       <c r="F29" s="2"/>
@@ -2668,17 +2731,17 @@
       <c r="H29" s="2"/>
     </row>
     <row r="30" spans="1:15">
-      <c r="A30" s="12">
+      <c r="A30" s="14">
         <v>12205</v>
       </c>
-      <c r="B30" s="12" t="s">
+      <c r="B30" s="14" t="s">
         <v>113</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" s="2">
         <v>1</v>
       </c>
-      <c r="E30" s="13" t="s">
+      <c r="E30" s="15" t="s">
         <v>114</v>
       </c>
       <c r="F30" s="2"/>
@@ -2686,71 +2749,71 @@
       <c r="H30" s="2"/>
     </row>
     <row r="31" spans="1:15">
-      <c r="A31" s="12">
+      <c r="A31" s="14">
         <v>12206</v>
       </c>
-      <c r="B31" s="12" t="s">
+      <c r="B31" s="14" t="s">
         <v>115</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" s="2">
         <v>2</v>
       </c>
-      <c r="E31" s="13" t="s">
+      <c r="E31" s="15" t="s">
         <v>116</v>
       </c>
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
     </row>
-    <row r="32" spans="1:15">
-      <c r="A32" s="12">
+    <row r="32" s="3" customFormat="1" spans="1:15">
+      <c r="A32" s="16">
         <v>12207</v>
       </c>
-      <c r="B32" s="12" t="s">
+      <c r="B32" s="16" t="s">
         <v>117</v>
       </c>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2">
-        <v>2</v>
-      </c>
-      <c r="E32" s="13" t="s">
+      <c r="C32" s="17"/>
+      <c r="D32" s="17">
+        <v>2</v>
+      </c>
+      <c r="E32" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
-      <c r="H32" s="2"/>
-    </row>
-    <row r="33" spans="1:8">
-      <c r="A33" s="12">
+      <c r="F32" s="17"/>
+      <c r="G32" s="17"/>
+      <c r="H32" s="17"/>
+    </row>
+    <row r="33" s="3" customFormat="1" spans="1:8">
+      <c r="A33" s="16">
         <v>12208</v>
       </c>
-      <c r="B33" s="12" t="s">
+      <c r="B33" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2">
-        <v>2</v>
-      </c>
-      <c r="E33" s="13" t="s">
+      <c r="C33" s="17"/>
+      <c r="D33" s="17">
+        <v>2</v>
+      </c>
+      <c r="E33" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
-      <c r="H33" s="2"/>
+      <c r="F33" s="17"/>
+      <c r="G33" s="17"/>
+      <c r="H33" s="17"/>
     </row>
     <row r="34" spans="1:8">
-      <c r="A34" s="12">
+      <c r="A34" s="14">
         <v>12209</v>
       </c>
-      <c r="B34" s="12" t="s">
+      <c r="B34" s="14" t="s">
         <v>121</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" s="2">
         <v>1</v>
       </c>
-      <c r="E34" s="13" t="s">
+      <c r="E34" s="15" t="s">
         <v>122</v>
       </c>
       <c r="F34" s="2"/>
@@ -2758,143 +2821,143 @@
       <c r="H34" s="2"/>
     </row>
     <row r="35" spans="1:8">
-      <c r="A35" s="12">
+      <c r="A35" s="14">
         <v>12210</v>
       </c>
-      <c r="B35" s="12" t="s">
+      <c r="B35" s="14" t="s">
         <v>123</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" s="2">
         <v>2</v>
       </c>
-      <c r="E35" s="13" t="s">
+      <c r="E35" s="15" t="s">
         <v>124</v>
       </c>
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
     </row>
-    <row r="36" spans="1:8">
-      <c r="A36" s="12">
+    <row r="36" s="4" customFormat="1" spans="1:8">
+      <c r="A36" s="14">
         <v>12211</v>
       </c>
-      <c r="B36" s="12" t="s">
+      <c r="B36" s="14" t="s">
         <v>125</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" s="2">
         <v>2</v>
       </c>
-      <c r="E36" s="13" t="s">
+      <c r="E36" s="15" t="s">
         <v>126</v>
       </c>
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
     </row>
-    <row r="37" spans="1:8">
-      <c r="A37" s="12">
+    <row r="37" s="3" customFormat="1" spans="1:8">
+      <c r="A37" s="19">
         <v>12212</v>
       </c>
-      <c r="B37" s="12" t="s">
+      <c r="B37" s="19" t="s">
         <v>127</v>
       </c>
-      <c r="C37" s="2"/>
-      <c r="D37" s="2">
+      <c r="C37" s="17"/>
+      <c r="D37" s="17">
         <v>3</v>
       </c>
-      <c r="E37" s="13" t="s">
+      <c r="E37" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="F37" s="2"/>
-      <c r="G37" s="2"/>
-      <c r="H37" s="2"/>
+      <c r="F37" s="17"/>
+      <c r="G37" s="17"/>
+      <c r="H37" s="17"/>
     </row>
     <row r="38" spans="1:8">
-      <c r="A38" s="12">
+      <c r="A38" s="14">
         <v>12213</v>
       </c>
-      <c r="B38" s="12" t="s">
+      <c r="B38" s="14" t="s">
         <v>129</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" s="2">
         <v>2</v>
       </c>
-      <c r="E38" s="13" t="s">
+      <c r="E38" s="15" t="s">
         <v>130</v>
       </c>
       <c r="F38" s="2"/>
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
     </row>
-    <row r="39" spans="1:8">
-      <c r="A39" s="12">
+    <row r="39" s="3" customFormat="1" spans="1:8">
+      <c r="A39" s="19">
         <v>12214</v>
       </c>
-      <c r="B39" s="12" t="s">
+      <c r="B39" s="19" t="s">
         <v>131</v>
       </c>
-      <c r="C39" s="2"/>
-      <c r="D39" s="2">
-        <v>2</v>
-      </c>
-      <c r="E39" s="13" t="s">
+      <c r="C39" s="17"/>
+      <c r="D39" s="17">
+        <v>2</v>
+      </c>
+      <c r="E39" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="F39" s="2"/>
-      <c r="G39" s="2"/>
-      <c r="H39" s="2"/>
+      <c r="F39" s="17"/>
+      <c r="G39" s="17"/>
+      <c r="H39" s="17"/>
     </row>
     <row r="40" spans="1:8">
-      <c r="A40" s="12">
+      <c r="A40" s="14">
         <v>12215</v>
       </c>
-      <c r="B40" s="12" t="s">
+      <c r="B40" s="14" t="s">
         <v>133</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" s="2">
         <v>2</v>
       </c>
-      <c r="E40" s="13" t="s">
+      <c r="E40" s="15" t="s">
         <v>134</v>
       </c>
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
       <c r="H40" s="2"/>
     </row>
-    <row r="41" spans="1:8">
-      <c r="A41" s="12">
+    <row r="41" s="3" customFormat="1" spans="1:8">
+      <c r="A41" s="19">
         <v>12216</v>
       </c>
-      <c r="B41" s="12" t="s">
+      <c r="B41" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="C41" s="2"/>
-      <c r="D41" s="2">
+      <c r="C41" s="17"/>
+      <c r="D41" s="17">
         <v>1</v>
       </c>
-      <c r="E41" s="13" t="s">
+      <c r="E41" s="18" t="s">
         <v>136</v>
       </c>
-      <c r="F41" s="2"/>
-      <c r="G41" s="2"/>
-      <c r="H41" s="2"/>
+      <c r="F41" s="17"/>
+      <c r="G41" s="17"/>
+      <c r="H41" s="17"/>
     </row>
     <row r="42" spans="1:8">
-      <c r="A42" s="12">
+      <c r="A42" s="14">
         <v>12217</v>
       </c>
-      <c r="B42" s="12" t="s">
+      <c r="B42" s="14" t="s">
         <v>137</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" s="2">
         <v>1</v>
       </c>
-      <c r="E42" s="13" t="s">
+      <c r="E42" s="15" t="s">
         <v>138</v>
       </c>
       <c r="F42" s="2"/>
@@ -2902,53 +2965,53 @@
       <c r="H42" s="2"/>
     </row>
     <row r="43" spans="1:8">
-      <c r="A43" s="12">
+      <c r="A43" s="14">
         <v>12218</v>
       </c>
-      <c r="B43" s="12" t="s">
+      <c r="B43" s="14" t="s">
         <v>139</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" s="2">
         <v>1</v>
       </c>
-      <c r="E43" s="13" t="s">
+      <c r="E43" s="15" t="s">
         <v>140</v>
       </c>
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
       <c r="H43" s="2"/>
     </row>
-    <row r="44" spans="1:8">
-      <c r="A44" s="12">
+    <row r="44" s="3" customFormat="1" spans="1:8">
+      <c r="A44" s="19">
         <v>12219</v>
       </c>
-      <c r="B44" s="12" t="s">
+      <c r="B44" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="C44" s="2"/>
-      <c r="D44" s="2">
+      <c r="C44" s="17"/>
+      <c r="D44" s="17">
         <v>1</v>
       </c>
-      <c r="E44" s="13" t="s">
+      <c r="E44" s="18" t="s">
         <v>142</v>
       </c>
-      <c r="F44" s="2"/>
-      <c r="G44" s="2"/>
-      <c r="H44" s="2"/>
+      <c r="F44" s="17"/>
+      <c r="G44" s="17"/>
+      <c r="H44" s="17"/>
     </row>
     <row r="45" spans="1:8">
-      <c r="A45" s="12">
+      <c r="A45" s="14">
         <v>12220</v>
       </c>
-      <c r="B45" s="12" t="s">
+      <c r="B45" s="14" t="s">
         <v>143</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" s="2">
         <v>2</v>
       </c>
-      <c r="E45" s="13" t="s">
+      <c r="E45" s="15" t="s">
         <v>144</v>
       </c>
       <c r="F45" s="2"/>
@@ -2956,17 +3019,17 @@
       <c r="H45" s="2"/>
     </row>
     <row r="46" spans="1:8">
-      <c r="A46" s="14">
-        <v>12251</v>
-      </c>
-      <c r="B46" s="14" t="s">
+      <c r="A46" s="19">
+        <v>12221</v>
+      </c>
+      <c r="B46" s="19" t="s">
         <v>145</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" s="2">
-        <v>3</v>
-      </c>
-      <c r="E46" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="E46" s="15" t="s">
         <v>146</v>
       </c>
       <c r="F46" s="2"/>
@@ -2974,17 +3037,17 @@
       <c r="H46" s="2"/>
     </row>
     <row r="47" spans="1:8">
-      <c r="A47" s="14">
-        <v>12252</v>
-      </c>
-      <c r="B47" s="14" t="s">
+      <c r="A47" s="20">
+        <v>12251</v>
+      </c>
+      <c r="B47" s="20" t="s">
         <v>147</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" s="2">
-        <v>2</v>
-      </c>
-      <c r="E47" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="15" t="s">
         <v>148</v>
       </c>
       <c r="F47" s="2"/>
@@ -2992,17 +3055,17 @@
       <c r="H47" s="2"/>
     </row>
     <row r="48" spans="1:8">
-      <c r="A48" s="14">
-        <v>12253</v>
-      </c>
-      <c r="B48" s="14" t="s">
+      <c r="A48" s="20">
+        <v>12252</v>
+      </c>
+      <c r="B48" s="20" t="s">
         <v>149</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" s="2">
         <v>2</v>
       </c>
-      <c r="E48" s="13" t="s">
+      <c r="E48" s="15" t="s">
         <v>150</v>
       </c>
       <c r="F48" s="2"/>
@@ -3010,17 +3073,17 @@
       <c r="H48" s="2"/>
     </row>
     <row r="49" spans="1:8">
-      <c r="A49" s="14">
-        <v>12254</v>
-      </c>
-      <c r="B49" s="14" t="s">
+      <c r="A49" s="20">
+        <v>12253</v>
+      </c>
+      <c r="B49" s="20" t="s">
         <v>151</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" s="2">
-        <v>1</v>
-      </c>
-      <c r="E49" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="E49" s="15" t="s">
         <v>152</v>
       </c>
       <c r="F49" s="2"/>
@@ -3028,17 +3091,17 @@
       <c r="H49" s="2"/>
     </row>
     <row r="50" spans="1:8">
-      <c r="A50" s="14">
-        <v>12255</v>
-      </c>
-      <c r="B50" s="14" t="s">
+      <c r="A50" s="20">
+        <v>12254</v>
+      </c>
+      <c r="B50" s="20" t="s">
         <v>153</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" s="2">
-        <v>2</v>
-      </c>
-      <c r="E50" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E50" s="15" t="s">
         <v>154</v>
       </c>
       <c r="F50" s="2"/>
@@ -3046,17 +3109,17 @@
       <c r="H50" s="2"/>
     </row>
     <row r="51" spans="1:8">
-      <c r="A51" s="14">
-        <v>12256</v>
-      </c>
-      <c r="B51" s="14" t="s">
+      <c r="A51" s="20">
+        <v>12255</v>
+      </c>
+      <c r="B51" s="20" t="s">
         <v>155</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" s="2">
         <v>2</v>
       </c>
-      <c r="E51" s="13" t="s">
+      <c r="E51" s="15" t="s">
         <v>156</v>
       </c>
       <c r="F51" s="2"/>
@@ -3064,17 +3127,17 @@
       <c r="H51" s="2"/>
     </row>
     <row r="52" spans="1:8">
-      <c r="A52" s="14">
-        <v>12257</v>
-      </c>
-      <c r="B52" s="14" t="s">
+      <c r="A52" s="20">
+        <v>12256</v>
+      </c>
+      <c r="B52" s="20" t="s">
         <v>157</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" s="2">
-        <v>1</v>
-      </c>
-      <c r="E52" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="E52" s="15" t="s">
         <v>158</v>
       </c>
       <c r="F52" s="2"/>
@@ -3082,17 +3145,17 @@
       <c r="H52" s="2"/>
     </row>
     <row r="53" spans="1:8">
-      <c r="A53" s="14">
-        <v>12259</v>
-      </c>
-      <c r="B53" s="14" t="s">
+      <c r="A53" s="20">
+        <v>12257</v>
+      </c>
+      <c r="B53" s="20" t="s">
         <v>159</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" s="2">
-        <v>3</v>
-      </c>
-      <c r="E53" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E53" s="15" t="s">
         <v>160</v>
       </c>
       <c r="F53" s="2"/>
@@ -3100,17 +3163,17 @@
       <c r="H53" s="2"/>
     </row>
     <row r="54" spans="1:8">
-      <c r="A54" s="14">
-        <v>12260</v>
-      </c>
-      <c r="B54" s="14" t="s">
+      <c r="A54" s="20">
+        <v>12259</v>
+      </c>
+      <c r="B54" s="20" t="s">
         <v>161</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" s="2">
-        <v>2</v>
-      </c>
-      <c r="E54" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="E54" s="15" t="s">
         <v>162</v>
       </c>
       <c r="F54" s="2"/>
@@ -3118,17 +3181,17 @@
       <c r="H54" s="2"/>
     </row>
     <row r="55" spans="1:8">
-      <c r="A55" s="14">
-        <v>12261</v>
-      </c>
-      <c r="B55" s="14" t="s">
+      <c r="A55" s="20">
+        <v>12260</v>
+      </c>
+      <c r="B55" s="20" t="s">
         <v>163</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" s="2">
         <v>2</v>
       </c>
-      <c r="E55" s="13" t="s">
+      <c r="E55" s="15" t="s">
         <v>164</v>
       </c>
       <c r="F55" s="2"/>
@@ -3136,497 +3199,569 @@
       <c r="H55" s="2"/>
     </row>
     <row r="56" spans="1:8">
-      <c r="A56" s="14">
-        <v>12262</v>
-      </c>
-      <c r="B56" s="14" t="s">
-        <v>165</v>
+      <c r="A56" s="20">
+        <v>12261</v>
+      </c>
+      <c r="B56" s="20" t="s">
+        <v>131</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" s="2">
         <v>2</v>
       </c>
-      <c r="E56" s="13" t="s">
-        <v>166</v>
+      <c r="E56" s="15" t="s">
+        <v>165</v>
       </c>
       <c r="F56" s="2"/>
       <c r="G56" s="2"/>
       <c r="H56" s="2"/>
     </row>
     <row r="57" spans="1:8">
-      <c r="A57" s="14">
-        <v>12263</v>
-      </c>
-      <c r="B57" s="14" t="s">
-        <v>167</v>
+      <c r="A57" s="20">
+        <v>12262</v>
+      </c>
+      <c r="B57" s="20" t="s">
+        <v>166</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" s="2">
-        <v>1</v>
-      </c>
-      <c r="E57" s="13" t="s">
-        <v>168</v>
+        <v>2</v>
+      </c>
+      <c r="E57" s="15" t="s">
+        <v>167</v>
       </c>
       <c r="F57" s="2"/>
       <c r="G57" s="2"/>
       <c r="H57" s="2"/>
     </row>
     <row r="58" spans="1:8">
-      <c r="A58" s="14">
-        <v>12264</v>
-      </c>
-      <c r="B58" s="14" t="s">
-        <v>169</v>
+      <c r="A58" s="20">
+        <v>12263</v>
+      </c>
+      <c r="B58" s="20" t="s">
+        <v>135</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" s="2">
         <v>1</v>
       </c>
-      <c r="E58" s="13" t="s">
-        <v>170</v>
+      <c r="E58" s="15" t="s">
+        <v>168</v>
       </c>
       <c r="F58" s="2"/>
       <c r="G58" s="2"/>
       <c r="H58" s="2"/>
     </row>
     <row r="59" spans="1:8">
-      <c r="A59" s="14">
-        <v>12265</v>
-      </c>
-      <c r="B59" s="14" t="s">
-        <v>171</v>
+      <c r="A59" s="20">
+        <v>12264</v>
+      </c>
+      <c r="B59" s="20" t="s">
+        <v>169</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" s="2">
         <v>1</v>
       </c>
-      <c r="E59" s="13" t="s">
-        <v>172</v>
+      <c r="E59" s="15" t="s">
+        <v>170</v>
       </c>
       <c r="F59" s="2"/>
       <c r="G59" s="2"/>
       <c r="H59" s="2"/>
     </row>
     <row r="60" spans="1:8">
-      <c r="A60" s="14">
-        <v>12266</v>
-      </c>
-      <c r="B60" s="14" t="s">
-        <v>173</v>
+      <c r="A60" s="20">
+        <v>12265</v>
+      </c>
+      <c r="B60" s="20" t="s">
+        <v>171</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" s="2">
         <v>1</v>
       </c>
-      <c r="E60" s="13" t="s">
-        <v>174</v>
+      <c r="E60" s="15" t="s">
+        <v>172</v>
       </c>
       <c r="F60" s="2"/>
       <c r="G60" s="2"/>
       <c r="H60" s="2"/>
     </row>
     <row r="61" spans="1:8">
-      <c r="A61" s="14">
-        <v>12267</v>
-      </c>
-      <c r="B61" s="14" t="s">
-        <v>175</v>
+      <c r="A61" s="20">
+        <v>12266</v>
+      </c>
+      <c r="B61" s="20" t="s">
+        <v>173</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" s="2">
-        <v>2</v>
-      </c>
-      <c r="E61" s="13" t="s">
-        <v>176</v>
+        <v>1</v>
+      </c>
+      <c r="E61" s="15" t="s">
+        <v>174</v>
       </c>
       <c r="F61" s="2"/>
       <c r="G61" s="2"/>
       <c r="H61" s="2"/>
     </row>
     <row r="62" spans="1:8">
-      <c r="A62" s="14">
-        <v>12268</v>
-      </c>
-      <c r="B62" s="14" t="s">
-        <v>177</v>
+      <c r="A62" s="20">
+        <v>12267</v>
+      </c>
+      <c r="B62" s="20" t="s">
+        <v>175</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" s="2">
         <v>2</v>
       </c>
-      <c r="E62" s="13" t="s">
-        <v>178</v>
+      <c r="E62" s="15" t="s">
+        <v>176</v>
       </c>
       <c r="F62" s="2"/>
       <c r="G62" s="2"/>
       <c r="H62" s="2"/>
     </row>
     <row r="63" spans="1:8">
-      <c r="A63" s="14">
-        <v>12269</v>
-      </c>
-      <c r="B63" s="14" t="s">
-        <v>179</v>
+      <c r="A63" s="20">
+        <v>12268</v>
+      </c>
+      <c r="B63" s="20" t="s">
+        <v>177</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" s="2">
         <v>2</v>
       </c>
-      <c r="E63" s="13" t="s">
-        <v>180</v>
+      <c r="E63" s="15" t="s">
+        <v>178</v>
       </c>
       <c r="F63" s="2"/>
       <c r="G63" s="2"/>
       <c r="H63" s="2"/>
     </row>
-    <row r="64" spans="1:8">
-      <c r="A64" s="15">
+    <row r="64" s="5" customFormat="1" spans="1:8">
+      <c r="A64" s="21">
+        <v>12269</v>
+      </c>
+      <c r="B64" s="21" t="s">
+        <v>179</v>
+      </c>
+      <c r="C64" s="22"/>
+      <c r="D64" s="22">
+        <v>2</v>
+      </c>
+      <c r="E64" s="23" t="s">
+        <v>180</v>
+      </c>
+      <c r="F64" s="22"/>
+      <c r="G64" s="22"/>
+      <c r="H64" s="22"/>
+    </row>
+    <row r="65" s="5" customFormat="1" spans="1:8">
+      <c r="A65" s="21">
+        <v>12270</v>
+      </c>
+      <c r="B65" s="21" t="s">
+        <v>181</v>
+      </c>
+      <c r="C65" s="22"/>
+      <c r="D65" s="22">
+        <v>1</v>
+      </c>
+      <c r="E65" s="23" t="s">
+        <v>182</v>
+      </c>
+      <c r="F65" s="22"/>
+      <c r="G65" s="22"/>
+      <c r="H65" s="22"/>
+    </row>
+    <row r="66" s="5" customFormat="1" spans="1:8">
+      <c r="A66" s="21">
+        <v>12271</v>
+      </c>
+      <c r="B66" s="21" t="s">
+        <v>183</v>
+      </c>
+      <c r="C66" s="22"/>
+      <c r="D66" s="22">
+        <v>1</v>
+      </c>
+      <c r="E66" s="23" t="s">
+        <v>184</v>
+      </c>
+      <c r="F66" s="22"/>
+      <c r="G66" s="22"/>
+      <c r="H66" s="22"/>
+    </row>
+    <row r="67" s="5" customFormat="1" spans="1:8">
+      <c r="A67" s="21">
+        <v>12272</v>
+      </c>
+      <c r="B67" s="21" t="s">
+        <v>185</v>
+      </c>
+      <c r="C67" s="22"/>
+      <c r="D67" s="22">
+        <v>2</v>
+      </c>
+      <c r="E67" s="23" t="s">
+        <v>186</v>
+      </c>
+      <c r="F67" s="22"/>
+      <c r="G67" s="22"/>
+      <c r="H67" s="22"/>
+    </row>
+    <row r="68" spans="1:8">
+      <c r="A68" s="24">
         <v>12301</v>
       </c>
-      <c r="B64" s="15" t="s">
-        <v>181</v>
-      </c>
-      <c r="D64" s="4">
+      <c r="B68" s="24" t="s">
+        <v>187</v>
+      </c>
+      <c r="D68" s="4">
         <v>4</v>
       </c>
-      <c r="E64" s="4" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="65" s="3" customFormat="1" spans="1:5">
-      <c r="A65" s="16">
+      <c r="E68" s="4" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="69" s="6" customFormat="1" spans="1:8">
+      <c r="A69" s="25">
         <v>12302</v>
       </c>
-      <c r="B65" s="16" t="s">
-        <v>183</v>
-      </c>
-      <c r="D65" s="3">
+      <c r="B69" s="25" t="s">
+        <v>189</v>
+      </c>
+      <c r="D69" s="6">
         <v>3</v>
       </c>
-      <c r="E65" s="3" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="15">
+      <c r="E69" s="6" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8">
+      <c r="A70" s="24">
         <v>12303</v>
       </c>
-      <c r="B66" s="15" t="s">
-        <v>185</v>
-      </c>
-      <c r="D66" s="4">
-        <v>2</v>
-      </c>
-      <c r="E66" s="4" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="16">
+      <c r="B70" s="24" t="s">
+        <v>191</v>
+      </c>
+      <c r="D70" s="4">
+        <v>2</v>
+      </c>
+      <c r="E70" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8">
+      <c r="A71" s="25">
         <v>12304</v>
       </c>
-      <c r="B67" s="15" t="s">
-        <v>187</v>
-      </c>
-      <c r="D67" s="4">
-        <v>2</v>
-      </c>
-      <c r="E67" s="4" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="15">
+      <c r="B71" s="24" t="s">
+        <v>193</v>
+      </c>
+      <c r="D71" s="4">
+        <v>2</v>
+      </c>
+      <c r="E71" s="4" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8">
+      <c r="A72" s="24">
         <v>12305</v>
       </c>
-      <c r="B68" s="15" t="s">
-        <v>189</v>
-      </c>
-      <c r="D68" s="4">
-        <v>2</v>
-      </c>
-      <c r="E68" s="4" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="69" s="3" customFormat="1" spans="1:5">
-      <c r="A69" s="16">
+      <c r="B72" s="24" t="s">
+        <v>195</v>
+      </c>
+      <c r="D72" s="4">
+        <v>2</v>
+      </c>
+      <c r="E72" s="4" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="73" s="6" customFormat="1" spans="1:8">
+      <c r="A73" s="25">
         <v>12306</v>
       </c>
-      <c r="B69" s="16" t="s">
-        <v>191</v>
-      </c>
-      <c r="D69" s="3">
+      <c r="B73" s="25" t="s">
+        <v>197</v>
+      </c>
+      <c r="D73" s="6">
         <v>4</v>
       </c>
-      <c r="E69" s="3" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="70" s="3" customFormat="1" spans="1:5">
-      <c r="A70" s="15">
+      <c r="E73" s="6" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="74" s="6" customFormat="1" spans="1:8">
+      <c r="A74" s="24">
         <v>12307</v>
       </c>
-      <c r="B70" s="16" t="s">
-        <v>193</v>
-      </c>
-      <c r="D70" s="3">
-        <v>2</v>
-      </c>
-      <c r="E70" s="3" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="17">
+      <c r="B74" s="25" t="s">
+        <v>199</v>
+      </c>
+      <c r="D74" s="6">
+        <v>2</v>
+      </c>
+      <c r="E74" s="6" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8">
+      <c r="A75" s="26">
         <v>12501</v>
       </c>
-      <c r="B71" s="17" t="s">
-        <v>195</v>
-      </c>
-      <c r="D71" s="4">
+      <c r="B75" s="26" t="s">
+        <v>201</v>
+      </c>
+      <c r="D75" s="4">
         <v>4</v>
       </c>
-      <c r="E71" s="4" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="17">
+      <c r="E75" s="4" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8">
+      <c r="A76" s="26">
         <v>12502</v>
       </c>
-      <c r="B72" s="17" t="s">
-        <v>197</v>
-      </c>
-      <c r="D72" s="4">
+      <c r="B76" s="26" t="s">
+        <v>203</v>
+      </c>
+      <c r="D76" s="4">
         <v>3</v>
       </c>
-      <c r="E72" s="4" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="17">
+      <c r="E76" s="4" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8">
+      <c r="A77" s="26">
         <v>12503</v>
       </c>
-      <c r="B73" s="17" t="s">
-        <v>199</v>
-      </c>
-      <c r="D73" s="4">
-        <v>4</v>
-      </c>
-      <c r="E73" s="4" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="17">
-        <v>12504</v>
-      </c>
-      <c r="B74" s="17" t="s">
-        <v>201</v>
-      </c>
-      <c r="D74" s="4">
-        <v>3</v>
-      </c>
-      <c r="E74" s="4" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="4">
-        <v>12601</v>
-      </c>
-      <c r="B75" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="D75" s="4">
-        <v>3</v>
-      </c>
-      <c r="E75" s="4" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="4">
-        <v>12602</v>
-      </c>
-      <c r="B76" s="17" t="s">
+      <c r="B77" s="26" t="s">
         <v>205</v>
-      </c>
-      <c r="D76" s="4">
-        <v>4</v>
-      </c>
-      <c r="E76" s="4" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="4">
-        <v>12603</v>
-      </c>
-      <c r="B77" s="4" t="s">
-        <v>207</v>
       </c>
       <c r="D77" s="4">
         <v>4</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="4">
-        <v>12604</v>
-      </c>
-      <c r="B78" s="4" t="s">
-        <v>209</v>
+        <v>206</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8">
+      <c r="A78" s="26">
+        <v>12504</v>
+      </c>
+      <c r="B78" s="26" t="s">
+        <v>207</v>
       </c>
       <c r="D78" s="4">
         <v>3</v>
       </c>
       <c r="E78" s="4" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8">
+      <c r="A79" s="4">
+        <v>12601</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="D79" s="4">
+        <v>3</v>
+      </c>
+      <c r="E79" s="4" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="4">
-        <v>12605</v>
-      </c>
-      <c r="B79" s="4" t="s">
+    <row r="80" spans="1:8">
+      <c r="A80" s="4">
+        <v>12602</v>
+      </c>
+      <c r="B80" s="26" t="s">
         <v>211</v>
       </c>
-      <c r="D79" s="4">
+      <c r="D80" s="4">
         <v>4</v>
       </c>
-      <c r="E79" s="4" t="s">
+      <c r="E80" s="4" t="s">
         <v>212</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="4">
-        <v>12606</v>
-      </c>
-      <c r="B80" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="D80" s="4">
-        <v>3</v>
-      </c>
-      <c r="E80" s="4" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="4">
-        <v>12607</v>
+        <v>12603</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D81" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="4">
-        <v>12608</v>
+        <v>12604</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D82" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="4">
-        <v>12609</v>
+        <v>12605</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D83" s="4">
         <v>4</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="4">
-        <v>12610</v>
+        <v>12606</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D84" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="4">
-        <v>12701</v>
+        <v>12607</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D85" s="4">
         <v>2</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="4">
-        <v>12702</v>
+        <v>12608</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D86" s="4">
         <v>2</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="4">
-        <v>12703</v>
+        <v>12609</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D87" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="4">
+        <v>12610</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="D88" s="4">
+        <v>4</v>
+      </c>
+      <c r="E88" s="4" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5">
+      <c r="A89" s="4">
+        <v>12701</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="D89" s="4">
+        <v>2</v>
+      </c>
+      <c r="E89" s="4" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5">
+      <c r="A90" s="4">
+        <v>12702</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="D90" s="4">
+        <v>2</v>
+      </c>
+      <c r="E90" s="4" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5">
+      <c r="A91" s="4">
+        <v>12703</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="D91" s="4">
+        <v>3</v>
+      </c>
+      <c r="E91" s="4" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5">
+      <c r="A92" s="4">
         <v>12704</v>
       </c>
-      <c r="B88" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="D88" s="4">
+      <c r="B92" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="D92" s="4">
         <v>3</v>
       </c>
-      <c r="E88" s="4" t="s">
-        <v>230</v>
+      <c r="E92" s="4" t="s">
+        <v>236</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/condition.xlsx
+++ b/hall/resources/sample/condition.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\A-work\config_SimMgmtVert1.0\游戏配置表\common\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
@@ -609,7 +614,7 @@
     <t>接取：指定\任意SLOT游戏投注N次</t>
   </si>
   <si>
-    <t>12221_游戏ID(0)_数量(默认金币)</t>
+    <t>12221_游戏ID(0)_数量(计算金币投注)</t>
   </si>
   <si>
     <t>累积：在SLOT游戏中获得N个X道具</t>
@@ -729,7 +734,7 @@
     <t>累积：指定\任意SLOT游戏投注N次</t>
   </si>
   <si>
-    <t>12272_游戏ID(0)_数量(默认金币)</t>
+    <t>12272_游戏ID(0)_数量(计算金币投注)</t>
   </si>
   <si>
     <t>游戏中奖倍数</t>
@@ -1091,12 +1096,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/hall/resources/sample/condition.xlsx
+++ b/hall/resources/sample/condition.xlsx
@@ -174,7 +174,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="239">
   <si>
     <t>id</t>
   </si>
@@ -569,115 +569,121 @@
     <t>12213_免费0(付费1)_次数</t>
   </si>
   <si>
+    <t>累积：拥有N个X星游客&lt;重复,可删除&gt;</t>
+  </si>
+  <si>
+    <t>12214_数量_星级</t>
+  </si>
+  <si>
+    <t>接取：经营收益 金币\能量\道具 累积达到N</t>
+  </si>
+  <si>
+    <t>12215_道具ID_数量</t>
+  </si>
+  <si>
+    <t>累积：研发N个游戏(不使用)</t>
+  </si>
+  <si>
+    <t>12216_数量</t>
+  </si>
+  <si>
+    <t>接取：拜访N次</t>
+  </si>
+  <si>
+    <t>12217_数量</t>
+  </si>
+  <si>
+    <t>接取：登陆N天</t>
+  </si>
+  <si>
+    <t>12218_数量</t>
+  </si>
+  <si>
+    <t>累积：解锁N个娱乐城&lt;重复,可删除&gt;</t>
+  </si>
+  <si>
+    <t>12219_数量</t>
+  </si>
+  <si>
+    <t>接取：消费N金币\钻石</t>
+  </si>
+  <si>
+    <t>12220_道具ID(仅钻石或金币)_数量</t>
+  </si>
+  <si>
+    <t>接取：指定\任意SLOT游戏投注N次</t>
+  </si>
+  <si>
+    <t>12221_游戏ID(0)_数量(计算金币投注)</t>
+  </si>
+  <si>
+    <t>累积：在SLOT游戏中获得N个X道具</t>
+  </si>
+  <si>
+    <t>12251_游戏ID(0)_道具ID_道具数量</t>
+  </si>
+  <si>
+    <t>累积：触发SWEET WIN N次</t>
+  </si>
+  <si>
+    <t>12252_大奖类型_次数</t>
+  </si>
+  <si>
+    <t>累积：触发MINI奖池N次</t>
+  </si>
+  <si>
+    <t>12253_奖池类型_次数</t>
+  </si>
+  <si>
+    <t>累积：触发免费游戏模式N次</t>
+  </si>
+  <si>
+    <t>12254_次数</t>
+  </si>
+  <si>
+    <t>累积：建筑升级N次</t>
+  </si>
+  <si>
+    <t>12255_建筑ID(0)_次数</t>
+  </si>
+  <si>
+    <t>累积：拥有N个X级以上建筑</t>
+  </si>
+  <si>
+    <t>12256_数量_等级</t>
+  </si>
+  <si>
+    <t>累积：观看N次广告</t>
+  </si>
+  <si>
+    <t>12257_次数</t>
+  </si>
+  <si>
+    <t>累积：拥有N个X星雇员</t>
+  </si>
+  <si>
+    <t>12259_雇员类型_数量_星级</t>
+  </si>
+  <si>
+    <t>累积：招商游客N次</t>
+  </si>
+  <si>
+    <t>12260_免费0(付费1)_次数</t>
+  </si>
+  <si>
     <t>累积：拥有N个X星游客</t>
   </si>
   <si>
-    <t>12214_数量_星级</t>
-  </si>
-  <si>
-    <t>接取：经营收益 金币\能量\道具 累积达到N</t>
-  </si>
-  <si>
-    <t>12215_道具ID_数量</t>
+    <t>12261_数量_星级</t>
+  </si>
+  <si>
+    <t>累积：经营收益 金币\能量\道具 累积达到N</t>
+  </si>
+  <si>
+    <t>12262_道具ID_数量</t>
   </si>
   <si>
     <t>累积：研发N个游戏</t>
-  </si>
-  <si>
-    <t>12216_数量</t>
-  </si>
-  <si>
-    <t>接取：拜访N次</t>
-  </si>
-  <si>
-    <t>12217_数量</t>
-  </si>
-  <si>
-    <t>接取：登陆N天</t>
-  </si>
-  <si>
-    <t>12218_数量</t>
-  </si>
-  <si>
-    <t>累积：解锁N个娱乐城&lt;重复,可删除&gt;</t>
-  </si>
-  <si>
-    <t>12219_数量</t>
-  </si>
-  <si>
-    <t>接取：消费N金币\钻石</t>
-  </si>
-  <si>
-    <t>12220_道具ID(仅钻石或金币)_数量</t>
-  </si>
-  <si>
-    <t>接取：指定\任意SLOT游戏投注N次</t>
-  </si>
-  <si>
-    <t>12221_游戏ID(0)_数量(计算金币投注)</t>
-  </si>
-  <si>
-    <t>累积：在SLOT游戏中获得N个X道具</t>
-  </si>
-  <si>
-    <t>12251_游戏ID(0)_道具ID_道具数量</t>
-  </si>
-  <si>
-    <t>累积：触发SWEET WIN N次</t>
-  </si>
-  <si>
-    <t>12252_大奖类型_次数</t>
-  </si>
-  <si>
-    <t>累积：触发MINI奖池N次</t>
-  </si>
-  <si>
-    <t>12253_奖池类型_次数</t>
-  </si>
-  <si>
-    <t>累积：触发免费游戏模式N次</t>
-  </si>
-  <si>
-    <t>12254_次数</t>
-  </si>
-  <si>
-    <t>累积：建筑升级N次</t>
-  </si>
-  <si>
-    <t>12255_建筑ID(0)_次数</t>
-  </si>
-  <si>
-    <t>累积：拥有N个X级以上建筑</t>
-  </si>
-  <si>
-    <t>12256_数量_等级</t>
-  </si>
-  <si>
-    <t>累积：观看N次广告</t>
-  </si>
-  <si>
-    <t>12257_次数</t>
-  </si>
-  <si>
-    <t>累积：拥有N个X星雇员</t>
-  </si>
-  <si>
-    <t>12259_雇员类型_数量_星级</t>
-  </si>
-  <si>
-    <t>累积：招商游客N次</t>
-  </si>
-  <si>
-    <t>12260_免费0(付费1)_次数</t>
-  </si>
-  <si>
-    <t>12261_数量_星级</t>
-  </si>
-  <si>
-    <t>累积：经营收益 金币\能量\道具 累积达到N</t>
-  </si>
-  <si>
-    <t>12262_道具ID_数量</t>
   </si>
   <si>
     <t>12263_数量</t>
@@ -3208,14 +3214,14 @@
         <v>12261</v>
       </c>
       <c r="B56" s="20" t="s">
-        <v>131</v>
+        <v>165</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" s="2">
         <v>2</v>
       </c>
       <c r="E56" s="15" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F56" s="2"/>
       <c r="G56" s="2"/>
@@ -3226,14 +3232,14 @@
         <v>12262</v>
       </c>
       <c r="B57" s="20" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" s="2">
         <v>2</v>
       </c>
       <c r="E57" s="15" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F57" s="2"/>
       <c r="G57" s="2"/>
@@ -3244,14 +3250,14 @@
         <v>12263</v>
       </c>
       <c r="B58" s="20" t="s">
-        <v>135</v>
+        <v>169</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" s="2">
         <v>1</v>
       </c>
       <c r="E58" s="15" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F58" s="2"/>
       <c r="G58" s="2"/>
@@ -3262,14 +3268,14 @@
         <v>12264</v>
       </c>
       <c r="B59" s="20" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" s="2">
         <v>1</v>
       </c>
       <c r="E59" s="15" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F59" s="2"/>
       <c r="G59" s="2"/>
@@ -3280,14 +3286,14 @@
         <v>12265</v>
       </c>
       <c r="B60" s="20" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" s="2">
         <v>1</v>
       </c>
       <c r="E60" s="15" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F60" s="2"/>
       <c r="G60" s="2"/>
@@ -3298,14 +3304,14 @@
         <v>12266</v>
       </c>
       <c r="B61" s="20" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" s="2">
         <v>1</v>
       </c>
       <c r="E61" s="15" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="F61" s="2"/>
       <c r="G61" s="2"/>
@@ -3316,14 +3322,14 @@
         <v>12267</v>
       </c>
       <c r="B62" s="20" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" s="2">
         <v>2</v>
       </c>
       <c r="E62" s="15" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F62" s="2"/>
       <c r="G62" s="2"/>
@@ -3334,14 +3340,14 @@
         <v>12268</v>
       </c>
       <c r="B63" s="20" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" s="2">
         <v>2</v>
       </c>
       <c r="E63" s="15" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F63" s="2"/>
       <c r="G63" s="2"/>
@@ -3352,14 +3358,14 @@
         <v>12269</v>
       </c>
       <c r="B64" s="21" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C64" s="22"/>
       <c r="D64" s="22">
         <v>2</v>
       </c>
       <c r="E64" s="23" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="F64" s="22"/>
       <c r="G64" s="22"/>
@@ -3370,14 +3376,14 @@
         <v>12270</v>
       </c>
       <c r="B65" s="21" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C65" s="22"/>
       <c r="D65" s="22">
         <v>1</v>
       </c>
       <c r="E65" s="23" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F65" s="22"/>
       <c r="G65" s="22"/>
@@ -3388,14 +3394,14 @@
         <v>12271</v>
       </c>
       <c r="B66" s="21" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C66" s="22"/>
       <c r="D66" s="22">
         <v>1</v>
       </c>
       <c r="E66" s="23" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F66" s="22"/>
       <c r="G66" s="22"/>
@@ -3406,14 +3412,14 @@
         <v>12272</v>
       </c>
       <c r="B67" s="21" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C67" s="22"/>
       <c r="D67" s="22">
         <v>2</v>
       </c>
       <c r="E67" s="23" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F67" s="22"/>
       <c r="G67" s="22"/>
@@ -3424,13 +3430,13 @@
         <v>12301</v>
       </c>
       <c r="B68" s="24" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D68" s="4">
         <v>4</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="69" s="6" customFormat="1" spans="1:8">
@@ -3438,13 +3444,13 @@
         <v>12302</v>
       </c>
       <c r="B69" s="25" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D69" s="6">
         <v>3</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="70" spans="1:8">
@@ -3452,13 +3458,13 @@
         <v>12303</v>
       </c>
       <c r="B70" s="24" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D70" s="4">
         <v>2</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="71" spans="1:8">
@@ -3466,13 +3472,13 @@
         <v>12304</v>
       </c>
       <c r="B71" s="24" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D71" s="4">
         <v>2</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="72" spans="1:8">
@@ -3480,13 +3486,13 @@
         <v>12305</v>
       </c>
       <c r="B72" s="24" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D72" s="4">
         <v>2</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="73" s="6" customFormat="1" spans="1:8">
@@ -3494,13 +3500,13 @@
         <v>12306</v>
       </c>
       <c r="B73" s="25" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D73" s="6">
         <v>4</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="74" s="6" customFormat="1" spans="1:8">
@@ -3508,13 +3514,13 @@
         <v>12307</v>
       </c>
       <c r="B74" s="25" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D74" s="6">
         <v>2</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="75" spans="1:8">
@@ -3522,13 +3528,13 @@
         <v>12501</v>
       </c>
       <c r="B75" s="26" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D75" s="4">
         <v>4</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="76" spans="1:8">
@@ -3536,13 +3542,13 @@
         <v>12502</v>
       </c>
       <c r="B76" s="26" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D76" s="4">
         <v>3</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="77" spans="1:8">
@@ -3550,13 +3556,13 @@
         <v>12503</v>
       </c>
       <c r="B77" s="26" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D77" s="4">
         <v>4</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="78" spans="1:8">
@@ -3564,13 +3570,13 @@
         <v>12504</v>
       </c>
       <c r="B78" s="26" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D78" s="4">
         <v>3</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="79" spans="1:8">
@@ -3578,13 +3584,13 @@
         <v>12601</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D79" s="4">
         <v>3</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="80" spans="1:8">
@@ -3592,13 +3598,13 @@
         <v>12602</v>
       </c>
       <c r="B80" s="26" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D80" s="4">
         <v>4</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -3606,13 +3612,13 @@
         <v>12603</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D81" s="4">
         <v>4</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -3620,13 +3626,13 @@
         <v>12604</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D82" s="4">
         <v>3</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -3634,13 +3640,13 @@
         <v>12605</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D83" s="4">
         <v>4</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -3648,13 +3654,13 @@
         <v>12606</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D84" s="4">
         <v>3</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -3662,13 +3668,13 @@
         <v>12607</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D85" s="4">
         <v>2</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -3676,13 +3682,13 @@
         <v>12608</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D86" s="4">
         <v>2</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -3690,13 +3696,13 @@
         <v>12609</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D87" s="4">
         <v>4</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -3704,13 +3710,13 @@
         <v>12610</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="D88" s="4">
         <v>4</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -3718,13 +3724,13 @@
         <v>12701</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D89" s="4">
         <v>2</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -3732,13 +3738,13 @@
         <v>12702</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D90" s="4">
         <v>2</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -3746,13 +3752,13 @@
         <v>12703</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D91" s="4">
         <v>3</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -3760,13 +3766,13 @@
         <v>12704</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D92" s="4">
         <v>3</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/condition.xlsx
+++ b/hall/resources/sample/condition.xlsx
@@ -115,7 +115,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E48" authorId="0">
+    <comment ref="E50" authorId="0">
       <text>
         <r>
           <rPr>
@@ -143,7 +143,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E49" authorId="0">
+    <comment ref="E51" authorId="0">
       <text>
         <r>
           <rPr>
@@ -174,7 +174,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="243">
   <si>
     <t>id</t>
   </si>
@@ -615,6 +615,18 @@
   </si>
   <si>
     <t>12221_游戏ID(0)_数量(计算金币投注)</t>
+  </si>
+  <si>
+    <t>接取：生成指定游客N次</t>
+  </si>
+  <si>
+    <t>12222_游客ID(0)_次数(单个邀请\一键邀请)</t>
+  </si>
+  <si>
+    <t>接取：完成斗仙牌N次</t>
+  </si>
+  <si>
+    <t>12223_次数(开始游戏并结算)</t>
   </si>
   <si>
     <t>累积：在SLOT游戏中获得N个X道具</t>
@@ -924,13 +936,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF7030A0"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFC00000"/>
+      <color theme="0" tint="-0.25"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -953,7 +959,13 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="9" tint="-0.25"/>
+      <color rgb="FFC00000"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF7030A0"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -1593,7 +1605,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1612,25 +1624,22 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
@@ -1642,7 +1651,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1651,25 +1660,16 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2000,7 +2000,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O92"/>
+  <dimension ref="A1:O94"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="4"/>
@@ -2015,82 +2015,82 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="15" spans="1:10">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="7" t="s">
+      <c r="C1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7"/>
-      <c r="F1" s="8" t="s">
+      <c r="E1" s="6"/>
+      <c r="F1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="7" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="15" spans="1:10">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8" t="s">
+      <c r="B2" s="7"/>
+      <c r="C2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7" t="s">
+      <c r="E2" s="6"/>
+      <c r="F2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="7" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="15" spans="1:10">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="7" t="s">
+      <c r="B3" s="7"/>
+      <c r="C3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8" t="s">
+      <c r="E3" s="7"/>
+      <c r="F3" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="7" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" ht="15" spans="1:10">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
     </row>
     <row r="5" ht="17.25" spans="1:10">
       <c r="A5" s="4">
@@ -2099,7 +2099,7 @@
       <c r="B5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="8" t="s">
         <v>16</v>
       </c>
       <c r="D5" s="4">
@@ -2108,10 +2108,10 @@
       <c r="E5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="F5" s="10">
+      <c r="F5" s="9">
         <v>48001</v>
       </c>
-      <c r="G5" s="11" t="s">
+      <c r="G5" s="10" t="s">
         <v>18</v>
       </c>
       <c r="H5" s="4" t="s">
@@ -2128,7 +2128,7 @@
       <c r="B6" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="8" t="s">
         <v>22</v>
       </c>
       <c r="D6" s="4">
@@ -2137,10 +2137,10 @@
       <c r="E6" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="10">
+      <c r="F6" s="9">
         <v>48002</v>
       </c>
-      <c r="G6" s="11" t="s">
+      <c r="G6" s="10" t="s">
         <v>24</v>
       </c>
       <c r="H6" s="4" t="s">
@@ -2157,7 +2157,7 @@
       <c r="B7" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D7" s="4">
@@ -2166,10 +2166,10 @@
       <c r="E7" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="F7" s="10">
+      <c r="F7" s="9">
         <v>49161</v>
       </c>
-      <c r="G7" s="11" t="s">
+      <c r="G7" s="10" t="s">
         <v>30</v>
       </c>
       <c r="H7" s="4" t="s">
@@ -2186,7 +2186,7 @@
       <c r="B8" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="11" t="s">
         <v>33</v>
       </c>
       <c r="D8" s="2">
@@ -2195,10 +2195,10 @@
       <c r="E8" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="12">
         <v>48005</v>
       </c>
-      <c r="G8" s="11" t="s">
+      <c r="G8" s="10" t="s">
         <v>35</v>
       </c>
       <c r="H8" s="2" t="s">
@@ -2215,17 +2215,17 @@
       <c r="B9" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="11" t="s">
         <v>38</v>
       </c>
       <c r="D9" s="2">
         <v>3</v>
       </c>
-      <c r="E9" s="13" t="s">
+      <c r="E9" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="F9" s="13"/>
-      <c r="G9" s="11"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="10"/>
       <c r="I9" s="2" t="s">
         <v>20</v>
       </c>
@@ -2237,7 +2237,7 @@
       <c r="B10" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="8" t="s">
         <v>41</v>
       </c>
       <c r="D10" s="4">
@@ -2246,10 +2246,10 @@
       <c r="E10" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F10" s="10">
+      <c r="F10" s="9">
         <v>48003</v>
       </c>
-      <c r="G10" s="11" t="s">
+      <c r="G10" s="10" t="s">
         <v>43</v>
       </c>
       <c r="H10" s="4" t="s">
@@ -2266,7 +2266,7 @@
       <c r="B11" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="8" t="s">
         <v>46</v>
       </c>
       <c r="D11" s="4">
@@ -2275,10 +2275,10 @@
       <c r="E11" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="F11" s="10">
+      <c r="F11" s="9">
         <v>48003</v>
       </c>
-      <c r="G11" s="11" t="s">
+      <c r="G11" s="10" t="s">
         <v>43</v>
       </c>
       <c r="H11" s="4" t="s">
@@ -2295,7 +2295,7 @@
       <c r="B12" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="C12" s="8" t="s">
         <v>49</v>
       </c>
       <c r="D12" s="4">
@@ -2304,10 +2304,10 @@
       <c r="E12" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="F12" s="10">
+      <c r="F12" s="9">
         <v>48003</v>
       </c>
-      <c r="G12" s="11" t="s">
+      <c r="G12" s="10" t="s">
         <v>43</v>
       </c>
       <c r="H12" s="4" t="s">
@@ -2324,7 +2324,7 @@
       <c r="B13" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="8" t="s">
         <v>52</v>
       </c>
       <c r="D13" s="4">
@@ -2333,10 +2333,10 @@
       <c r="E13" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="F13" s="10">
+      <c r="F13" s="9">
         <v>48004</v>
       </c>
-      <c r="G13" s="11" t="s">
+      <c r="G13" s="10" t="s">
         <v>54</v>
       </c>
       <c r="H13" s="4" t="s">
@@ -2353,7 +2353,7 @@
       <c r="B14" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="11" t="s">
         <v>57</v>
       </c>
       <c r="D14" s="2">
@@ -2362,10 +2362,10 @@
       <c r="E14" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="F14" s="13">
+      <c r="F14" s="12">
         <v>48004</v>
       </c>
-      <c r="G14" s="11" t="s">
+      <c r="G14" s="10" t="s">
         <v>54</v>
       </c>
       <c r="H14" s="2" t="s">
@@ -2382,7 +2382,7 @@
       <c r="B15" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="C15" s="11" t="s">
         <v>60</v>
       </c>
       <c r="D15" s="2">
@@ -2391,10 +2391,10 @@
       <c r="E15" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="F15" s="13">
+      <c r="F15" s="12">
         <v>48006</v>
       </c>
-      <c r="G15" s="11" t="s">
+      <c r="G15" s="10" t="s">
         <v>62</v>
       </c>
       <c r="H15" s="2" t="s">
@@ -2403,7 +2403,7 @@
       <c r="I15" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="J15" s="13" t="s">
+      <c r="J15" s="12" t="s">
         <v>63</v>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       <c r="B16" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C16" s="12" t="s">
+      <c r="C16" s="11" t="s">
         <v>65</v>
       </c>
       <c r="D16" s="2">
@@ -2423,10 +2423,10 @@
       <c r="E16" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="F16" s="13">
+      <c r="F16" s="12">
         <v>48004</v>
       </c>
-      <c r="G16" s="11" t="s">
+      <c r="G16" s="10" t="s">
         <v>54</v>
       </c>
       <c r="H16" s="2" t="s">
@@ -2435,7 +2435,7 @@
       <c r="I16" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="J16" s="13"/>
+      <c r="J16" s="12"/>
     </row>
     <row r="17" s="2" customFormat="1" ht="17.25" spans="1:15">
       <c r="A17" s="2">
@@ -2444,7 +2444,7 @@
       <c r="B17" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C17" s="12" t="s">
+      <c r="C17" s="11" t="s">
         <v>68</v>
       </c>
       <c r="D17" s="2">
@@ -2453,10 +2453,10 @@
       <c r="E17" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="F17" s="13">
+      <c r="F17" s="12">
         <v>48004</v>
       </c>
-      <c r="G17" s="11" t="s">
+      <c r="G17" s="10" t="s">
         <v>54</v>
       </c>
       <c r="H17" s="2" t="s">
@@ -2465,7 +2465,7 @@
       <c r="I17" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="J17" s="13"/>
+      <c r="J17" s="12"/>
     </row>
     <row r="18" s="2" customFormat="1" spans="1:15">
       <c r="A18" s="2">
@@ -2474,7 +2474,7 @@
       <c r="B18" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="C18" s="11" t="s">
         <v>71</v>
       </c>
       <c r="D18" s="2">
@@ -2497,7 +2497,7 @@
       <c r="B19" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C19" s="12" t="s">
+      <c r="C19" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D19" s="2">
@@ -2520,7 +2520,7 @@
       <c r="B20" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C20" s="12" t="s">
+      <c r="C20" s="11" t="s">
         <v>77</v>
       </c>
       <c r="D20" s="2">
@@ -2549,7 +2549,7 @@
       <c r="B21" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C21" s="12" t="s">
+      <c r="C21" s="11" t="s">
         <v>83</v>
       </c>
       <c r="D21" s="2">
@@ -2572,7 +2572,7 @@
       <c r="B22" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="C22" s="12" t="s">
+      <c r="C22" s="11" t="s">
         <v>86</v>
       </c>
       <c r="D22" s="2">
@@ -2604,7 +2604,7 @@
       <c r="B23" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C23" s="12" t="s">
+      <c r="C23" s="11" t="s">
         <v>93</v>
       </c>
       <c r="D23" s="2">
@@ -2636,7 +2636,7 @@
       <c r="B24" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C24" s="12" t="s">
+      <c r="C24" s="11" t="s">
         <v>100</v>
       </c>
       <c r="D24" s="2">
@@ -2659,7 +2659,7 @@
       <c r="B25" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="C25" s="9" t="s">
+      <c r="C25" s="8" t="s">
         <v>103</v>
       </c>
       <c r="D25" s="4">
@@ -2670,17 +2670,17 @@
       </c>
     </row>
     <row r="26" spans="1:15">
-      <c r="A26" s="14">
+      <c r="A26" s="13">
         <v>12201</v>
       </c>
-      <c r="B26" s="14" t="s">
+      <c r="B26" s="13" t="s">
         <v>105</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" s="2">
         <v>2</v>
       </c>
-      <c r="E26" s="15" t="s">
+      <c r="E26" s="14" t="s">
         <v>106</v>
       </c>
       <c r="F26" s="2"/>
@@ -2688,17 +2688,17 @@
       <c r="H26" s="2"/>
     </row>
     <row r="27" spans="1:15">
-      <c r="A27" s="14">
+      <c r="A27" s="13">
         <v>12202</v>
       </c>
-      <c r="B27" s="14" t="s">
+      <c r="B27" s="13" t="s">
         <v>107</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" s="2">
         <v>3</v>
       </c>
-      <c r="E27" s="15" t="s">
+      <c r="E27" s="14" t="s">
         <v>108</v>
       </c>
       <c r="F27" s="2"/>
@@ -2706,17 +2706,17 @@
       <c r="H27" s="2"/>
     </row>
     <row r="28" spans="1:15">
-      <c r="A28" s="14">
+      <c r="A28" s="13">
         <v>12203</v>
       </c>
-      <c r="B28" s="14" t="s">
+      <c r="B28" s="13" t="s">
         <v>109</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" s="2">
         <v>2</v>
       </c>
-      <c r="E28" s="15" t="s">
+      <c r="E28" s="14" t="s">
         <v>110</v>
       </c>
       <c r="F28" s="2"/>
@@ -2724,17 +2724,17 @@
       <c r="H28" s="2"/>
     </row>
     <row r="29" spans="1:15">
-      <c r="A29" s="14">
+      <c r="A29" s="13">
         <v>12204</v>
       </c>
-      <c r="B29" s="14" t="s">
+      <c r="B29" s="13" t="s">
         <v>111</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" s="2">
         <v>2</v>
       </c>
-      <c r="E29" s="15" t="s">
+      <c r="E29" s="14" t="s">
         <v>112</v>
       </c>
       <c r="F29" s="2"/>
@@ -2742,17 +2742,17 @@
       <c r="H29" s="2"/>
     </row>
     <row r="30" spans="1:15">
-      <c r="A30" s="14">
+      <c r="A30" s="13">
         <v>12205</v>
       </c>
-      <c r="B30" s="14" t="s">
+      <c r="B30" s="13" t="s">
         <v>113</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" s="2">
         <v>1</v>
       </c>
-      <c r="E30" s="15" t="s">
+      <c r="E30" s="14" t="s">
         <v>114</v>
       </c>
       <c r="F30" s="2"/>
@@ -2760,17 +2760,17 @@
       <c r="H30" s="2"/>
     </row>
     <row r="31" spans="1:15">
-      <c r="A31" s="14">
+      <c r="A31" s="13">
         <v>12206</v>
       </c>
-      <c r="B31" s="14" t="s">
+      <c r="B31" s="13" t="s">
         <v>115</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" s="2">
         <v>2</v>
       </c>
-      <c r="E31" s="15" t="s">
+      <c r="E31" s="14" t="s">
         <v>116</v>
       </c>
       <c r="F31" s="2"/>
@@ -2778,53 +2778,53 @@
       <c r="H31" s="2"/>
     </row>
     <row r="32" s="3" customFormat="1" spans="1:15">
-      <c r="A32" s="16">
+      <c r="A32" s="15">
         <v>12207</v>
       </c>
-      <c r="B32" s="16" t="s">
+      <c r="B32" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="C32" s="17"/>
-      <c r="D32" s="17">
-        <v>2</v>
-      </c>
-      <c r="E32" s="18" t="s">
+      <c r="C32" s="16"/>
+      <c r="D32" s="16">
+        <v>2</v>
+      </c>
+      <c r="E32" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="F32" s="17"/>
-      <c r="G32" s="17"/>
-      <c r="H32" s="17"/>
+      <c r="F32" s="16"/>
+      <c r="G32" s="16"/>
+      <c r="H32" s="16"/>
     </row>
     <row r="33" s="3" customFormat="1" spans="1:8">
-      <c r="A33" s="16">
+      <c r="A33" s="15">
         <v>12208</v>
       </c>
-      <c r="B33" s="16" t="s">
+      <c r="B33" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="C33" s="17"/>
-      <c r="D33" s="17">
-        <v>2</v>
-      </c>
-      <c r="E33" s="18" t="s">
+      <c r="C33" s="16"/>
+      <c r="D33" s="16">
+        <v>2</v>
+      </c>
+      <c r="E33" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="F33" s="17"/>
-      <c r="G33" s="17"/>
-      <c r="H33" s="17"/>
+      <c r="F33" s="16"/>
+      <c r="G33" s="16"/>
+      <c r="H33" s="16"/>
     </row>
     <row r="34" spans="1:8">
-      <c r="A34" s="14">
+      <c r="A34" s="13">
         <v>12209</v>
       </c>
-      <c r="B34" s="14" t="s">
+      <c r="B34" s="13" t="s">
         <v>121</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" s="2">
         <v>1</v>
       </c>
-      <c r="E34" s="15" t="s">
+      <c r="E34" s="14" t="s">
         <v>122</v>
       </c>
       <c r="F34" s="2"/>
@@ -2832,17 +2832,17 @@
       <c r="H34" s="2"/>
     </row>
     <row r="35" spans="1:8">
-      <c r="A35" s="14">
+      <c r="A35" s="13">
         <v>12210</v>
       </c>
-      <c r="B35" s="14" t="s">
+      <c r="B35" s="13" t="s">
         <v>123</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" s="2">
         <v>2</v>
       </c>
-      <c r="E35" s="15" t="s">
+      <c r="E35" s="14" t="s">
         <v>124</v>
       </c>
       <c r="F35" s="2"/>
@@ -2850,17 +2850,17 @@
       <c r="H35" s="2"/>
     </row>
     <row r="36" s="4" customFormat="1" spans="1:8">
-      <c r="A36" s="14">
+      <c r="A36" s="13">
         <v>12211</v>
       </c>
-      <c r="B36" s="14" t="s">
+      <c r="B36" s="13" t="s">
         <v>125</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" s="2">
         <v>2</v>
       </c>
-      <c r="E36" s="15" t="s">
+      <c r="E36" s="14" t="s">
         <v>126</v>
       </c>
       <c r="F36" s="2"/>
@@ -2868,35 +2868,35 @@
       <c r="H36" s="2"/>
     </row>
     <row r="37" s="3" customFormat="1" spans="1:8">
-      <c r="A37" s="19">
+      <c r="A37" s="15">
         <v>12212</v>
       </c>
-      <c r="B37" s="19" t="s">
+      <c r="B37" s="15" t="s">
         <v>127</v>
       </c>
-      <c r="C37" s="17"/>
-      <c r="D37" s="17">
+      <c r="C37" s="16"/>
+      <c r="D37" s="16">
         <v>3</v>
       </c>
-      <c r="E37" s="18" t="s">
+      <c r="E37" s="17" t="s">
         <v>128</v>
       </c>
-      <c r="F37" s="17"/>
-      <c r="G37" s="17"/>
-      <c r="H37" s="17"/>
+      <c r="F37" s="16"/>
+      <c r="G37" s="16"/>
+      <c r="H37" s="16"/>
     </row>
     <row r="38" spans="1:8">
-      <c r="A38" s="14">
+      <c r="A38" s="13">
         <v>12213</v>
       </c>
-      <c r="B38" s="14" t="s">
+      <c r="B38" s="13" t="s">
         <v>129</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" s="2">
         <v>2</v>
       </c>
-      <c r="E38" s="15" t="s">
+      <c r="E38" s="14" t="s">
         <v>130</v>
       </c>
       <c r="F38" s="2"/>
@@ -2904,35 +2904,35 @@
       <c r="H38" s="2"/>
     </row>
     <row r="39" s="3" customFormat="1" spans="1:8">
-      <c r="A39" s="19">
+      <c r="A39" s="15">
         <v>12214</v>
       </c>
-      <c r="B39" s="19" t="s">
+      <c r="B39" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="C39" s="17"/>
-      <c r="D39" s="17">
-        <v>2</v>
-      </c>
-      <c r="E39" s="18" t="s">
+      <c r="C39" s="16"/>
+      <c r="D39" s="16">
+        <v>2</v>
+      </c>
+      <c r="E39" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="F39" s="17"/>
-      <c r="G39" s="17"/>
-      <c r="H39" s="17"/>
+      <c r="F39" s="16"/>
+      <c r="G39" s="16"/>
+      <c r="H39" s="16"/>
     </row>
     <row r="40" spans="1:8">
-      <c r="A40" s="14">
+      <c r="A40" s="13">
         <v>12215</v>
       </c>
-      <c r="B40" s="14" t="s">
+      <c r="B40" s="13" t="s">
         <v>133</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" s="2">
         <v>2</v>
       </c>
-      <c r="E40" s="15" t="s">
+      <c r="E40" s="14" t="s">
         <v>134</v>
       </c>
       <c r="F40" s="2"/>
@@ -2940,35 +2940,35 @@
       <c r="H40" s="2"/>
     </row>
     <row r="41" s="3" customFormat="1" spans="1:8">
-      <c r="A41" s="19">
+      <c r="A41" s="15">
         <v>12216</v>
       </c>
-      <c r="B41" s="19" t="s">
+      <c r="B41" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="C41" s="17"/>
-      <c r="D41" s="17">
+      <c r="C41" s="16"/>
+      <c r="D41" s="16">
         <v>1</v>
       </c>
-      <c r="E41" s="18" t="s">
+      <c r="E41" s="17" t="s">
         <v>136</v>
       </c>
-      <c r="F41" s="17"/>
-      <c r="G41" s="17"/>
-      <c r="H41" s="17"/>
+      <c r="F41" s="16"/>
+      <c r="G41" s="16"/>
+      <c r="H41" s="16"/>
     </row>
     <row r="42" spans="1:8">
-      <c r="A42" s="14">
+      <c r="A42" s="13">
         <v>12217</v>
       </c>
-      <c r="B42" s="14" t="s">
+      <c r="B42" s="13" t="s">
         <v>137</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" s="2">
         <v>1</v>
       </c>
-      <c r="E42" s="15" t="s">
+      <c r="E42" s="14" t="s">
         <v>138</v>
       </c>
       <c r="F42" s="2"/>
@@ -2976,17 +2976,17 @@
       <c r="H42" s="2"/>
     </row>
     <row r="43" spans="1:8">
-      <c r="A43" s="14">
+      <c r="A43" s="13">
         <v>12218</v>
       </c>
-      <c r="B43" s="14" t="s">
+      <c r="B43" s="13" t="s">
         <v>139</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" s="2">
         <v>1</v>
       </c>
-      <c r="E43" s="15" t="s">
+      <c r="E43" s="14" t="s">
         <v>140</v>
       </c>
       <c r="F43" s="2"/>
@@ -2994,35 +2994,35 @@
       <c r="H43" s="2"/>
     </row>
     <row r="44" s="3" customFormat="1" spans="1:8">
-      <c r="A44" s="19">
+      <c r="A44" s="15">
         <v>12219</v>
       </c>
-      <c r="B44" s="19" t="s">
+      <c r="B44" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="C44" s="17"/>
-      <c r="D44" s="17">
+      <c r="C44" s="16"/>
+      <c r="D44" s="16">
         <v>1</v>
       </c>
-      <c r="E44" s="18" t="s">
+      <c r="E44" s="17" t="s">
         <v>142</v>
       </c>
-      <c r="F44" s="17"/>
-      <c r="G44" s="17"/>
-      <c r="H44" s="17"/>
+      <c r="F44" s="16"/>
+      <c r="G44" s="16"/>
+      <c r="H44" s="16"/>
     </row>
     <row r="45" spans="1:8">
-      <c r="A45" s="14">
+      <c r="A45" s="13">
         <v>12220</v>
       </c>
-      <c r="B45" s="14" t="s">
+      <c r="B45" s="13" t="s">
         <v>143</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" s="2">
         <v>2</v>
       </c>
-      <c r="E45" s="15" t="s">
+      <c r="E45" s="14" t="s">
         <v>144</v>
       </c>
       <c r="F45" s="2"/>
@@ -3030,17 +3030,17 @@
       <c r="H45" s="2"/>
     </row>
     <row r="46" spans="1:8">
-      <c r="A46" s="19">
+      <c r="A46" s="13">
         <v>12221</v>
       </c>
-      <c r="B46" s="19" t="s">
+      <c r="B46" s="13" t="s">
         <v>145</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" s="2">
         <v>2</v>
       </c>
-      <c r="E46" s="15" t="s">
+      <c r="E46" s="14" t="s">
         <v>146</v>
       </c>
       <c r="F46" s="2"/>
@@ -3048,17 +3048,17 @@
       <c r="H46" s="2"/>
     </row>
     <row r="47" spans="1:8">
-      <c r="A47" s="20">
-        <v>12251</v>
-      </c>
-      <c r="B47" s="20" t="s">
+      <c r="A47" s="18">
+        <v>12222</v>
+      </c>
+      <c r="B47" s="18" t="s">
         <v>147</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" s="2">
-        <v>3</v>
-      </c>
-      <c r="E47" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="E47" s="14" t="s">
         <v>148</v>
       </c>
       <c r="F47" s="2"/>
@@ -3066,17 +3066,17 @@
       <c r="H47" s="2"/>
     </row>
     <row r="48" spans="1:8">
-      <c r="A48" s="20">
-        <v>12252</v>
-      </c>
-      <c r="B48" s="20" t="s">
+      <c r="A48" s="18">
+        <v>12223</v>
+      </c>
+      <c r="B48" s="18" t="s">
         <v>149</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" s="2">
-        <v>2</v>
-      </c>
-      <c r="E48" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="E48" s="14" t="s">
         <v>150</v>
       </c>
       <c r="F48" s="2"/>
@@ -3084,17 +3084,17 @@
       <c r="H48" s="2"/>
     </row>
     <row r="49" spans="1:8">
-      <c r="A49" s="20">
-        <v>12253</v>
-      </c>
-      <c r="B49" s="20" t="s">
+      <c r="A49" s="19">
+        <v>12251</v>
+      </c>
+      <c r="B49" s="19" t="s">
         <v>151</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" s="2">
-        <v>2</v>
-      </c>
-      <c r="E49" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="E49" s="14" t="s">
         <v>152</v>
       </c>
       <c r="F49" s="2"/>
@@ -3102,17 +3102,17 @@
       <c r="H49" s="2"/>
     </row>
     <row r="50" spans="1:8">
-      <c r="A50" s="20">
-        <v>12254</v>
-      </c>
-      <c r="B50" s="20" t="s">
+      <c r="A50" s="19">
+        <v>12252</v>
+      </c>
+      <c r="B50" s="19" t="s">
         <v>153</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" s="2">
-        <v>1</v>
-      </c>
-      <c r="E50" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="E50" s="14" t="s">
         <v>154</v>
       </c>
       <c r="F50" s="2"/>
@@ -3120,17 +3120,17 @@
       <c r="H50" s="2"/>
     </row>
     <row r="51" spans="1:8">
-      <c r="A51" s="20">
-        <v>12255</v>
-      </c>
-      <c r="B51" s="20" t="s">
+      <c r="A51" s="19">
+        <v>12253</v>
+      </c>
+      <c r="B51" s="19" t="s">
         <v>155</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" s="2">
         <v>2</v>
       </c>
-      <c r="E51" s="15" t="s">
+      <c r="E51" s="14" t="s">
         <v>156</v>
       </c>
       <c r="F51" s="2"/>
@@ -3138,17 +3138,17 @@
       <c r="H51" s="2"/>
     </row>
     <row r="52" spans="1:8">
-      <c r="A52" s="20">
-        <v>12256</v>
-      </c>
-      <c r="B52" s="20" t="s">
+      <c r="A52" s="19">
+        <v>12254</v>
+      </c>
+      <c r="B52" s="19" t="s">
         <v>157</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" s="2">
-        <v>2</v>
-      </c>
-      <c r="E52" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="E52" s="14" t="s">
         <v>158</v>
       </c>
       <c r="F52" s="2"/>
@@ -3156,17 +3156,17 @@
       <c r="H52" s="2"/>
     </row>
     <row r="53" spans="1:8">
-      <c r="A53" s="20">
-        <v>12257</v>
-      </c>
-      <c r="B53" s="20" t="s">
+      <c r="A53" s="19">
+        <v>12255</v>
+      </c>
+      <c r="B53" s="19" t="s">
         <v>159</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" s="2">
-        <v>1</v>
-      </c>
-      <c r="E53" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="E53" s="14" t="s">
         <v>160</v>
       </c>
       <c r="F53" s="2"/>
@@ -3174,17 +3174,17 @@
       <c r="H53" s="2"/>
     </row>
     <row r="54" spans="1:8">
-      <c r="A54" s="20">
-        <v>12259</v>
-      </c>
-      <c r="B54" s="20" t="s">
+      <c r="A54" s="19">
+        <v>12256</v>
+      </c>
+      <c r="B54" s="19" t="s">
         <v>161</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" s="2">
-        <v>3</v>
-      </c>
-      <c r="E54" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="E54" s="14" t="s">
         <v>162</v>
       </c>
       <c r="F54" s="2"/>
@@ -3192,17 +3192,17 @@
       <c r="H54" s="2"/>
     </row>
     <row r="55" spans="1:8">
-      <c r="A55" s="20">
-        <v>12260</v>
-      </c>
-      <c r="B55" s="20" t="s">
+      <c r="A55" s="19">
+        <v>12257</v>
+      </c>
+      <c r="B55" s="19" t="s">
         <v>163</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" s="2">
-        <v>2</v>
-      </c>
-      <c r="E55" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="E55" s="14" t="s">
         <v>164</v>
       </c>
       <c r="F55" s="2"/>
@@ -3210,17 +3210,17 @@
       <c r="H55" s="2"/>
     </row>
     <row r="56" spans="1:8">
-      <c r="A56" s="20">
-        <v>12261</v>
-      </c>
-      <c r="B56" s="20" t="s">
+      <c r="A56" s="19">
+        <v>12259</v>
+      </c>
+      <c r="B56" s="19" t="s">
         <v>165</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" s="2">
-        <v>2</v>
-      </c>
-      <c r="E56" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="E56" s="14" t="s">
         <v>166</v>
       </c>
       <c r="F56" s="2"/>
@@ -3228,17 +3228,17 @@
       <c r="H56" s="2"/>
     </row>
     <row r="57" spans="1:8">
-      <c r="A57" s="20">
-        <v>12262</v>
-      </c>
-      <c r="B57" s="20" t="s">
+      <c r="A57" s="19">
+        <v>12260</v>
+      </c>
+      <c r="B57" s="19" t="s">
         <v>167</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" s="2">
         <v>2</v>
       </c>
-      <c r="E57" s="15" t="s">
+      <c r="E57" s="14" t="s">
         <v>168</v>
       </c>
       <c r="F57" s="2"/>
@@ -3246,17 +3246,17 @@
       <c r="H57" s="2"/>
     </row>
     <row r="58" spans="1:8">
-      <c r="A58" s="20">
-        <v>12263</v>
-      </c>
-      <c r="B58" s="20" t="s">
+      <c r="A58" s="19">
+        <v>12261</v>
+      </c>
+      <c r="B58" s="19" t="s">
         <v>169</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" s="2">
-        <v>1</v>
-      </c>
-      <c r="E58" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="E58" s="14" t="s">
         <v>170</v>
       </c>
       <c r="F58" s="2"/>
@@ -3264,17 +3264,17 @@
       <c r="H58" s="2"/>
     </row>
     <row r="59" spans="1:8">
-      <c r="A59" s="20">
-        <v>12264</v>
-      </c>
-      <c r="B59" s="20" t="s">
+      <c r="A59" s="19">
+        <v>12262</v>
+      </c>
+      <c r="B59" s="19" t="s">
         <v>171</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" s="2">
-        <v>1</v>
-      </c>
-      <c r="E59" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="E59" s="14" t="s">
         <v>172</v>
       </c>
       <c r="F59" s="2"/>
@@ -3282,17 +3282,17 @@
       <c r="H59" s="2"/>
     </row>
     <row r="60" spans="1:8">
-      <c r="A60" s="20">
-        <v>12265</v>
-      </c>
-      <c r="B60" s="20" t="s">
+      <c r="A60" s="19">
+        <v>12263</v>
+      </c>
+      <c r="B60" s="19" t="s">
         <v>173</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" s="2">
         <v>1</v>
       </c>
-      <c r="E60" s="15" t="s">
+      <c r="E60" s="14" t="s">
         <v>174</v>
       </c>
       <c r="F60" s="2"/>
@@ -3300,17 +3300,17 @@
       <c r="H60" s="2"/>
     </row>
     <row r="61" spans="1:8">
-      <c r="A61" s="20">
-        <v>12266</v>
-      </c>
-      <c r="B61" s="20" t="s">
+      <c r="A61" s="19">
+        <v>12264</v>
+      </c>
+      <c r="B61" s="19" t="s">
         <v>175</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" s="2">
         <v>1</v>
       </c>
-      <c r="E61" s="15" t="s">
+      <c r="E61" s="14" t="s">
         <v>176</v>
       </c>
       <c r="F61" s="2"/>
@@ -3318,17 +3318,17 @@
       <c r="H61" s="2"/>
     </row>
     <row r="62" spans="1:8">
-      <c r="A62" s="20">
-        <v>12267</v>
-      </c>
-      <c r="B62" s="20" t="s">
+      <c r="A62" s="19">
+        <v>12265</v>
+      </c>
+      <c r="B62" s="19" t="s">
         <v>177</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" s="2">
-        <v>2</v>
-      </c>
-      <c r="E62" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="E62" s="14" t="s">
         <v>178</v>
       </c>
       <c r="F62" s="2"/>
@@ -3336,156 +3336,164 @@
       <c r="H62" s="2"/>
     </row>
     <row r="63" spans="1:8">
-      <c r="A63" s="20">
-        <v>12268</v>
-      </c>
-      <c r="B63" s="20" t="s">
+      <c r="A63" s="19">
+        <v>12266</v>
+      </c>
+      <c r="B63" s="19" t="s">
         <v>179</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" s="2">
-        <v>2</v>
-      </c>
-      <c r="E63" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="E63" s="14" t="s">
         <v>180</v>
       </c>
       <c r="F63" s="2"/>
       <c r="G63" s="2"/>
       <c r="H63" s="2"/>
     </row>
-    <row r="64" s="5" customFormat="1" spans="1:8">
-      <c r="A64" s="21">
+    <row r="64" spans="1:8">
+      <c r="A64" s="19">
+        <v>12267</v>
+      </c>
+      <c r="B64" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" s="2">
+        <v>2</v>
+      </c>
+      <c r="E64" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="F64" s="2"/>
+      <c r="G64" s="2"/>
+      <c r="H64" s="2"/>
+    </row>
+    <row r="65" spans="1:8">
+      <c r="A65" s="19">
+        <v>12268</v>
+      </c>
+      <c r="B65" s="19" t="s">
+        <v>183</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" s="2">
+        <v>2</v>
+      </c>
+      <c r="E65" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="F65" s="2"/>
+      <c r="G65" s="2"/>
+      <c r="H65" s="2"/>
+    </row>
+    <row r="66" s="4" customFormat="1" spans="1:8">
+      <c r="A66" s="19">
         <v>12269</v>
       </c>
-      <c r="B64" s="21" t="s">
-        <v>181</v>
-      </c>
-      <c r="C64" s="22"/>
-      <c r="D64" s="22">
-        <v>2</v>
-      </c>
-      <c r="E64" s="23" t="s">
-        <v>182</v>
-      </c>
-      <c r="F64" s="22"/>
-      <c r="G64" s="22"/>
-      <c r="H64" s="22"/>
-    </row>
-    <row r="65" s="5" customFormat="1" spans="1:8">
-      <c r="A65" s="21">
+      <c r="B66" s="19" t="s">
+        <v>185</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" s="2">
+        <v>2</v>
+      </c>
+      <c r="E66" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="F66" s="2"/>
+      <c r="G66" s="2"/>
+      <c r="H66" s="2"/>
+    </row>
+    <row r="67" s="4" customFormat="1" spans="1:8">
+      <c r="A67" s="19">
         <v>12270</v>
       </c>
-      <c r="B65" s="21" t="s">
-        <v>183</v>
-      </c>
-      <c r="C65" s="22"/>
-      <c r="D65" s="22">
+      <c r="B67" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" s="2">
         <v>1</v>
       </c>
-      <c r="E65" s="23" t="s">
-        <v>184</v>
-      </c>
-      <c r="F65" s="22"/>
-      <c r="G65" s="22"/>
-      <c r="H65" s="22"/>
-    </row>
-    <row r="66" s="5" customFormat="1" spans="1:8">
-      <c r="A66" s="21">
+      <c r="E67" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="F67" s="2"/>
+      <c r="G67" s="2"/>
+      <c r="H67" s="2"/>
+    </row>
+    <row r="68" s="4" customFormat="1" spans="1:8">
+      <c r="A68" s="19">
         <v>12271</v>
       </c>
-      <c r="B66" s="21" t="s">
-        <v>185</v>
-      </c>
-      <c r="C66" s="22"/>
-      <c r="D66" s="22">
+      <c r="B68" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" s="2">
         <v>1</v>
       </c>
-      <c r="E66" s="23" t="s">
-        <v>186</v>
-      </c>
-      <c r="F66" s="22"/>
-      <c r="G66" s="22"/>
-      <c r="H66" s="22"/>
-    </row>
-    <row r="67" s="5" customFormat="1" spans="1:8">
-      <c r="A67" s="21">
+      <c r="E68" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="F68" s="2"/>
+      <c r="G68" s="2"/>
+      <c r="H68" s="2"/>
+    </row>
+    <row r="69" s="4" customFormat="1" spans="1:8">
+      <c r="A69" s="19">
         <v>12272</v>
       </c>
-      <c r="B67" s="21" t="s">
-        <v>187</v>
-      </c>
-      <c r="C67" s="22"/>
-      <c r="D67" s="22">
-        <v>2</v>
-      </c>
-      <c r="E67" s="23" t="s">
-        <v>188</v>
-      </c>
-      <c r="F67" s="22"/>
-      <c r="G67" s="22"/>
-      <c r="H67" s="22"/>
-    </row>
-    <row r="68" spans="1:8">
-      <c r="A68" s="24">
+      <c r="B69" s="19" t="s">
+        <v>191</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" s="2">
+        <v>2</v>
+      </c>
+      <c r="E69" s="14" t="s">
+        <v>192</v>
+      </c>
+      <c r="F69" s="2"/>
+      <c r="G69" s="2"/>
+      <c r="H69" s="2"/>
+    </row>
+    <row r="70" spans="1:8">
+      <c r="A70" s="20">
         <v>12301</v>
       </c>
-      <c r="B68" s="24" t="s">
-        <v>189</v>
-      </c>
-      <c r="D68" s="4">
+      <c r="B70" s="20" t="s">
+        <v>193</v>
+      </c>
+      <c r="D70" s="4">
         <v>4</v>
-      </c>
-      <c r="E68" s="4" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="69" s="6" customFormat="1" spans="1:8">
-      <c r="A69" s="25">
-        <v>12302</v>
-      </c>
-      <c r="B69" s="25" t="s">
-        <v>191</v>
-      </c>
-      <c r="D69" s="6">
-        <v>3</v>
-      </c>
-      <c r="E69" s="6" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8">
-      <c r="A70" s="24">
-        <v>12303</v>
-      </c>
-      <c r="B70" s="24" t="s">
-        <v>193</v>
-      </c>
-      <c r="D70" s="4">
-        <v>2</v>
       </c>
       <c r="E70" s="4" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="71" spans="1:8">
-      <c r="A71" s="25">
-        <v>12304</v>
-      </c>
-      <c r="B71" s="24" t="s">
+    <row r="71" s="5" customFormat="1" spans="1:8">
+      <c r="A71" s="21">
+        <v>12302</v>
+      </c>
+      <c r="B71" s="21" t="s">
         <v>195</v>
       </c>
-      <c r="D71" s="4">
-        <v>2</v>
-      </c>
-      <c r="E71" s="4" t="s">
+      <c r="D71" s="5">
+        <v>3</v>
+      </c>
+      <c r="E71" s="5" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="72" spans="1:8">
-      <c r="A72" s="24">
-        <v>12305</v>
-      </c>
-      <c r="B72" s="24" t="s">
+      <c r="A72" s="20">
+        <v>12303</v>
+      </c>
+      <c r="B72" s="20" t="s">
         <v>197</v>
       </c>
       <c r="D72" s="4">
@@ -3495,67 +3503,67 @@
         <v>198</v>
       </c>
     </row>
-    <row r="73" s="6" customFormat="1" spans="1:8">
-      <c r="A73" s="25">
+    <row r="73" spans="1:8">
+      <c r="A73" s="21">
+        <v>12304</v>
+      </c>
+      <c r="B73" s="20" t="s">
+        <v>199</v>
+      </c>
+      <c r="D73" s="4">
+        <v>2</v>
+      </c>
+      <c r="E73" s="4" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8">
+      <c r="A74" s="20">
+        <v>12305</v>
+      </c>
+      <c r="B74" s="20" t="s">
+        <v>201</v>
+      </c>
+      <c r="D74" s="4">
+        <v>2</v>
+      </c>
+      <c r="E74" s="4" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="75" s="5" customFormat="1" spans="1:8">
+      <c r="A75" s="21">
         <v>12306</v>
       </c>
-      <c r="B73" s="25" t="s">
-        <v>199</v>
-      </c>
-      <c r="D73" s="6">
+      <c r="B75" s="21" t="s">
+        <v>203</v>
+      </c>
+      <c r="D75" s="5">
         <v>4</v>
       </c>
-      <c r="E73" s="6" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="74" s="6" customFormat="1" spans="1:8">
-      <c r="A74" s="24">
+      <c r="E75" s="5" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="76" s="5" customFormat="1" spans="1:8">
+      <c r="A76" s="20">
         <v>12307</v>
       </c>
-      <c r="B74" s="25" t="s">
-        <v>201</v>
-      </c>
-      <c r="D74" s="6">
-        <v>2</v>
-      </c>
-      <c r="E74" s="6" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8">
-      <c r="A75" s="26">
+      <c r="B76" s="21" t="s">
+        <v>205</v>
+      </c>
+      <c r="D76" s="5">
+        <v>2</v>
+      </c>
+      <c r="E76" s="5" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8">
+      <c r="A77" s="22">
         <v>12501</v>
       </c>
-      <c r="B75" s="26" t="s">
-        <v>203</v>
-      </c>
-      <c r="D75" s="4">
-        <v>4</v>
-      </c>
-      <c r="E75" s="4" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8">
-      <c r="A76" s="26">
-        <v>12502</v>
-      </c>
-      <c r="B76" s="26" t="s">
-        <v>205</v>
-      </c>
-      <c r="D76" s="4">
-        <v>3</v>
-      </c>
-      <c r="E76" s="4" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8">
-      <c r="A77" s="26">
-        <v>12503</v>
-      </c>
-      <c r="B77" s="26" t="s">
+      <c r="B77" s="22" t="s">
         <v>207</v>
       </c>
       <c r="D77" s="4">
@@ -3566,10 +3574,10 @@
       </c>
     </row>
     <row r="78" spans="1:8">
-      <c r="A78" s="26">
-        <v>12504</v>
-      </c>
-      <c r="B78" s="26" t="s">
+      <c r="A78" s="22">
+        <v>12502</v>
+      </c>
+      <c r="B78" s="22" t="s">
         <v>209</v>
       </c>
       <c r="D78" s="4">
@@ -3580,28 +3588,28 @@
       </c>
     </row>
     <row r="79" spans="1:8">
-      <c r="A79" s="4">
-        <v>12601</v>
-      </c>
-      <c r="B79" s="4" t="s">
+      <c r="A79" s="22">
+        <v>12503</v>
+      </c>
+      <c r="B79" s="22" t="s">
         <v>211</v>
       </c>
       <c r="D79" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E79" s="4" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="80" spans="1:8">
-      <c r="A80" s="4">
-        <v>12602</v>
-      </c>
-      <c r="B80" s="26" t="s">
+      <c r="A80" s="22">
+        <v>12504</v>
+      </c>
+      <c r="B80" s="22" t="s">
         <v>213</v>
       </c>
       <c r="D80" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E80" s="4" t="s">
         <v>214</v>
@@ -3609,13 +3617,13 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="4">
-        <v>12603</v>
+        <v>12601</v>
       </c>
       <c r="B81" s="4" t="s">
         <v>215</v>
       </c>
       <c r="D81" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E81" s="4" t="s">
         <v>216</v>
@@ -3623,13 +3631,13 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="4">
-        <v>12604</v>
-      </c>
-      <c r="B82" s="4" t="s">
+        <v>12602</v>
+      </c>
+      <c r="B82" s="22" t="s">
         <v>217</v>
       </c>
       <c r="D82" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E82" s="4" t="s">
         <v>218</v>
@@ -3637,7 +3645,7 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="4">
-        <v>12605</v>
+        <v>12603</v>
       </c>
       <c r="B83" s="4" t="s">
         <v>219</v>
@@ -3651,7 +3659,7 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="4">
-        <v>12606</v>
+        <v>12604</v>
       </c>
       <c r="B84" s="4" t="s">
         <v>221</v>
@@ -3665,13 +3673,13 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="4">
-        <v>12607</v>
+        <v>12605</v>
       </c>
       <c r="B85" s="4" t="s">
         <v>223</v>
       </c>
       <c r="D85" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E85" s="4" t="s">
         <v>224</v>
@@ -3679,13 +3687,13 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="4">
-        <v>12608</v>
+        <v>12606</v>
       </c>
       <c r="B86" s="4" t="s">
         <v>225</v>
       </c>
       <c r="D86" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E86" s="4" t="s">
         <v>226</v>
@@ -3693,13 +3701,13 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="4">
-        <v>12609</v>
+        <v>12607</v>
       </c>
       <c r="B87" s="4" t="s">
         <v>227</v>
       </c>
       <c r="D87" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E87" s="4" t="s">
         <v>228</v>
@@ -3707,13 +3715,13 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="4">
-        <v>12610</v>
+        <v>12608</v>
       </c>
       <c r="B88" s="4" t="s">
         <v>229</v>
       </c>
       <c r="D88" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E88" s="4" t="s">
         <v>230</v>
@@ -3721,13 +3729,13 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="4">
-        <v>12701</v>
+        <v>12609</v>
       </c>
       <c r="B89" s="4" t="s">
         <v>231</v>
       </c>
       <c r="D89" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E89" s="4" t="s">
         <v>232</v>
@@ -3735,13 +3743,13 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="4">
-        <v>12702</v>
+        <v>12610</v>
       </c>
       <c r="B90" s="4" t="s">
         <v>233</v>
       </c>
       <c r="D90" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E90" s="4" t="s">
         <v>234</v>
@@ -3749,13 +3757,13 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="4">
-        <v>12703</v>
+        <v>12701</v>
       </c>
       <c r="B91" s="4" t="s">
         <v>235</v>
       </c>
       <c r="D91" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E91" s="4" t="s">
         <v>236</v>
@@ -3763,16 +3771,44 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="4">
-        <v>12704</v>
+        <v>12702</v>
       </c>
       <c r="B92" s="4" t="s">
         <v>237</v>
       </c>
       <c r="D92" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E92" s="4" t="s">
         <v>238</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5">
+      <c r="A93" s="4">
+        <v>12703</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="D93" s="4">
+        <v>3</v>
+      </c>
+      <c r="E93" s="4" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5">
+      <c r="A94" s="4">
+        <v>12704</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="D94" s="4">
+        <v>3</v>
+      </c>
+      <c r="E94" s="4" t="s">
+        <v>242</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/condition.xlsx
+++ b/hall/resources/sample/condition.xlsx
@@ -115,7 +115,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E50" authorId="0">
+    <comment ref="E51" authorId="0">
       <text>
         <r>
           <rPr>
@@ -143,7 +143,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E51" authorId="0">
+    <comment ref="E52" authorId="0">
       <text>
         <r>
           <rPr>
@@ -174,7 +174,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="245">
   <si>
     <t>id</t>
   </si>
@@ -627,6 +627,12 @@
   </si>
   <si>
     <t>12223_次数(开始游戏并结算)</t>
+  </si>
+  <si>
+    <t>接邓：完成N次成就任务</t>
+  </si>
+  <si>
+    <t>12224_次数(领取奖励)</t>
   </si>
   <si>
     <t>累积：在SLOT游戏中获得N个X道具</t>
@@ -2000,7 +2006,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O94"/>
+  <dimension ref="A1:O95"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="4"/>
@@ -3084,15 +3090,15 @@
       <c r="H48" s="2"/>
     </row>
     <row r="49" spans="1:8">
-      <c r="A49" s="19">
-        <v>12251</v>
-      </c>
-      <c r="B49" s="19" t="s">
+      <c r="A49" s="18">
+        <v>12224</v>
+      </c>
+      <c r="B49" s="18" t="s">
         <v>151</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E49" s="14" t="s">
         <v>152</v>
@@ -3103,14 +3109,14 @@
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="19">
-        <v>12252</v>
+        <v>12251</v>
       </c>
       <c r="B50" s="19" t="s">
         <v>153</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E50" s="14" t="s">
         <v>154</v>
@@ -3121,7 +3127,7 @@
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="19">
-        <v>12253</v>
+        <v>12252</v>
       </c>
       <c r="B51" s="19" t="s">
         <v>155</v>
@@ -3139,14 +3145,14 @@
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="19">
-        <v>12254</v>
+        <v>12253</v>
       </c>
       <c r="B52" s="19" t="s">
         <v>157</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E52" s="14" t="s">
         <v>158</v>
@@ -3157,14 +3163,14 @@
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="19">
-        <v>12255</v>
+        <v>12254</v>
       </c>
       <c r="B53" s="19" t="s">
         <v>159</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E53" s="14" t="s">
         <v>160</v>
@@ -3175,7 +3181,7 @@
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="19">
-        <v>12256</v>
+        <v>12255</v>
       </c>
       <c r="B54" s="19" t="s">
         <v>161</v>
@@ -3193,14 +3199,14 @@
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="19">
-        <v>12257</v>
+        <v>12256</v>
       </c>
       <c r="B55" s="19" t="s">
         <v>163</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E55" s="14" t="s">
         <v>164</v>
@@ -3211,14 +3217,14 @@
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="19">
-        <v>12259</v>
+        <v>12257</v>
       </c>
       <c r="B56" s="19" t="s">
         <v>165</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E56" s="14" t="s">
         <v>166</v>
@@ -3229,14 +3235,14 @@
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="19">
-        <v>12260</v>
+        <v>12259</v>
       </c>
       <c r="B57" s="19" t="s">
         <v>167</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E57" s="14" t="s">
         <v>168</v>
@@ -3247,7 +3253,7 @@
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="19">
-        <v>12261</v>
+        <v>12260</v>
       </c>
       <c r="B58" s="19" t="s">
         <v>169</v>
@@ -3265,7 +3271,7 @@
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="19">
-        <v>12262</v>
+        <v>12261</v>
       </c>
       <c r="B59" s="19" t="s">
         <v>171</v>
@@ -3283,14 +3289,14 @@
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="19">
-        <v>12263</v>
+        <v>12262</v>
       </c>
       <c r="B60" s="19" t="s">
         <v>173</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E60" s="14" t="s">
         <v>174</v>
@@ -3301,7 +3307,7 @@
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="19">
-        <v>12264</v>
+        <v>12263</v>
       </c>
       <c r="B61" s="19" t="s">
         <v>175</v>
@@ -3319,7 +3325,7 @@
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="19">
-        <v>12265</v>
+        <v>12264</v>
       </c>
       <c r="B62" s="19" t="s">
         <v>177</v>
@@ -3337,7 +3343,7 @@
     </row>
     <row r="63" spans="1:8">
       <c r="A63" s="19">
-        <v>12266</v>
+        <v>12265</v>
       </c>
       <c r="B63" s="19" t="s">
         <v>179</v>
@@ -3355,14 +3361,14 @@
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="19">
-        <v>12267</v>
+        <v>12266</v>
       </c>
       <c r="B64" s="19" t="s">
         <v>181</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E64" s="14" t="s">
         <v>182</v>
@@ -3373,7 +3379,7 @@
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="19">
-        <v>12268</v>
+        <v>12267</v>
       </c>
       <c r="B65" s="19" t="s">
         <v>183</v>
@@ -3389,9 +3395,9 @@
       <c r="G65" s="2"/>
       <c r="H65" s="2"/>
     </row>
-    <row r="66" s="4" customFormat="1" spans="1:8">
+    <row r="66" spans="1:8">
       <c r="A66" s="19">
-        <v>12269</v>
+        <v>12268</v>
       </c>
       <c r="B66" s="19" t="s">
         <v>185</v>
@@ -3409,14 +3415,14 @@
     </row>
     <row r="67" s="4" customFormat="1" spans="1:8">
       <c r="A67" s="19">
-        <v>12270</v>
+        <v>12269</v>
       </c>
       <c r="B67" s="19" t="s">
         <v>187</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E67" s="14" t="s">
         <v>188</v>
@@ -3427,7 +3433,7 @@
     </row>
     <row r="68" s="4" customFormat="1" spans="1:8">
       <c r="A68" s="19">
-        <v>12271</v>
+        <v>12270</v>
       </c>
       <c r="B68" s="19" t="s">
         <v>189</v>
@@ -3445,14 +3451,14 @@
     </row>
     <row r="69" s="4" customFormat="1" spans="1:8">
       <c r="A69" s="19">
-        <v>12272</v>
+        <v>12271</v>
       </c>
       <c r="B69" s="19" t="s">
         <v>191</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E69" s="14" t="s">
         <v>192</v>
@@ -3461,51 +3467,55 @@
       <c r="G69" s="2"/>
       <c r="H69" s="2"/>
     </row>
-    <row r="70" spans="1:8">
-      <c r="A70" s="20">
+    <row r="70" s="4" customFormat="1" spans="1:8">
+      <c r="A70" s="19">
+        <v>12272</v>
+      </c>
+      <c r="B70" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" s="2">
+        <v>2</v>
+      </c>
+      <c r="E70" s="14" t="s">
+        <v>194</v>
+      </c>
+      <c r="F70" s="2"/>
+      <c r="G70" s="2"/>
+      <c r="H70" s="2"/>
+    </row>
+    <row r="71" spans="1:8">
+      <c r="A71" s="20">
         <v>12301</v>
       </c>
-      <c r="B70" s="20" t="s">
-        <v>193</v>
-      </c>
-      <c r="D70" s="4">
+      <c r="B71" s="20" t="s">
+        <v>195</v>
+      </c>
+      <c r="D71" s="4">
         <v>4</v>
       </c>
-      <c r="E70" s="4" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="71" s="5" customFormat="1" spans="1:8">
-      <c r="A71" s="21">
+      <c r="E71" s="4" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="72" s="5" customFormat="1" spans="1:8">
+      <c r="A72" s="21">
         <v>12302</v>
       </c>
-      <c r="B71" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="D71" s="5">
+      <c r="B72" s="21" t="s">
+        <v>197</v>
+      </c>
+      <c r="D72" s="5">
         <v>3</v>
       </c>
-      <c r="E71" s="5" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8">
-      <c r="A72" s="20">
+      <c r="E72" s="5" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8">
+      <c r="A73" s="20">
         <v>12303</v>
-      </c>
-      <c r="B72" s="20" t="s">
-        <v>197</v>
-      </c>
-      <c r="D72" s="4">
-        <v>2</v>
-      </c>
-      <c r="E72" s="4" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8">
-      <c r="A73" s="21">
-        <v>12304</v>
       </c>
       <c r="B73" s="20" t="s">
         <v>199</v>
@@ -3518,8 +3528,8 @@
       </c>
     </row>
     <row r="74" spans="1:8">
-      <c r="A74" s="20">
-        <v>12305</v>
+      <c r="A74" s="21">
+        <v>12304</v>
       </c>
       <c r="B74" s="20" t="s">
         <v>201</v>
@@ -3531,57 +3541,57 @@
         <v>202</v>
       </c>
     </row>
-    <row r="75" s="5" customFormat="1" spans="1:8">
-      <c r="A75" s="21">
+    <row r="75" spans="1:8">
+      <c r="A75" s="20">
+        <v>12305</v>
+      </c>
+      <c r="B75" s="20" t="s">
+        <v>203</v>
+      </c>
+      <c r="D75" s="4">
+        <v>2</v>
+      </c>
+      <c r="E75" s="4" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="76" s="5" customFormat="1" spans="1:8">
+      <c r="A76" s="21">
         <v>12306</v>
-      </c>
-      <c r="B75" s="21" t="s">
-        <v>203</v>
-      </c>
-      <c r="D75" s="5">
-        <v>4</v>
-      </c>
-      <c r="E75" s="5" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="76" s="5" customFormat="1" spans="1:8">
-      <c r="A76" s="20">
-        <v>12307</v>
       </c>
       <c r="B76" s="21" t="s">
         <v>205</v>
       </c>
       <c r="D76" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E76" s="5" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="77" spans="1:8">
-      <c r="A77" s="22">
-        <v>12501</v>
-      </c>
-      <c r="B77" s="22" t="s">
+    <row r="77" s="5" customFormat="1" spans="1:8">
+      <c r="A77" s="20">
+        <v>12307</v>
+      </c>
+      <c r="B77" s="21" t="s">
         <v>207</v>
       </c>
-      <c r="D77" s="4">
-        <v>4</v>
-      </c>
-      <c r="E77" s="4" t="s">
+      <c r="D77" s="5">
+        <v>2</v>
+      </c>
+      <c r="E77" s="5" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="78" spans="1:8">
       <c r="A78" s="22">
-        <v>12502</v>
+        <v>12501</v>
       </c>
       <c r="B78" s="22" t="s">
         <v>209</v>
       </c>
       <c r="D78" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E78" s="4" t="s">
         <v>210</v>
@@ -3589,13 +3599,13 @@
     </row>
     <row r="79" spans="1:8">
       <c r="A79" s="22">
-        <v>12503</v>
+        <v>12502</v>
       </c>
       <c r="B79" s="22" t="s">
         <v>211</v>
       </c>
       <c r="D79" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E79" s="4" t="s">
         <v>212</v>
@@ -3603,23 +3613,23 @@
     </row>
     <row r="80" spans="1:8">
       <c r="A80" s="22">
-        <v>12504</v>
+        <v>12503</v>
       </c>
       <c r="B80" s="22" t="s">
         <v>213</v>
       </c>
       <c r="D80" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E80" s="4" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="81" spans="1:5">
-      <c r="A81" s="4">
-        <v>12601</v>
-      </c>
-      <c r="B81" s="4" t="s">
+      <c r="A81" s="22">
+        <v>12504</v>
+      </c>
+      <c r="B81" s="22" t="s">
         <v>215</v>
       </c>
       <c r="D81" s="4">
@@ -3631,13 +3641,13 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="4">
-        <v>12602</v>
-      </c>
-      <c r="B82" s="22" t="s">
+        <v>12601</v>
+      </c>
+      <c r="B82" s="4" t="s">
         <v>217</v>
       </c>
       <c r="D82" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E82" s="4" t="s">
         <v>218</v>
@@ -3645,9 +3655,9 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="4">
-        <v>12603</v>
-      </c>
-      <c r="B83" s="4" t="s">
+        <v>12602</v>
+      </c>
+      <c r="B83" s="22" t="s">
         <v>219</v>
       </c>
       <c r="D83" s="4">
@@ -3659,13 +3669,13 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="4">
-        <v>12604</v>
+        <v>12603</v>
       </c>
       <c r="B84" s="4" t="s">
         <v>221</v>
       </c>
       <c r="D84" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E84" s="4" t="s">
         <v>222</v>
@@ -3673,13 +3683,13 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="4">
-        <v>12605</v>
+        <v>12604</v>
       </c>
       <c r="B85" s="4" t="s">
         <v>223</v>
       </c>
       <c r="D85" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E85" s="4" t="s">
         <v>224</v>
@@ -3687,13 +3697,13 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="4">
-        <v>12606</v>
+        <v>12605</v>
       </c>
       <c r="B86" s="4" t="s">
         <v>225</v>
       </c>
       <c r="D86" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E86" s="4" t="s">
         <v>226</v>
@@ -3701,13 +3711,13 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="4">
-        <v>12607</v>
+        <v>12606</v>
       </c>
       <c r="B87" s="4" t="s">
         <v>227</v>
       </c>
       <c r="D87" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E87" s="4" t="s">
         <v>228</v>
@@ -3715,7 +3725,7 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="4">
-        <v>12608</v>
+        <v>12607</v>
       </c>
       <c r="B88" s="4" t="s">
         <v>229</v>
@@ -3729,13 +3739,13 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="4">
-        <v>12609</v>
+        <v>12608</v>
       </c>
       <c r="B89" s="4" t="s">
         <v>231</v>
       </c>
       <c r="D89" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E89" s="4" t="s">
         <v>232</v>
@@ -3743,7 +3753,7 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="4">
-        <v>12610</v>
+        <v>12609</v>
       </c>
       <c r="B90" s="4" t="s">
         <v>233</v>
@@ -3757,13 +3767,13 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="4">
-        <v>12701</v>
+        <v>12610</v>
       </c>
       <c r="B91" s="4" t="s">
         <v>235</v>
       </c>
       <c r="D91" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E91" s="4" t="s">
         <v>236</v>
@@ -3771,7 +3781,7 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="4">
-        <v>12702</v>
+        <v>12701</v>
       </c>
       <c r="B92" s="4" t="s">
         <v>237</v>
@@ -3785,13 +3795,13 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="4">
-        <v>12703</v>
+        <v>12702</v>
       </c>
       <c r="B93" s="4" t="s">
         <v>239</v>
       </c>
       <c r="D93" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E93" s="4" t="s">
         <v>240</v>
@@ -3799,7 +3809,7 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="4">
-        <v>12704</v>
+        <v>12703</v>
       </c>
       <c r="B94" s="4" t="s">
         <v>241</v>
@@ -3809,6 +3819,20 @@
       </c>
       <c r="E94" s="4" t="s">
         <v>242</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5">
+      <c r="A95" s="4">
+        <v>12704</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="D95" s="4">
+        <v>3</v>
+      </c>
+      <c r="E95" s="4" t="s">
+        <v>244</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/condition.xlsx
+++ b/hall/resources/sample/condition.xlsx
@@ -174,7 +174,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="247">
   <si>
     <t>id</t>
   </si>
@@ -629,7 +629,7 @@
     <t>12223_次数(开始游戏并结算)</t>
   </si>
   <si>
-    <t>接邓：完成N次成就任务</t>
+    <t>接取：完成N次成就任务</t>
   </si>
   <si>
     <t>12224_次数(领取奖励)</t>
@@ -759,6 +759,12 @@
   </si>
   <si>
     <t>12272_游戏ID(0)_数量(计算金币投注)</t>
+  </si>
+  <si>
+    <t>累积：解锁指定建筑</t>
+  </si>
+  <si>
+    <t>12273_场景ID_建筑ID</t>
   </si>
   <si>
     <t>游戏中奖倍数</t>
@@ -2006,7 +2012,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O95"/>
+  <dimension ref="A1:O96"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="4"/>
@@ -3485,51 +3491,55 @@
       <c r="G70" s="2"/>
       <c r="H70" s="2"/>
     </row>
-    <row r="71" spans="1:8">
-      <c r="A71" s="20">
+    <row r="71" s="4" customFormat="1" spans="1:8">
+      <c r="A71" s="19">
+        <v>12273</v>
+      </c>
+      <c r="B71" s="19" t="s">
+        <v>195</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" s="2">
+        <v>2</v>
+      </c>
+      <c r="E71" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="F71" s="2"/>
+      <c r="G71" s="2"/>
+      <c r="H71" s="2"/>
+    </row>
+    <row r="72" spans="1:8">
+      <c r="A72" s="20">
         <v>12301</v>
       </c>
-      <c r="B71" s="20" t="s">
-        <v>195</v>
-      </c>
-      <c r="D71" s="4">
+      <c r="B72" s="20" t="s">
+        <v>197</v>
+      </c>
+      <c r="D72" s="4">
         <v>4</v>
       </c>
-      <c r="E71" s="4" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="72" s="5" customFormat="1" spans="1:8">
-      <c r="A72" s="21">
+      <c r="E72" s="4" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="73" s="5" customFormat="1" spans="1:8">
+      <c r="A73" s="21">
         <v>12302</v>
       </c>
-      <c r="B72" s="21" t="s">
-        <v>197</v>
-      </c>
-      <c r="D72" s="5">
+      <c r="B73" s="21" t="s">
+        <v>199</v>
+      </c>
+      <c r="D73" s="5">
         <v>3</v>
       </c>
-      <c r="E72" s="5" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8">
-      <c r="A73" s="20">
+      <c r="E73" s="5" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8">
+      <c r="A74" s="20">
         <v>12303</v>
-      </c>
-      <c r="B73" s="20" t="s">
-        <v>199</v>
-      </c>
-      <c r="D73" s="4">
-        <v>2</v>
-      </c>
-      <c r="E73" s="4" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8">
-      <c r="A74" s="21">
-        <v>12304</v>
       </c>
       <c r="B74" s="20" t="s">
         <v>201</v>
@@ -3542,8 +3552,8 @@
       </c>
     </row>
     <row r="75" spans="1:8">
-      <c r="A75" s="20">
-        <v>12305</v>
+      <c r="A75" s="21">
+        <v>12304</v>
       </c>
       <c r="B75" s="20" t="s">
         <v>203</v>
@@ -3555,57 +3565,57 @@
         <v>204</v>
       </c>
     </row>
-    <row r="76" s="5" customFormat="1" spans="1:8">
-      <c r="A76" s="21">
+    <row r="76" spans="1:8">
+      <c r="A76" s="20">
+        <v>12305</v>
+      </c>
+      <c r="B76" s="20" t="s">
+        <v>205</v>
+      </c>
+      <c r="D76" s="4">
+        <v>2</v>
+      </c>
+      <c r="E76" s="4" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="77" s="5" customFormat="1" spans="1:8">
+      <c r="A77" s="21">
         <v>12306</v>
-      </c>
-      <c r="B76" s="21" t="s">
-        <v>205</v>
-      </c>
-      <c r="D76" s="5">
-        <v>4</v>
-      </c>
-      <c r="E76" s="5" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="77" s="5" customFormat="1" spans="1:8">
-      <c r="A77" s="20">
-        <v>12307</v>
       </c>
       <c r="B77" s="21" t="s">
         <v>207</v>
       </c>
       <c r="D77" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E77" s="5" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="78" spans="1:8">
-      <c r="A78" s="22">
-        <v>12501</v>
-      </c>
-      <c r="B78" s="22" t="s">
+    <row r="78" s="5" customFormat="1" spans="1:8">
+      <c r="A78" s="20">
+        <v>12307</v>
+      </c>
+      <c r="B78" s="21" t="s">
         <v>209</v>
       </c>
-      <c r="D78" s="4">
-        <v>4</v>
-      </c>
-      <c r="E78" s="4" t="s">
+      <c r="D78" s="5">
+        <v>2</v>
+      </c>
+      <c r="E78" s="5" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="79" spans="1:8">
       <c r="A79" s="22">
-        <v>12502</v>
+        <v>12501</v>
       </c>
       <c r="B79" s="22" t="s">
         <v>211</v>
       </c>
       <c r="D79" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E79" s="4" t="s">
         <v>212</v>
@@ -3613,13 +3623,13 @@
     </row>
     <row r="80" spans="1:8">
       <c r="A80" s="22">
-        <v>12503</v>
+        <v>12502</v>
       </c>
       <c r="B80" s="22" t="s">
         <v>213</v>
       </c>
       <c r="D80" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E80" s="4" t="s">
         <v>214</v>
@@ -3627,23 +3637,23 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="22">
-        <v>12504</v>
+        <v>12503</v>
       </c>
       <c r="B81" s="22" t="s">
         <v>215</v>
       </c>
       <c r="D81" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E81" s="4" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="82" spans="1:5">
-      <c r="A82" s="4">
-        <v>12601</v>
-      </c>
-      <c r="B82" s="4" t="s">
+      <c r="A82" s="22">
+        <v>12504</v>
+      </c>
+      <c r="B82" s="22" t="s">
         <v>217</v>
       </c>
       <c r="D82" s="4">
@@ -3655,13 +3665,13 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="4">
-        <v>12602</v>
-      </c>
-      <c r="B83" s="22" t="s">
+        <v>12601</v>
+      </c>
+      <c r="B83" s="4" t="s">
         <v>219</v>
       </c>
       <c r="D83" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E83" s="4" t="s">
         <v>220</v>
@@ -3669,9 +3679,9 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="4">
-        <v>12603</v>
-      </c>
-      <c r="B84" s="4" t="s">
+        <v>12602</v>
+      </c>
+      <c r="B84" s="22" t="s">
         <v>221</v>
       </c>
       <c r="D84" s="4">
@@ -3683,13 +3693,13 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="4">
-        <v>12604</v>
+        <v>12603</v>
       </c>
       <c r="B85" s="4" t="s">
         <v>223</v>
       </c>
       <c r="D85" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E85" s="4" t="s">
         <v>224</v>
@@ -3697,13 +3707,13 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="4">
-        <v>12605</v>
+        <v>12604</v>
       </c>
       <c r="B86" s="4" t="s">
         <v>225</v>
       </c>
       <c r="D86" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E86" s="4" t="s">
         <v>226</v>
@@ -3711,13 +3721,13 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="4">
-        <v>12606</v>
+        <v>12605</v>
       </c>
       <c r="B87" s="4" t="s">
         <v>227</v>
       </c>
       <c r="D87" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E87" s="4" t="s">
         <v>228</v>
@@ -3725,13 +3735,13 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="4">
-        <v>12607</v>
+        <v>12606</v>
       </c>
       <c r="B88" s="4" t="s">
         <v>229</v>
       </c>
       <c r="D88" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E88" s="4" t="s">
         <v>230</v>
@@ -3739,7 +3749,7 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="4">
-        <v>12608</v>
+        <v>12607</v>
       </c>
       <c r="B89" s="4" t="s">
         <v>231</v>
@@ -3753,13 +3763,13 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="4">
-        <v>12609</v>
+        <v>12608</v>
       </c>
       <c r="B90" s="4" t="s">
         <v>233</v>
       </c>
       <c r="D90" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E90" s="4" t="s">
         <v>234</v>
@@ -3767,7 +3777,7 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="4">
-        <v>12610</v>
+        <v>12609</v>
       </c>
       <c r="B91" s="4" t="s">
         <v>235</v>
@@ -3781,13 +3791,13 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="4">
-        <v>12701</v>
+        <v>12610</v>
       </c>
       <c r="B92" s="4" t="s">
         <v>237</v>
       </c>
       <c r="D92" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E92" s="4" t="s">
         <v>238</v>
@@ -3795,7 +3805,7 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="4">
-        <v>12702</v>
+        <v>12701</v>
       </c>
       <c r="B93" s="4" t="s">
         <v>239</v>
@@ -3809,13 +3819,13 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="4">
-        <v>12703</v>
+        <v>12702</v>
       </c>
       <c r="B94" s="4" t="s">
         <v>241</v>
       </c>
       <c r="D94" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E94" s="4" t="s">
         <v>242</v>
@@ -3823,7 +3833,7 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="4">
-        <v>12704</v>
+        <v>12703</v>
       </c>
       <c r="B95" s="4" t="s">
         <v>243</v>
@@ -3833,6 +3843,20 @@
       </c>
       <c r="E95" s="4" t="s">
         <v>244</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5">
+      <c r="A96" s="4">
+        <v>12704</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="D96" s="4">
+        <v>3</v>
+      </c>
+      <c r="E96" s="4" t="s">
+        <v>246</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/condition.xlsx
+++ b/hall/resources/sample/condition.xlsx
@@ -115,7 +115,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E51" authorId="0">
+    <comment ref="E52" authorId="0">
       <text>
         <r>
           <rPr>
@@ -143,7 +143,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E52" authorId="0">
+    <comment ref="E53" authorId="0">
       <text>
         <r>
           <rPr>
@@ -174,7 +174,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="249">
   <si>
     <t>id</t>
   </si>
@@ -614,7 +614,7 @@
     <t>接取：指定\任意SLOT游戏投注N次</t>
   </si>
   <si>
-    <t>12221_游戏ID(0)_数量(计算金币投注)</t>
+    <t>12221_游戏ID(0)_数量</t>
   </si>
   <si>
     <t>接取：生成指定游客N次</t>
@@ -633,6 +633,12 @@
   </si>
   <si>
     <t>12224_次数(领取奖励)</t>
+  </si>
+  <si>
+    <t>接取：指定\任意游戏赢钱</t>
+  </si>
+  <si>
+    <t>12225_游戏ID(0 = 任意游戏)（不区分倍场）_货币ID(金币或钻石)_赢钱数量(投注赢钱+各类模式赢钱，除 好友提供的加成外)</t>
   </si>
   <si>
     <t>累积：在SLOT游戏中获得N个X道具</t>
@@ -2012,11 +2018,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O96"/>
+  <dimension ref="A1:O97"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="4"/>
-    <col min="2" max="2" width="38.525" style="4" customWidth="1"/>
+    <col min="2" max="2" width="40.5833333333333" style="4" customWidth="1"/>
     <col min="3" max="3" width="19.625" style="4" customWidth="1"/>
     <col min="4" max="4" width="17.625" style="4" customWidth="1"/>
     <col min="5" max="5" width="102.375" style="4" customWidth="1"/>
@@ -3060,10 +3066,10 @@
       <c r="H46" s="2"/>
     </row>
     <row r="47" spans="1:8">
-      <c r="A47" s="18">
+      <c r="A47" s="13">
         <v>12222</v>
       </c>
-      <c r="B47" s="18" t="s">
+      <c r="B47" s="13" t="s">
         <v>147</v>
       </c>
       <c r="C47" s="2"/>
@@ -3078,10 +3084,10 @@
       <c r="H47" s="2"/>
     </row>
     <row r="48" spans="1:8">
-      <c r="A48" s="18">
+      <c r="A48" s="13">
         <v>12223</v>
       </c>
-      <c r="B48" s="18" t="s">
+      <c r="B48" s="13" t="s">
         <v>149</v>
       </c>
       <c r="C48" s="2"/>
@@ -3096,10 +3102,10 @@
       <c r="H48" s="2"/>
     </row>
     <row r="49" spans="1:8">
-      <c r="A49" s="18">
+      <c r="A49" s="13">
         <v>12224</v>
       </c>
-      <c r="B49" s="18" t="s">
+      <c r="B49" s="13" t="s">
         <v>151</v>
       </c>
       <c r="C49" s="2"/>
@@ -3114,10 +3120,10 @@
       <c r="H49" s="2"/>
     </row>
     <row r="50" spans="1:8">
-      <c r="A50" s="19">
-        <v>12251</v>
-      </c>
-      <c r="B50" s="19" t="s">
+      <c r="A50" s="18">
+        <v>12225</v>
+      </c>
+      <c r="B50" s="18" t="s">
         <v>153</v>
       </c>
       <c r="C50" s="2"/>
@@ -3133,14 +3139,14 @@
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="19">
-        <v>12252</v>
+        <v>12251</v>
       </c>
       <c r="B51" s="19" t="s">
         <v>155</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E51" s="14" t="s">
         <v>156</v>
@@ -3151,7 +3157,7 @@
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="19">
-        <v>12253</v>
+        <v>12252</v>
       </c>
       <c r="B52" s="19" t="s">
         <v>157</v>
@@ -3169,14 +3175,14 @@
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="19">
-        <v>12254</v>
+        <v>12253</v>
       </c>
       <c r="B53" s="19" t="s">
         <v>159</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E53" s="14" t="s">
         <v>160</v>
@@ -3187,14 +3193,14 @@
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="19">
-        <v>12255</v>
+        <v>12254</v>
       </c>
       <c r="B54" s="19" t="s">
         <v>161</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E54" s="14" t="s">
         <v>162</v>
@@ -3205,7 +3211,7 @@
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="19">
-        <v>12256</v>
+        <v>12255</v>
       </c>
       <c r="B55" s="19" t="s">
         <v>163</v>
@@ -3223,14 +3229,14 @@
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="19">
-        <v>12257</v>
+        <v>12256</v>
       </c>
       <c r="B56" s="19" t="s">
         <v>165</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E56" s="14" t="s">
         <v>166</v>
@@ -3241,14 +3247,14 @@
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="19">
-        <v>12259</v>
+        <v>12257</v>
       </c>
       <c r="B57" s="19" t="s">
         <v>167</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E57" s="14" t="s">
         <v>168</v>
@@ -3259,14 +3265,14 @@
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="19">
-        <v>12260</v>
+        <v>12259</v>
       </c>
       <c r="B58" s="19" t="s">
         <v>169</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E58" s="14" t="s">
         <v>170</v>
@@ -3277,7 +3283,7 @@
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="19">
-        <v>12261</v>
+        <v>12260</v>
       </c>
       <c r="B59" s="19" t="s">
         <v>171</v>
@@ -3295,7 +3301,7 @@
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="19">
-        <v>12262</v>
+        <v>12261</v>
       </c>
       <c r="B60" s="19" t="s">
         <v>173</v>
@@ -3313,14 +3319,14 @@
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="19">
-        <v>12263</v>
+        <v>12262</v>
       </c>
       <c r="B61" s="19" t="s">
         <v>175</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E61" s="14" t="s">
         <v>176</v>
@@ -3331,7 +3337,7 @@
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="19">
-        <v>12264</v>
+        <v>12263</v>
       </c>
       <c r="B62" s="19" t="s">
         <v>177</v>
@@ -3349,7 +3355,7 @@
     </row>
     <row r="63" spans="1:8">
       <c r="A63" s="19">
-        <v>12265</v>
+        <v>12264</v>
       </c>
       <c r="B63" s="19" t="s">
         <v>179</v>
@@ -3367,7 +3373,7 @@
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="19">
-        <v>12266</v>
+        <v>12265</v>
       </c>
       <c r="B64" s="19" t="s">
         <v>181</v>
@@ -3385,14 +3391,14 @@
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="19">
-        <v>12267</v>
+        <v>12266</v>
       </c>
       <c r="B65" s="19" t="s">
         <v>183</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E65" s="14" t="s">
         <v>184</v>
@@ -3403,7 +3409,7 @@
     </row>
     <row r="66" spans="1:8">
       <c r="A66" s="19">
-        <v>12268</v>
+        <v>12267</v>
       </c>
       <c r="B66" s="19" t="s">
         <v>185</v>
@@ -3419,9 +3425,9 @@
       <c r="G66" s="2"/>
       <c r="H66" s="2"/>
     </row>
-    <row r="67" s="4" customFormat="1" spans="1:8">
+    <row r="67" spans="1:8">
       <c r="A67" s="19">
-        <v>12269</v>
+        <v>12268</v>
       </c>
       <c r="B67" s="19" t="s">
         <v>187</v>
@@ -3439,14 +3445,14 @@
     </row>
     <row r="68" s="4" customFormat="1" spans="1:8">
       <c r="A68" s="19">
-        <v>12270</v>
+        <v>12269</v>
       </c>
       <c r="B68" s="19" t="s">
         <v>189</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E68" s="14" t="s">
         <v>190</v>
@@ -3457,7 +3463,7 @@
     </row>
     <row r="69" s="4" customFormat="1" spans="1:8">
       <c r="A69" s="19">
-        <v>12271</v>
+        <v>12270</v>
       </c>
       <c r="B69" s="19" t="s">
         <v>191</v>
@@ -3475,14 +3481,14 @@
     </row>
     <row r="70" s="4" customFormat="1" spans="1:8">
       <c r="A70" s="19">
-        <v>12272</v>
+        <v>12271</v>
       </c>
       <c r="B70" s="19" t="s">
         <v>193</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E70" s="14" t="s">
         <v>194</v>
@@ -3493,7 +3499,7 @@
     </row>
     <row r="71" s="4" customFormat="1" spans="1:8">
       <c r="A71" s="19">
-        <v>12273</v>
+        <v>12272</v>
       </c>
       <c r="B71" s="19" t="s">
         <v>195</v>
@@ -3509,51 +3515,55 @@
       <c r="G71" s="2"/>
       <c r="H71" s="2"/>
     </row>
-    <row r="72" spans="1:8">
-      <c r="A72" s="20">
+    <row r="72" s="4" customFormat="1" spans="1:8">
+      <c r="A72" s="19">
+        <v>12273</v>
+      </c>
+      <c r="B72" s="19" t="s">
+        <v>197</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" s="2">
+        <v>2</v>
+      </c>
+      <c r="E72" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="F72" s="2"/>
+      <c r="G72" s="2"/>
+      <c r="H72" s="2"/>
+    </row>
+    <row r="73" spans="1:8">
+      <c r="A73" s="20">
         <v>12301</v>
       </c>
-      <c r="B72" s="20" t="s">
-        <v>197</v>
-      </c>
-      <c r="D72" s="4">
+      <c r="B73" s="20" t="s">
+        <v>199</v>
+      </c>
+      <c r="D73" s="4">
         <v>4</v>
       </c>
-      <c r="E72" s="4" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="73" s="5" customFormat="1" spans="1:8">
-      <c r="A73" s="21">
+      <c r="E73" s="4" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="74" s="5" customFormat="1" spans="1:8">
+      <c r="A74" s="21">
         <v>12302</v>
       </c>
-      <c r="B73" s="21" t="s">
-        <v>199</v>
-      </c>
-      <c r="D73" s="5">
+      <c r="B74" s="21" t="s">
+        <v>201</v>
+      </c>
+      <c r="D74" s="5">
         <v>3</v>
       </c>
-      <c r="E73" s="5" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8">
-      <c r="A74" s="20">
+      <c r="E74" s="5" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8">
+      <c r="A75" s="20">
         <v>12303</v>
-      </c>
-      <c r="B74" s="20" t="s">
-        <v>201</v>
-      </c>
-      <c r="D74" s="4">
-        <v>2</v>
-      </c>
-      <c r="E74" s="4" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8">
-      <c r="A75" s="21">
-        <v>12304</v>
       </c>
       <c r="B75" s="20" t="s">
         <v>203</v>
@@ -3566,8 +3576,8 @@
       </c>
     </row>
     <row r="76" spans="1:8">
-      <c r="A76" s="20">
-        <v>12305</v>
+      <c r="A76" s="21">
+        <v>12304</v>
       </c>
       <c r="B76" s="20" t="s">
         <v>205</v>
@@ -3579,57 +3589,57 @@
         <v>206</v>
       </c>
     </row>
-    <row r="77" s="5" customFormat="1" spans="1:8">
-      <c r="A77" s="21">
+    <row r="77" spans="1:8">
+      <c r="A77" s="20">
+        <v>12305</v>
+      </c>
+      <c r="B77" s="20" t="s">
+        <v>207</v>
+      </c>
+      <c r="D77" s="4">
+        <v>2</v>
+      </c>
+      <c r="E77" s="4" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="78" s="5" customFormat="1" spans="1:8">
+      <c r="A78" s="21">
         <v>12306</v>
-      </c>
-      <c r="B77" s="21" t="s">
-        <v>207</v>
-      </c>
-      <c r="D77" s="5">
-        <v>4</v>
-      </c>
-      <c r="E77" s="5" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="78" s="5" customFormat="1" spans="1:8">
-      <c r="A78" s="20">
-        <v>12307</v>
       </c>
       <c r="B78" s="21" t="s">
         <v>209</v>
       </c>
       <c r="D78" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E78" s="5" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="79" spans="1:8">
-      <c r="A79" s="22">
-        <v>12501</v>
-      </c>
-      <c r="B79" s="22" t="s">
+    <row r="79" s="5" customFormat="1" spans="1:8">
+      <c r="A79" s="20">
+        <v>12307</v>
+      </c>
+      <c r="B79" s="21" t="s">
         <v>211</v>
       </c>
-      <c r="D79" s="4">
-        <v>4</v>
-      </c>
-      <c r="E79" s="4" t="s">
+      <c r="D79" s="5">
+        <v>2</v>
+      </c>
+      <c r="E79" s="5" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="80" spans="1:8">
       <c r="A80" s="22">
-        <v>12502</v>
+        <v>12501</v>
       </c>
       <c r="B80" s="22" t="s">
         <v>213</v>
       </c>
       <c r="D80" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E80" s="4" t="s">
         <v>214</v>
@@ -3637,13 +3647,13 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="22">
-        <v>12503</v>
+        <v>12502</v>
       </c>
       <c r="B81" s="22" t="s">
         <v>215</v>
       </c>
       <c r="D81" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E81" s="4" t="s">
         <v>216</v>
@@ -3651,23 +3661,23 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="22">
-        <v>12504</v>
+        <v>12503</v>
       </c>
       <c r="B82" s="22" t="s">
         <v>217</v>
       </c>
       <c r="D82" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E82" s="4" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="83" spans="1:5">
-      <c r="A83" s="4">
-        <v>12601</v>
-      </c>
-      <c r="B83" s="4" t="s">
+      <c r="A83" s="22">
+        <v>12504</v>
+      </c>
+      <c r="B83" s="22" t="s">
         <v>219</v>
       </c>
       <c r="D83" s="4">
@@ -3679,13 +3689,13 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="4">
-        <v>12602</v>
-      </c>
-      <c r="B84" s="22" t="s">
+        <v>12601</v>
+      </c>
+      <c r="B84" s="4" t="s">
         <v>221</v>
       </c>
       <c r="D84" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E84" s="4" t="s">
         <v>222</v>
@@ -3693,9 +3703,9 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="4">
-        <v>12603</v>
-      </c>
-      <c r="B85" s="4" t="s">
+        <v>12602</v>
+      </c>
+      <c r="B85" s="22" t="s">
         <v>223</v>
       </c>
       <c r="D85" s="4">
@@ -3707,13 +3717,13 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="4">
-        <v>12604</v>
+        <v>12603</v>
       </c>
       <c r="B86" s="4" t="s">
         <v>225</v>
       </c>
       <c r="D86" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E86" s="4" t="s">
         <v>226</v>
@@ -3721,13 +3731,13 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="4">
-        <v>12605</v>
+        <v>12604</v>
       </c>
       <c r="B87" s="4" t="s">
         <v>227</v>
       </c>
       <c r="D87" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E87" s="4" t="s">
         <v>228</v>
@@ -3735,13 +3745,13 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="4">
-        <v>12606</v>
+        <v>12605</v>
       </c>
       <c r="B88" s="4" t="s">
         <v>229</v>
       </c>
       <c r="D88" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E88" s="4" t="s">
         <v>230</v>
@@ -3749,13 +3759,13 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="4">
-        <v>12607</v>
+        <v>12606</v>
       </c>
       <c r="B89" s="4" t="s">
         <v>231</v>
       </c>
       <c r="D89" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E89" s="4" t="s">
         <v>232</v>
@@ -3763,7 +3773,7 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="4">
-        <v>12608</v>
+        <v>12607</v>
       </c>
       <c r="B90" s="4" t="s">
         <v>233</v>
@@ -3777,13 +3787,13 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="4">
-        <v>12609</v>
+        <v>12608</v>
       </c>
       <c r="B91" s="4" t="s">
         <v>235</v>
       </c>
       <c r="D91" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E91" s="4" t="s">
         <v>236</v>
@@ -3791,7 +3801,7 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="4">
-        <v>12610</v>
+        <v>12609</v>
       </c>
       <c r="B92" s="4" t="s">
         <v>237</v>
@@ -3805,13 +3815,13 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="4">
-        <v>12701</v>
+        <v>12610</v>
       </c>
       <c r="B93" s="4" t="s">
         <v>239</v>
       </c>
       <c r="D93" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E93" s="4" t="s">
         <v>240</v>
@@ -3819,7 +3829,7 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="4">
-        <v>12702</v>
+        <v>12701</v>
       </c>
       <c r="B94" s="4" t="s">
         <v>241</v>
@@ -3833,13 +3843,13 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="4">
-        <v>12703</v>
+        <v>12702</v>
       </c>
       <c r="B95" s="4" t="s">
         <v>243</v>
       </c>
       <c r="D95" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E95" s="4" t="s">
         <v>244</v>
@@ -3847,7 +3857,7 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="4">
-        <v>12704</v>
+        <v>12703</v>
       </c>
       <c r="B96" s="4" t="s">
         <v>245</v>
@@ -3857,6 +3867,20 @@
       </c>
       <c r="E96" s="4" t="s">
         <v>246</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5">
+      <c r="A97" s="4">
+        <v>12704</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="D97" s="4">
+        <v>3</v>
+      </c>
+      <c r="E97" s="4" t="s">
+        <v>248</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/condition.xlsx
+++ b/hall/resources/sample/condition.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\A-work\config_SimMgmtVert1.0\游戏配置表\common\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\common\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="condition" sheetId="1" r:id="rId1"/>
@@ -165,7 +165,8 @@
 mini	1
 minor	2
 major	3
-grand	4</t>
+grand	4
+jackpot         5  </t>
         </r>
       </text>
     </comment>
@@ -174,7 +175,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="253">
   <si>
     <t>id</t>
   </si>
@@ -647,22 +648,22 @@
     <t>12251_游戏ID(0)_道具ID_道具数量</t>
   </si>
   <si>
-    <t>累积：触发SWEET WIN N次</t>
-  </si>
-  <si>
-    <t>12252_大奖类型_次数</t>
-  </si>
-  <si>
-    <t>累积：触发MINI奖池N次</t>
-  </si>
-  <si>
-    <t>12253_奖池类型_次数</t>
-  </si>
-  <si>
-    <t>累积：触发免费游戏模式N次</t>
-  </si>
-  <si>
-    <t>12254_次数</t>
+    <t>累积：指定\任意SLOT游戏触发SWEET WIN N次</t>
+  </si>
+  <si>
+    <t>12252_游戏ID(0 = 任意游戏)_大奖类型_次数</t>
+  </si>
+  <si>
+    <t>累积：指定\任意SLOT游戏触发MINI奖池N次</t>
+  </si>
+  <si>
+    <t>12253_游戏ID(0 = 任意游戏)_奖池类型_次数</t>
+  </si>
+  <si>
+    <t>累积：指定\任意SLOT游戏触发免费游戏模式N次</t>
+  </si>
+  <si>
+    <t>12254_游戏ID(0 = 任意游戏)_次数</t>
   </si>
   <si>
     <t>累积：建筑升级N次</t>
@@ -771,6 +772,18 @@
   </si>
   <si>
     <t>12273_场景ID_建筑ID</t>
+  </si>
+  <si>
+    <t>累积：指定\任意SLOT游戏赢钱</t>
+  </si>
+  <si>
+    <t>12276_游戏ID(0 = 任意游戏)（不区分倍场）_货币ID(金币或钻石)_赢钱数量(投注赢钱+各类模式赢钱，除 好友提供的加成外)</t>
+  </si>
+  <si>
+    <t>累积：指定SLOT游戏触发财神到模式的次数</t>
+  </si>
+  <si>
+    <t>12275_游戏ID（默认101200=财神来了）_次数</t>
   </si>
   <si>
     <t>游戏中奖倍数</t>
@@ -933,7 +946,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="31">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -984,6 +997,12 @@
     <font>
       <sz val="11"/>
       <color rgb="FF7030A0"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -1493,137 +1512,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1683,6 +1702,9 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1758,6 +1780,7 @@
   <colors>
     <mruColors>
       <color rgb="00F4F8B9"/>
+      <color rgb="00FF0000"/>
     </mruColors>
   </colors>
   <extLst>
@@ -2018,7 +2041,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O97"/>
+  <dimension ref="A1:O99"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="4"/>
@@ -3164,9 +3187,9 @@
       </c>
       <c r="C52" s="2"/>
       <c r="D52" s="2">
-        <v>2</v>
-      </c>
-      <c r="E52" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="E52" s="20" t="s">
         <v>158</v>
       </c>
       <c r="F52" s="2"/>
@@ -3182,9 +3205,9 @@
       </c>
       <c r="C53" s="2"/>
       <c r="D53" s="2">
-        <v>2</v>
-      </c>
-      <c r="E53" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="E53" s="20" t="s">
         <v>160</v>
       </c>
       <c r="F53" s="2"/>
@@ -3200,9 +3223,9 @@
       </c>
       <c r="C54" s="2"/>
       <c r="D54" s="2">
-        <v>1</v>
-      </c>
-      <c r="E54" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="E54" s="20" t="s">
         <v>162</v>
       </c>
       <c r="F54" s="2"/>
@@ -3533,67 +3556,75 @@
       <c r="G72" s="2"/>
       <c r="H72" s="2"/>
     </row>
-    <row r="73" spans="1:8">
-      <c r="A73" s="20">
+    <row r="73" customFormat="1" spans="1:8">
+      <c r="A73" s="19">
+        <v>12274</v>
+      </c>
+      <c r="B73" s="19" t="s">
+        <v>199</v>
+      </c>
+      <c r="C73" s="4"/>
+      <c r="D73" s="4">
+        <v>3</v>
+      </c>
+      <c r="E73" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="F73" s="4"/>
+      <c r="G73" s="4"/>
+      <c r="H73" s="4"/>
+    </row>
+    <row r="74" customFormat="1" spans="1:8">
+      <c r="A74" s="19">
+        <v>12275</v>
+      </c>
+      <c r="B74" s="19" t="s">
+        <v>201</v>
+      </c>
+      <c r="C74" s="4"/>
+      <c r="D74" s="4">
+        <v>2</v>
+      </c>
+      <c r="E74" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="F74" s="4"/>
+      <c r="G74" s="4"/>
+      <c r="H74" s="4"/>
+    </row>
+    <row r="75" spans="1:8">
+      <c r="A75" s="21">
         <v>12301</v>
       </c>
-      <c r="B73" s="20" t="s">
-        <v>199</v>
-      </c>
-      <c r="D73" s="4">
+      <c r="B75" s="21" t="s">
+        <v>203</v>
+      </c>
+      <c r="D75" s="4">
         <v>4</v>
-      </c>
-      <c r="E73" s="4" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="74" s="5" customFormat="1" spans="1:8">
-      <c r="A74" s="21">
-        <v>12302</v>
-      </c>
-      <c r="B74" s="21" t="s">
-        <v>201</v>
-      </c>
-      <c r="D74" s="5">
-        <v>3</v>
-      </c>
-      <c r="E74" s="5" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8">
-      <c r="A75" s="20">
-        <v>12303</v>
-      </c>
-      <c r="B75" s="20" t="s">
-        <v>203</v>
-      </c>
-      <c r="D75" s="4">
-        <v>2</v>
       </c>
       <c r="E75" s="4" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="76" spans="1:8">
-      <c r="A76" s="21">
-        <v>12304</v>
-      </c>
-      <c r="B76" s="20" t="s">
+    <row r="76" s="5" customFormat="1" spans="1:8">
+      <c r="A76" s="22">
+        <v>12302</v>
+      </c>
+      <c r="B76" s="22" t="s">
         <v>205</v>
       </c>
-      <c r="D76" s="4">
-        <v>2</v>
-      </c>
-      <c r="E76" s="4" t="s">
+      <c r="D76" s="5">
+        <v>3</v>
+      </c>
+      <c r="E76" s="5" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="77" spans="1:8">
-      <c r="A77" s="20">
-        <v>12305</v>
-      </c>
-      <c r="B77" s="20" t="s">
+      <c r="A77" s="21">
+        <v>12303</v>
+      </c>
+      <c r="B77" s="21" t="s">
         <v>207</v>
       </c>
       <c r="D77" s="4">
@@ -3603,67 +3634,67 @@
         <v>208</v>
       </c>
     </row>
-    <row r="78" s="5" customFormat="1" spans="1:8">
-      <c r="A78" s="21">
-        <v>12306</v>
+    <row r="78" spans="1:8">
+      <c r="A78" s="22">
+        <v>12304</v>
       </c>
       <c r="B78" s="21" t="s">
         <v>209</v>
       </c>
-      <c r="D78" s="5">
-        <v>4</v>
-      </c>
-      <c r="E78" s="5" t="s">
+      <c r="D78" s="4">
+        <v>2</v>
+      </c>
+      <c r="E78" s="4" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="79" s="5" customFormat="1" spans="1:8">
-      <c r="A79" s="20">
-        <v>12307</v>
+    <row r="79" spans="1:8">
+      <c r="A79" s="21">
+        <v>12305</v>
       </c>
       <c r="B79" s="21" t="s">
         <v>211</v>
       </c>
-      <c r="D79" s="5">
-        <v>2</v>
-      </c>
-      <c r="E79" s="5" t="s">
+      <c r="D79" s="4">
+        <v>2</v>
+      </c>
+      <c r="E79" s="4" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="80" spans="1:8">
+    <row r="80" s="5" customFormat="1" spans="1:8">
       <c r="A80" s="22">
-        <v>12501</v>
+        <v>12306</v>
       </c>
       <c r="B80" s="22" t="s">
         <v>213</v>
       </c>
-      <c r="D80" s="4">
+      <c r="D80" s="5">
         <v>4</v>
       </c>
-      <c r="E80" s="4" t="s">
+      <c r="E80" s="5" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="22">
-        <v>12502</v>
+    <row r="81" s="5" customFormat="1" spans="1:5">
+      <c r="A81" s="21">
+        <v>12307</v>
       </c>
       <c r="B81" s="22" t="s">
         <v>215</v>
       </c>
-      <c r="D81" s="4">
-        <v>3</v>
-      </c>
-      <c r="E81" s="4" t="s">
+      <c r="D81" s="5">
+        <v>2</v>
+      </c>
+      <c r="E81" s="5" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="82" spans="1:5">
-      <c r="A82" s="22">
-        <v>12503</v>
-      </c>
-      <c r="B82" s="22" t="s">
+      <c r="A82" s="23">
+        <v>12501</v>
+      </c>
+      <c r="B82" s="23" t="s">
         <v>217</v>
       </c>
       <c r="D82" s="4">
@@ -3674,10 +3705,10 @@
       </c>
     </row>
     <row r="83" spans="1:5">
-      <c r="A83" s="22">
-        <v>12504</v>
-      </c>
-      <c r="B83" s="22" t="s">
+      <c r="A83" s="23">
+        <v>12502</v>
+      </c>
+      <c r="B83" s="23" t="s">
         <v>219</v>
       </c>
       <c r="D83" s="4">
@@ -3688,28 +3719,28 @@
       </c>
     </row>
     <row r="84" spans="1:5">
-      <c r="A84" s="4">
-        <v>12601</v>
-      </c>
-      <c r="B84" s="4" t="s">
+      <c r="A84" s="23">
+        <v>12503</v>
+      </c>
+      <c r="B84" s="23" t="s">
         <v>221</v>
       </c>
       <c r="D84" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E84" s="4" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="85" spans="1:5">
-      <c r="A85" s="4">
-        <v>12602</v>
-      </c>
-      <c r="B85" s="22" t="s">
+      <c r="A85" s="23">
+        <v>12504</v>
+      </c>
+      <c r="B85" s="23" t="s">
         <v>223</v>
       </c>
       <c r="D85" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E85" s="4" t="s">
         <v>224</v>
@@ -3717,13 +3748,13 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="4">
-        <v>12603</v>
+        <v>12601</v>
       </c>
       <c r="B86" s="4" t="s">
         <v>225</v>
       </c>
       <c r="D86" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E86" s="4" t="s">
         <v>226</v>
@@ -3731,13 +3762,13 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="4">
-        <v>12604</v>
-      </c>
-      <c r="B87" s="4" t="s">
+        <v>12602</v>
+      </c>
+      <c r="B87" s="23" t="s">
         <v>227</v>
       </c>
       <c r="D87" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E87" s="4" t="s">
         <v>228</v>
@@ -3745,7 +3776,7 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="4">
-        <v>12605</v>
+        <v>12603</v>
       </c>
       <c r="B88" s="4" t="s">
         <v>229</v>
@@ -3759,7 +3790,7 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="4">
-        <v>12606</v>
+        <v>12604</v>
       </c>
       <c r="B89" s="4" t="s">
         <v>231</v>
@@ -3773,13 +3804,13 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="4">
-        <v>12607</v>
+        <v>12605</v>
       </c>
       <c r="B90" s="4" t="s">
         <v>233</v>
       </c>
       <c r="D90" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E90" s="4" t="s">
         <v>234</v>
@@ -3787,13 +3818,13 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="4">
-        <v>12608</v>
+        <v>12606</v>
       </c>
       <c r="B91" s="4" t="s">
         <v>235</v>
       </c>
       <c r="D91" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E91" s="4" t="s">
         <v>236</v>
@@ -3801,13 +3832,13 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="4">
-        <v>12609</v>
+        <v>12607</v>
       </c>
       <c r="B92" s="4" t="s">
         <v>237</v>
       </c>
       <c r="D92" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E92" s="4" t="s">
         <v>238</v>
@@ -3815,13 +3846,13 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="4">
-        <v>12610</v>
+        <v>12608</v>
       </c>
       <c r="B93" s="4" t="s">
         <v>239</v>
       </c>
       <c r="D93" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E93" s="4" t="s">
         <v>240</v>
@@ -3829,13 +3860,13 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="4">
-        <v>12701</v>
+        <v>12609</v>
       </c>
       <c r="B94" s="4" t="s">
         <v>241</v>
       </c>
       <c r="D94" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E94" s="4" t="s">
         <v>242</v>
@@ -3843,13 +3874,13 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="4">
-        <v>12702</v>
+        <v>12610</v>
       </c>
       <c r="B95" s="4" t="s">
         <v>243</v>
       </c>
       <c r="D95" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E95" s="4" t="s">
         <v>244</v>
@@ -3857,13 +3888,13 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="4">
-        <v>12703</v>
+        <v>12701</v>
       </c>
       <c r="B96" s="4" t="s">
         <v>245</v>
       </c>
       <c r="D96" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E96" s="4" t="s">
         <v>246</v>
@@ -3871,16 +3902,44 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="4">
-        <v>12704</v>
+        <v>12702</v>
       </c>
       <c r="B97" s="4" t="s">
         <v>247</v>
       </c>
       <c r="D97" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E97" s="4" t="s">
         <v>248</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5">
+      <c r="A98" s="4">
+        <v>12703</v>
+      </c>
+      <c r="B98" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="D98" s="4">
+        <v>3</v>
+      </c>
+      <c r="E98" s="4" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5">
+      <c r="A99" s="4">
+        <v>12704</v>
+      </c>
+      <c r="B99" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="D99" s="4">
+        <v>3</v>
+      </c>
+      <c r="E99" s="4" t="s">
+        <v>252</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/condition.xlsx
+++ b/hall/resources/sample/condition.xlsx
@@ -783,7 +783,7 @@
     <t>累积：指定SLOT游戏触发财神到模式的次数</t>
   </si>
   <si>
-    <t>12275_游戏ID（默认101200=财神来了）_次数</t>
+    <t>12275_次数</t>
   </si>
   <si>
     <t>游戏中奖倍数</t>
@@ -3583,7 +3583,7 @@
       </c>
       <c r="C74" s="4"/>
       <c r="D74" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E74" s="4" t="s">
         <v>202</v>

--- a/hall/resources/sample/condition.xlsx
+++ b/hall/resources/sample/condition.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\common\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\A-work\config_SimMgmtVert1.0\游戏配置表\common\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="24045" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="condition" sheetId="1" r:id="rId1"/>
@@ -175,7 +175,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="255">
   <si>
     <t>id</t>
   </si>
@@ -784,6 +784,12 @@
   </si>
   <si>
     <t>12275_次数</t>
+  </si>
+  <si>
+    <t>累积：指定/任意游戏技能达到N级(总等级)</t>
+  </si>
+  <si>
+    <t>12276_游戏ID(0)_技能总等级</t>
   </si>
   <si>
     <t>游戏中奖倍数</t>
@@ -2041,7 +2047,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O99"/>
+  <dimension ref="A1:O100"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="4"/>
@@ -3592,51 +3598,55 @@
       <c r="G74" s="4"/>
       <c r="H74" s="4"/>
     </row>
-    <row r="75" spans="1:8">
-      <c r="A75" s="21">
-        <v>12301</v>
-      </c>
-      <c r="B75" s="21" t="s">
+    <row r="75" customFormat="1" spans="1:8">
+      <c r="A75" s="19">
+        <v>12276</v>
+      </c>
+      <c r="B75" s="19" t="s">
         <v>203</v>
       </c>
+      <c r="C75" s="4"/>
       <c r="D75" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E75" s="4" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="76" s="5" customFormat="1" spans="1:8">
-      <c r="A76" s="22">
+      <c r="F75" s="4"/>
+      <c r="G75" s="4"/>
+      <c r="H75" s="4"/>
+    </row>
+    <row r="76" spans="1:8">
+      <c r="A76" s="21">
+        <v>12301</v>
+      </c>
+      <c r="B76" s="21" t="s">
+        <v>205</v>
+      </c>
+      <c r="D76" s="4">
+        <v>4</v>
+      </c>
+      <c r="E76" s="4" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="77" s="5" customFormat="1" spans="1:8">
+      <c r="A77" s="22">
         <v>12302</v>
       </c>
-      <c r="B76" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="D76" s="5">
+      <c r="B77" s="22" t="s">
+        <v>207</v>
+      </c>
+      <c r="D77" s="5">
         <v>3</v>
       </c>
-      <c r="E76" s="5" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8">
-      <c r="A77" s="21">
+      <c r="E77" s="5" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8">
+      <c r="A78" s="21">
         <v>12303</v>
-      </c>
-      <c r="B77" s="21" t="s">
-        <v>207</v>
-      </c>
-      <c r="D77" s="4">
-        <v>2</v>
-      </c>
-      <c r="E77" s="4" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8">
-      <c r="A78" s="22">
-        <v>12304</v>
       </c>
       <c r="B78" s="21" t="s">
         <v>209</v>
@@ -3649,8 +3659,8 @@
       </c>
     </row>
     <row r="79" spans="1:8">
-      <c r="A79" s="21">
-        <v>12305</v>
+      <c r="A79" s="22">
+        <v>12304</v>
       </c>
       <c r="B79" s="21" t="s">
         <v>211</v>
@@ -3662,57 +3672,57 @@
         <v>212</v>
       </c>
     </row>
-    <row r="80" s="5" customFormat="1" spans="1:8">
-      <c r="A80" s="22">
+    <row r="80" spans="1:8">
+      <c r="A80" s="21">
+        <v>12305</v>
+      </c>
+      <c r="B80" s="21" t="s">
+        <v>213</v>
+      </c>
+      <c r="D80" s="4">
+        <v>2</v>
+      </c>
+      <c r="E80" s="4" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="81" s="5" customFormat="1" spans="1:5">
+      <c r="A81" s="22">
         <v>12306</v>
-      </c>
-      <c r="B80" s="22" t="s">
-        <v>213</v>
-      </c>
-      <c r="D80" s="5">
-        <v>4</v>
-      </c>
-      <c r="E80" s="5" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="81" s="5" customFormat="1" spans="1:5">
-      <c r="A81" s="21">
-        <v>12307</v>
       </c>
       <c r="B81" s="22" t="s">
         <v>215</v>
       </c>
       <c r="D81" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E81" s="5" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="82" spans="1:5">
-      <c r="A82" s="23">
-        <v>12501</v>
-      </c>
-      <c r="B82" s="23" t="s">
+    <row r="82" s="5" customFormat="1" spans="1:5">
+      <c r="A82" s="21">
+        <v>12307</v>
+      </c>
+      <c r="B82" s="22" t="s">
         <v>217</v>
       </c>
-      <c r="D82" s="4">
-        <v>4</v>
-      </c>
-      <c r="E82" s="4" t="s">
+      <c r="D82" s="5">
+        <v>2</v>
+      </c>
+      <c r="E82" s="5" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="23">
-        <v>12502</v>
+        <v>12501</v>
       </c>
       <c r="B83" s="23" t="s">
         <v>219</v>
       </c>
       <c r="D83" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E83" s="4" t="s">
         <v>220</v>
@@ -3720,13 +3730,13 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="23">
-        <v>12503</v>
+        <v>12502</v>
       </c>
       <c r="B84" s="23" t="s">
         <v>221</v>
       </c>
       <c r="D84" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E84" s="4" t="s">
         <v>222</v>
@@ -3734,23 +3744,23 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="23">
-        <v>12504</v>
+        <v>12503</v>
       </c>
       <c r="B85" s="23" t="s">
         <v>223</v>
       </c>
       <c r="D85" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E85" s="4" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="86" spans="1:5">
-      <c r="A86" s="4">
-        <v>12601</v>
-      </c>
-      <c r="B86" s="4" t="s">
+      <c r="A86" s="23">
+        <v>12504</v>
+      </c>
+      <c r="B86" s="23" t="s">
         <v>225</v>
       </c>
       <c r="D86" s="4">
@@ -3762,13 +3772,13 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="4">
-        <v>12602</v>
-      </c>
-      <c r="B87" s="23" t="s">
+        <v>12601</v>
+      </c>
+      <c r="B87" s="4" t="s">
         <v>227</v>
       </c>
       <c r="D87" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E87" s="4" t="s">
         <v>228</v>
@@ -3776,9 +3786,9 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="4">
-        <v>12603</v>
-      </c>
-      <c r="B88" s="4" t="s">
+        <v>12602</v>
+      </c>
+      <c r="B88" s="23" t="s">
         <v>229</v>
       </c>
       <c r="D88" s="4">
@@ -3790,13 +3800,13 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="4">
-        <v>12604</v>
+        <v>12603</v>
       </c>
       <c r="B89" s="4" t="s">
         <v>231</v>
       </c>
       <c r="D89" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E89" s="4" t="s">
         <v>232</v>
@@ -3804,13 +3814,13 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="4">
-        <v>12605</v>
+        <v>12604</v>
       </c>
       <c r="B90" s="4" t="s">
         <v>233</v>
       </c>
       <c r="D90" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E90" s="4" t="s">
         <v>234</v>
@@ -3818,13 +3828,13 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="4">
-        <v>12606</v>
+        <v>12605</v>
       </c>
       <c r="B91" s="4" t="s">
         <v>235</v>
       </c>
       <c r="D91" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E91" s="4" t="s">
         <v>236</v>
@@ -3832,13 +3842,13 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="4">
-        <v>12607</v>
+        <v>12606</v>
       </c>
       <c r="B92" s="4" t="s">
         <v>237</v>
       </c>
       <c r="D92" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E92" s="4" t="s">
         <v>238</v>
@@ -3846,7 +3856,7 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="4">
-        <v>12608</v>
+        <v>12607</v>
       </c>
       <c r="B93" s="4" t="s">
         <v>239</v>
@@ -3860,13 +3870,13 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="4">
-        <v>12609</v>
+        <v>12608</v>
       </c>
       <c r="B94" s="4" t="s">
         <v>241</v>
       </c>
       <c r="D94" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E94" s="4" t="s">
         <v>242</v>
@@ -3874,7 +3884,7 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="4">
-        <v>12610</v>
+        <v>12609</v>
       </c>
       <c r="B95" s="4" t="s">
         <v>243</v>
@@ -3888,13 +3898,13 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="4">
-        <v>12701</v>
+        <v>12610</v>
       </c>
       <c r="B96" s="4" t="s">
         <v>245</v>
       </c>
       <c r="D96" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E96" s="4" t="s">
         <v>246</v>
@@ -3902,7 +3912,7 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="4">
-        <v>12702</v>
+        <v>12701</v>
       </c>
       <c r="B97" s="4" t="s">
         <v>247</v>
@@ -3916,13 +3926,13 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="4">
-        <v>12703</v>
+        <v>12702</v>
       </c>
       <c r="B98" s="4" t="s">
         <v>249</v>
       </c>
       <c r="D98" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E98" s="4" t="s">
         <v>250</v>
@@ -3930,7 +3940,7 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="4">
-        <v>12704</v>
+        <v>12703</v>
       </c>
       <c r="B99" s="4" t="s">
         <v>251</v>
@@ -3940,6 +3950,20 @@
       </c>
       <c r="E99" s="4" t="s">
         <v>252</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5">
+      <c r="A100" s="4">
+        <v>12704</v>
+      </c>
+      <c r="B100" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="D100" s="4">
+        <v>3</v>
+      </c>
+      <c r="E100" s="4" t="s">
+        <v>254</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/condition.xlsx
+++ b/hall/resources/sample/condition.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="24045" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="condition" sheetId="1" r:id="rId1"/>
@@ -115,7 +115,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E52" authorId="0">
+    <comment ref="E54" authorId="0">
       <text>
         <r>
           <rPr>
@@ -143,7 +143,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E53" authorId="0">
+    <comment ref="E55" authorId="0">
       <text>
         <r>
           <rPr>
@@ -175,7 +175,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="261">
   <si>
     <t>id</t>
   </si>
@@ -642,6 +642,18 @@
     <t>12225_游戏ID(0 = 任意游戏)（不区分倍场）_货币ID(金币或钻石)_赢钱数量(投注赢钱+各类模式赢钱，除 好友提供的加成外)</t>
   </si>
   <si>
+    <t>接取：赛季商城购买N次商品</t>
+  </si>
+  <si>
+    <t>12226_次数</t>
+  </si>
+  <si>
+    <t>接取：赛季宝石镶嵌N次</t>
+  </si>
+  <si>
+    <t>12227_次数</t>
+  </si>
+  <si>
     <t>累积：在SLOT游戏中获得N个X道具</t>
   </si>
   <si>
@@ -790,6 +802,12 @@
   </si>
   <si>
     <t>12276_游戏ID(0)_技能总等级</t>
+  </si>
+  <si>
+    <t>累积：指定游戏的指定技能达到N级</t>
+  </si>
+  <si>
+    <t>12277_游戏ID_技能ID_等级</t>
   </si>
   <si>
     <t>游戏中奖倍数</t>
@@ -952,7 +970,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -996,19 +1014,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFC00000"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF7030A0"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -1518,137 +1524,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1703,14 +1709,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2047,7 +2047,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O100"/>
+  <dimension ref="A1:O103"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="4"/>
@@ -3149,10 +3149,10 @@
       <c r="H49" s="2"/>
     </row>
     <row r="50" spans="1:8">
-      <c r="A50" s="18">
+      <c r="A50" s="13">
         <v>12225</v>
       </c>
-      <c r="B50" s="18" t="s">
+      <c r="B50" s="13" t="s">
         <v>153</v>
       </c>
       <c r="C50" s="2"/>
@@ -3167,15 +3167,15 @@
       <c r="H50" s="2"/>
     </row>
     <row r="51" spans="1:8">
-      <c r="A51" s="19">
-        <v>12251</v>
-      </c>
-      <c r="B51" s="19" t="s">
+      <c r="A51" s="13">
+        <v>12226</v>
+      </c>
+      <c r="B51" s="13" t="s">
         <v>155</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E51" s="14" t="s">
         <v>156</v>
@@ -3185,17 +3185,17 @@
       <c r="H51" s="2"/>
     </row>
     <row r="52" spans="1:8">
-      <c r="A52" s="19">
-        <v>12252</v>
-      </c>
-      <c r="B52" s="19" t="s">
+      <c r="A52" s="13">
+        <v>12227</v>
+      </c>
+      <c r="B52" s="13" t="s">
         <v>157</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" s="2">
-        <v>3</v>
-      </c>
-      <c r="E52" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="E52" s="14" t="s">
         <v>158</v>
       </c>
       <c r="F52" s="2"/>
@@ -3203,17 +3203,17 @@
       <c r="H52" s="2"/>
     </row>
     <row r="53" spans="1:8">
-      <c r="A53" s="19">
-        <v>12253</v>
-      </c>
-      <c r="B53" s="19" t="s">
+      <c r="A53" s="18">
+        <v>12251</v>
+      </c>
+      <c r="B53" s="18" t="s">
         <v>159</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" s="2">
         <v>3</v>
       </c>
-      <c r="E53" s="20" t="s">
+      <c r="E53" s="14" t="s">
         <v>160</v>
       </c>
       <c r="F53" s="2"/>
@@ -3221,17 +3221,17 @@
       <c r="H53" s="2"/>
     </row>
     <row r="54" spans="1:8">
-      <c r="A54" s="19">
-        <v>12254</v>
-      </c>
-      <c r="B54" s="19" t="s">
+      <c r="A54" s="18">
+        <v>12252</v>
+      </c>
+      <c r="B54" s="18" t="s">
         <v>161</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" s="2">
-        <v>2</v>
-      </c>
-      <c r="E54" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="E54" s="14" t="s">
         <v>162</v>
       </c>
       <c r="F54" s="2"/>
@@ -3239,15 +3239,15 @@
       <c r="H54" s="2"/>
     </row>
     <row r="55" spans="1:8">
-      <c r="A55" s="19">
-        <v>12255</v>
-      </c>
-      <c r="B55" s="19" t="s">
+      <c r="A55" s="18">
+        <v>12253</v>
+      </c>
+      <c r="B55" s="18" t="s">
         <v>163</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E55" s="14" t="s">
         <v>164</v>
@@ -3257,10 +3257,10 @@
       <c r="H55" s="2"/>
     </row>
     <row r="56" spans="1:8">
-      <c r="A56" s="19">
-        <v>12256</v>
-      </c>
-      <c r="B56" s="19" t="s">
+      <c r="A56" s="18">
+        <v>12254</v>
+      </c>
+      <c r="B56" s="18" t="s">
         <v>165</v>
       </c>
       <c r="C56" s="2"/>
@@ -3275,15 +3275,15 @@
       <c r="H56" s="2"/>
     </row>
     <row r="57" spans="1:8">
-      <c r="A57" s="19">
-        <v>12257</v>
-      </c>
-      <c r="B57" s="19" t="s">
+      <c r="A57" s="18">
+        <v>12255</v>
+      </c>
+      <c r="B57" s="18" t="s">
         <v>167</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E57" s="14" t="s">
         <v>168</v>
@@ -3293,15 +3293,15 @@
       <c r="H57" s="2"/>
     </row>
     <row r="58" spans="1:8">
-      <c r="A58" s="19">
-        <v>12259</v>
-      </c>
-      <c r="B58" s="19" t="s">
+      <c r="A58" s="18">
+        <v>12256</v>
+      </c>
+      <c r="B58" s="18" t="s">
         <v>169</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E58" s="14" t="s">
         <v>170</v>
@@ -3311,15 +3311,15 @@
       <c r="H58" s="2"/>
     </row>
     <row r="59" spans="1:8">
-      <c r="A59" s="19">
-        <v>12260</v>
-      </c>
-      <c r="B59" s="19" t="s">
+      <c r="A59" s="18">
+        <v>12257</v>
+      </c>
+      <c r="B59" s="18" t="s">
         <v>171</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E59" s="14" t="s">
         <v>172</v>
@@ -3329,15 +3329,15 @@
       <c r="H59" s="2"/>
     </row>
     <row r="60" spans="1:8">
-      <c r="A60" s="19">
-        <v>12261</v>
-      </c>
-      <c r="B60" s="19" t="s">
+      <c r="A60" s="18">
+        <v>12259</v>
+      </c>
+      <c r="B60" s="18" t="s">
         <v>173</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E60" s="14" t="s">
         <v>174</v>
@@ -3347,10 +3347,10 @@
       <c r="H60" s="2"/>
     </row>
     <row r="61" spans="1:8">
-      <c r="A61" s="19">
-        <v>12262</v>
-      </c>
-      <c r="B61" s="19" t="s">
+      <c r="A61" s="18">
+        <v>12260</v>
+      </c>
+      <c r="B61" s="18" t="s">
         <v>175</v>
       </c>
       <c r="C61" s="2"/>
@@ -3365,15 +3365,15 @@
       <c r="H61" s="2"/>
     </row>
     <row r="62" spans="1:8">
-      <c r="A62" s="19">
-        <v>12263</v>
-      </c>
-      <c r="B62" s="19" t="s">
+      <c r="A62" s="18">
+        <v>12261</v>
+      </c>
+      <c r="B62" s="18" t="s">
         <v>177</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E62" s="14" t="s">
         <v>178</v>
@@ -3383,15 +3383,15 @@
       <c r="H62" s="2"/>
     </row>
     <row r="63" spans="1:8">
-      <c r="A63" s="19">
-        <v>12264</v>
-      </c>
-      <c r="B63" s="19" t="s">
+      <c r="A63" s="18">
+        <v>12262</v>
+      </c>
+      <c r="B63" s="18" t="s">
         <v>179</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E63" s="14" t="s">
         <v>180</v>
@@ -3401,10 +3401,10 @@
       <c r="H63" s="2"/>
     </row>
     <row r="64" spans="1:8">
-      <c r="A64" s="19">
-        <v>12265</v>
-      </c>
-      <c r="B64" s="19" t="s">
+      <c r="A64" s="18">
+        <v>12263</v>
+      </c>
+      <c r="B64" s="18" t="s">
         <v>181</v>
       </c>
       <c r="C64" s="2"/>
@@ -3419,10 +3419,10 @@
       <c r="H64" s="2"/>
     </row>
     <row r="65" spans="1:8">
-      <c r="A65" s="19">
-        <v>12266</v>
-      </c>
-      <c r="B65" s="19" t="s">
+      <c r="A65" s="18">
+        <v>12264</v>
+      </c>
+      <c r="B65" s="18" t="s">
         <v>183</v>
       </c>
       <c r="C65" s="2"/>
@@ -3437,15 +3437,15 @@
       <c r="H65" s="2"/>
     </row>
     <row r="66" spans="1:8">
-      <c r="A66" s="19">
-        <v>12267</v>
-      </c>
-      <c r="B66" s="19" t="s">
+      <c r="A66" s="18">
+        <v>12265</v>
+      </c>
+      <c r="B66" s="18" t="s">
         <v>185</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E66" s="14" t="s">
         <v>186</v>
@@ -3455,15 +3455,15 @@
       <c r="H66" s="2"/>
     </row>
     <row r="67" spans="1:8">
-      <c r="A67" s="19">
-        <v>12268</v>
-      </c>
-      <c r="B67" s="19" t="s">
+      <c r="A67" s="18">
+        <v>12266</v>
+      </c>
+      <c r="B67" s="18" t="s">
         <v>187</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E67" s="14" t="s">
         <v>188</v>
@@ -3472,11 +3472,11 @@
       <c r="G67" s="2"/>
       <c r="H67" s="2"/>
     </row>
-    <row r="68" s="4" customFormat="1" spans="1:8">
-      <c r="A68" s="19">
-        <v>12269</v>
-      </c>
-      <c r="B68" s="19" t="s">
+    <row r="68" spans="1:8">
+      <c r="A68" s="18">
+        <v>12267</v>
+      </c>
+      <c r="B68" s="18" t="s">
         <v>189</v>
       </c>
       <c r="C68" s="2"/>
@@ -3490,16 +3490,16 @@
       <c r="G68" s="2"/>
       <c r="H68" s="2"/>
     </row>
-    <row r="69" s="4" customFormat="1" spans="1:8">
-      <c r="A69" s="19">
-        <v>12270</v>
-      </c>
-      <c r="B69" s="19" t="s">
+    <row r="69" spans="1:8">
+      <c r="A69" s="18">
+        <v>12268</v>
+      </c>
+      <c r="B69" s="18" t="s">
         <v>191</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E69" s="14" t="s">
         <v>192</v>
@@ -3509,15 +3509,15 @@
       <c r="H69" s="2"/>
     </row>
     <row r="70" s="4" customFormat="1" spans="1:8">
-      <c r="A70" s="19">
-        <v>12271</v>
-      </c>
-      <c r="B70" s="19" t="s">
+      <c r="A70" s="18">
+        <v>12269</v>
+      </c>
+      <c r="B70" s="18" t="s">
         <v>193</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E70" s="14" t="s">
         <v>194</v>
@@ -3527,15 +3527,15 @@
       <c r="H70" s="2"/>
     </row>
     <row r="71" s="4" customFormat="1" spans="1:8">
-      <c r="A71" s="19">
-        <v>12272</v>
-      </c>
-      <c r="B71" s="19" t="s">
+      <c r="A71" s="18">
+        <v>12270</v>
+      </c>
+      <c r="B71" s="18" t="s">
         <v>195</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E71" s="14" t="s">
         <v>196</v>
@@ -3545,15 +3545,15 @@
       <c r="H71" s="2"/>
     </row>
     <row r="72" s="4" customFormat="1" spans="1:8">
-      <c r="A72" s="19">
-        <v>12273</v>
-      </c>
-      <c r="B72" s="19" t="s">
+      <c r="A72" s="18">
+        <v>12271</v>
+      </c>
+      <c r="B72" s="18" t="s">
         <v>197</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E72" s="14" t="s">
         <v>198</v>
@@ -3562,219 +3562,231 @@
       <c r="G72" s="2"/>
       <c r="H72" s="2"/>
     </row>
-    <row r="73" customFormat="1" spans="1:8">
-      <c r="A73" s="19">
-        <v>12274</v>
-      </c>
-      <c r="B73" s="19" t="s">
+    <row r="73" s="4" customFormat="1" spans="1:8">
+      <c r="A73" s="18">
+        <v>12272</v>
+      </c>
+      <c r="B73" s="18" t="s">
         <v>199</v>
       </c>
-      <c r="C73" s="4"/>
-      <c r="D73" s="4">
-        <v>3</v>
+      <c r="C73" s="2"/>
+      <c r="D73" s="2">
+        <v>2</v>
       </c>
       <c r="E73" s="14" t="s">
         <v>200</v>
       </c>
-      <c r="F73" s="4"/>
-      <c r="G73" s="4"/>
-      <c r="H73" s="4"/>
-    </row>
-    <row r="74" customFormat="1" spans="1:8">
-      <c r="A74" s="19">
-        <v>12275</v>
-      </c>
-      <c r="B74" s="19" t="s">
+      <c r="F73" s="2"/>
+      <c r="G73" s="2"/>
+      <c r="H73" s="2"/>
+    </row>
+    <row r="74" s="4" customFormat="1" spans="1:8">
+      <c r="A74" s="18">
+        <v>12273</v>
+      </c>
+      <c r="B74" s="18" t="s">
         <v>201</v>
       </c>
-      <c r="C74" s="4"/>
-      <c r="D74" s="4">
-        <v>1</v>
-      </c>
-      <c r="E74" s="4" t="s">
+      <c r="C74" s="2"/>
+      <c r="D74" s="2">
+        <v>2</v>
+      </c>
+      <c r="E74" s="14" t="s">
         <v>202</v>
       </c>
-      <c r="F74" s="4"/>
-      <c r="G74" s="4"/>
-      <c r="H74" s="4"/>
+      <c r="F74" s="2"/>
+      <c r="G74" s="2"/>
+      <c r="H74" s="2"/>
     </row>
     <row r="75" customFormat="1" spans="1:8">
-      <c r="A75" s="19">
-        <v>12276</v>
-      </c>
-      <c r="B75" s="19" t="s">
+      <c r="A75" s="18">
+        <v>12274</v>
+      </c>
+      <c r="B75" s="18" t="s">
         <v>203</v>
       </c>
       <c r="C75" s="4"/>
       <c r="D75" s="4">
-        <v>2</v>
-      </c>
-      <c r="E75" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E75" s="14" t="s">
         <v>204</v>
       </c>
       <c r="F75" s="4"/>
       <c r="G75" s="4"/>
       <c r="H75" s="4"/>
     </row>
-    <row r="76" spans="1:8">
-      <c r="A76" s="21">
-        <v>12301</v>
-      </c>
-      <c r="B76" s="21" t="s">
+    <row r="76" customFormat="1" spans="1:8">
+      <c r="A76" s="18">
+        <v>12275</v>
+      </c>
+      <c r="B76" s="18" t="s">
         <v>205</v>
       </c>
+      <c r="C76" s="4"/>
       <c r="D76" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E76" s="4" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="77" s="5" customFormat="1" spans="1:8">
-      <c r="A77" s="22">
-        <v>12302</v>
-      </c>
-      <c r="B77" s="22" t="s">
+      <c r="F76" s="4"/>
+      <c r="G76" s="4"/>
+      <c r="H76" s="4"/>
+    </row>
+    <row r="77" customFormat="1" spans="1:8">
+      <c r="A77" s="18">
+        <v>12276</v>
+      </c>
+      <c r="B77" s="18" t="s">
         <v>207</v>
       </c>
-      <c r="D77" s="5">
+      <c r="C77" s="4"/>
+      <c r="D77" s="4">
+        <v>2</v>
+      </c>
+      <c r="E77" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="F77" s="4"/>
+      <c r="G77" s="4"/>
+      <c r="H77" s="4"/>
+    </row>
+    <row r="78" customFormat="1" spans="1:8">
+      <c r="A78" s="18">
+        <v>12277</v>
+      </c>
+      <c r="B78" s="18" t="s">
+        <v>209</v>
+      </c>
+      <c r="C78" s="4"/>
+      <c r="D78" s="4">
         <v>3</v>
-      </c>
-      <c r="E77" s="5" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8">
-      <c r="A78" s="21">
-        <v>12303</v>
-      </c>
-      <c r="B78" s="21" t="s">
-        <v>209</v>
-      </c>
-      <c r="D78" s="4">
-        <v>2</v>
       </c>
       <c r="E78" s="4" t="s">
         <v>210</v>
       </c>
+      <c r="F78" s="4"/>
+      <c r="G78" s="4"/>
+      <c r="H78" s="4"/>
     </row>
     <row r="79" spans="1:8">
-      <c r="A79" s="22">
-        <v>12304</v>
-      </c>
-      <c r="B79" s="21" t="s">
+      <c r="A79" s="19">
+        <v>12301</v>
+      </c>
+      <c r="B79" s="19" t="s">
         <v>211</v>
       </c>
       <c r="D79" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E79" s="4" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="80" spans="1:8">
-      <c r="A80" s="21">
+    <row r="80" s="5" customFormat="1" spans="1:8">
+      <c r="A80" s="20">
+        <v>12302</v>
+      </c>
+      <c r="B80" s="20" t="s">
+        <v>213</v>
+      </c>
+      <c r="D80" s="5">
+        <v>3</v>
+      </c>
+      <c r="E80" s="5" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="19">
+        <v>12303</v>
+      </c>
+      <c r="B81" s="19" t="s">
+        <v>215</v>
+      </c>
+      <c r="D81" s="4">
+        <v>2</v>
+      </c>
+      <c r="E81" s="4" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="20">
+        <v>12304</v>
+      </c>
+      <c r="B82" s="19" t="s">
+        <v>217</v>
+      </c>
+      <c r="D82" s="4">
+        <v>2</v>
+      </c>
+      <c r="E82" s="4" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" s="19">
         <v>12305</v>
       </c>
-      <c r="B80" s="21" t="s">
-        <v>213</v>
-      </c>
-      <c r="D80" s="4">
-        <v>2</v>
-      </c>
-      <c r="E80" s="4" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="81" s="5" customFormat="1" spans="1:5">
-      <c r="A81" s="22">
-        <v>12306</v>
-      </c>
-      <c r="B81" s="22" t="s">
-        <v>215</v>
-      </c>
-      <c r="D81" s="5">
-        <v>4</v>
-      </c>
-      <c r="E81" s="5" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="82" s="5" customFormat="1" spans="1:5">
-      <c r="A82" s="21">
-        <v>12307</v>
-      </c>
-      <c r="B82" s="22" t="s">
-        <v>217</v>
-      </c>
-      <c r="D82" s="5">
-        <v>2</v>
-      </c>
-      <c r="E82" s="5" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5">
-      <c r="A83" s="23">
-        <v>12501</v>
-      </c>
-      <c r="B83" s="23" t="s">
+      <c r="B83" s="19" t="s">
         <v>219</v>
       </c>
       <c r="D83" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E83" s="4" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="84" spans="1:5">
-      <c r="A84" s="23">
-        <v>12502</v>
-      </c>
-      <c r="B84" s="23" t="s">
+    <row r="84" s="5" customFormat="1" spans="1:5">
+      <c r="A84" s="20">
+        <v>12306</v>
+      </c>
+      <c r="B84" s="20" t="s">
         <v>221</v>
       </c>
-      <c r="D84" s="4">
-        <v>3</v>
-      </c>
-      <c r="E84" s="4" t="s">
+      <c r="D84" s="5">
+        <v>4</v>
+      </c>
+      <c r="E84" s="5" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="85" spans="1:5">
-      <c r="A85" s="23">
-        <v>12503</v>
-      </c>
-      <c r="B85" s="23" t="s">
+    <row r="85" s="5" customFormat="1" spans="1:5">
+      <c r="A85" s="19">
+        <v>12307</v>
+      </c>
+      <c r="B85" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="D85" s="4">
+      <c r="D85" s="5">
+        <v>2</v>
+      </c>
+      <c r="E85" s="5" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="A86" s="21">
+        <v>12501</v>
+      </c>
+      <c r="B86" s="21" t="s">
+        <v>225</v>
+      </c>
+      <c r="D86" s="4">
         <v>4</v>
-      </c>
-      <c r="E85" s="4" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5">
-      <c r="A86" s="23">
-        <v>12504</v>
-      </c>
-      <c r="B86" s="23" t="s">
-        <v>225</v>
-      </c>
-      <c r="D86" s="4">
-        <v>3</v>
       </c>
       <c r="E86" s="4" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="87" spans="1:5">
-      <c r="A87" s="4">
-        <v>12601</v>
-      </c>
-      <c r="B87" s="4" t="s">
+      <c r="A87" s="21">
+        <v>12502</v>
+      </c>
+      <c r="B87" s="21" t="s">
         <v>227</v>
       </c>
       <c r="D87" s="4">
@@ -3785,10 +3797,10 @@
       </c>
     </row>
     <row r="88" spans="1:5">
-      <c r="A88" s="4">
-        <v>12602</v>
-      </c>
-      <c r="B88" s="23" t="s">
+      <c r="A88" s="21">
+        <v>12503</v>
+      </c>
+      <c r="B88" s="21" t="s">
         <v>229</v>
       </c>
       <c r="D88" s="4">
@@ -3799,14 +3811,14 @@
       </c>
     </row>
     <row r="89" spans="1:5">
-      <c r="A89" s="4">
-        <v>12603</v>
-      </c>
-      <c r="B89" s="4" t="s">
+      <c r="A89" s="21">
+        <v>12504</v>
+      </c>
+      <c r="B89" s="21" t="s">
         <v>231</v>
       </c>
       <c r="D89" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E89" s="4" t="s">
         <v>232</v>
@@ -3814,7 +3826,7 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="4">
-        <v>12604</v>
+        <v>12601</v>
       </c>
       <c r="B90" s="4" t="s">
         <v>233</v>
@@ -3828,9 +3840,9 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="4">
-        <v>12605</v>
-      </c>
-      <c r="B91" s="4" t="s">
+        <v>12602</v>
+      </c>
+      <c r="B91" s="21" t="s">
         <v>235</v>
       </c>
       <c r="D91" s="4">
@@ -3842,13 +3854,13 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="4">
-        <v>12606</v>
+        <v>12603</v>
       </c>
       <c r="B92" s="4" t="s">
         <v>237</v>
       </c>
       <c r="D92" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E92" s="4" t="s">
         <v>238</v>
@@ -3856,13 +3868,13 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="4">
-        <v>12607</v>
+        <v>12604</v>
       </c>
       <c r="B93" s="4" t="s">
         <v>239</v>
       </c>
       <c r="D93" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E93" s="4" t="s">
         <v>240</v>
@@ -3870,13 +3882,13 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="4">
-        <v>12608</v>
+        <v>12605</v>
       </c>
       <c r="B94" s="4" t="s">
         <v>241</v>
       </c>
       <c r="D94" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E94" s="4" t="s">
         <v>242</v>
@@ -3884,13 +3896,13 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="4">
-        <v>12609</v>
+        <v>12606</v>
       </c>
       <c r="B95" s="4" t="s">
         <v>243</v>
       </c>
       <c r="D95" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E95" s="4" t="s">
         <v>244</v>
@@ -3898,13 +3910,13 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="4">
-        <v>12610</v>
+        <v>12607</v>
       </c>
       <c r="B96" s="4" t="s">
         <v>245</v>
       </c>
       <c r="D96" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E96" s="4" t="s">
         <v>246</v>
@@ -3912,7 +3924,7 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="4">
-        <v>12701</v>
+        <v>12608</v>
       </c>
       <c r="B97" s="4" t="s">
         <v>247</v>
@@ -3926,13 +3938,13 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="4">
-        <v>12702</v>
+        <v>12609</v>
       </c>
       <c r="B98" s="4" t="s">
         <v>249</v>
       </c>
       <c r="D98" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E98" s="4" t="s">
         <v>250</v>
@@ -3940,13 +3952,13 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="4">
-        <v>12703</v>
+        <v>12610</v>
       </c>
       <c r="B99" s="4" t="s">
         <v>251</v>
       </c>
       <c r="D99" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E99" s="4" t="s">
         <v>252</v>
@@ -3954,16 +3966,58 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="4">
-        <v>12704</v>
+        <v>12701</v>
       </c>
       <c r="B100" s="4" t="s">
         <v>253</v>
       </c>
       <c r="D100" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E100" s="4" t="s">
         <v>254</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5">
+      <c r="A101" s="4">
+        <v>12702</v>
+      </c>
+      <c r="B101" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="D101" s="4">
+        <v>2</v>
+      </c>
+      <c r="E101" s="4" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5">
+      <c r="A102" s="4">
+        <v>12703</v>
+      </c>
+      <c r="B102" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="D102" s="4">
+        <v>3</v>
+      </c>
+      <c r="E102" s="4" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5">
+      <c r="A103" s="4">
+        <v>12704</v>
+      </c>
+      <c r="B103" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="D103" s="4">
+        <v>3</v>
+      </c>
+      <c r="E103" s="4" t="s">
+        <v>260</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/condition.xlsx
+++ b/hall/resources/sample/condition.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\A-work\config_SimMgmtVert1.0\游戏配置表\common\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\common\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="condition" sheetId="1" r:id="rId1"/>
@@ -810,154 +810,154 @@
     <t>12277_游戏ID_技能ID_等级</t>
   </si>
   <si>
-    <t>游戏中奖倍数</t>
+    <t>接取：游戏中奖倍数</t>
   </si>
   <si>
     <t>12301_游戏ID（0=任意游戏）_大于等于总押注条件_游戏中奖具体倍数_大于等于中奖倍数的次数（接取任务后，截止到任务时间结束期间）</t>
   </si>
   <si>
-    <t>游戏下注次数(消耗能量)</t>
+    <t>接取：游戏下注次数(消耗能量)</t>
   </si>
   <si>
     <t>12302_游戏ID（0=任意游戏）_大于等于总押注条件_等于目标投注次数（接取任务后，截止到任务时间结束期间，消耗能量的下注）</t>
   </si>
   <si>
-    <t>卡池抽奖次数</t>
+    <t>接取：卡池抽奖次数</t>
   </si>
   <si>
     <t>12303_卡池ID（0=任意卡池）_卡池中抽奖的次数（接取任务后，截止到任务时间结束期间）</t>
   </si>
   <si>
-    <t>技能研究次数</t>
+    <t>接取：技能研究次数</t>
   </si>
   <si>
     <t>12304_游戏ID（0=任意游戏）_研究院游戏属性研究次数（接取任务后，截止到任务时间结束期间）</t>
   </si>
   <si>
-    <t>联盟捐献次数</t>
+    <t>接取：联盟捐献次数</t>
   </si>
   <si>
     <t>12305_大于等于捐献条件_大于等于目标的捐献次数（接取任务后，截止到任务时间结束期间）</t>
   </si>
   <si>
-    <t>游戏赢奖金额(时间限制)</t>
+    <t>接取：游戏赢奖金额(时间限制)</t>
   </si>
   <si>
     <t>12306_游戏ID（0=任意游戏）_大于等于总押注条件_货币ID_大于等于目标获胜金额（接取任务后，截止到任务时间结束期间，消耗能量的下注条件作为前提）</t>
   </si>
   <si>
-    <t>接取联盟任务后的个人累计充值(时间限制)</t>
+    <t>接取：接取联盟任务后的个人累计充值(时间限制)</t>
   </si>
   <si>
     <t>12307_接取任务后，截止到任务时间结束期间，渠道ID_个人累计充值大于等于金额</t>
   </si>
   <si>
-    <t>游戏下注次数(消耗能量,触发特殊模式)</t>
+    <t>接取：游戏下注次数(消耗能量,触发特殊模式)</t>
   </si>
   <si>
     <t>12501_游戏id（0=任意游戏）_下注具体次数_游戏模式id_触发模式次数</t>
   </si>
   <si>
-    <t>游戏下注次数（消耗能量，累计赢奖）</t>
+    <t>接取：游戏下注次数（消耗能量，累计赢奖）</t>
   </si>
   <si>
     <t>12502_游戏id（0=任意游戏）_下注具体次数_累计赢奖</t>
   </si>
   <si>
-    <t>游戏下注次数（消耗能量，触发大奖次数）</t>
+    <t>接取：游戏下注次数（消耗能量，触发大奖次数）</t>
   </si>
   <si>
     <t>12503_游戏id（0=任意游戏）_下注具体次数_中奖倍数（大于或等于此倍数）_大奖次数</t>
   </si>
   <si>
-    <t>游戏下注次数（消耗能量，累计下注金额）</t>
+    <t>接取：游戏下注次数（消耗能量，累计下注金额）</t>
   </si>
   <si>
     <t>12502_游戏id（0=任意游戏）_下注具体次数_累计下注金额</t>
   </si>
   <si>
-    <t>游戏赢奖金额（赛季玩法，累计赢奖）</t>
+    <t>累积：游戏赢奖金额（赛季玩法，累计赢奖）</t>
   </si>
   <si>
     <t>12601_游戏id（0=任意游戏）_下注具体次数_累计赢奖</t>
   </si>
   <si>
-    <t>游戏下注次数(赛季玩法,触发特殊模式)</t>
+    <t>累积：游戏下注次数(赛季玩法,触发特殊模式)</t>
   </si>
   <si>
     <t>12602_游戏id（0=任意游戏）_下注具体次数_游戏模式id_触发模式次数</t>
   </si>
   <si>
-    <t>游戏中奖倍数（赛季玩法）</t>
+    <t>累积：游戏中奖倍数（赛季玩法）</t>
   </si>
   <si>
     <t>12603_游戏ID（0=任意游戏）_下注具体次数_游戏中奖具体倍数_大于等于中奖倍数的次数</t>
   </si>
   <si>
-    <t>游戏中奖次数（赛季玩法）</t>
+    <t>累积：游戏中奖次数（赛季玩法）</t>
   </si>
   <si>
     <t>12604_游戏ID（0=任意游戏）_下注具体次数_中奖次数</t>
   </si>
   <si>
-    <t>游戏图标出现次数（赛季玩法）</t>
+    <t>累积：游戏图标出现次数（赛季玩法）</t>
   </si>
   <si>
     <t>12605_游戏ID（0=任意游戏）_下注具体次数_游戏元素ID_出现的次数</t>
   </si>
   <si>
-    <t>游戏某局的中奖金额（赛季玩法）</t>
+    <t>累积：游戏某局的中奖金额（赛季玩法）</t>
   </si>
   <si>
     <t>12606_游戏ID（0=任意游戏）_下注具体次数_任意局数大于等于目标获胜金额</t>
   </si>
   <si>
-    <t>游戏竞技匹配次数（赛季玩法）</t>
+    <t>累积：游戏竞技匹配次数（赛季玩法）</t>
   </si>
   <si>
     <t>12607_游戏ID（0=任意游戏）_竞技匹配成功的次数</t>
   </si>
   <si>
-    <t>宝石掉落次数（赛季玩法）</t>
+    <t>累积：宝石掉落次数（赛季玩法）</t>
   </si>
   <si>
     <t>12608_游戏ID（0=任意游戏）_宝石掉落的次数</t>
   </si>
   <si>
-    <t>赛季币累计赢取金额（赛季玩法）</t>
+    <t>累积：赛季币累计赢取金额（赛季玩法）</t>
   </si>
   <si>
     <t>12609_游戏ID(0 = 任意游戏)（不区分倍场）_大于等于总押注条件_货币ID(赛季币)_大于等于目标获胜金额</t>
   </si>
   <si>
-    <t>游戏投注次数（赛季玩法）</t>
+    <t>累积：游戏投注次数（赛季玩法）</t>
   </si>
   <si>
     <t>12610_游戏ID(0 = 任意游戏)（不区分倍场)_大于等于总押注条件_货币ID(赛季币)_等于目标投注次数</t>
   </si>
   <si>
-    <t>挖掘格子数量</t>
-  </si>
-  <si>
-    <t>12701_游戏ID（0=任意游戏）_挖掘格子的数量</t>
-  </si>
-  <si>
-    <t>挖掘深度</t>
-  </si>
-  <si>
-    <t>12702_游戏ID（0=任意游戏）_挖掘的深度</t>
-  </si>
-  <si>
-    <t>挖掘过程使用的道具</t>
-  </si>
-  <si>
-    <t>12702_游戏ID（0=任意游戏）_挖掘使用的道具ID_挖掘使用该道具的数量</t>
-  </si>
-  <si>
-    <t>在挖矿小游戏中兑换的次数</t>
-  </si>
-  <si>
-    <t>12702_游戏ID（0=任意游戏）_在兑换商店使用兑换物的ID（0=所有兑换物）_兑换的次数</t>
+    <t>累积：挖掘格子数量</t>
+  </si>
+  <si>
+    <t>12701_挖掘格子的数量</t>
+  </si>
+  <si>
+    <t>累积：挖掘深度</t>
+  </si>
+  <si>
+    <t>12702_挖掘的深度</t>
+  </si>
+  <si>
+    <t>累积：挖掘过程使用的道具</t>
+  </si>
+  <si>
+    <t>12702_挖掘使用的道具ID_挖掘使用该道具的数量</t>
+  </si>
+  <si>
+    <t>累积：在挖矿小游戏中兑换的次数</t>
+  </si>
+  <si>
+    <t>12702_在兑换商店使用兑换物的ID（0=所有兑换物）_兑换的次数</t>
   </si>
 </sst>
 </file>
@@ -3972,7 +3972,7 @@
         <v>253</v>
       </c>
       <c r="D100" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E100" s="4" t="s">
         <v>254</v>
@@ -3986,7 +3986,7 @@
         <v>255</v>
       </c>
       <c r="D101" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E101" s="4" t="s">
         <v>256</v>
@@ -4000,7 +4000,7 @@
         <v>257</v>
       </c>
       <c r="D102" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E102" s="4" t="s">
         <v>258</v>
@@ -4014,7 +4014,7 @@
         <v>259</v>
       </c>
       <c r="D103" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E103" s="4" t="s">
         <v>260</v>

--- a/hall/resources/sample/condition.xlsx
+++ b/hall/resources/sample/condition.xlsx
@@ -789,7 +789,7 @@
     <t>累积：指定\任意SLOT游戏赢钱</t>
   </si>
   <si>
-    <t>12276_游戏ID(0 = 任意游戏)（不区分倍场）_货币ID(金币或钻石)_赢钱数量(投注赢钱+各类模式赢钱，除 好友提供的加成外)</t>
+    <t>12274_游戏ID(0 = 任意游戏)（不区分倍场）_货币ID(金币或钻石)_赢钱数量(投注赢钱+各类模式赢钱，除 好友提供的加成外)</t>
   </si>
   <si>
     <t>累积：指定SLOT游戏触发财神到模式的次数</t>

--- a/hall/resources/sample/condition.xlsx
+++ b/hall/resources/sample/condition.xlsx
@@ -170,12 +170,38 @@
         </r>
       </text>
     </comment>
+    <comment ref="E83" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1 - 白色品质
+2 - 绿色品质
+3 - 蓝色品质
+4 - 紫色品质
+5 - 金色品质</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="273">
   <si>
     <t>id</t>
   </si>
@@ -808,6 +834,42 @@
   </si>
   <si>
     <t>12277_游戏ID_技能ID_等级</t>
+  </si>
+  <si>
+    <t>累积：联盟捐献次数</t>
+  </si>
+  <si>
+    <t>12278_次数</t>
+  </si>
+  <si>
+    <t>累积：拜访过程中赠送礼物的次数</t>
+  </si>
+  <si>
+    <t>12279_次数</t>
+  </si>
+  <si>
+    <t>累积：拜访过程中试玩别人slot游戏的次数</t>
+  </si>
+  <si>
+    <t>12280_游戏ID（0=任意游戏）_次数</t>
+  </si>
+  <si>
+    <t>累积：完成斗仙牌N次</t>
+  </si>
+  <si>
+    <t>12281_次数(开始游戏并结算)</t>
+  </si>
+  <si>
+    <t>累积：赛季宝石合成N次</t>
+  </si>
+  <si>
+    <t>12282_宝石品质（0=不限品质）_次数</t>
+  </si>
+  <si>
+    <t>累积：卡池抽卡次数（不管游客还是雇员）</t>
+  </si>
+  <si>
+    <t>12283_次数</t>
   </si>
   <si>
     <t>接取：游戏中奖倍数</t>
@@ -2047,7 +2109,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O103"/>
+  <dimension ref="A1:O109"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="4"/>
@@ -3670,193 +3732,217 @@
       <c r="G78" s="4"/>
       <c r="H78" s="4"/>
     </row>
-    <row r="79" spans="1:8">
-      <c r="A79" s="19">
-        <v>12301</v>
-      </c>
-      <c r="B79" s="19" t="s">
+    <row r="79" customFormat="1" spans="1:8">
+      <c r="A79" s="18">
+        <v>12278</v>
+      </c>
+      <c r="B79" s="18" t="s">
         <v>211</v>
       </c>
+      <c r="C79" s="4"/>
       <c r="D79" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E79" s="4" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="80" s="5" customFormat="1" spans="1:8">
-      <c r="A80" s="20">
-        <v>12302</v>
-      </c>
-      <c r="B80" s="20" t="s">
+      <c r="F79" s="4"/>
+      <c r="G79" s="4"/>
+      <c r="H79" s="4"/>
+    </row>
+    <row r="80" customFormat="1" spans="1:8">
+      <c r="A80" s="18">
+        <v>12279</v>
+      </c>
+      <c r="B80" s="18" t="s">
         <v>213</v>
       </c>
-      <c r="D80" s="5">
-        <v>3</v>
-      </c>
-      <c r="E80" s="5" t="s">
+      <c r="C80" s="4"/>
+      <c r="D80" s="4">
+        <v>1</v>
+      </c>
+      <c r="E80" s="4" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="19">
-        <v>12303</v>
-      </c>
-      <c r="B81" s="19" t="s">
+      <c r="F80" s="4"/>
+      <c r="G80" s="4"/>
+      <c r="H80" s="4"/>
+    </row>
+    <row r="81" customFormat="1" spans="1:8">
+      <c r="A81" s="18">
+        <v>12280</v>
+      </c>
+      <c r="B81" s="18" t="s">
         <v>215</v>
       </c>
+      <c r="C81" s="4"/>
       <c r="D81" s="4">
         <v>2</v>
       </c>
       <c r="E81" s="4" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="82" spans="1:5">
-      <c r="A82" s="20">
-        <v>12304</v>
-      </c>
-      <c r="B82" s="19" t="s">
+      <c r="F81" s="4"/>
+      <c r="G81" s="4"/>
+      <c r="H81" s="4"/>
+    </row>
+    <row r="82" customFormat="1" spans="1:8">
+      <c r="A82" s="18">
+        <v>12281</v>
+      </c>
+      <c r="B82" s="18" t="s">
         <v>217</v>
       </c>
+      <c r="C82" s="4"/>
       <c r="D82" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E82" s="4" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="83" spans="1:5">
-      <c r="A83" s="19">
-        <v>12305</v>
-      </c>
-      <c r="B83" s="19" t="s">
+      <c r="F82" s="4"/>
+      <c r="G82" s="4"/>
+      <c r="H82" s="4"/>
+    </row>
+    <row r="83" customFormat="1" spans="1:8">
+      <c r="A83" s="18">
+        <v>12282</v>
+      </c>
+      <c r="B83" s="18" t="s">
         <v>219</v>
       </c>
+      <c r="C83" s="4"/>
       <c r="D83" s="4">
         <v>2</v>
       </c>
       <c r="E83" s="4" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="84" s="5" customFormat="1" spans="1:5">
-      <c r="A84" s="20">
-        <v>12306</v>
-      </c>
-      <c r="B84" s="20" t="s">
+      <c r="F83" s="4"/>
+      <c r="G83" s="4"/>
+      <c r="H83" s="4"/>
+    </row>
+    <row r="84" customFormat="1" spans="1:8">
+      <c r="A84" s="18">
+        <v>12283</v>
+      </c>
+      <c r="B84" s="18" t="s">
         <v>221</v>
       </c>
-      <c r="D84" s="5">
+      <c r="C84" s="4"/>
+      <c r="D84" s="4">
+        <v>1</v>
+      </c>
+      <c r="E84" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="F84" s="4"/>
+      <c r="G84" s="4"/>
+      <c r="H84" s="4"/>
+    </row>
+    <row r="85" spans="1:8">
+      <c r="A85" s="19">
+        <v>12301</v>
+      </c>
+      <c r="B85" s="19" t="s">
+        <v>223</v>
+      </c>
+      <c r="D85" s="4">
         <v>4</v>
       </c>
-      <c r="E84" s="5" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="85" s="5" customFormat="1" spans="1:5">
-      <c r="A85" s="19">
-        <v>12307</v>
-      </c>
-      <c r="B85" s="20" t="s">
-        <v>223</v>
-      </c>
-      <c r="D85" s="5">
-        <v>2</v>
-      </c>
-      <c r="E85" s="5" t="s">
+      <c r="E85" s="4" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="86" spans="1:5">
-      <c r="A86" s="21">
-        <v>12501</v>
-      </c>
-      <c r="B86" s="21" t="s">
+    <row r="86" s="5" customFormat="1" spans="1:8">
+      <c r="A86" s="20">
+        <v>12302</v>
+      </c>
+      <c r="B86" s="20" t="s">
         <v>225</v>
       </c>
-      <c r="D86" s="4">
-        <v>4</v>
-      </c>
-      <c r="E86" s="4" t="s">
+      <c r="D86" s="5">
+        <v>3</v>
+      </c>
+      <c r="E86" s="5" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="87" spans="1:5">
-      <c r="A87" s="21">
-        <v>12502</v>
-      </c>
-      <c r="B87" s="21" t="s">
+    <row r="87" spans="1:8">
+      <c r="A87" s="19">
+        <v>12303</v>
+      </c>
+      <c r="B87" s="19" t="s">
         <v>227</v>
       </c>
       <c r="D87" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E87" s="4" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="88" spans="1:5">
-      <c r="A88" s="21">
-        <v>12503</v>
-      </c>
-      <c r="B88" s="21" t="s">
+    <row r="88" spans="1:8">
+      <c r="A88" s="20">
+        <v>12304</v>
+      </c>
+      <c r="B88" s="19" t="s">
         <v>229</v>
       </c>
       <c r="D88" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E88" s="4" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="89" spans="1:5">
-      <c r="A89" s="21">
-        <v>12504</v>
-      </c>
-      <c r="B89" s="21" t="s">
+    <row r="89" spans="1:8">
+      <c r="A89" s="19">
+        <v>12305</v>
+      </c>
+      <c r="B89" s="19" t="s">
         <v>231</v>
       </c>
       <c r="D89" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E89" s="4" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="90" spans="1:5">
-      <c r="A90" s="4">
-        <v>12601</v>
-      </c>
-      <c r="B90" s="4" t="s">
+    <row r="90" s="5" customFormat="1" spans="1:8">
+      <c r="A90" s="20">
+        <v>12306</v>
+      </c>
+      <c r="B90" s="20" t="s">
         <v>233</v>
       </c>
-      <c r="D90" s="4">
-        <v>3</v>
-      </c>
-      <c r="E90" s="4" t="s">
+      <c r="D90" s="5">
+        <v>4</v>
+      </c>
+      <c r="E90" s="5" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="91" spans="1:5">
-      <c r="A91" s="4">
-        <v>12602</v>
-      </c>
-      <c r="B91" s="21" t="s">
+    <row r="91" s="5" customFormat="1" spans="1:8">
+      <c r="A91" s="19">
+        <v>12307</v>
+      </c>
+      <c r="B91" s="20" t="s">
         <v>235</v>
       </c>
-      <c r="D91" s="4">
-        <v>4</v>
-      </c>
-      <c r="E91" s="4" t="s">
+      <c r="D91" s="5">
+        <v>2</v>
+      </c>
+      <c r="E91" s="5" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="92" spans="1:5">
-      <c r="A92" s="4">
-        <v>12603</v>
-      </c>
-      <c r="B92" s="4" t="s">
+    <row r="92" spans="1:8">
+      <c r="A92" s="21">
+        <v>12501</v>
+      </c>
+      <c r="B92" s="21" t="s">
         <v>237</v>
       </c>
       <c r="D92" s="4">
@@ -3866,11 +3952,11 @@
         <v>238</v>
       </c>
     </row>
-    <row r="93" spans="1:5">
-      <c r="A93" s="4">
-        <v>12604</v>
-      </c>
-      <c r="B93" s="4" t="s">
+    <row r="93" spans="1:8">
+      <c r="A93" s="21">
+        <v>12502</v>
+      </c>
+      <c r="B93" s="21" t="s">
         <v>239</v>
       </c>
       <c r="D93" s="4">
@@ -3880,11 +3966,11 @@
         <v>240</v>
       </c>
     </row>
-    <row r="94" spans="1:5">
-      <c r="A94" s="4">
-        <v>12605</v>
-      </c>
-      <c r="B94" s="4" t="s">
+    <row r="94" spans="1:8">
+      <c r="A94" s="21">
+        <v>12503</v>
+      </c>
+      <c r="B94" s="21" t="s">
         <v>241</v>
       </c>
       <c r="D94" s="4">
@@ -3894,11 +3980,11 @@
         <v>242</v>
       </c>
     </row>
-    <row r="95" spans="1:5">
-      <c r="A95" s="4">
-        <v>12606</v>
-      </c>
-      <c r="B95" s="4" t="s">
+    <row r="95" spans="1:8">
+      <c r="A95" s="21">
+        <v>12504</v>
+      </c>
+      <c r="B95" s="21" t="s">
         <v>243</v>
       </c>
       <c r="D95" s="4">
@@ -3908,15 +3994,15 @@
         <v>244</v>
       </c>
     </row>
-    <row r="96" spans="1:5">
+    <row r="96" spans="1:8">
       <c r="A96" s="4">
-        <v>12607</v>
+        <v>12601</v>
       </c>
       <c r="B96" s="4" t="s">
         <v>245</v>
       </c>
       <c r="D96" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E96" s="4" t="s">
         <v>246</v>
@@ -3924,13 +4010,13 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="4">
-        <v>12608</v>
-      </c>
-      <c r="B97" s="4" t="s">
+        <v>12602</v>
+      </c>
+      <c r="B97" s="21" t="s">
         <v>247</v>
       </c>
       <c r="D97" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E97" s="4" t="s">
         <v>248</v>
@@ -3938,7 +4024,7 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="4">
-        <v>12609</v>
+        <v>12603</v>
       </c>
       <c r="B98" s="4" t="s">
         <v>249</v>
@@ -3952,13 +4038,13 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="4">
-        <v>12610</v>
+        <v>12604</v>
       </c>
       <c r="B99" s="4" t="s">
         <v>251</v>
       </c>
       <c r="D99" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E99" s="4" t="s">
         <v>252</v>
@@ -3966,13 +4052,13 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="4">
-        <v>12701</v>
+        <v>12605</v>
       </c>
       <c r="B100" s="4" t="s">
         <v>253</v>
       </c>
       <c r="D100" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E100" s="4" t="s">
         <v>254</v>
@@ -3980,13 +4066,13 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="4">
-        <v>12702</v>
+        <v>12606</v>
       </c>
       <c r="B101" s="4" t="s">
         <v>255</v>
       </c>
       <c r="D101" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E101" s="4" t="s">
         <v>256</v>
@@ -3994,7 +4080,7 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="4">
-        <v>12703</v>
+        <v>12607</v>
       </c>
       <c r="B102" s="4" t="s">
         <v>257</v>
@@ -4008,7 +4094,7 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="4">
-        <v>12704</v>
+        <v>12608</v>
       </c>
       <c r="B103" s="4" t="s">
         <v>259</v>
@@ -4018,6 +4104,90 @@
       </c>
       <c r="E103" s="4" t="s">
         <v>260</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5">
+      <c r="A104" s="4">
+        <v>12609</v>
+      </c>
+      <c r="B104" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="D104" s="4">
+        <v>4</v>
+      </c>
+      <c r="E104" s="4" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5">
+      <c r="A105" s="4">
+        <v>12610</v>
+      </c>
+      <c r="B105" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="D105" s="4">
+        <v>4</v>
+      </c>
+      <c r="E105" s="4" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5">
+      <c r="A106" s="4">
+        <v>12701</v>
+      </c>
+      <c r="B106" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="D106" s="4">
+        <v>1</v>
+      </c>
+      <c r="E106" s="4" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5">
+      <c r="A107" s="4">
+        <v>12702</v>
+      </c>
+      <c r="B107" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="D107" s="4">
+        <v>1</v>
+      </c>
+      <c r="E107" s="4" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5">
+      <c r="A108" s="4">
+        <v>12703</v>
+      </c>
+      <c r="B108" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D108" s="4">
+        <v>2</v>
+      </c>
+      <c r="E108" s="4" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5">
+      <c r="A109" s="4">
+        <v>12704</v>
+      </c>
+      <c r="B109" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="D109" s="4">
+        <v>2</v>
+      </c>
+      <c r="E109" s="4" t="s">
+        <v>272</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/condition.xlsx
+++ b/hall/resources/sample/condition.xlsx
@@ -201,7 +201,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="275">
   <si>
     <t>id</t>
   </si>
@@ -872,6 +872,12 @@
     <t>12283_次数</t>
   </si>
   <si>
+    <t>累积：签到次数</t>
+  </si>
+  <si>
+    <t>12284_次数</t>
+  </si>
+  <si>
     <t>接取：游戏中奖倍数</t>
   </si>
   <si>
@@ -914,109 +920,109 @@
     <t>12307_接取任务后，截止到任务时间结束期间，渠道ID_个人累计充值大于等于金额</t>
   </si>
   <si>
-    <t>接取：游戏下注次数(消耗能量,触发特殊模式)</t>
+    <t>多人任务：游戏下注次数(消耗能量,触发特殊模式)</t>
   </si>
   <si>
     <t>12501_游戏id（0=任意游戏）_下注具体次数_游戏模式id_触发模式次数</t>
   </si>
   <si>
-    <t>接取：游戏下注次数（消耗能量，累计赢奖）</t>
+    <t>多人任务：游戏下注次数（消耗能量，累计赢奖）</t>
   </si>
   <si>
     <t>12502_游戏id（0=任意游戏）_下注具体次数_累计赢奖</t>
   </si>
   <si>
-    <t>接取：游戏下注次数（消耗能量，触发大奖次数）</t>
+    <t>多人任务：游戏下注次数（消耗能量，触发大奖次数）</t>
   </si>
   <si>
     <t>12503_游戏id（0=任意游戏）_下注具体次数_中奖倍数（大于或等于此倍数）_大奖次数</t>
   </si>
   <si>
-    <t>接取：游戏下注次数（消耗能量，累计下注金额）</t>
+    <t>多人任务：游戏下注次数（消耗能量，累计下注金额）</t>
   </si>
   <si>
     <t>12502_游戏id（0=任意游戏）_下注具体次数_累计下注金额</t>
   </si>
   <si>
-    <t>累积：游戏赢奖金额（赛季玩法，累计赢奖）</t>
+    <t>接取：游戏赢奖金额（赛季玩法，累计赢奖）</t>
   </si>
   <si>
     <t>12601_游戏id（0=任意游戏）_下注具体次数_累计赢奖</t>
   </si>
   <si>
-    <t>累积：游戏下注次数(赛季玩法,触发特殊模式)</t>
+    <t>接取：游戏下注次数(赛季玩法,触发特殊模式)</t>
   </si>
   <si>
     <t>12602_游戏id（0=任意游戏）_下注具体次数_游戏模式id_触发模式次数</t>
   </si>
   <si>
-    <t>累积：游戏中奖倍数（赛季玩法）</t>
+    <t>接取：游戏中奖倍数（赛季玩法）</t>
   </si>
   <si>
     <t>12603_游戏ID（0=任意游戏）_下注具体次数_游戏中奖具体倍数_大于等于中奖倍数的次数</t>
   </si>
   <si>
-    <t>累积：游戏中奖次数（赛季玩法）</t>
+    <t>接取：游戏中奖次数（赛季玩法）</t>
   </si>
   <si>
     <t>12604_游戏ID（0=任意游戏）_下注具体次数_中奖次数</t>
   </si>
   <si>
-    <t>累积：游戏图标出现次数（赛季玩法）</t>
+    <t>接取：游戏图标出现次数（赛季玩法）</t>
   </si>
   <si>
     <t>12605_游戏ID（0=任意游戏）_下注具体次数_游戏元素ID_出现的次数</t>
   </si>
   <si>
-    <t>累积：游戏某局的中奖金额（赛季玩法）</t>
+    <t>接取：游戏某局的中奖金额（赛季玩法）</t>
   </si>
   <si>
     <t>12606_游戏ID（0=任意游戏）_下注具体次数_任意局数大于等于目标获胜金额</t>
   </si>
   <si>
-    <t>累积：游戏竞技匹配次数（赛季玩法）</t>
+    <t>接取：游戏竞技匹配次数（赛季玩法）</t>
   </si>
   <si>
     <t>12607_游戏ID（0=任意游戏）_竞技匹配成功的次数</t>
   </si>
   <si>
-    <t>累积：宝石掉落次数（赛季玩法）</t>
+    <t>接取：宝石掉落次数（赛季玩法）</t>
   </si>
   <si>
     <t>12608_游戏ID（0=任意游戏）_宝石掉落的次数</t>
   </si>
   <si>
-    <t>累积：赛季币累计赢取金额（赛季玩法）</t>
+    <t>接取：赛季币累计赢取金额（赛季玩法）</t>
   </si>
   <si>
     <t>12609_游戏ID(0 = 任意游戏)（不区分倍场）_大于等于总押注条件_货币ID(赛季币)_大于等于目标获胜金额</t>
   </si>
   <si>
-    <t>累积：游戏投注次数（赛季玩法）</t>
+    <t>接取：游戏投注次数（赛季玩法）</t>
   </si>
   <si>
     <t>12610_游戏ID(0 = 任意游戏)（不区分倍场)_大于等于总押注条件_货币ID(赛季币)_等于目标投注次数</t>
   </si>
   <si>
-    <t>累积：挖掘格子数量</t>
+    <t>接取：挖掘格子数量</t>
   </si>
   <si>
     <t>12701_挖掘格子的数量</t>
   </si>
   <si>
-    <t>累积：挖掘深度</t>
+    <t>接取：挖掘深度</t>
   </si>
   <si>
     <t>12702_挖掘的深度</t>
   </si>
   <si>
-    <t>累积：挖掘过程使用的道具</t>
+    <t>接取：挖掘过程使用的道具</t>
   </si>
   <si>
     <t>12702_挖掘使用的道具ID_挖掘使用该道具的数量</t>
   </si>
   <si>
-    <t>累积：在挖矿小游戏中兑换的次数</t>
+    <t>接取：在挖矿小游戏中兑换的次数</t>
   </si>
   <si>
     <t>12702_在兑换商店使用兑换物的ID（0=所有兑换物）_兑换的次数</t>
@@ -2109,7 +2115,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O109"/>
+  <dimension ref="A1:O110"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="4"/>
@@ -3840,51 +3846,55 @@
       <c r="G84" s="4"/>
       <c r="H84" s="4"/>
     </row>
-    <row r="85" spans="1:8">
-      <c r="A85" s="19">
-        <v>12301</v>
-      </c>
-      <c r="B85" s="19" t="s">
+    <row r="85" customFormat="1" spans="1:8">
+      <c r="A85" s="18">
+        <v>12284</v>
+      </c>
+      <c r="B85" s="18" t="s">
         <v>223</v>
       </c>
+      <c r="C85" s="4"/>
       <c r="D85" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E85" s="4" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="86" s="5" customFormat="1" spans="1:8">
-      <c r="A86" s="20">
+      <c r="F85" s="4"/>
+      <c r="G85" s="4"/>
+      <c r="H85" s="4"/>
+    </row>
+    <row r="86" spans="1:8">
+      <c r="A86" s="19">
+        <v>12301</v>
+      </c>
+      <c r="B86" s="19" t="s">
+        <v>225</v>
+      </c>
+      <c r="D86" s="4">
+        <v>4</v>
+      </c>
+      <c r="E86" s="4" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="87" s="5" customFormat="1" spans="1:8">
+      <c r="A87" s="20">
         <v>12302</v>
       </c>
-      <c r="B86" s="20" t="s">
-        <v>225</v>
-      </c>
-      <c r="D86" s="5">
+      <c r="B87" s="20" t="s">
+        <v>227</v>
+      </c>
+      <c r="D87" s="5">
         <v>3</v>
       </c>
-      <c r="E86" s="5" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8">
-      <c r="A87" s="19">
+      <c r="E87" s="5" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8">
+      <c r="A88" s="19">
         <v>12303</v>
-      </c>
-      <c r="B87" s="19" t="s">
-        <v>227</v>
-      </c>
-      <c r="D87" s="4">
-        <v>2</v>
-      </c>
-      <c r="E87" s="4" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8">
-      <c r="A88" s="20">
-        <v>12304</v>
       </c>
       <c r="B88" s="19" t="s">
         <v>229</v>
@@ -3897,8 +3907,8 @@
       </c>
     </row>
     <row r="89" spans="1:8">
-      <c r="A89" s="19">
-        <v>12305</v>
+      <c r="A89" s="20">
+        <v>12304</v>
       </c>
       <c r="B89" s="19" t="s">
         <v>231</v>
@@ -3910,57 +3920,57 @@
         <v>232</v>
       </c>
     </row>
-    <row r="90" s="5" customFormat="1" spans="1:8">
-      <c r="A90" s="20">
+    <row r="90" spans="1:8">
+      <c r="A90" s="19">
+        <v>12305</v>
+      </c>
+      <c r="B90" s="19" t="s">
+        <v>233</v>
+      </c>
+      <c r="D90" s="4">
+        <v>2</v>
+      </c>
+      <c r="E90" s="4" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="91" s="5" customFormat="1" spans="1:8">
+      <c r="A91" s="20">
         <v>12306</v>
-      </c>
-      <c r="B90" s="20" t="s">
-        <v>233</v>
-      </c>
-      <c r="D90" s="5">
-        <v>4</v>
-      </c>
-      <c r="E90" s="5" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="91" s="5" customFormat="1" spans="1:8">
-      <c r="A91" s="19">
-        <v>12307</v>
       </c>
       <c r="B91" s="20" t="s">
         <v>235</v>
       </c>
       <c r="D91" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E91" s="5" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="92" spans="1:8">
-      <c r="A92" s="21">
-        <v>12501</v>
-      </c>
-      <c r="B92" s="21" t="s">
+    <row r="92" s="5" customFormat="1" spans="1:8">
+      <c r="A92" s="19">
+        <v>12307</v>
+      </c>
+      <c r="B92" s="20" t="s">
         <v>237</v>
       </c>
-      <c r="D92" s="4">
-        <v>4</v>
-      </c>
-      <c r="E92" s="4" t="s">
+      <c r="D92" s="5">
+        <v>2</v>
+      </c>
+      <c r="E92" s="5" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="93" spans="1:8">
       <c r="A93" s="21">
-        <v>12502</v>
+        <v>12501</v>
       </c>
       <c r="B93" s="21" t="s">
         <v>239</v>
       </c>
       <c r="D93" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E93" s="4" t="s">
         <v>240</v>
@@ -3968,13 +3978,13 @@
     </row>
     <row r="94" spans="1:8">
       <c r="A94" s="21">
-        <v>12503</v>
+        <v>12502</v>
       </c>
       <c r="B94" s="21" t="s">
         <v>241</v>
       </c>
       <c r="D94" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E94" s="4" t="s">
         <v>242</v>
@@ -3982,23 +3992,23 @@
     </row>
     <row r="95" spans="1:8">
       <c r="A95" s="21">
-        <v>12504</v>
+        <v>12503</v>
       </c>
       <c r="B95" s="21" t="s">
         <v>243</v>
       </c>
       <c r="D95" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E95" s="4" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="96" spans="1:8">
-      <c r="A96" s="4">
-        <v>12601</v>
-      </c>
-      <c r="B96" s="4" t="s">
+      <c r="A96" s="21">
+        <v>12504</v>
+      </c>
+      <c r="B96" s="21" t="s">
         <v>245</v>
       </c>
       <c r="D96" s="4">
@@ -4010,13 +4020,13 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="4">
-        <v>12602</v>
-      </c>
-      <c r="B97" s="21" t="s">
+        <v>12601</v>
+      </c>
+      <c r="B97" s="4" t="s">
         <v>247</v>
       </c>
       <c r="D97" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E97" s="4" t="s">
         <v>248</v>
@@ -4024,9 +4034,9 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="4">
-        <v>12603</v>
-      </c>
-      <c r="B98" s="4" t="s">
+        <v>12602</v>
+      </c>
+      <c r="B98" s="21" t="s">
         <v>249</v>
       </c>
       <c r="D98" s="4">
@@ -4038,13 +4048,13 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="4">
-        <v>12604</v>
+        <v>12603</v>
       </c>
       <c r="B99" s="4" t="s">
         <v>251</v>
       </c>
       <c r="D99" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E99" s="4" t="s">
         <v>252</v>
@@ -4052,13 +4062,13 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="4">
-        <v>12605</v>
+        <v>12604</v>
       </c>
       <c r="B100" s="4" t="s">
         <v>253</v>
       </c>
       <c r="D100" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E100" s="4" t="s">
         <v>254</v>
@@ -4066,13 +4076,13 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="4">
-        <v>12606</v>
+        <v>12605</v>
       </c>
       <c r="B101" s="4" t="s">
         <v>255</v>
       </c>
       <c r="D101" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E101" s="4" t="s">
         <v>256</v>
@@ -4080,13 +4090,13 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="4">
-        <v>12607</v>
+        <v>12606</v>
       </c>
       <c r="B102" s="4" t="s">
         <v>257</v>
       </c>
       <c r="D102" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E102" s="4" t="s">
         <v>258</v>
@@ -4094,7 +4104,7 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="4">
-        <v>12608</v>
+        <v>12607</v>
       </c>
       <c r="B103" s="4" t="s">
         <v>259</v>
@@ -4108,13 +4118,13 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="4">
-        <v>12609</v>
+        <v>12608</v>
       </c>
       <c r="B104" s="4" t="s">
         <v>261</v>
       </c>
       <c r="D104" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E104" s="4" t="s">
         <v>262</v>
@@ -4122,7 +4132,7 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="4">
-        <v>12610</v>
+        <v>12609</v>
       </c>
       <c r="B105" s="4" t="s">
         <v>263</v>
@@ -4136,13 +4146,13 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="4">
-        <v>12701</v>
+        <v>12610</v>
       </c>
       <c r="B106" s="4" t="s">
         <v>265</v>
       </c>
       <c r="D106" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E106" s="4" t="s">
         <v>266</v>
@@ -4150,7 +4160,7 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="4">
-        <v>12702</v>
+        <v>12701</v>
       </c>
       <c r="B107" s="4" t="s">
         <v>267</v>
@@ -4164,13 +4174,13 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="4">
-        <v>12703</v>
+        <v>12702</v>
       </c>
       <c r="B108" s="4" t="s">
         <v>269</v>
       </c>
       <c r="D108" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E108" s="4" t="s">
         <v>270</v>
@@ -4178,7 +4188,7 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="4">
-        <v>12704</v>
+        <v>12703</v>
       </c>
       <c r="B109" s="4" t="s">
         <v>271</v>
@@ -4188,6 +4198,20 @@
       </c>
       <c r="E109" s="4" t="s">
         <v>272</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5">
+      <c r="A110" s="4">
+        <v>12704</v>
+      </c>
+      <c r="B110" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="D110" s="4">
+        <v>2</v>
+      </c>
+      <c r="E110" s="4" t="s">
+        <v>274</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/condition.xlsx
+++ b/hall/resources/sample/condition.xlsx
@@ -133,6 +133,28 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
+所有场景等级之和</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E56" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
 大奖名称	大奖类型
 sweet win	1
 big win	2
@@ -143,7 +165,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E55" authorId="0">
+    <comment ref="E57" authorId="0">
       <text>
         <r>
           <rPr>
@@ -170,7 +192,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E83" authorId="0">
+    <comment ref="E85" authorId="0">
       <text>
         <r>
           <rPr>
@@ -201,7 +223,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="279">
   <si>
     <t>id</t>
   </si>
@@ -680,6 +702,18 @@
     <t>12227_次数</t>
   </si>
   <si>
+    <t>接取：签到次数</t>
+  </si>
+  <si>
+    <t>12228_次数</t>
+  </si>
+  <si>
+    <t>接取：场景等级</t>
+  </si>
+  <si>
+    <t>12229_等级</t>
+  </si>
+  <si>
     <t>累积：在SLOT游戏中获得N个X道具</t>
   </si>
   <si>
@@ -872,12 +906,6 @@
     <t>12283_次数</t>
   </si>
   <si>
-    <t>累积：签到次数</t>
-  </si>
-  <si>
-    <t>12284_次数</t>
-  </si>
-  <si>
     <t>接取：游戏中奖倍数</t>
   </si>
   <si>
@@ -944,40 +972,40 @@
     <t>12502_游戏id（0=任意游戏）_下注具体次数_累计下注金额</t>
   </si>
   <si>
-    <t>接取：游戏赢奖金额（赛季玩法，累计赢奖）</t>
-  </si>
-  <si>
-    <t>12601_游戏id（0=任意游戏）_下注具体次数_累计赢奖</t>
-  </si>
-  <si>
-    <t>接取：游戏下注次数(赛季玩法,触发特殊模式)</t>
-  </si>
-  <si>
-    <t>12602_游戏id（0=任意游戏）_下注具体次数_游戏模式id_触发模式次数</t>
-  </si>
-  <si>
-    <t>接取：游戏中奖倍数（赛季玩法）</t>
-  </si>
-  <si>
-    <t>12603_游戏ID（0=任意游戏）_下注具体次数_游戏中奖具体倍数_大于等于中奖倍数的次数</t>
-  </si>
-  <si>
-    <t>接取：游戏中奖次数（赛季玩法）</t>
-  </si>
-  <si>
-    <t>12604_游戏ID（0=任意游戏）_下注具体次数_中奖次数</t>
-  </si>
-  <si>
-    <t>接取：游戏图标出现次数（赛季玩法）</t>
-  </si>
-  <si>
-    <t>12605_游戏ID（0=任意游戏）_下注具体次数_游戏元素ID_出现的次数</t>
-  </si>
-  <si>
-    <t>接取：游戏某局的中奖金额（赛季玩法）</t>
-  </si>
-  <si>
-    <t>12606_游戏ID（0=任意游戏）_下注具体次数_任意局数大于等于目标获胜金额</t>
+    <t>接取：游戏5局赢奖金额（赛季玩法，累计赢奖）</t>
+  </si>
+  <si>
+    <t>12601_游戏id（0=任意游戏）_累计赢奖</t>
+  </si>
+  <si>
+    <t>接取：超级明星游戏100局出现樱桃的次数(赛季玩法,触发特殊模式)</t>
+  </si>
+  <si>
+    <t>12602__游戏模式id_触发模式次数</t>
+  </si>
+  <si>
+    <t>接取：游戏30局触发2倍奖励几次（赛季玩法）</t>
+  </si>
+  <si>
+    <t>12603_游戏ID（0=任意游戏）大于等于中奖倍数的次数</t>
+  </si>
+  <si>
+    <t>接取：游戏5局中奖次数（赛季玩法）</t>
+  </si>
+  <si>
+    <t>12604_游戏ID（0=任意游戏）_中奖次数</t>
+  </si>
+  <si>
+    <t>接取：超级明星游戏5局出现铃铛图标的次数（赛季玩法）</t>
+  </si>
+  <si>
+    <t>12605_游戏元素ID_出现的次数</t>
+  </si>
+  <si>
+    <t>接取：游戏3局的中奖金额（赛季玩法）</t>
+  </si>
+  <si>
+    <t>12606_游戏ID（0=任意游戏）_任意局数大于等于目标获胜金额</t>
   </si>
   <si>
     <t>接取：游戏竞技匹配次数（赛季玩法）</t>
@@ -1002,6 +1030,12 @@
   </si>
   <si>
     <t>12610_游戏ID(0 = 任意游戏)（不区分倍场)_大于等于总押注条件_货币ID(赛季币)_等于目标投注次数</t>
+  </si>
+  <si>
+    <t>接取：游戏50局触发5倍奖励几次（赛季玩法）</t>
+  </si>
+  <si>
+    <t>12611_游戏ID（0=任意游戏）大于等于中奖倍数的次数</t>
   </si>
   <si>
     <t>接取：挖掘格子数量</t>
@@ -1231,12 +1265,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2115,7 +2149,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O110"/>
+  <dimension ref="A1:O112"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="4"/>
@@ -3271,15 +3305,15 @@
       <c r="H52" s="2"/>
     </row>
     <row r="53" spans="1:8">
-      <c r="A53" s="18">
-        <v>12251</v>
-      </c>
-      <c r="B53" s="18" t="s">
+      <c r="A53" s="13">
+        <v>12228</v>
+      </c>
+      <c r="B53" s="13" t="s">
         <v>159</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E53" s="14" t="s">
         <v>160</v>
@@ -3289,15 +3323,15 @@
       <c r="H53" s="2"/>
     </row>
     <row r="54" spans="1:8">
-      <c r="A54" s="18">
-        <v>12252</v>
-      </c>
-      <c r="B54" s="18" t="s">
+      <c r="A54" s="13">
+        <v>12229</v>
+      </c>
+      <c r="B54" s="13" t="s">
         <v>161</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E54" s="14" t="s">
         <v>162</v>
@@ -3308,7 +3342,7 @@
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="18">
-        <v>12253</v>
+        <v>12251</v>
       </c>
       <c r="B55" s="18" t="s">
         <v>163</v>
@@ -3326,14 +3360,14 @@
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="18">
-        <v>12254</v>
+        <v>12252</v>
       </c>
       <c r="B56" s="18" t="s">
         <v>165</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E56" s="14" t="s">
         <v>166</v>
@@ -3344,14 +3378,14 @@
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="18">
-        <v>12255</v>
+        <v>12253</v>
       </c>
       <c r="B57" s="18" t="s">
         <v>167</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E57" s="14" t="s">
         <v>168</v>
@@ -3362,7 +3396,7 @@
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="18">
-        <v>12256</v>
+        <v>12254</v>
       </c>
       <c r="B58" s="18" t="s">
         <v>169</v>
@@ -3380,14 +3414,14 @@
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="18">
-        <v>12257</v>
+        <v>12255</v>
       </c>
       <c r="B59" s="18" t="s">
         <v>171</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E59" s="14" t="s">
         <v>172</v>
@@ -3398,14 +3432,14 @@
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="18">
-        <v>12259</v>
+        <v>12256</v>
       </c>
       <c r="B60" s="18" t="s">
         <v>173</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E60" s="14" t="s">
         <v>174</v>
@@ -3416,14 +3450,14 @@
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="18">
-        <v>12260</v>
+        <v>12257</v>
       </c>
       <c r="B61" s="18" t="s">
         <v>175</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E61" s="14" t="s">
         <v>176</v>
@@ -3434,14 +3468,14 @@
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="18">
-        <v>12261</v>
+        <v>12259</v>
       </c>
       <c r="B62" s="18" t="s">
         <v>177</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E62" s="14" t="s">
         <v>178</v>
@@ -3452,7 +3486,7 @@
     </row>
     <row r="63" spans="1:8">
       <c r="A63" s="18">
-        <v>12262</v>
+        <v>12260</v>
       </c>
       <c r="B63" s="18" t="s">
         <v>179</v>
@@ -3470,14 +3504,14 @@
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="18">
-        <v>12263</v>
+        <v>12261</v>
       </c>
       <c r="B64" s="18" t="s">
         <v>181</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E64" s="14" t="s">
         <v>182</v>
@@ -3488,14 +3522,14 @@
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="18">
-        <v>12264</v>
+        <v>12262</v>
       </c>
       <c r="B65" s="18" t="s">
         <v>183</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E65" s="14" t="s">
         <v>184</v>
@@ -3506,7 +3540,7 @@
     </row>
     <row r="66" spans="1:8">
       <c r="A66" s="18">
-        <v>12265</v>
+        <v>12263</v>
       </c>
       <c r="B66" s="18" t="s">
         <v>185</v>
@@ -3524,7 +3558,7 @@
     </row>
     <row r="67" spans="1:8">
       <c r="A67" s="18">
-        <v>12266</v>
+        <v>12264</v>
       </c>
       <c r="B67" s="18" t="s">
         <v>187</v>
@@ -3542,14 +3576,14 @@
     </row>
     <row r="68" spans="1:8">
       <c r="A68" s="18">
-        <v>12267</v>
+        <v>12265</v>
       </c>
       <c r="B68" s="18" t="s">
         <v>189</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E68" s="14" t="s">
         <v>190</v>
@@ -3560,14 +3594,14 @@
     </row>
     <row r="69" spans="1:8">
       <c r="A69" s="18">
-        <v>12268</v>
+        <v>12266</v>
       </c>
       <c r="B69" s="18" t="s">
         <v>191</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E69" s="14" t="s">
         <v>192</v>
@@ -3576,9 +3610,9 @@
       <c r="G69" s="2"/>
       <c r="H69" s="2"/>
     </row>
-    <row r="70" s="4" customFormat="1" spans="1:8">
+    <row r="70" spans="1:8">
       <c r="A70" s="18">
-        <v>12269</v>
+        <v>12267</v>
       </c>
       <c r="B70" s="18" t="s">
         <v>193</v>
@@ -3594,16 +3628,16 @@
       <c r="G70" s="2"/>
       <c r="H70" s="2"/>
     </row>
-    <row r="71" s="4" customFormat="1" spans="1:8">
+    <row r="71" spans="1:8">
       <c r="A71" s="18">
-        <v>12270</v>
+        <v>12268</v>
       </c>
       <c r="B71" s="18" t="s">
         <v>195</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E71" s="14" t="s">
         <v>196</v>
@@ -3614,14 +3648,14 @@
     </row>
     <row r="72" s="4" customFormat="1" spans="1:8">
       <c r="A72" s="18">
-        <v>12271</v>
+        <v>12269</v>
       </c>
       <c r="B72" s="18" t="s">
         <v>197</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E72" s="14" t="s">
         <v>198</v>
@@ -3632,14 +3666,14 @@
     </row>
     <row r="73" s="4" customFormat="1" spans="1:8">
       <c r="A73" s="18">
-        <v>12272</v>
+        <v>12270</v>
       </c>
       <c r="B73" s="18" t="s">
         <v>199</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E73" s="14" t="s">
         <v>200</v>
@@ -3650,14 +3684,14 @@
     </row>
     <row r="74" s="4" customFormat="1" spans="1:8">
       <c r="A74" s="18">
-        <v>12273</v>
+        <v>12271</v>
       </c>
       <c r="B74" s="18" t="s">
         <v>201</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E74" s="14" t="s">
         <v>202</v>
@@ -3666,54 +3700,54 @@
       <c r="G74" s="2"/>
       <c r="H74" s="2"/>
     </row>
-    <row r="75" customFormat="1" spans="1:8">
+    <row r="75" s="4" customFormat="1" spans="1:8">
       <c r="A75" s="18">
-        <v>12274</v>
+        <v>12272</v>
       </c>
       <c r="B75" s="18" t="s">
         <v>203</v>
       </c>
-      <c r="C75" s="4"/>
-      <c r="D75" s="4">
-        <v>3</v>
+      <c r="C75" s="2"/>
+      <c r="D75" s="2">
+        <v>2</v>
       </c>
       <c r="E75" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="F75" s="4"/>
-      <c r="G75" s="4"/>
-      <c r="H75" s="4"/>
-    </row>
-    <row r="76" customFormat="1" spans="1:8">
+      <c r="F75" s="2"/>
+      <c r="G75" s="2"/>
+      <c r="H75" s="2"/>
+    </row>
+    <row r="76" s="4" customFormat="1" spans="1:8">
       <c r="A76" s="18">
-        <v>12275</v>
+        <v>12273</v>
       </c>
       <c r="B76" s="18" t="s">
         <v>205</v>
       </c>
-      <c r="C76" s="4"/>
-      <c r="D76" s="4">
-        <v>1</v>
-      </c>
-      <c r="E76" s="4" t="s">
+      <c r="C76" s="2"/>
+      <c r="D76" s="2">
+        <v>2</v>
+      </c>
+      <c r="E76" s="14" t="s">
         <v>206</v>
       </c>
-      <c r="F76" s="4"/>
-      <c r="G76" s="4"/>
-      <c r="H76" s="4"/>
+      <c r="F76" s="2"/>
+      <c r="G76" s="2"/>
+      <c r="H76" s="2"/>
     </row>
     <row r="77" customFormat="1" spans="1:8">
       <c r="A77" s="18">
-        <v>12276</v>
+        <v>12274</v>
       </c>
       <c r="B77" s="18" t="s">
         <v>207</v>
       </c>
       <c r="C77" s="4"/>
       <c r="D77" s="4">
-        <v>2</v>
-      </c>
-      <c r="E77" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E77" s="14" t="s">
         <v>208</v>
       </c>
       <c r="F77" s="4"/>
@@ -3722,14 +3756,14 @@
     </row>
     <row r="78" customFormat="1" spans="1:8">
       <c r="A78" s="18">
-        <v>12277</v>
+        <v>12275</v>
       </c>
       <c r="B78" s="18" t="s">
         <v>209</v>
       </c>
       <c r="C78" s="4"/>
       <c r="D78" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E78" s="4" t="s">
         <v>210</v>
@@ -3740,14 +3774,14 @@
     </row>
     <row r="79" customFormat="1" spans="1:8">
       <c r="A79" s="18">
-        <v>12278</v>
+        <v>12276</v>
       </c>
       <c r="B79" s="18" t="s">
         <v>211</v>
       </c>
       <c r="C79" s="4"/>
       <c r="D79" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E79" s="4" t="s">
         <v>212</v>
@@ -3758,14 +3792,14 @@
     </row>
     <row r="80" customFormat="1" spans="1:8">
       <c r="A80" s="18">
-        <v>12279</v>
+        <v>12277</v>
       </c>
       <c r="B80" s="18" t="s">
         <v>213</v>
       </c>
       <c r="C80" s="4"/>
       <c r="D80" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E80" s="4" t="s">
         <v>214</v>
@@ -3776,14 +3810,14 @@
     </row>
     <row r="81" customFormat="1" spans="1:8">
       <c r="A81" s="18">
-        <v>12280</v>
+        <v>12278</v>
       </c>
       <c r="B81" s="18" t="s">
         <v>215</v>
       </c>
       <c r="C81" s="4"/>
       <c r="D81" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E81" s="4" t="s">
         <v>216</v>
@@ -3794,7 +3828,7 @@
     </row>
     <row r="82" customFormat="1" spans="1:8">
       <c r="A82" s="18">
-        <v>12281</v>
+        <v>12279</v>
       </c>
       <c r="B82" s="18" t="s">
         <v>217</v>
@@ -3812,7 +3846,7 @@
     </row>
     <row r="83" customFormat="1" spans="1:8">
       <c r="A83" s="18">
-        <v>12282</v>
+        <v>12280</v>
       </c>
       <c r="B83" s="18" t="s">
         <v>219</v>
@@ -3830,7 +3864,7 @@
     </row>
     <row r="84" customFormat="1" spans="1:8">
       <c r="A84" s="18">
-        <v>12283</v>
+        <v>12281</v>
       </c>
       <c r="B84" s="18" t="s">
         <v>221</v>
@@ -3848,14 +3882,14 @@
     </row>
     <row r="85" customFormat="1" spans="1:8">
       <c r="A85" s="18">
-        <v>12284</v>
+        <v>12282</v>
       </c>
       <c r="B85" s="18" t="s">
         <v>223</v>
       </c>
       <c r="C85" s="4"/>
       <c r="D85" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E85" s="4" t="s">
         <v>224</v>
@@ -3864,51 +3898,55 @@
       <c r="G85" s="4"/>
       <c r="H85" s="4"/>
     </row>
-    <row r="86" spans="1:8">
-      <c r="A86" s="19">
-        <v>12301</v>
-      </c>
-      <c r="B86" s="19" t="s">
+    <row r="86" customFormat="1" spans="1:8">
+      <c r="A86" s="18">
+        <v>12283</v>
+      </c>
+      <c r="B86" s="18" t="s">
         <v>225</v>
       </c>
+      <c r="C86" s="4"/>
       <c r="D86" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E86" s="4" t="s">
         <v>226</v>
       </c>
-    </row>
-    <row r="87" s="5" customFormat="1" spans="1:8">
-      <c r="A87" s="20">
+      <c r="F86" s="4"/>
+      <c r="G86" s="4"/>
+      <c r="H86" s="4"/>
+    </row>
+    <row r="87" spans="1:8">
+      <c r="A87" s="19">
+        <v>12301</v>
+      </c>
+      <c r="B87" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="D87" s="4">
+        <v>4</v>
+      </c>
+      <c r="E87" s="4" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="88" s="5" customFormat="1" spans="1:8">
+      <c r="A88" s="20">
         <v>12302</v>
       </c>
-      <c r="B87" s="20" t="s">
-        <v>227</v>
-      </c>
-      <c r="D87" s="5">
+      <c r="B88" s="20" t="s">
+        <v>229</v>
+      </c>
+      <c r="D88" s="5">
         <v>3</v>
       </c>
-      <c r="E87" s="5" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8">
-      <c r="A88" s="19">
+      <c r="E88" s="5" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8">
+      <c r="A89" s="19">
         <v>12303</v>
-      </c>
-      <c r="B88" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="D88" s="4">
-        <v>2</v>
-      </c>
-      <c r="E88" s="4" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8">
-      <c r="A89" s="20">
-        <v>12304</v>
       </c>
       <c r="B89" s="19" t="s">
         <v>231</v>
@@ -3921,8 +3959,8 @@
       </c>
     </row>
     <row r="90" spans="1:8">
-      <c r="A90" s="19">
-        <v>12305</v>
+      <c r="A90" s="20">
+        <v>12304</v>
       </c>
       <c r="B90" s="19" t="s">
         <v>233</v>
@@ -3934,57 +3972,57 @@
         <v>234</v>
       </c>
     </row>
-    <row r="91" s="5" customFormat="1" spans="1:8">
-      <c r="A91" s="20">
+    <row r="91" spans="1:8">
+      <c r="A91" s="19">
+        <v>12305</v>
+      </c>
+      <c r="B91" s="19" t="s">
+        <v>235</v>
+      </c>
+      <c r="D91" s="4">
+        <v>2</v>
+      </c>
+      <c r="E91" s="4" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="92" s="5" customFormat="1" spans="1:8">
+      <c r="A92" s="20">
         <v>12306</v>
-      </c>
-      <c r="B91" s="20" t="s">
-        <v>235</v>
-      </c>
-      <c r="D91" s="5">
-        <v>4</v>
-      </c>
-      <c r="E91" s="5" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="92" s="5" customFormat="1" spans="1:8">
-      <c r="A92" s="19">
-        <v>12307</v>
       </c>
       <c r="B92" s="20" t="s">
         <v>237</v>
       </c>
       <c r="D92" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E92" s="5" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="93" spans="1:8">
-      <c r="A93" s="21">
-        <v>12501</v>
-      </c>
-      <c r="B93" s="21" t="s">
+    <row r="93" s="5" customFormat="1" spans="1:8">
+      <c r="A93" s="19">
+        <v>12307</v>
+      </c>
+      <c r="B93" s="20" t="s">
         <v>239</v>
       </c>
-      <c r="D93" s="4">
-        <v>4</v>
-      </c>
-      <c r="E93" s="4" t="s">
+      <c r="D93" s="5">
+        <v>2</v>
+      </c>
+      <c r="E93" s="5" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="94" spans="1:8">
       <c r="A94" s="21">
-        <v>12502</v>
+        <v>12501</v>
       </c>
       <c r="B94" s="21" t="s">
         <v>241</v>
       </c>
       <c r="D94" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E94" s="4" t="s">
         <v>242</v>
@@ -3992,13 +4030,13 @@
     </row>
     <row r="95" spans="1:8">
       <c r="A95" s="21">
-        <v>12503</v>
+        <v>12502</v>
       </c>
       <c r="B95" s="21" t="s">
         <v>243</v>
       </c>
       <c r="D95" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E95" s="4" t="s">
         <v>244</v>
@@ -4006,23 +4044,23 @@
     </row>
     <row r="96" spans="1:8">
       <c r="A96" s="21">
-        <v>12504</v>
+        <v>12503</v>
       </c>
       <c r="B96" s="21" t="s">
         <v>245</v>
       </c>
       <c r="D96" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E96" s="4" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="97" spans="1:5">
-      <c r="A97" s="4">
-        <v>12601</v>
-      </c>
-      <c r="B97" s="4" t="s">
+      <c r="A97" s="21">
+        <v>12504</v>
+      </c>
+      <c r="B97" s="21" t="s">
         <v>247</v>
       </c>
       <c r="D97" s="4">
@@ -4034,13 +4072,13 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="4">
-        <v>12602</v>
-      </c>
-      <c r="B98" s="21" t="s">
+        <v>12601</v>
+      </c>
+      <c r="B98" s="4" t="s">
         <v>249</v>
       </c>
       <c r="D98" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E98" s="4" t="s">
         <v>250</v>
@@ -4048,13 +4086,13 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="4">
-        <v>12603</v>
-      </c>
-      <c r="B99" s="4" t="s">
+        <v>12602</v>
+      </c>
+      <c r="B99" s="21" t="s">
         <v>251</v>
       </c>
       <c r="D99" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E99" s="4" t="s">
         <v>252</v>
@@ -4062,13 +4100,13 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="4">
-        <v>12604</v>
+        <v>12603</v>
       </c>
       <c r="B100" s="4" t="s">
         <v>253</v>
       </c>
       <c r="D100" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E100" s="4" t="s">
         <v>254</v>
@@ -4076,13 +4114,13 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="4">
-        <v>12605</v>
+        <v>12604</v>
       </c>
       <c r="B101" s="4" t="s">
         <v>255</v>
       </c>
       <c r="D101" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E101" s="4" t="s">
         <v>256</v>
@@ -4090,13 +4128,13 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="4">
-        <v>12606</v>
+        <v>12605</v>
       </c>
       <c r="B102" s="4" t="s">
         <v>257</v>
       </c>
       <c r="D102" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E102" s="4" t="s">
         <v>258</v>
@@ -4104,7 +4142,7 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="4">
-        <v>12607</v>
+        <v>12606</v>
       </c>
       <c r="B103" s="4" t="s">
         <v>259</v>
@@ -4118,7 +4156,7 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="4">
-        <v>12608</v>
+        <v>12607</v>
       </c>
       <c r="B104" s="4" t="s">
         <v>261</v>
@@ -4132,13 +4170,13 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="4">
-        <v>12609</v>
+        <v>12608</v>
       </c>
       <c r="B105" s="4" t="s">
         <v>263</v>
       </c>
       <c r="D105" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E105" s="4" t="s">
         <v>264</v>
@@ -4146,7 +4184,7 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="4">
-        <v>12610</v>
+        <v>12609</v>
       </c>
       <c r="B106" s="4" t="s">
         <v>265</v>
@@ -4160,13 +4198,13 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="4">
-        <v>12701</v>
+        <v>12610</v>
       </c>
       <c r="B107" s="4" t="s">
         <v>267</v>
       </c>
       <c r="D107" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E107" s="4" t="s">
         <v>268</v>
@@ -4174,13 +4212,13 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="4">
-        <v>12702</v>
+        <v>12611</v>
       </c>
       <c r="B108" s="4" t="s">
         <v>269</v>
       </c>
       <c r="D108" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E108" s="4" t="s">
         <v>270</v>
@@ -4188,13 +4226,13 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="4">
-        <v>12703</v>
+        <v>12701</v>
       </c>
       <c r="B109" s="4" t="s">
         <v>271</v>
       </c>
       <c r="D109" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E109" s="4" t="s">
         <v>272</v>
@@ -4202,16 +4240,44 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="4">
-        <v>12704</v>
+        <v>12702</v>
       </c>
       <c r="B110" s="4" t="s">
         <v>273</v>
       </c>
       <c r="D110" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E110" s="4" t="s">
         <v>274</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5">
+      <c r="A111" s="4">
+        <v>12703</v>
+      </c>
+      <c r="B111" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="D111" s="4">
+        <v>2</v>
+      </c>
+      <c r="E111" s="4" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5">
+      <c r="A112" s="4">
+        <v>12704</v>
+      </c>
+      <c r="B112" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="D112" s="4">
+        <v>2</v>
+      </c>
+      <c r="E112" s="4" t="s">
+        <v>278</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/condition.xlsx
+++ b/hall/resources/sample/condition.xlsx
@@ -1023,13 +1023,13 @@
     <t>接取：赛季币累计赢取金额（赛季玩法）</t>
   </si>
   <si>
-    <t>12609_游戏ID(0 = 任意游戏)（不区分倍场）_大于等于总押注条件_货币ID(赛季币)_大于等于目标获胜金额</t>
+    <t>12609_游戏ID(0 = 任意游戏)（不区分倍场）_大于等于总押注条件_大于等于目标获胜金额</t>
   </si>
   <si>
     <t>接取：游戏投注次数（赛季玩法）</t>
   </si>
   <si>
-    <t>12610_游戏ID(0 = 任意游戏)（不区分倍场)_大于等于总押注条件_货币ID(赛季币)_等于目标投注次数</t>
+    <t>12610_游戏ID(0 = 任意游戏)（不区分倍场)_大于等于总押注条件_等于目标投注次数</t>
   </si>
   <si>
     <t>接取：游戏50局触发5倍奖励几次（赛季玩法）</t>
@@ -1265,12 +1265,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -4190,7 +4190,7 @@
         <v>265</v>
       </c>
       <c r="D106" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E106" s="4" t="s">
         <v>266</v>
@@ -4204,7 +4204,7 @@
         <v>267</v>
       </c>
       <c r="D107" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E107" s="4" t="s">
         <v>268</v>

--- a/hall/resources/sample/condition.xlsx
+++ b/hall/resources/sample/condition.xlsx
@@ -708,7 +708,7 @@
     <t>12228_次数</t>
   </si>
   <si>
-    <t>接取：场景等级</t>
+    <t>累积：场景等级</t>
   </si>
   <si>
     <t>12229_等级</t>
@@ -1265,12 +1265,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/hall/resources/sample/condition.xlsx
+++ b/hall/resources/sample/condition.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\common\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\A-work\config_SimMgmtVert1.0\游戏配置表\common\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="condition" sheetId="1" r:id="rId1"/>
@@ -223,7 +223,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="283">
   <si>
     <t>id</t>
   </si>
@@ -904,6 +904,18 @@
   </si>
   <si>
     <t>12283_次数</t>
+  </si>
+  <si>
+    <t>当天累积：观看N次广告</t>
+  </si>
+  <si>
+    <t>12284_次数</t>
+  </si>
+  <si>
+    <t>当天累积：完成N次任意通行证任务</t>
+  </si>
+  <si>
+    <t>12285_次数</t>
   </si>
   <si>
     <t>接取：游戏中奖倍数</t>
@@ -2149,7 +2161,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O112"/>
+  <dimension ref="A1:O114"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="4"/>
@@ -3916,65 +3928,73 @@
       <c r="G86" s="4"/>
       <c r="H86" s="4"/>
     </row>
-    <row r="87" spans="1:8">
-      <c r="A87" s="19">
-        <v>12301</v>
-      </c>
-      <c r="B87" s="19" t="s">
+    <row r="87" customFormat="1" spans="1:8">
+      <c r="A87" s="18">
+        <v>12284</v>
+      </c>
+      <c r="B87" s="18" t="s">
         <v>227</v>
       </c>
+      <c r="C87" s="4"/>
       <c r="D87" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E87" s="4" t="s">
         <v>228</v>
       </c>
-    </row>
-    <row r="88" s="5" customFormat="1" spans="1:8">
-      <c r="A88" s="20">
-        <v>12302</v>
-      </c>
-      <c r="B88" s="20" t="s">
+      <c r="F87" s="4"/>
+      <c r="G87" s="4"/>
+      <c r="H87" s="4"/>
+    </row>
+    <row r="88" customFormat="1" spans="1:8">
+      <c r="A88" s="18">
+        <v>12285</v>
+      </c>
+      <c r="B88" s="18" t="s">
         <v>229</v>
       </c>
-      <c r="D88" s="5">
-        <v>3</v>
-      </c>
-      <c r="E88" s="5" t="s">
+      <c r="C88" s="4"/>
+      <c r="D88" s="4">
+        <v>1</v>
+      </c>
+      <c r="E88" s="4" t="s">
         <v>230</v>
       </c>
+      <c r="F88" s="4"/>
+      <c r="G88" s="4"/>
+      <c r="H88" s="4"/>
     </row>
     <row r="89" spans="1:8">
       <c r="A89" s="19">
-        <v>12303</v>
+        <v>12301</v>
       </c>
       <c r="B89" s="19" t="s">
         <v>231</v>
       </c>
       <c r="D89" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E89" s="4" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="90" spans="1:8">
+    <row r="90" s="5" customFormat="1" spans="1:8">
       <c r="A90" s="20">
-        <v>12304</v>
-      </c>
-      <c r="B90" s="19" t="s">
+        <v>12302</v>
+      </c>
+      <c r="B90" s="20" t="s">
         <v>233</v>
       </c>
-      <c r="D90" s="4">
-        <v>2</v>
-      </c>
-      <c r="E90" s="4" t="s">
+      <c r="D90" s="5">
+        <v>3</v>
+      </c>
+      <c r="E90" s="5" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="91" spans="1:8">
       <c r="A91" s="19">
-        <v>12305</v>
+        <v>12303</v>
       </c>
       <c r="B91" s="19" t="s">
         <v>235</v>
@@ -3986,65 +4006,65 @@
         <v>236</v>
       </c>
     </row>
-    <row r="92" s="5" customFormat="1" spans="1:8">
+    <row r="92" spans="1:8">
       <c r="A92" s="20">
+        <v>12304</v>
+      </c>
+      <c r="B92" s="19" t="s">
+        <v>237</v>
+      </c>
+      <c r="D92" s="4">
+        <v>2</v>
+      </c>
+      <c r="E92" s="4" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8">
+      <c r="A93" s="19">
+        <v>12305</v>
+      </c>
+      <c r="B93" s="19" t="s">
+        <v>239</v>
+      </c>
+      <c r="D93" s="4">
+        <v>2</v>
+      </c>
+      <c r="E93" s="4" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="94" s="5" customFormat="1" spans="1:8">
+      <c r="A94" s="20">
         <v>12306</v>
       </c>
-      <c r="B92" s="20" t="s">
-        <v>237</v>
-      </c>
-      <c r="D92" s="5">
+      <c r="B94" s="20" t="s">
+        <v>241</v>
+      </c>
+      <c r="D94" s="5">
         <v>4</v>
       </c>
-      <c r="E92" s="5" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="93" s="5" customFormat="1" spans="1:8">
-      <c r="A93" s="19">
+      <c r="E94" s="5" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="95" s="5" customFormat="1" spans="1:8">
+      <c r="A95" s="19">
         <v>12307</v>
       </c>
-      <c r="B93" s="20" t="s">
-        <v>239</v>
-      </c>
-      <c r="D93" s="5">
-        <v>2</v>
-      </c>
-      <c r="E93" s="5" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="94" spans="1:8">
-      <c r="A94" s="21">
-        <v>12501</v>
-      </c>
-      <c r="B94" s="21" t="s">
-        <v>241</v>
-      </c>
-      <c r="D94" s="4">
-        <v>4</v>
-      </c>
-      <c r="E94" s="4" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8">
-      <c r="A95" s="21">
-        <v>12502</v>
-      </c>
-      <c r="B95" s="21" t="s">
+      <c r="B95" s="20" t="s">
         <v>243</v>
       </c>
-      <c r="D95" s="4">
-        <v>3</v>
-      </c>
-      <c r="E95" s="4" t="s">
+      <c r="D95" s="5">
+        <v>2</v>
+      </c>
+      <c r="E95" s="5" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="96" spans="1:8">
       <c r="A96" s="21">
-        <v>12503</v>
+        <v>12501</v>
       </c>
       <c r="B96" s="21" t="s">
         <v>245</v>
@@ -4058,7 +4078,7 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="21">
-        <v>12504</v>
+        <v>12502</v>
       </c>
       <c r="B97" s="21" t="s">
         <v>247</v>
@@ -4071,28 +4091,28 @@
       </c>
     </row>
     <row r="98" spans="1:5">
-      <c r="A98" s="4">
-        <v>12601</v>
-      </c>
-      <c r="B98" s="4" t="s">
+      <c r="A98" s="21">
+        <v>12503</v>
+      </c>
+      <c r="B98" s="21" t="s">
         <v>249</v>
       </c>
       <c r="D98" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E98" s="4" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="99" spans="1:5">
-      <c r="A99" s="4">
-        <v>12602</v>
+      <c r="A99" s="21">
+        <v>12504</v>
       </c>
       <c r="B99" s="21" t="s">
         <v>251</v>
       </c>
       <c r="D99" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E99" s="4" t="s">
         <v>252</v>
@@ -4100,7 +4120,7 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="4">
-        <v>12603</v>
+        <v>12601</v>
       </c>
       <c r="B100" s="4" t="s">
         <v>253</v>
@@ -4114,9 +4134,9 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="4">
-        <v>12604</v>
-      </c>
-      <c r="B101" s="4" t="s">
+        <v>12602</v>
+      </c>
+      <c r="B101" s="21" t="s">
         <v>255</v>
       </c>
       <c r="D101" s="4">
@@ -4128,7 +4148,7 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="4">
-        <v>12605</v>
+        <v>12603</v>
       </c>
       <c r="B102" s="4" t="s">
         <v>257</v>
@@ -4142,7 +4162,7 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="4">
-        <v>12606</v>
+        <v>12604</v>
       </c>
       <c r="B103" s="4" t="s">
         <v>259</v>
@@ -4156,7 +4176,7 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="4">
-        <v>12607</v>
+        <v>12605</v>
       </c>
       <c r="B104" s="4" t="s">
         <v>261</v>
@@ -4170,7 +4190,7 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="4">
-        <v>12608</v>
+        <v>12606</v>
       </c>
       <c r="B105" s="4" t="s">
         <v>263</v>
@@ -4184,13 +4204,13 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="4">
-        <v>12609</v>
+        <v>12607</v>
       </c>
       <c r="B106" s="4" t="s">
         <v>265</v>
       </c>
       <c r="D106" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E106" s="4" t="s">
         <v>266</v>
@@ -4198,13 +4218,13 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="4">
-        <v>12610</v>
+        <v>12608</v>
       </c>
       <c r="B107" s="4" t="s">
         <v>267</v>
       </c>
       <c r="D107" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E107" s="4" t="s">
         <v>268</v>
@@ -4212,13 +4232,13 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="4">
-        <v>12611</v>
+        <v>12609</v>
       </c>
       <c r="B108" s="4" t="s">
         <v>269</v>
       </c>
       <c r="D108" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E108" s="4" t="s">
         <v>270</v>
@@ -4226,13 +4246,13 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="4">
-        <v>12701</v>
+        <v>12610</v>
       </c>
       <c r="B109" s="4" t="s">
         <v>271</v>
       </c>
       <c r="D109" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E109" s="4" t="s">
         <v>272</v>
@@ -4240,13 +4260,13 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="4">
-        <v>12702</v>
+        <v>12611</v>
       </c>
       <c r="B110" s="4" t="s">
         <v>273</v>
       </c>
       <c r="D110" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E110" s="4" t="s">
         <v>274</v>
@@ -4254,13 +4274,13 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="4">
-        <v>12703</v>
+        <v>12701</v>
       </c>
       <c r="B111" s="4" t="s">
         <v>275</v>
       </c>
       <c r="D111" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E111" s="4" t="s">
         <v>276</v>
@@ -4268,16 +4288,44 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="4">
-        <v>12704</v>
+        <v>12702</v>
       </c>
       <c r="B112" s="4" t="s">
         <v>277</v>
       </c>
       <c r="D112" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E112" s="4" t="s">
         <v>278</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5">
+      <c r="A113" s="4">
+        <v>12703</v>
+      </c>
+      <c r="B113" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="D113" s="4">
+        <v>2</v>
+      </c>
+      <c r="E113" s="4" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5">
+      <c r="A114" s="4">
+        <v>12704</v>
+      </c>
+      <c r="B114" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="D114" s="4">
+        <v>2</v>
+      </c>
+      <c r="E114" s="4" t="s">
+        <v>282</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/condition.xlsx
+++ b/hall/resources/sample/condition.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\A-work\config_SimMgmtVert1.0\游戏配置表\common\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\common\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="condition" sheetId="1" r:id="rId1"/>
@@ -137,7 +137,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E56" authorId="0">
+    <comment ref="E55" authorId="0">
       <text>
         <r>
           <rPr>
@@ -183,6 +183,60 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
+1 - 白色品质
+2 - 绿色品质
+3 - 蓝色品质
+4 - 紫色品质
+5 - 金色品质</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E61" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+大奖名称	大奖类型
+sweet win	1
+big win	2
+mega win	3
+epic win	4
+legendary win	5
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E62" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
 奖池名称	奖池类型
 mini	1
 minor	2
@@ -192,7 +246,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E85" authorId="0">
+    <comment ref="E90" authorId="0">
       <text>
         <r>
           <rPr>
@@ -223,7 +277,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="293">
   <si>
     <t>id</t>
   </si>
@@ -712,6 +766,36 @@
   </si>
   <si>
     <t>12229_等级</t>
+  </si>
+  <si>
+    <t>接取：触发大奖 N次</t>
+  </si>
+  <si>
+    <t>12230_游戏ID(0 = 任意游戏)_大奖类型_次数</t>
+  </si>
+  <si>
+    <t>接取：卡池抽卡次数（不管游客还是雇员）</t>
+  </si>
+  <si>
+    <t>12231_次数</t>
+  </si>
+  <si>
+    <t>接取：赛季宝石合成N次</t>
+  </si>
+  <si>
+    <t>12232_宝石品质（0=不限品质）_次数</t>
+  </si>
+  <si>
+    <t>接取：拜访过程中赠送礼物的次数</t>
+  </si>
+  <si>
+    <t>12233_次数</t>
+  </si>
+  <si>
+    <t>接取：拜访过程中试玩别人slot游戏的次数</t>
+  </si>
+  <si>
+    <t>12234_游戏ID（0=任意游戏）_次数</t>
   </si>
   <si>
     <t>累积：在SLOT游戏中获得N个X道具</t>
@@ -1277,12 +1361,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2161,7 +2245,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O114"/>
+  <dimension ref="A1:O119"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="4"/>
@@ -3353,10 +3437,10 @@
       <c r="H54" s="2"/>
     </row>
     <row r="55" spans="1:8">
-      <c r="A55" s="18">
-        <v>12251</v>
-      </c>
-      <c r="B55" s="18" t="s">
+      <c r="A55" s="13">
+        <v>12230</v>
+      </c>
+      <c r="B55" s="13" t="s">
         <v>163</v>
       </c>
       <c r="C55" s="2"/>
@@ -3371,17 +3455,17 @@
       <c r="H55" s="2"/>
     </row>
     <row r="56" spans="1:8">
-      <c r="A56" s="18">
-        <v>12252</v>
-      </c>
-      <c r="B56" s="18" t="s">
+      <c r="A56" s="13">
+        <v>12231</v>
+      </c>
+      <c r="B56" s="13" t="s">
         <v>165</v>
       </c>
       <c r="C56" s="2"/>
-      <c r="D56" s="2">
-        <v>3</v>
-      </c>
-      <c r="E56" s="14" t="s">
+      <c r="D56" s="4">
+        <v>1</v>
+      </c>
+      <c r="E56" s="4" t="s">
         <v>166</v>
       </c>
       <c r="F56" s="2"/>
@@ -3389,17 +3473,17 @@
       <c r="H56" s="2"/>
     </row>
     <row r="57" spans="1:8">
-      <c r="A57" s="18">
-        <v>12253</v>
-      </c>
-      <c r="B57" s="18" t="s">
+      <c r="A57" s="13">
+        <v>12232</v>
+      </c>
+      <c r="B57" s="13" t="s">
         <v>167</v>
       </c>
-      <c r="C57" s="2"/>
-      <c r="D57" s="2">
-        <v>3</v>
-      </c>
-      <c r="E57" s="14" t="s">
+      <c r="C57" s="4"/>
+      <c r="D57" s="4">
+        <v>2</v>
+      </c>
+      <c r="E57" s="4" t="s">
         <v>168</v>
       </c>
       <c r="F57" s="2"/>
@@ -3407,17 +3491,17 @@
       <c r="H57" s="2"/>
     </row>
     <row r="58" spans="1:8">
-      <c r="A58" s="18">
-        <v>12254</v>
-      </c>
-      <c r="B58" s="18" t="s">
+      <c r="A58" s="13">
+        <v>12233</v>
+      </c>
+      <c r="B58" s="13" t="s">
         <v>169</v>
       </c>
-      <c r="C58" s="2"/>
-      <c r="D58" s="2">
-        <v>2</v>
-      </c>
-      <c r="E58" s="14" t="s">
+      <c r="C58" s="4"/>
+      <c r="D58" s="4">
+        <v>1</v>
+      </c>
+      <c r="E58" s="4" t="s">
         <v>170</v>
       </c>
       <c r="F58" s="2"/>
@@ -3425,17 +3509,17 @@
       <c r="H58" s="2"/>
     </row>
     <row r="59" spans="1:8">
-      <c r="A59" s="18">
-        <v>12255</v>
-      </c>
-      <c r="B59" s="18" t="s">
+      <c r="A59" s="13">
+        <v>12234</v>
+      </c>
+      <c r="B59" s="13" t="s">
         <v>171</v>
       </c>
-      <c r="C59" s="2"/>
-      <c r="D59" s="2">
-        <v>2</v>
-      </c>
-      <c r="E59" s="14" t="s">
+      <c r="C59" s="4"/>
+      <c r="D59" s="4">
+        <v>2</v>
+      </c>
+      <c r="E59" s="4" t="s">
         <v>172</v>
       </c>
       <c r="F59" s="2"/>
@@ -3444,14 +3528,14 @@
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="18">
-        <v>12256</v>
+        <v>12251</v>
       </c>
       <c r="B60" s="18" t="s">
         <v>173</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E60" s="14" t="s">
         <v>174</v>
@@ -3462,14 +3546,14 @@
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="18">
-        <v>12257</v>
+        <v>12252</v>
       </c>
       <c r="B61" s="18" t="s">
         <v>175</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E61" s="14" t="s">
         <v>176</v>
@@ -3480,7 +3564,7 @@
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="18">
-        <v>12259</v>
+        <v>12253</v>
       </c>
       <c r="B62" s="18" t="s">
         <v>177</v>
@@ -3498,7 +3582,7 @@
     </row>
     <row r="63" spans="1:8">
       <c r="A63" s="18">
-        <v>12260</v>
+        <v>12254</v>
       </c>
       <c r="B63" s="18" t="s">
         <v>179</v>
@@ -3516,7 +3600,7 @@
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="18">
-        <v>12261</v>
+        <v>12255</v>
       </c>
       <c r="B64" s="18" t="s">
         <v>181</v>
@@ -3534,7 +3618,7 @@
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="18">
-        <v>12262</v>
+        <v>12256</v>
       </c>
       <c r="B65" s="18" t="s">
         <v>183</v>
@@ -3552,7 +3636,7 @@
     </row>
     <row r="66" spans="1:8">
       <c r="A66" s="18">
-        <v>12263</v>
+        <v>12257</v>
       </c>
       <c r="B66" s="18" t="s">
         <v>185</v>
@@ -3570,14 +3654,14 @@
     </row>
     <row r="67" spans="1:8">
       <c r="A67" s="18">
-        <v>12264</v>
+        <v>12259</v>
       </c>
       <c r="B67" s="18" t="s">
         <v>187</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E67" s="14" t="s">
         <v>188</v>
@@ -3588,14 +3672,14 @@
     </row>
     <row r="68" spans="1:8">
       <c r="A68" s="18">
-        <v>12265</v>
+        <v>12260</v>
       </c>
       <c r="B68" s="18" t="s">
         <v>189</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E68" s="14" t="s">
         <v>190</v>
@@ -3606,14 +3690,14 @@
     </row>
     <row r="69" spans="1:8">
       <c r="A69" s="18">
-        <v>12266</v>
+        <v>12261</v>
       </c>
       <c r="B69" s="18" t="s">
         <v>191</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E69" s="14" t="s">
         <v>192</v>
@@ -3624,7 +3708,7 @@
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="18">
-        <v>12267</v>
+        <v>12262</v>
       </c>
       <c r="B70" s="18" t="s">
         <v>193</v>
@@ -3642,14 +3726,14 @@
     </row>
     <row r="71" spans="1:8">
       <c r="A71" s="18">
-        <v>12268</v>
+        <v>12263</v>
       </c>
       <c r="B71" s="18" t="s">
         <v>195</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E71" s="14" t="s">
         <v>196</v>
@@ -3658,16 +3742,16 @@
       <c r="G71" s="2"/>
       <c r="H71" s="2"/>
     </row>
-    <row r="72" s="4" customFormat="1" spans="1:8">
+    <row r="72" spans="1:8">
       <c r="A72" s="18">
-        <v>12269</v>
+        <v>12264</v>
       </c>
       <c r="B72" s="18" t="s">
         <v>197</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E72" s="14" t="s">
         <v>198</v>
@@ -3676,9 +3760,9 @@
       <c r="G72" s="2"/>
       <c r="H72" s="2"/>
     </row>
-    <row r="73" s="4" customFormat="1" spans="1:8">
+    <row r="73" spans="1:8">
       <c r="A73" s="18">
-        <v>12270</v>
+        <v>12265</v>
       </c>
       <c r="B73" s="18" t="s">
         <v>199</v>
@@ -3694,9 +3778,9 @@
       <c r="G73" s="2"/>
       <c r="H73" s="2"/>
     </row>
-    <row r="74" s="4" customFormat="1" spans="1:8">
+    <row r="74" spans="1:8">
       <c r="A74" s="18">
-        <v>12271</v>
+        <v>12266</v>
       </c>
       <c r="B74" s="18" t="s">
         <v>201</v>
@@ -3712,9 +3796,9 @@
       <c r="G74" s="2"/>
       <c r="H74" s="2"/>
     </row>
-    <row r="75" s="4" customFormat="1" spans="1:8">
+    <row r="75" spans="1:8">
       <c r="A75" s="18">
-        <v>12272</v>
+        <v>12267</v>
       </c>
       <c r="B75" s="18" t="s">
         <v>203</v>
@@ -3730,9 +3814,9 @@
       <c r="G75" s="2"/>
       <c r="H75" s="2"/>
     </row>
-    <row r="76" s="4" customFormat="1" spans="1:8">
+    <row r="76" spans="1:8">
       <c r="A76" s="18">
-        <v>12273</v>
+        <v>12268</v>
       </c>
       <c r="B76" s="18" t="s">
         <v>205</v>
@@ -3748,108 +3832,108 @@
       <c r="G76" s="2"/>
       <c r="H76" s="2"/>
     </row>
-    <row r="77" customFormat="1" spans="1:8">
+    <row r="77" s="4" customFormat="1" spans="1:8">
       <c r="A77" s="18">
-        <v>12274</v>
+        <v>12269</v>
       </c>
       <c r="B77" s="18" t="s">
         <v>207</v>
       </c>
-      <c r="C77" s="4"/>
-      <c r="D77" s="4">
-        <v>3</v>
+      <c r="C77" s="2"/>
+      <c r="D77" s="2">
+        <v>2</v>
       </c>
       <c r="E77" s="14" t="s">
         <v>208</v>
       </c>
-      <c r="F77" s="4"/>
-      <c r="G77" s="4"/>
-      <c r="H77" s="4"/>
-    </row>
-    <row r="78" customFormat="1" spans="1:8">
+      <c r="F77" s="2"/>
+      <c r="G77" s="2"/>
+      <c r="H77" s="2"/>
+    </row>
+    <row r="78" s="4" customFormat="1" spans="1:8">
       <c r="A78" s="18">
-        <v>12275</v>
+        <v>12270</v>
       </c>
       <c r="B78" s="18" t="s">
         <v>209</v>
       </c>
-      <c r="C78" s="4"/>
-      <c r="D78" s="4">
+      <c r="C78" s="2"/>
+      <c r="D78" s="2">
         <v>1</v>
       </c>
-      <c r="E78" s="4" t="s">
+      <c r="E78" s="14" t="s">
         <v>210</v>
       </c>
-      <c r="F78" s="4"/>
-      <c r="G78" s="4"/>
-      <c r="H78" s="4"/>
-    </row>
-    <row r="79" customFormat="1" spans="1:8">
+      <c r="F78" s="2"/>
+      <c r="G78" s="2"/>
+      <c r="H78" s="2"/>
+    </row>
+    <row r="79" s="4" customFormat="1" spans="1:8">
       <c r="A79" s="18">
-        <v>12276</v>
+        <v>12271</v>
       </c>
       <c r="B79" s="18" t="s">
         <v>211</v>
       </c>
-      <c r="C79" s="4"/>
-      <c r="D79" s="4">
-        <v>2</v>
-      </c>
-      <c r="E79" s="4" t="s">
+      <c r="C79" s="2"/>
+      <c r="D79" s="2">
+        <v>1</v>
+      </c>
+      <c r="E79" s="14" t="s">
         <v>212</v>
       </c>
-      <c r="F79" s="4"/>
-      <c r="G79" s="4"/>
-      <c r="H79" s="4"/>
-    </row>
-    <row r="80" customFormat="1" spans="1:8">
+      <c r="F79" s="2"/>
+      <c r="G79" s="2"/>
+      <c r="H79" s="2"/>
+    </row>
+    <row r="80" s="4" customFormat="1" spans="1:8">
       <c r="A80" s="18">
-        <v>12277</v>
+        <v>12272</v>
       </c>
       <c r="B80" s="18" t="s">
         <v>213</v>
       </c>
-      <c r="C80" s="4"/>
-      <c r="D80" s="4">
-        <v>3</v>
-      </c>
-      <c r="E80" s="4" t="s">
+      <c r="C80" s="2"/>
+      <c r="D80" s="2">
+        <v>2</v>
+      </c>
+      <c r="E80" s="14" t="s">
         <v>214</v>
       </c>
-      <c r="F80" s="4"/>
-      <c r="G80" s="4"/>
-      <c r="H80" s="4"/>
-    </row>
-    <row r="81" customFormat="1" spans="1:8">
+      <c r="F80" s="2"/>
+      <c r="G80" s="2"/>
+      <c r="H80" s="2"/>
+    </row>
+    <row r="81" s="4" customFormat="1" spans="1:8">
       <c r="A81" s="18">
-        <v>12278</v>
+        <v>12273</v>
       </c>
       <c r="B81" s="18" t="s">
         <v>215</v>
       </c>
-      <c r="C81" s="4"/>
-      <c r="D81" s="4">
-        <v>1</v>
-      </c>
-      <c r="E81" s="4" t="s">
+      <c r="C81" s="2"/>
+      <c r="D81" s="2">
+        <v>2</v>
+      </c>
+      <c r="E81" s="14" t="s">
         <v>216</v>
       </c>
-      <c r="F81" s="4"/>
-      <c r="G81" s="4"/>
-      <c r="H81" s="4"/>
+      <c r="F81" s="2"/>
+      <c r="G81" s="2"/>
+      <c r="H81" s="2"/>
     </row>
     <row r="82" customFormat="1" spans="1:8">
       <c r="A82" s="18">
-        <v>12279</v>
+        <v>12274</v>
       </c>
       <c r="B82" s="18" t="s">
         <v>217</v>
       </c>
       <c r="C82" s="4"/>
       <c r="D82" s="4">
-        <v>1</v>
-      </c>
-      <c r="E82" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E82" s="14" t="s">
         <v>218</v>
       </c>
       <c r="F82" s="4"/>
@@ -3858,14 +3942,14 @@
     </row>
     <row r="83" customFormat="1" spans="1:8">
       <c r="A83" s="18">
-        <v>12280</v>
+        <v>12275</v>
       </c>
       <c r="B83" s="18" t="s">
         <v>219</v>
       </c>
       <c r="C83" s="4"/>
       <c r="D83" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E83" s="4" t="s">
         <v>220</v>
@@ -3876,14 +3960,14 @@
     </row>
     <row r="84" customFormat="1" spans="1:8">
       <c r="A84" s="18">
-        <v>12281</v>
+        <v>12276</v>
       </c>
       <c r="B84" s="18" t="s">
         <v>221</v>
       </c>
       <c r="C84" s="4"/>
       <c r="D84" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E84" s="4" t="s">
         <v>222</v>
@@ -3894,14 +3978,14 @@
     </row>
     <row r="85" customFormat="1" spans="1:8">
       <c r="A85" s="18">
-        <v>12282</v>
+        <v>12277</v>
       </c>
       <c r="B85" s="18" t="s">
         <v>223</v>
       </c>
       <c r="C85" s="4"/>
       <c r="D85" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E85" s="4" t="s">
         <v>224</v>
@@ -3912,7 +3996,7 @@
     </row>
     <row r="86" customFormat="1" spans="1:8">
       <c r="A86" s="18">
-        <v>12283</v>
+        <v>12278</v>
       </c>
       <c r="B86" s="18" t="s">
         <v>225</v>
@@ -3930,7 +4014,7 @@
     </row>
     <row r="87" customFormat="1" spans="1:8">
       <c r="A87" s="18">
-        <v>12284</v>
+        <v>12279</v>
       </c>
       <c r="B87" s="18" t="s">
         <v>227</v>
@@ -3948,14 +4032,14 @@
     </row>
     <row r="88" customFormat="1" spans="1:8">
       <c r="A88" s="18">
-        <v>12285</v>
+        <v>12280</v>
       </c>
       <c r="B88" s="18" t="s">
         <v>229</v>
       </c>
       <c r="C88" s="4"/>
       <c r="D88" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E88" s="4" t="s">
         <v>230</v>
@@ -3964,225 +4048,245 @@
       <c r="G88" s="4"/>
       <c r="H88" s="4"/>
     </row>
-    <row r="89" spans="1:8">
-      <c r="A89" s="19">
-        <v>12301</v>
-      </c>
-      <c r="B89" s="19" t="s">
+    <row r="89" customFormat="1" spans="1:8">
+      <c r="A89" s="18">
+        <v>12281</v>
+      </c>
+      <c r="B89" s="18" t="s">
         <v>231</v>
       </c>
+      <c r="C89" s="4"/>
       <c r="D89" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E89" s="4" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="90" s="5" customFormat="1" spans="1:8">
-      <c r="A90" s="20">
-        <v>12302</v>
-      </c>
-      <c r="B90" s="20" t="s">
+      <c r="F89" s="4"/>
+      <c r="G89" s="4"/>
+      <c r="H89" s="4"/>
+    </row>
+    <row r="90" customFormat="1" spans="1:8">
+      <c r="A90" s="18">
+        <v>12282</v>
+      </c>
+      <c r="B90" s="18" t="s">
         <v>233</v>
       </c>
-      <c r="D90" s="5">
-        <v>3</v>
-      </c>
-      <c r="E90" s="5" t="s">
+      <c r="C90" s="4"/>
+      <c r="D90" s="4">
+        <v>2</v>
+      </c>
+      <c r="E90" s="4" t="s">
         <v>234</v>
       </c>
-    </row>
-    <row r="91" spans="1:8">
-      <c r="A91" s="19">
-        <v>12303</v>
-      </c>
-      <c r="B91" s="19" t="s">
+      <c r="F90" s="4"/>
+      <c r="G90" s="4"/>
+      <c r="H90" s="4"/>
+    </row>
+    <row r="91" customFormat="1" spans="1:8">
+      <c r="A91" s="18">
+        <v>12283</v>
+      </c>
+      <c r="B91" s="18" t="s">
         <v>235</v>
       </c>
+      <c r="C91" s="4"/>
       <c r="D91" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E91" s="4" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="92" spans="1:8">
-      <c r="A92" s="20">
-        <v>12304</v>
-      </c>
-      <c r="B92" s="19" t="s">
+      <c r="F91" s="4"/>
+      <c r="G91" s="4"/>
+      <c r="H91" s="4"/>
+    </row>
+    <row r="92" customFormat="1" spans="1:8">
+      <c r="A92" s="18">
+        <v>12284</v>
+      </c>
+      <c r="B92" s="18" t="s">
         <v>237</v>
       </c>
+      <c r="C92" s="4"/>
       <c r="D92" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E92" s="4" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="93" spans="1:8">
-      <c r="A93" s="19">
-        <v>12305</v>
-      </c>
-      <c r="B93" s="19" t="s">
+      <c r="F92" s="4"/>
+      <c r="G92" s="4"/>
+      <c r="H92" s="4"/>
+    </row>
+    <row r="93" customFormat="1" spans="1:8">
+      <c r="A93" s="18">
+        <v>12285</v>
+      </c>
+      <c r="B93" s="18" t="s">
         <v>239</v>
       </c>
+      <c r="C93" s="4"/>
       <c r="D93" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E93" s="4" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="94" s="5" customFormat="1" spans="1:8">
-      <c r="A94" s="20">
-        <v>12306</v>
-      </c>
-      <c r="B94" s="20" t="s">
+      <c r="F93" s="4"/>
+      <c r="G93" s="4"/>
+      <c r="H93" s="4"/>
+    </row>
+    <row r="94" spans="1:8">
+      <c r="A94" s="19">
+        <v>12301</v>
+      </c>
+      <c r="B94" s="19" t="s">
         <v>241</v>
       </c>
-      <c r="D94" s="5">
+      <c r="D94" s="4">
         <v>4</v>
       </c>
-      <c r="E94" s="5" t="s">
+      <c r="E94" s="4" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="95" s="5" customFormat="1" spans="1:8">
-      <c r="A95" s="19">
-        <v>12307</v>
+      <c r="A95" s="20">
+        <v>12302</v>
       </c>
       <c r="B95" s="20" t="s">
         <v>243</v>
       </c>
       <c r="D95" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E95" s="5" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="96" spans="1:8">
-      <c r="A96" s="21">
-        <v>12501</v>
-      </c>
-      <c r="B96" s="21" t="s">
+      <c r="A96" s="19">
+        <v>12303</v>
+      </c>
+      <c r="B96" s="19" t="s">
         <v>245</v>
       </c>
       <c r="D96" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E96" s="4" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="97" spans="1:5">
-      <c r="A97" s="21">
-        <v>12502</v>
-      </c>
-      <c r="B97" s="21" t="s">
+      <c r="A97" s="20">
+        <v>12304</v>
+      </c>
+      <c r="B97" s="19" t="s">
         <v>247</v>
       </c>
       <c r="D97" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E97" s="4" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="98" spans="1:5">
-      <c r="A98" s="21">
-        <v>12503</v>
-      </c>
-      <c r="B98" s="21" t="s">
+      <c r="A98" s="19">
+        <v>12305</v>
+      </c>
+      <c r="B98" s="19" t="s">
         <v>249</v>
       </c>
       <c r="D98" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E98" s="4" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="99" spans="1:5">
-      <c r="A99" s="21">
-        <v>12504</v>
-      </c>
-      <c r="B99" s="21" t="s">
+    <row r="99" s="5" customFormat="1" spans="1:5">
+      <c r="A99" s="20">
+        <v>12306</v>
+      </c>
+      <c r="B99" s="20" t="s">
         <v>251</v>
       </c>
-      <c r="D99" s="4">
-        <v>3</v>
-      </c>
-      <c r="E99" s="4" t="s">
+      <c r="D99" s="5">
+        <v>4</v>
+      </c>
+      <c r="E99" s="5" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="100" spans="1:5">
-      <c r="A100" s="4">
-        <v>12601</v>
-      </c>
-      <c r="B100" s="4" t="s">
+    <row r="100" s="5" customFormat="1" spans="1:5">
+      <c r="A100" s="19">
+        <v>12307</v>
+      </c>
+      <c r="B100" s="20" t="s">
         <v>253</v>
       </c>
-      <c r="D100" s="4">
-        <v>2</v>
-      </c>
-      <c r="E100" s="4" t="s">
+      <c r="D100" s="5">
+        <v>2</v>
+      </c>
+      <c r="E100" s="5" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="101" spans="1:5">
-      <c r="A101" s="4">
-        <v>12602</v>
+      <c r="A101" s="21">
+        <v>12501</v>
       </c>
       <c r="B101" s="21" t="s">
         <v>255</v>
       </c>
       <c r="D101" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E101" s="4" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="102" spans="1:5">
-      <c r="A102" s="4">
-        <v>12603</v>
-      </c>
-      <c r="B102" s="4" t="s">
+      <c r="A102" s="21">
+        <v>12502</v>
+      </c>
+      <c r="B102" s="21" t="s">
         <v>257</v>
       </c>
       <c r="D102" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E102" s="4" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="103" spans="1:5">
-      <c r="A103" s="4">
-        <v>12604</v>
-      </c>
-      <c r="B103" s="4" t="s">
+      <c r="A103" s="21">
+        <v>12503</v>
+      </c>
+      <c r="B103" s="21" t="s">
         <v>259</v>
       </c>
       <c r="D103" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E103" s="4" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="104" spans="1:5">
-      <c r="A104" s="4">
-        <v>12605</v>
-      </c>
-      <c r="B104" s="4" t="s">
+      <c r="A104" s="21">
+        <v>12504</v>
+      </c>
+      <c r="B104" s="21" t="s">
         <v>261</v>
       </c>
       <c r="D104" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E104" s="4" t="s">
         <v>262</v>
@@ -4190,7 +4294,7 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="4">
-        <v>12606</v>
+        <v>12601</v>
       </c>
       <c r="B105" s="4" t="s">
         <v>263</v>
@@ -4204,9 +4308,9 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="4">
-        <v>12607</v>
-      </c>
-      <c r="B106" s="4" t="s">
+        <v>12602</v>
+      </c>
+      <c r="B106" s="21" t="s">
         <v>265</v>
       </c>
       <c r="D106" s="4">
@@ -4218,7 +4322,7 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="4">
-        <v>12608</v>
+        <v>12603</v>
       </c>
       <c r="B107" s="4" t="s">
         <v>267</v>
@@ -4232,13 +4336,13 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="4">
-        <v>12609</v>
+        <v>12604</v>
       </c>
       <c r="B108" s="4" t="s">
         <v>269</v>
       </c>
       <c r="D108" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E108" s="4" t="s">
         <v>270</v>
@@ -4246,13 +4350,13 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="4">
-        <v>12610</v>
+        <v>12605</v>
       </c>
       <c r="B109" s="4" t="s">
         <v>271</v>
       </c>
       <c r="D109" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E109" s="4" t="s">
         <v>272</v>
@@ -4260,7 +4364,7 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="4">
-        <v>12611</v>
+        <v>12606</v>
       </c>
       <c r="B110" s="4" t="s">
         <v>273</v>
@@ -4274,13 +4378,13 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="4">
-        <v>12701</v>
+        <v>12607</v>
       </c>
       <c r="B111" s="4" t="s">
         <v>275</v>
       </c>
       <c r="D111" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E111" s="4" t="s">
         <v>276</v>
@@ -4288,13 +4392,13 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="4">
-        <v>12702</v>
+        <v>12608</v>
       </c>
       <c r="B112" s="4" t="s">
         <v>277</v>
       </c>
       <c r="D112" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E112" s="4" t="s">
         <v>278</v>
@@ -4302,13 +4406,13 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="4">
-        <v>12703</v>
+        <v>12609</v>
       </c>
       <c r="B113" s="4" t="s">
         <v>279</v>
       </c>
       <c r="D113" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E113" s="4" t="s">
         <v>280</v>
@@ -4316,16 +4420,86 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="4">
-        <v>12704</v>
+        <v>12610</v>
       </c>
       <c r="B114" s="4" t="s">
         <v>281</v>
       </c>
       <c r="D114" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E114" s="4" t="s">
         <v>282</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5">
+      <c r="A115" s="4">
+        <v>12611</v>
+      </c>
+      <c r="B115" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="D115" s="4">
+        <v>2</v>
+      </c>
+      <c r="E115" s="4" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5">
+      <c r="A116" s="4">
+        <v>12701</v>
+      </c>
+      <c r="B116" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="D116" s="4">
+        <v>1</v>
+      </c>
+      <c r="E116" s="4" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5">
+      <c r="A117" s="4">
+        <v>12702</v>
+      </c>
+      <c r="B117" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="D117" s="4">
+        <v>1</v>
+      </c>
+      <c r="E117" s="4" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5">
+      <c r="A118" s="4">
+        <v>12703</v>
+      </c>
+      <c r="B118" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="D118" s="4">
+        <v>2</v>
+      </c>
+      <c r="E118" s="4" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5">
+      <c r="A119" s="4">
+        <v>12704</v>
+      </c>
+      <c r="B119" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="D119" s="4">
+        <v>2</v>
+      </c>
+      <c r="E119" s="4" t="s">
+        <v>292</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/condition.xlsx
+++ b/hall/resources/sample/condition.xlsx
@@ -1149,13 +1149,13 @@
     <t>接取：挖掘过程使用的道具</t>
   </si>
   <si>
-    <t>12702_挖掘使用的道具ID_挖掘使用该道具的数量</t>
+    <t>12703_挖掘使用的道具ID_挖掘使用该道具的数量</t>
   </si>
   <si>
     <t>接取：在挖矿小游戏中兑换的次数</t>
   </si>
   <si>
-    <t>12702_在兑换商店使用兑换物的ID（0=所有兑换物）_兑换的次数</t>
+    <t>12704_在兑换商店使用兑换物的ID（0=所有兑换物）_兑换的次数</t>
   </si>
 </sst>
 </file>
@@ -3479,7 +3479,6 @@
       <c r="B57" s="13" t="s">
         <v>167</v>
       </c>
-      <c r="C57" s="4"/>
       <c r="D57" s="4">
         <v>2</v>
       </c>
@@ -3497,7 +3496,6 @@
       <c r="B58" s="13" t="s">
         <v>169</v>
       </c>
-      <c r="C58" s="4"/>
       <c r="D58" s="4">
         <v>1</v>
       </c>
@@ -3515,7 +3513,6 @@
       <c r="B59" s="13" t="s">
         <v>171</v>
       </c>
-      <c r="C59" s="4"/>
       <c r="D59" s="4">
         <v>2</v>
       </c>
